--- a/02 - config/example_small/agents.xlsx
+++ b/02 - config/example_small/agents.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1566" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1566" uniqueCount="297">
   <si>
     <t>general/agent_id</t>
   </si>
@@ -456,366 +456,375 @@
     <t>meter/prob_missing</t>
   </si>
   <si>
-    <t>QveFhCPMjUCLHLg</t>
-  </si>
-  <si>
-    <t>sxaUGNMrvcigHeL</t>
-  </si>
-  <si>
-    <t>Cy95LEFFXIqQoxd</t>
-  </si>
-  <si>
-    <t>FI4GHcNuYMGvnFE</t>
-  </si>
-  <si>
-    <t>Ol3ZbzNKoYXzo14</t>
-  </si>
-  <si>
-    <t>TUYOkj7s4CwdhnT</t>
-  </si>
-  <si>
-    <t>FYqAQIwbaleIAD4</t>
-  </si>
-  <si>
-    <t>Eu9PJTCFX7DzRtd</t>
-  </si>
-  <si>
-    <t>CdI3uCq5HvQ6HkJ</t>
-  </si>
-  <si>
-    <t>6iMNz4QpWagXXJm</t>
+    <t>WKaDlzVqwb0qILK</t>
+  </si>
+  <si>
+    <t>mcnuVftQ2oeXVK6</t>
+  </si>
+  <si>
+    <t>sBE7lqgjreHlQGx</t>
+  </si>
+  <si>
+    <t>Ykkp2llyiKROWVf</t>
+  </si>
+  <si>
+    <t>maIjQWr9vjk0Uni</t>
+  </si>
+  <si>
+    <t>kizSgfHv1LkxSkV</t>
+  </si>
+  <si>
+    <t>TLeFhLumgkw1SdF</t>
+  </si>
+  <si>
+    <t>QToR2KzakBC9DB3</t>
+  </si>
+  <si>
+    <t>3MIheuHptB4Wuoo</t>
+  </si>
+  <si>
+    <t>wrHtoob8tnX3WC2</t>
+  </si>
+  <si>
+    <t>hh_3648_0.csv</t>
+  </si>
+  <si>
+    <t>hh_5527_0.csv</t>
+  </si>
+  <si>
+    <t>hh_2532_0.csv</t>
+  </si>
+  <si>
+    <t>hh_3863_0.csv</t>
+  </si>
+  <si>
+    <t>hh_2959_0.csv</t>
+  </si>
+  <si>
+    <t>hh_3125_0.csv</t>
+  </si>
+  <si>
+    <t>hh_3564_0.csv</t>
+  </si>
+  <si>
+    <t>naive_average</t>
+  </si>
+  <si>
+    <t>[2, 0, 2, 2, 0, 0, 96, 2, 0, 0, 672]</t>
+  </si>
+  <si>
+    <t>heat_3648_0.csv</t>
+  </si>
+  <si>
+    <t>heat_gen_4_pu.csv</t>
+  </si>
+  <si>
+    <t>heat_2532_0.csv</t>
+  </si>
+  <si>
+    <t>heat_3863_0.csv</t>
+  </si>
+  <si>
+    <t>heat_2959_0.csv</t>
+  </si>
+  <si>
+    <t>heat_gen_0_pu.csv</t>
+  </si>
+  <si>
+    <t>heat_3564_0.csv</t>
+  </si>
+  <si>
+    <t>dhw_gen_0_pu.csv</t>
+  </si>
+  <si>
+    <t>dhw_gen_2_pu.csv</t>
+  </si>
+  <si>
+    <t>dhw_gen_3_pu.csv</t>
+  </si>
+  <si>
+    <t>dhw_gen_6_pu.csv</t>
+  </si>
+  <si>
+    <t>dhw_gen_4_pu.csv</t>
+  </si>
+  <si>
+    <t>dhw_gen_5_pu.csv</t>
+  </si>
+  <si>
+    <t>pv_config.json</t>
+  </si>
+  <si>
+    <t>smoothed</t>
+  </si>
+  <si>
+    <t>green_local</t>
+  </si>
+  <si>
+    <t>wind_Enercon_E-53-800_800000_53.json</t>
+  </si>
+  <si>
+    <t>wind_Nordex_MM92_3300000_131.json</t>
+  </si>
+  <si>
+    <t>wind_Siemens_SWT-3.6-130_3600000_130.json</t>
+  </si>
+  <si>
+    <t>weather</t>
+  </si>
+  <si>
+    <t>local</t>
+  </si>
+  <si>
+    <t>ev_fulltime_41.csv</t>
+  </si>
+  <si>
+    <t>ev_fulltime_48.csv</t>
+  </si>
+  <si>
+    <t>ev_fulltime_49.csv</t>
+  </si>
+  <si>
+    <t>ev_fulltime_45.csv</t>
+  </si>
+  <si>
+    <t>ev_fulltime_47.csv</t>
+  </si>
+  <si>
+    <t>ev_parttime_90.csv</t>
+  </si>
+  <si>
+    <t>price_sensitive</t>
+  </si>
+  <si>
+    <t>ev_close</t>
+  </si>
+  <si>
+    <t>True</t>
+  </si>
+  <si>
+    <t>naive</t>
+  </si>
+  <si>
+    <t>linear</t>
+  </si>
+  <si>
+    <t>general/sub_id</t>
+  </si>
+  <si>
+    <t>general/parameters/apartments_independent</t>
+  </si>
+  <si>
+    <t>general/parameters/apartments</t>
+  </si>
+  <si>
+    <t>okrkLU7dEv9zBJu</t>
+  </si>
+  <si>
+    <t>5u20qBHjWa2Ic0d</t>
+  </si>
+  <si>
+    <t>main</t>
+  </si>
+  <si>
+    <t>MORBhkg1gGsYALg</t>
+  </si>
+  <si>
+    <t>Bl3ZuCYrEkpnyDK</t>
+  </si>
+  <si>
+    <t>ae2InbMZR1Q3ylz</t>
+  </si>
+  <si>
+    <t>AMSglV9XMfUDQdc</t>
+  </si>
+  <si>
+    <t>bgMVEHxHOCD2ZHP</t>
+  </si>
+  <si>
+    <t>ZySixt5otl0xAbX</t>
+  </si>
+  <si>
+    <t>w3eCmzQpkDLZgPU</t>
+  </si>
+  <si>
+    <t>G1YXjrOhuOF8r1k</t>
+  </si>
+  <si>
+    <t>PcDKRpWO6qmoz0Z</t>
+  </si>
+  <si>
+    <t>0qnUQ37A1spIXrY</t>
+  </si>
+  <si>
+    <t>lUalunDMN7lpPO6</t>
+  </si>
+  <si>
+    <t>k3O9vOHMtRq1jRm</t>
+  </si>
+  <si>
+    <t>BurM61AIDtzgbMX</t>
+  </si>
+  <si>
+    <t>HRcyEZSSEcK9HhM</t>
+  </si>
+  <si>
+    <t>hh_1158_4.csv</t>
+  </si>
+  <si>
+    <t>hh_1546_2.csv</t>
+  </si>
+  <si>
+    <t>hh_3296_0.csv</t>
+  </si>
+  <si>
+    <t>hh_1720_0.csv</t>
+  </si>
+  <si>
+    <t>hh_1266_0.csv</t>
   </si>
   <si>
     <t>hh_2012_3.csv</t>
   </si>
   <si>
-    <t>hh_3125_0.csv</t>
-  </si>
-  <si>
-    <t>hh_3863_0.csv</t>
-  </si>
-  <si>
-    <t>hh_3648_0.csv</t>
-  </si>
-  <si>
-    <t>hh_3296_0.csv</t>
-  </si>
-  <si>
-    <t>hh_5527_0.csv</t>
-  </si>
-  <si>
-    <t>hh_3564_0.csv</t>
-  </si>
-  <si>
-    <t>naive_average</t>
-  </si>
-  <si>
-    <t>[2, 0, 2, 2, 0, 0, 96, 2, 0, 0, 672]</t>
-  </si>
-  <si>
-    <t>heat_2012_3.csv</t>
+    <t>hh_2455_0.csv</t>
+  </si>
+  <si>
+    <t>hh_2262_0.csv</t>
+  </si>
+  <si>
+    <t>hh_1009_1.csv</t>
+  </si>
+  <si>
+    <t>hh_2687_0.csv</t>
+  </si>
+  <si>
+    <t>heat_gen_5_pu.csv</t>
+  </si>
+  <si>
+    <t>heat_gen_3_pu.csv</t>
   </si>
   <si>
     <t>heat_gen_1_pu.csv</t>
   </si>
   <si>
-    <t>heat_3863_0.csv</t>
-  </si>
-  <si>
-    <t>heat_3648_0.csv</t>
-  </si>
-  <si>
-    <t>heat_3296_0.csv</t>
-  </si>
-  <si>
-    <t>heat_gen_0_pu.csv</t>
-  </si>
-  <si>
-    <t>heat_3564_0.csv</t>
+    <t>heat_gen_2_pu.csv</t>
   </si>
   <si>
     <t>dhw_gen_1_pu.csv</t>
   </si>
   <si>
-    <t>dhw_gen_2_pu.csv</t>
-  </si>
-  <si>
-    <t>dhw_gen_6_pu.csv</t>
-  </si>
-  <si>
-    <t>dhw_gen_4_pu.csv</t>
-  </si>
-  <si>
-    <t>pv_config.json</t>
-  </si>
-  <si>
-    <t>smoothed</t>
-  </si>
-  <si>
-    <t>green_local</t>
+    <t>pv_1_pu.csv</t>
+  </si>
+  <si>
+    <t>pv_2_pu.csv</t>
   </si>
   <si>
     <t>wind_Vestas_V117-3.3-MW_3300000_117.json</t>
   </si>
   <si>
-    <t>wind_Senvion-REpower_3.2M122_3200000_122.json</t>
-  </si>
-  <si>
-    <t>wind_Nordex_MM92_3300000_131.json</t>
-  </si>
-  <si>
-    <t>wind_Enercon_E-53-800_800000_53.json</t>
-  </si>
-  <si>
-    <t>weather</t>
-  </si>
-  <si>
-    <t>local</t>
-  </si>
-  <si>
-    <t>ev_fulltime_41.csv</t>
+    <t>fixed_gen_1_pu.csv</t>
+  </si>
+  <si>
+    <t>ev_freetime_1.csv</t>
   </si>
   <si>
     <t>ev_freetime_2.csv</t>
   </si>
   <si>
-    <t>ev_fulltime_46.csv</t>
-  </si>
-  <si>
-    <t>ev_fulltime_45.csv</t>
-  </si>
-  <si>
-    <t>price_sensitive</t>
-  </si>
-  <si>
-    <t>ev_close</t>
-  </si>
-  <si>
-    <t>True</t>
-  </si>
-  <si>
-    <t>naive</t>
-  </si>
-  <si>
-    <t>linear</t>
-  </si>
-  <si>
-    <t>general/sub_id</t>
-  </si>
-  <si>
-    <t>general/parameters/apartments_independent</t>
-  </si>
-  <si>
-    <t>general/parameters/apartments</t>
-  </si>
-  <si>
-    <t>47wQFyvSiM02uLB</t>
-  </si>
-  <si>
-    <t>d8fP0ZjbiN9H9VV</t>
-  </si>
-  <si>
-    <t>main</t>
-  </si>
-  <si>
-    <t>G4K9OKE5m27JRhW</t>
-  </si>
-  <si>
-    <t>BWU2Vr1jAMJ82As</t>
-  </si>
-  <si>
-    <t>ABxrYFYX5tmJDCu</t>
-  </si>
-  <si>
-    <t>E7PlPJjGQccD0i5</t>
-  </si>
-  <si>
-    <t>X2xDxgacQVpUWjt</t>
-  </si>
-  <si>
-    <t>fmyMzLatzH7jpiG</t>
-  </si>
-  <si>
-    <t>VYWhifA3RxS3HvK</t>
-  </si>
-  <si>
-    <t>6AYvmQ3NeIHXISz</t>
-  </si>
-  <si>
-    <t>oNmhF60ij6EtEGy</t>
-  </si>
-  <si>
-    <t>ltt1IlUN95h3yPZ</t>
-  </si>
-  <si>
-    <t>xxnKv6Z26k2TU3A</t>
-  </si>
-  <si>
-    <t>UiLLRzk5TIJXHPt</t>
-  </si>
-  <si>
-    <t>SzpfMeEwouFu93O</t>
-  </si>
-  <si>
-    <t>zX0PWEvaOjvo9BN</t>
-  </si>
-  <si>
-    <t>hh_2455_0.csv</t>
-  </si>
-  <si>
-    <t>hh_1416_1.csv</t>
-  </si>
-  <si>
-    <t>hh_2262_0.csv</t>
-  </si>
-  <si>
-    <t>hh_1720_0.csv</t>
-  </si>
-  <si>
-    <t>hh_1266_0.csv</t>
-  </si>
-  <si>
-    <t>hh_1546_2.csv</t>
-  </si>
-  <si>
-    <t>hh_1158_4.csv</t>
-  </si>
-  <si>
-    <t>heat_gen_3_pu.csv</t>
-  </si>
-  <si>
-    <t>heat_gen_2_pu.csv</t>
-  </si>
-  <si>
-    <t>heat_gen_5_pu.csv</t>
-  </si>
-  <si>
-    <t>heat_gen_4_pu.csv</t>
-  </si>
-  <si>
-    <t>dhw_gen_3_pu.csv</t>
-  </si>
-  <si>
-    <t>dhw_gen_0_pu.csv</t>
-  </si>
-  <si>
-    <t>dhw_gen_5_pu.csv</t>
-  </si>
-  <si>
-    <t>pv_2_pu.csv</t>
-  </si>
-  <si>
-    <t>pv_1_pu.csv</t>
-  </si>
-  <si>
-    <t>fixed_gen_1_pu.csv</t>
-  </si>
-  <si>
-    <t>ev_fulltime_49.csv</t>
-  </si>
-  <si>
-    <t>ev_freetime_3.csv</t>
+    <t>i</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>o</t>
+  </si>
+  <si>
+    <t>_</t>
   </si>
   <si>
     <t>c</t>
   </si>
   <si>
-    <t>s</t>
-  </si>
-  <si>
-    <t>o</t>
-  </si>
-  <si>
     <t>n</t>
   </si>
   <si>
-    <t>i</t>
-  </si>
-  <si>
-    <t>_</t>
-  </si>
-  <si>
-    <t>m</t>
-  </si>
-  <si>
     <t>general/parameters/type</t>
   </si>
   <si>
     <t>general/fcast_retraining_frequency</t>
   </si>
   <si>
-    <t>gOO7Px7u3dP0ifU</t>
-  </si>
-  <si>
-    <t>LruijZ1H3pGygC0</t>
-  </si>
-  <si>
-    <t>rc4zjcSLiKI9Z7N</t>
-  </si>
-  <si>
-    <t>kx5vPgAm2vhA9Jh</t>
+    <t>ECGOnSW8WADYhYT</t>
+  </si>
+  <si>
+    <t>JLZ2nNizqi9Z6WL</t>
+  </si>
+  <si>
+    <t>pWrRQ5sGDp5e59p</t>
+  </si>
+  <si>
+    <t>grRgMFsDz987rgG</t>
+  </si>
+  <si>
+    <t>office</t>
   </si>
   <si>
     <t>retail</t>
   </si>
   <si>
-    <t>office</t>
+    <t>office_pu_0.csv</t>
   </si>
   <si>
     <t>retail_pu_0.csv</t>
   </si>
   <si>
-    <t>office_pu_0.csv</t>
+    <t>YrM2KlV24c6EpVK</t>
+  </si>
+  <si>
+    <t>GOw1Mue80BXXDwc</t>
+  </si>
+  <si>
+    <t>tobacco</t>
+  </si>
+  <si>
+    <t>food</t>
+  </si>
+  <si>
+    <t>tobacco_pu_0.csv</t>
+  </si>
+  <si>
+    <t>food_pu_0.csv</t>
+  </si>
+  <si>
+    <t>ev_parttime_89.csv</t>
+  </si>
+  <si>
+    <t>full</t>
+  </si>
+  <si>
+    <t>znibXFFKBylRUZR</t>
+  </si>
+  <si>
+    <t>xwTKTPT383KkdQE</t>
+  </si>
+  <si>
+    <t>TWCV1vstf48hPvT</t>
+  </si>
+  <si>
+    <t>eux7LCBDYu36BPy</t>
+  </si>
+  <si>
+    <t>SmWE7XCDFO7t9eu</t>
+  </si>
+  <si>
+    <t>tPulIZT1ZhxrczV</t>
   </si>
   <si>
     <t>pv_3_pu.csv</t>
   </si>
   <si>
-    <t>ev_fulltime_48.csv</t>
-  </si>
-  <si>
-    <t>ev_parttime_88.csv</t>
-  </si>
-  <si>
-    <t>full</t>
-  </si>
-  <si>
-    <t>62Kc0VERqR0AViZ</t>
-  </si>
-  <si>
-    <t>DYRVv1IXiZECbsT</t>
-  </si>
-  <si>
-    <t>tobacco</t>
-  </si>
-  <si>
-    <t>food</t>
-  </si>
-  <si>
-    <t>tobacco_pu_0.csv</t>
-  </si>
-  <si>
-    <t>food_pu_0.csv</t>
-  </si>
-  <si>
-    <t>dwdwJ90KYzu88zn</t>
-  </si>
-  <si>
-    <t>WDozTlqMW8mnegx</t>
-  </si>
-  <si>
-    <t>nzvEsB7smt6eGaf</t>
-  </si>
-  <si>
-    <t>QW9r9ivXNRmHQT6</t>
-  </si>
-  <si>
-    <t>aqMm8nn525pQlUo</t>
-  </si>
-  <si>
-    <t>vqTkP3bmds0tZkw</t>
-  </si>
-  <si>
     <t>psh/owner</t>
   </si>
   <si>
@@ -876,31 +885,31 @@
     <t>hydrogen/quality</t>
   </si>
   <si>
-    <t>mIDgenjenPoYVW0</t>
-  </si>
-  <si>
-    <t>hst3WNS5Vyf0S3Y</t>
-  </si>
-  <si>
-    <t>kCvXco84lz3fzGO</t>
-  </si>
-  <si>
-    <t>0RoMk48e0rVZe5s</t>
-  </si>
-  <si>
-    <t>EvCak41CmYwAfwv</t>
-  </si>
-  <si>
-    <t>UHHXG6AdzwCBK8x</t>
-  </si>
-  <si>
-    <t>AucNr33l1Ep7CYk</t>
-  </si>
-  <si>
-    <t>2EtLkweFWcfRNq3</t>
-  </si>
-  <si>
-    <t>JcsuDo2QAU6981P</t>
+    <t>IrDk0suEMJe1Jrq</t>
+  </si>
+  <si>
+    <t>ca7DXvsRif58Ywi</t>
+  </si>
+  <si>
+    <t>UYHS8KkFEgWdMat</t>
+  </si>
+  <si>
+    <t>53DJ8459GxzasDU</t>
+  </si>
+  <si>
+    <t>wUdW9MWYe3v90V7</t>
+  </si>
+  <si>
+    <t>wjruqoUV91OXGae</t>
+  </si>
+  <si>
+    <t>bBt3I255Zgyiiu6</t>
+  </si>
+  <si>
+    <t>3KsTujBHlQ7RVF0</t>
+  </si>
+  <si>
+    <t>kqCfqR3JvHUAq71</t>
   </si>
 </sst>
 </file>
@@ -1733,7 +1742,7 @@
         <v>1</v>
       </c>
       <c r="O2">
-        <v>2012000</v>
+        <v>3648000</v>
       </c>
       <c r="P2" t="s">
         <v>155</v>
@@ -1790,7 +1799,7 @@
         <v>164</v>
       </c>
       <c r="AJ2">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="AK2" t="s">
         <v>162</v>
@@ -1817,7 +1826,7 @@
         <v>1</v>
       </c>
       <c r="AS2">
-        <v>1800000</v>
+        <v>2100000</v>
       </c>
       <c r="AT2" t="s">
         <v>171</v>
@@ -1850,10 +1859,10 @@
         <v>1</v>
       </c>
       <c r="BD2">
-        <v>3300</v>
+        <v>5900</v>
       </c>
       <c r="BE2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="BF2">
         <v>0</v>
@@ -1865,7 +1874,7 @@
         <v>1</v>
       </c>
       <c r="BI2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="BJ2">
         <v>2</v>
@@ -1874,7 +1883,7 @@
         <v>9</v>
       </c>
       <c r="BL2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BM2">
         <v>1</v>
@@ -1886,38 +1895,38 @@
         <v>1</v>
       </c>
       <c r="BP2">
-        <v>1600</v>
+        <v>2100</v>
       </c>
       <c r="BQ2" t="s">
+        <v>180</v>
+      </c>
+      <c r="BR2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BS2" t="s">
+        <v>183</v>
+      </c>
+      <c r="BT2">
+        <v>2</v>
+      </c>
+      <c r="BU2">
+        <v>9</v>
+      </c>
+      <c r="BV2" t="s">
+        <v>179</v>
+      </c>
+      <c r="BW2">
+        <v>0</v>
+      </c>
+      <c r="BX2">
+        <v>0</v>
+      </c>
+      <c r="BY2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CC2" t="s">
         <v>178</v>
       </c>
-      <c r="BR2" t="b">
-        <v>1</v>
-      </c>
-      <c r="BS2" t="s">
-        <v>182</v>
-      </c>
-      <c r="BT2">
-        <v>2</v>
-      </c>
-      <c r="BU2">
-        <v>9</v>
-      </c>
-      <c r="BV2" t="s">
-        <v>177</v>
-      </c>
-      <c r="BW2">
-        <v>0</v>
-      </c>
-      <c r="BX2">
-        <v>0</v>
-      </c>
-      <c r="BY2" t="b">
-        <v>1</v>
-      </c>
-      <c r="CC2" t="s">
-        <v>176</v>
-      </c>
       <c r="CD2">
         <v>2</v>
       </c>
@@ -1925,7 +1934,7 @@
         <v>9</v>
       </c>
       <c r="CF2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CG2">
         <v>0</v>
@@ -1937,49 +1946,19 @@
         <v>1</v>
       </c>
       <c r="CL2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CM2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO2" t="b">
         <v>1</v>
       </c>
-      <c r="CP2" t="s">
-        <v>184</v>
-      </c>
-      <c r="CQ2">
-        <v>75000</v>
-      </c>
-      <c r="CR2">
-        <v>20000</v>
-      </c>
-      <c r="CS2">
-        <v>7200</v>
-      </c>
-      <c r="CT2">
-        <v>11000</v>
-      </c>
-      <c r="CU2">
-        <v>100000</v>
-      </c>
-      <c r="CV2">
-        <v>0.9</v>
-      </c>
-      <c r="CW2">
-        <v>0.8</v>
-      </c>
-      <c r="CX2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CY2" t="b">
-        <v>0</v>
-      </c>
       <c r="DJ2" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="DK2">
         <v>0.05</v>
@@ -1994,40 +1973,22 @@
         <v>8.5</v>
       </c>
       <c r="DO2" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="DP2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="DQ2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS2" t="s">
-        <v>190</v>
-      </c>
-      <c r="DT2">
-        <v>2000</v>
-      </c>
-      <c r="DU2">
-        <v>2000</v>
-      </c>
-      <c r="DV2">
-        <v>0.95</v>
-      </c>
-      <c r="DW2">
-        <v>0.1</v>
-      </c>
-      <c r="DX2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DY2" t="b">
-        <v>0</v>
+        <v>193</v>
       </c>
       <c r="DZ2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="EA2">
         <v>0</v>
@@ -2036,28 +1997,28 @@
         <v>0</v>
       </c>
       <c r="EC2" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="EG2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="EH2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="EI2">
         <v>96</v>
       </c>
       <c r="EJ2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="EK2">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="EL2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="EM2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="EN2">
         <v>0</v>
@@ -2077,10 +2038,10 @@
         <v>146</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G3">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="H3">
         <v>2</v>
@@ -2089,7 +2050,7 @@
         <v>2.6</v>
       </c>
       <c r="J3">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="K3">
         <v>1</v>
@@ -2104,7 +2065,7 @@
         <v>1</v>
       </c>
       <c r="O3">
-        <v>3125000</v>
+        <v>5527000</v>
       </c>
       <c r="P3" t="s">
         <v>156</v>
@@ -2155,7 +2116,7 @@
         <v>1</v>
       </c>
       <c r="AH3">
-        <v>5500000</v>
+        <v>19500000</v>
       </c>
       <c r="AI3" t="s">
         <v>165</v>
@@ -2188,7 +2149,7 @@
         <v>1</v>
       </c>
       <c r="AS3">
-        <v>2400000</v>
+        <v>3200000</v>
       </c>
       <c r="AT3" t="s">
         <v>172</v>
@@ -2212,16 +2173,31 @@
         <v>90</v>
       </c>
       <c r="BA3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC3" t="b">
         <v>1</v>
       </c>
+      <c r="BD3">
+        <v>7200</v>
+      </c>
+      <c r="BE3" t="s">
+        <v>177</v>
+      </c>
+      <c r="BF3">
+        <v>0</v>
+      </c>
+      <c r="BG3">
+        <v>40</v>
+      </c>
+      <c r="BH3" t="b">
+        <v>1</v>
+      </c>
       <c r="BI3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="BJ3">
         <v>2</v>
@@ -2230,38 +2206,29 @@
         <v>9</v>
       </c>
       <c r="BL3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BM3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BN3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BO3" t="b">
         <v>1</v>
       </c>
-      <c r="BP3">
-        <v>2500</v>
-      </c>
-      <c r="BQ3" t="s">
+      <c r="BS3" t="s">
+        <v>183</v>
+      </c>
+      <c r="BT3">
+        <v>2</v>
+      </c>
+      <c r="BU3">
+        <v>9</v>
+      </c>
+      <c r="BV3" t="s">
         <v>179</v>
       </c>
-      <c r="BR3" t="b">
-        <v>1</v>
-      </c>
-      <c r="BS3" t="s">
-        <v>182</v>
-      </c>
-      <c r="BT3">
-        <v>2</v>
-      </c>
-      <c r="BU3">
-        <v>9</v>
-      </c>
-      <c r="BV3" t="s">
-        <v>177</v>
-      </c>
       <c r="BW3">
         <v>0</v>
       </c>
@@ -2272,7 +2239,7 @@
         <v>1</v>
       </c>
       <c r="CC3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="CD3">
         <v>2</v>
@@ -2281,7 +2248,7 @@
         <v>9</v>
       </c>
       <c r="CF3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CG3">
         <v>0</v>
@@ -2293,49 +2260,19 @@
         <v>1</v>
       </c>
       <c r="CL3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CM3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO3" t="b">
         <v>1</v>
       </c>
-      <c r="CP3" t="s">
-        <v>185</v>
-      </c>
-      <c r="CQ3">
-        <v>75000</v>
-      </c>
-      <c r="CR3">
-        <v>20000</v>
-      </c>
-      <c r="CS3">
-        <v>7200</v>
-      </c>
-      <c r="CT3">
-        <v>11000</v>
-      </c>
-      <c r="CU3">
-        <v>100000</v>
-      </c>
-      <c r="CV3">
-        <v>0.9</v>
-      </c>
-      <c r="CW3">
-        <v>0.8</v>
-      </c>
-      <c r="CX3" t="b">
-        <v>0</v>
-      </c>
-      <c r="CY3" t="b">
-        <v>0</v>
-      </c>
       <c r="DJ3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="DK3">
         <v>0.05</v>
@@ -2350,22 +2287,40 @@
         <v>8.5</v>
       </c>
       <c r="DO3" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="DP3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="DQ3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS3" t="s">
-        <v>190</v>
+        <v>193</v>
+      </c>
+      <c r="DT3">
+        <v>5500</v>
+      </c>
+      <c r="DU3">
+        <v>5500</v>
+      </c>
+      <c r="DV3">
+        <v>0.95</v>
+      </c>
+      <c r="DW3">
+        <v>0.1</v>
+      </c>
+      <c r="DX3" t="b">
+        <v>0</v>
+      </c>
+      <c r="DY3" t="b">
+        <v>0</v>
       </c>
       <c r="DZ3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="EA3">
         <v>0</v>
@@ -2374,25 +2329,25 @@
         <v>0</v>
       </c>
       <c r="EC3" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="EG3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="EH3" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="EI3">
         <v>96</v>
       </c>
       <c r="EJ3" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="EK3">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="EL3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="EM3">
         <v>0</v>
@@ -2442,10 +2397,10 @@
         <v>1</v>
       </c>
       <c r="O4">
-        <v>2012000</v>
+        <v>2532000</v>
       </c>
       <c r="P4" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="Q4" t="s">
         <v>162</v>
@@ -2496,7 +2451,7 @@
         <v>5500000</v>
       </c>
       <c r="AI4" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AJ4">
         <v>55</v>
@@ -2526,7 +2481,7 @@
         <v>1</v>
       </c>
       <c r="AS4">
-        <v>2100000</v>
+        <v>1800000</v>
       </c>
       <c r="AT4" t="s">
         <v>173</v>
@@ -2559,10 +2514,10 @@
         <v>1</v>
       </c>
       <c r="BD4">
-        <v>3300</v>
+        <v>3700</v>
       </c>
       <c r="BE4" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="BF4">
         <v>0</v>
@@ -2574,7 +2529,7 @@
         <v>1</v>
       </c>
       <c r="BI4" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="BJ4">
         <v>2</v>
@@ -2583,7 +2538,7 @@
         <v>9</v>
       </c>
       <c r="BL4" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BM4">
         <v>1</v>
@@ -2595,16 +2550,16 @@
         <v>1</v>
       </c>
       <c r="BP4">
-        <v>1700</v>
+        <v>2000</v>
       </c>
       <c r="BQ4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="BR4" t="b">
         <v>1</v>
       </c>
       <c r="BS4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="BT4">
         <v>2</v>
@@ -2613,7 +2568,7 @@
         <v>9</v>
       </c>
       <c r="BV4" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BW4">
         <v>0</v>
@@ -2625,7 +2580,7 @@
         <v>1</v>
       </c>
       <c r="CC4" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="CD4">
         <v>2</v>
@@ -2634,7 +2589,7 @@
         <v>9</v>
       </c>
       <c r="CF4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CG4">
         <v>0</v>
@@ -2646,49 +2601,19 @@
         <v>1</v>
       </c>
       <c r="CL4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CM4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO4" t="b">
         <v>1</v>
       </c>
-      <c r="CP4" t="s">
-        <v>186</v>
-      </c>
-      <c r="CQ4">
-        <v>50000</v>
-      </c>
-      <c r="CR4">
-        <v>15000</v>
-      </c>
-      <c r="CS4">
-        <v>7200</v>
-      </c>
-      <c r="CT4">
-        <v>7200</v>
-      </c>
-      <c r="CU4">
-        <v>50000</v>
-      </c>
-      <c r="CV4">
-        <v>0.9</v>
-      </c>
-      <c r="CW4">
-        <v>0.8</v>
-      </c>
-      <c r="CX4" t="b">
-        <v>0</v>
-      </c>
-      <c r="CY4" t="b">
-        <v>0</v>
-      </c>
       <c r="DJ4" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="DK4">
         <v>0.05</v>
@@ -2703,10 +2628,10 @@
         <v>8.5</v>
       </c>
       <c r="DO4" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="DP4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="DQ4">
         <v>1</v>
@@ -2715,13 +2640,13 @@
         <v>1</v>
       </c>
       <c r="DS4" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="DT4">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="DU4">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="DV4">
         <v>0.95</v>
@@ -2736,7 +2661,7 @@
         <v>0</v>
       </c>
       <c r="DZ4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="EA4">
         <v>0</v>
@@ -2745,28 +2670,28 @@
         <v>0</v>
       </c>
       <c r="EC4" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="EG4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="EH4" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="EI4">
         <v>96</v>
       </c>
       <c r="EJ4" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="EK4">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="EL4" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="EM4">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="EN4">
         <v>0</v>
@@ -2816,7 +2741,7 @@
         <v>3863000</v>
       </c>
       <c r="P5" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q5" t="s">
         <v>162</v>
@@ -2867,10 +2792,10 @@
         <v>19500000</v>
       </c>
       <c r="AI5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AJ5">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="AK5" t="s">
         <v>162</v>
@@ -2897,10 +2822,10 @@
         <v>1</v>
       </c>
       <c r="AS5">
-        <v>2800000</v>
+        <v>2400000</v>
       </c>
       <c r="AT5" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="AU5">
         <v>55</v>
@@ -2921,16 +2846,31 @@
         <v>90</v>
       </c>
       <c r="BA5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC5" t="b">
         <v>1</v>
       </c>
+      <c r="BD5">
+        <v>4900</v>
+      </c>
+      <c r="BE5" t="s">
+        <v>177</v>
+      </c>
+      <c r="BF5">
+        <v>0</v>
+      </c>
+      <c r="BG5">
+        <v>40</v>
+      </c>
+      <c r="BH5" t="b">
+        <v>1</v>
+      </c>
       <c r="BI5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="BJ5">
         <v>2</v>
@@ -2939,7 +2879,7 @@
         <v>9</v>
       </c>
       <c r="BL5" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BM5">
         <v>1</v>
@@ -2951,16 +2891,16 @@
         <v>1</v>
       </c>
       <c r="BP5">
-        <v>2300</v>
+        <v>2900</v>
       </c>
       <c r="BQ5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="BR5" t="b">
         <v>1</v>
       </c>
       <c r="BS5" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="BT5">
         <v>2</v>
@@ -2969,7 +2909,7 @@
         <v>9</v>
       </c>
       <c r="BV5" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BW5">
         <v>0</v>
@@ -2981,7 +2921,7 @@
         <v>1</v>
       </c>
       <c r="CC5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="CD5">
         <v>2</v>
@@ -2990,7 +2930,7 @@
         <v>9</v>
       </c>
       <c r="CF5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CG5">
         <v>0</v>
@@ -3002,7 +2942,7 @@
         <v>1</v>
       </c>
       <c r="CL5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CM5">
         <v>1</v>
@@ -3014,22 +2954,22 @@
         <v>1</v>
       </c>
       <c r="CP5" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="CQ5">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="CR5">
-        <v>25000</v>
+        <v>15000</v>
       </c>
       <c r="CS5">
-        <v>11000</v>
+        <v>7200</v>
       </c>
       <c r="CT5">
-        <v>22000</v>
+        <v>7200</v>
       </c>
       <c r="CU5">
-        <v>200000</v>
+        <v>50000</v>
       </c>
       <c r="CV5">
         <v>0.9</v>
@@ -3044,7 +2984,7 @@
         <v>0</v>
       </c>
       <c r="DJ5" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="DK5">
         <v>0.05</v>
@@ -3059,22 +2999,40 @@
         <v>8.5</v>
       </c>
       <c r="DO5" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="DP5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="DQ5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS5" t="s">
-        <v>190</v>
+        <v>193</v>
+      </c>
+      <c r="DT5">
+        <v>3900</v>
+      </c>
+      <c r="DU5">
+        <v>3900</v>
+      </c>
+      <c r="DV5">
+        <v>0.95</v>
+      </c>
+      <c r="DW5">
+        <v>0.1</v>
+      </c>
+      <c r="DX5" t="b">
+        <v>0</v>
+      </c>
+      <c r="DY5" t="b">
+        <v>0</v>
       </c>
       <c r="DZ5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="EA5">
         <v>0</v>
@@ -3083,28 +3041,28 @@
         <v>0</v>
       </c>
       <c r="EC5" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="EG5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="EH5" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="EI5">
         <v>96</v>
       </c>
       <c r="EJ5" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="EK5">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="EL5" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="EM5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="EN5">
         <v>0</v>
@@ -3124,10 +3082,10 @@
         <v>149</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H6">
         <v>2</v>
@@ -3136,7 +3094,7 @@
         <v>2.6</v>
       </c>
       <c r="J6">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -3151,10 +3109,10 @@
         <v>1</v>
       </c>
       <c r="O6">
-        <v>3648000</v>
+        <v>2959000</v>
       </c>
       <c r="P6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q6" t="s">
         <v>162</v>
@@ -3202,10 +3160,10 @@
         <v>1</v>
       </c>
       <c r="AH6">
-        <v>19500000</v>
+        <v>5500000</v>
       </c>
       <c r="AI6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AJ6">
         <v>35</v>
@@ -3235,10 +3193,10 @@
         <v>1</v>
       </c>
       <c r="AS6">
-        <v>3200000</v>
+        <v>2100000</v>
       </c>
       <c r="AT6" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="AU6">
         <v>55</v>
@@ -3268,10 +3226,10 @@
         <v>1</v>
       </c>
       <c r="BD6">
-        <v>6000</v>
+        <v>3700</v>
       </c>
       <c r="BE6" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="BF6">
         <v>-20</v>
@@ -3283,7 +3241,7 @@
         <v>1</v>
       </c>
       <c r="BI6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="BJ6">
         <v>2</v>
@@ -3292,7 +3250,7 @@
         <v>9</v>
       </c>
       <c r="BL6" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BM6">
         <v>0</v>
@@ -3304,7 +3262,7 @@
         <v>1</v>
       </c>
       <c r="BS6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="BT6">
         <v>2</v>
@@ -3313,7 +3271,7 @@
         <v>9</v>
       </c>
       <c r="BV6" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BW6">
         <v>0</v>
@@ -3325,7 +3283,7 @@
         <v>1</v>
       </c>
       <c r="CC6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="CD6">
         <v>2</v>
@@ -3334,7 +3292,7 @@
         <v>9</v>
       </c>
       <c r="CF6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CG6">
         <v>0</v>
@@ -3346,19 +3304,49 @@
         <v>1</v>
       </c>
       <c r="CL6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CM6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO6" t="b">
         <v>1</v>
       </c>
+      <c r="CP6" t="s">
+        <v>186</v>
+      </c>
+      <c r="CQ6">
+        <v>75000</v>
+      </c>
+      <c r="CR6">
+        <v>20000</v>
+      </c>
+      <c r="CS6">
+        <v>7200</v>
+      </c>
+      <c r="CT6">
+        <v>11000</v>
+      </c>
+      <c r="CU6">
+        <v>100000</v>
+      </c>
+      <c r="CV6">
+        <v>0.9</v>
+      </c>
+      <c r="CW6">
+        <v>0.8</v>
+      </c>
+      <c r="CX6" t="b">
+        <v>0</v>
+      </c>
+      <c r="CY6" t="b">
+        <v>0</v>
+      </c>
       <c r="DJ6" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="DK6">
         <v>0.05</v>
@@ -3373,40 +3361,22 @@
         <v>8.5</v>
       </c>
       <c r="DO6" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="DP6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="DQ6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS6" t="s">
-        <v>190</v>
-      </c>
-      <c r="DT6">
-        <v>3600</v>
-      </c>
-      <c r="DU6">
-        <v>3600</v>
-      </c>
-      <c r="DV6">
-        <v>0.95</v>
-      </c>
-      <c r="DW6">
-        <v>0.1</v>
-      </c>
-      <c r="DX6" t="b">
-        <v>0</v>
-      </c>
-      <c r="DY6" t="b">
-        <v>0</v>
+        <v>193</v>
       </c>
       <c r="DZ6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="EA6">
         <v>0</v>
@@ -3415,28 +3385,28 @@
         <v>0</v>
       </c>
       <c r="EC6" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="EG6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="EH6" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="EI6">
         <v>96</v>
       </c>
       <c r="EJ6" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="EK6">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="EL6" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="EM6">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="EN6">
         <v>0</v>
@@ -3456,10 +3426,10 @@
         <v>150</v>
       </c>
       <c r="F7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G7">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H7">
         <v>2</v>
@@ -3468,7 +3438,7 @@
         <v>2.6</v>
       </c>
       <c r="J7">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="K7">
         <v>1</v>
@@ -3483,10 +3453,10 @@
         <v>1</v>
       </c>
       <c r="O7">
-        <v>3296000</v>
+        <v>3125000</v>
       </c>
       <c r="P7" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q7" t="s">
         <v>162</v>
@@ -3534,10 +3504,10 @@
         <v>1</v>
       </c>
       <c r="AH7">
-        <v>19500000</v>
+        <v>5500000</v>
       </c>
       <c r="AI7" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AJ7">
         <v>55</v>
@@ -3567,10 +3537,10 @@
         <v>1</v>
       </c>
       <c r="AS7">
-        <v>2400000</v>
+        <v>1800000</v>
       </c>
       <c r="AT7" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AU7">
         <v>55</v>
@@ -3600,10 +3570,10 @@
         <v>1</v>
       </c>
       <c r="BD7">
-        <v>4700</v>
+        <v>4200</v>
       </c>
       <c r="BE7" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="BF7">
         <v>-20</v>
@@ -3615,7 +3585,7 @@
         <v>1</v>
       </c>
       <c r="BI7" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="BJ7">
         <v>2</v>
@@ -3624,7 +3594,7 @@
         <v>9</v>
       </c>
       <c r="BL7" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BM7">
         <v>0</v>
@@ -3636,7 +3606,7 @@
         <v>1</v>
       </c>
       <c r="BS7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="BT7">
         <v>2</v>
@@ -3645,7 +3615,7 @@
         <v>9</v>
       </c>
       <c r="BV7" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BW7">
         <v>0</v>
@@ -3657,7 +3627,7 @@
         <v>1</v>
       </c>
       <c r="CC7" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="CD7">
         <v>2</v>
@@ -3666,7 +3636,7 @@
         <v>9</v>
       </c>
       <c r="CF7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CG7">
         <v>0</v>
@@ -3678,7 +3648,7 @@
         <v>1</v>
       </c>
       <c r="CL7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CM7">
         <v>0</v>
@@ -3690,7 +3660,7 @@
         <v>1</v>
       </c>
       <c r="DJ7" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="DK7">
         <v>0.05</v>
@@ -3705,10 +3675,10 @@
         <v>8.5</v>
       </c>
       <c r="DO7" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="DP7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="DQ7">
         <v>1</v>
@@ -3717,13 +3687,13 @@
         <v>1</v>
       </c>
       <c r="DS7" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="DT7">
-        <v>3300</v>
+        <v>3100</v>
       </c>
       <c r="DU7">
-        <v>3300</v>
+        <v>3100</v>
       </c>
       <c r="DV7">
         <v>0.95</v>
@@ -3738,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="DZ7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="EA7">
         <v>0</v>
@@ -3747,28 +3717,28 @@
         <v>0</v>
       </c>
       <c r="EC7" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="EG7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="EH7" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="EI7">
         <v>96</v>
       </c>
       <c r="EJ7" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="EK7">
         <v>48</v>
       </c>
       <c r="EL7" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="EM7">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="EN7">
         <v>0</v>
@@ -3788,10 +3758,10 @@
         <v>151</v>
       </c>
       <c r="F8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G8">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="H8">
         <v>2</v>
@@ -3800,7 +3770,7 @@
         <v>2.6</v>
       </c>
       <c r="J8">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="K8">
         <v>1</v>
@@ -3815,10 +3785,10 @@
         <v>1</v>
       </c>
       <c r="O8">
-        <v>5527000</v>
+        <v>3564000</v>
       </c>
       <c r="P8" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q8" t="s">
         <v>162</v>
@@ -3866,10 +3836,10 @@
         <v>1</v>
       </c>
       <c r="AH8">
-        <v>5500000</v>
+        <v>19500000</v>
       </c>
       <c r="AI8" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="AJ8">
         <v>55</v>
@@ -3899,7 +3869,7 @@
         <v>1</v>
       </c>
       <c r="AS8">
-        <v>2100000</v>
+        <v>2800000</v>
       </c>
       <c r="AT8" t="s">
         <v>174</v>
@@ -3932,10 +3902,10 @@
         <v>1</v>
       </c>
       <c r="BD8">
-        <v>9800</v>
+        <v>5300</v>
       </c>
       <c r="BE8" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="BF8">
         <v>0</v>
@@ -3947,7 +3917,7 @@
         <v>1</v>
       </c>
       <c r="BI8" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="BJ8">
         <v>2</v>
@@ -3956,7 +3926,7 @@
         <v>9</v>
       </c>
       <c r="BL8" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BM8">
         <v>0</v>
@@ -3968,7 +3938,7 @@
         <v>1</v>
       </c>
       <c r="BS8" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="BT8">
         <v>2</v>
@@ -3977,7 +3947,7 @@
         <v>9</v>
       </c>
       <c r="BV8" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BW8">
         <v>0</v>
@@ -3989,7 +3959,7 @@
         <v>1</v>
       </c>
       <c r="CC8" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="CD8">
         <v>2</v>
@@ -3998,7 +3968,7 @@
         <v>9</v>
       </c>
       <c r="CF8" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CG8">
         <v>0</v>
@@ -4010,19 +3980,79 @@
         <v>1</v>
       </c>
       <c r="CL8" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CM8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CO8" t="b">
         <v>1</v>
       </c>
+      <c r="CP8" t="s">
+        <v>187</v>
+      </c>
+      <c r="CQ8">
+        <v>100000</v>
+      </c>
+      <c r="CR8">
+        <v>25000</v>
+      </c>
+      <c r="CS8">
+        <v>11000</v>
+      </c>
+      <c r="CT8">
+        <v>22000</v>
+      </c>
+      <c r="CU8">
+        <v>200000</v>
+      </c>
+      <c r="CV8">
+        <v>0.9</v>
+      </c>
+      <c r="CW8">
+        <v>0.8</v>
+      </c>
+      <c r="CX8" t="b">
+        <v>0</v>
+      </c>
+      <c r="CY8" t="b">
+        <v>0</v>
+      </c>
+      <c r="CZ8" t="s">
+        <v>190</v>
+      </c>
+      <c r="DA8">
+        <v>75000</v>
+      </c>
+      <c r="DB8">
+        <v>20000</v>
+      </c>
+      <c r="DC8">
+        <v>7200</v>
+      </c>
+      <c r="DD8">
+        <v>11000</v>
+      </c>
+      <c r="DE8">
+        <v>100000</v>
+      </c>
+      <c r="DF8">
+        <v>0.9</v>
+      </c>
+      <c r="DG8">
+        <v>0.8</v>
+      </c>
+      <c r="DH8" t="b">
+        <v>0</v>
+      </c>
+      <c r="DI8" t="b">
+        <v>0</v>
+      </c>
       <c r="DJ8" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="DK8">
         <v>0.05</v>
@@ -4037,10 +4067,10 @@
         <v>8.5</v>
       </c>
       <c r="DO8" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="DP8" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="DQ8">
         <v>1</v>
@@ -4049,13 +4079,13 @@
         <v>1</v>
       </c>
       <c r="DS8" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="DT8">
-        <v>5500</v>
+        <v>3600</v>
       </c>
       <c r="DU8">
-        <v>5500</v>
+        <v>3600</v>
       </c>
       <c r="DV8">
         <v>0.95</v>
@@ -4070,7 +4100,7 @@
         <v>0</v>
       </c>
       <c r="DZ8" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="EA8">
         <v>0</v>
@@ -4079,28 +4109,28 @@
         <v>0</v>
       </c>
       <c r="EC8" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="EG8" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="EH8" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="EI8">
         <v>96</v>
       </c>
       <c r="EJ8" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="EK8">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="EL8" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="EM8">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="EN8">
         <v>0</v>
@@ -4147,10 +4177,10 @@
         <v>1</v>
       </c>
       <c r="O9">
-        <v>5527000</v>
+        <v>3863000</v>
       </c>
       <c r="P9" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="Q9" t="s">
         <v>162</v>
@@ -4201,7 +4231,7 @@
         <v>19500000</v>
       </c>
       <c r="AI9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="AJ9">
         <v>55</v>
@@ -4234,7 +4264,7 @@
         <v>3200000</v>
       </c>
       <c r="AT9" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="AU9">
         <v>55</v>
@@ -4264,10 +4294,10 @@
         <v>1</v>
       </c>
       <c r="BD9">
-        <v>8700</v>
+        <v>4700</v>
       </c>
       <c r="BE9" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="BF9">
         <v>0</v>
@@ -4279,7 +4309,7 @@
         <v>1</v>
       </c>
       <c r="BI9" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="BJ9">
         <v>2</v>
@@ -4288,19 +4318,28 @@
         <v>9</v>
       </c>
       <c r="BL9" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BM9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BN9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BO9" t="b">
         <v>1</v>
       </c>
+      <c r="BP9">
+        <v>2800</v>
+      </c>
+      <c r="BQ9" t="s">
+        <v>182</v>
+      </c>
+      <c r="BR9" t="b">
+        <v>1</v>
+      </c>
       <c r="BS9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="BT9">
         <v>2</v>
@@ -4309,7 +4348,7 @@
         <v>9</v>
       </c>
       <c r="BV9" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BW9">
         <v>0</v>
@@ -4321,7 +4360,7 @@
         <v>1</v>
       </c>
       <c r="CC9" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="CD9">
         <v>2</v>
@@ -4330,7 +4369,7 @@
         <v>9</v>
       </c>
       <c r="CF9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CG9">
         <v>0</v>
@@ -4342,7 +4381,7 @@
         <v>1</v>
       </c>
       <c r="CL9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CM9">
         <v>1</v>
@@ -4354,22 +4393,22 @@
         <v>1</v>
       </c>
       <c r="CP9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="CQ9">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="CR9">
-        <v>15000</v>
+        <v>20000</v>
       </c>
       <c r="CS9">
         <v>7200</v>
       </c>
       <c r="CT9">
-        <v>7200</v>
+        <v>11000</v>
       </c>
       <c r="CU9">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="CV9">
         <v>0.9</v>
@@ -4384,7 +4423,7 @@
         <v>0</v>
       </c>
       <c r="DJ9" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="DK9">
         <v>0.05</v>
@@ -4399,10 +4438,10 @@
         <v>8.5</v>
       </c>
       <c r="DO9" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="DP9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="DQ9">
         <v>1</v>
@@ -4411,13 +4450,13 @@
         <v>1</v>
       </c>
       <c r="DS9" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="DT9">
-        <v>5500</v>
+        <v>3900</v>
       </c>
       <c r="DU9">
-        <v>5500</v>
+        <v>3900</v>
       </c>
       <c r="DV9">
         <v>0.95</v>
@@ -4432,7 +4471,7 @@
         <v>0</v>
       </c>
       <c r="DZ9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="EA9">
         <v>0</v>
@@ -4441,28 +4480,28 @@
         <v>0</v>
       </c>
       <c r="EC9" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="EG9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="EH9" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="EI9">
         <v>96</v>
       </c>
       <c r="EJ9" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="EK9">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="EL9" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="EM9">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="EN9">
         <v>0</v>
@@ -4566,7 +4605,7 @@
         <v>170</v>
       </c>
       <c r="AJ10">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="AK10" t="s">
         <v>162</v>
@@ -4596,7 +4635,7 @@
         <v>2800000</v>
       </c>
       <c r="AT10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="AU10">
         <v>55</v>
@@ -4617,31 +4656,16 @@
         <v>90</v>
       </c>
       <c r="BA10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC10" t="b">
         <v>1</v>
       </c>
-      <c r="BD10">
-        <v>5400</v>
-      </c>
-      <c r="BE10" t="s">
-        <v>175</v>
-      </c>
-      <c r="BF10">
-        <v>0</v>
-      </c>
-      <c r="BG10">
-        <v>40</v>
-      </c>
-      <c r="BH10" t="b">
-        <v>1</v>
-      </c>
       <c r="BI10" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="BJ10">
         <v>2</v>
@@ -4650,7 +4674,7 @@
         <v>9</v>
       </c>
       <c r="BL10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BM10">
         <v>0</v>
@@ -4662,7 +4686,7 @@
         <v>1</v>
       </c>
       <c r="BS10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="BT10">
         <v>2</v>
@@ -4671,7 +4695,7 @@
         <v>9</v>
       </c>
       <c r="BV10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BW10">
         <v>0</v>
@@ -4683,7 +4707,7 @@
         <v>1</v>
       </c>
       <c r="CC10" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="CD10">
         <v>2</v>
@@ -4692,7 +4716,7 @@
         <v>9</v>
       </c>
       <c r="CF10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CG10">
         <v>0</v>
@@ -4704,19 +4728,49 @@
         <v>1</v>
       </c>
       <c r="CL10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CM10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO10" t="b">
         <v>1</v>
       </c>
+      <c r="CP10" t="s">
+        <v>189</v>
+      </c>
+      <c r="CQ10">
+        <v>50000</v>
+      </c>
+      <c r="CR10">
+        <v>15000</v>
+      </c>
+      <c r="CS10">
+        <v>7200</v>
+      </c>
+      <c r="CT10">
+        <v>7200</v>
+      </c>
+      <c r="CU10">
+        <v>50000</v>
+      </c>
+      <c r="CV10">
+        <v>0.9</v>
+      </c>
+      <c r="CW10">
+        <v>0.8</v>
+      </c>
+      <c r="CX10" t="b">
+        <v>0</v>
+      </c>
+      <c r="CY10" t="b">
+        <v>0</v>
+      </c>
       <c r="DJ10" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="DK10">
         <v>0.05</v>
@@ -4731,10 +4785,10 @@
         <v>8.5</v>
       </c>
       <c r="DO10" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="DP10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="DQ10">
         <v>0</v>
@@ -4743,10 +4797,10 @@
         <v>0</v>
       </c>
       <c r="DS10" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="DZ10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="EA10">
         <v>0</v>
@@ -4755,28 +4809,28 @@
         <v>0</v>
       </c>
       <c r="EC10" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="EG10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="EH10" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="EI10">
         <v>96</v>
       </c>
       <c r="EJ10" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="EK10">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="EL10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="EM10">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="EN10">
         <v>0</v>
@@ -4823,10 +4877,10 @@
         <v>1</v>
       </c>
       <c r="O11">
-        <v>3648000</v>
+        <v>5527000</v>
       </c>
       <c r="P11" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="Q11" t="s">
         <v>162</v>
@@ -4877,10 +4931,10 @@
         <v>5500000</v>
       </c>
       <c r="AI11" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="AJ11">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="AK11" t="s">
         <v>162</v>
@@ -4907,10 +4961,10 @@
         <v>1</v>
       </c>
       <c r="AS11">
-        <v>1800000</v>
+        <v>2400000</v>
       </c>
       <c r="AT11" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AU11">
         <v>55</v>
@@ -4931,31 +4985,16 @@
         <v>90</v>
       </c>
       <c r="BA11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC11" t="b">
         <v>1</v>
       </c>
-      <c r="BD11">
-        <v>4800</v>
-      </c>
-      <c r="BE11" t="s">
-        <v>175</v>
-      </c>
-      <c r="BF11">
-        <v>0</v>
-      </c>
-      <c r="BG11">
-        <v>40</v>
-      </c>
-      <c r="BH11" t="b">
-        <v>1</v>
-      </c>
       <c r="BI11" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="BJ11">
         <v>2</v>
@@ -4964,7 +5003,7 @@
         <v>9</v>
       </c>
       <c r="BL11" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BM11">
         <v>1</v>
@@ -4976,7 +5015,7 @@
         <v>1</v>
       </c>
       <c r="BP11">
-        <v>2500</v>
+        <v>3300</v>
       </c>
       <c r="BQ11" t="s">
         <v>181</v>
@@ -4985,7 +5024,7 @@
         <v>1</v>
       </c>
       <c r="BS11" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="BT11">
         <v>2</v>
@@ -4994,7 +5033,7 @@
         <v>9</v>
       </c>
       <c r="BV11" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BW11">
         <v>0</v>
@@ -5006,7 +5045,7 @@
         <v>1</v>
       </c>
       <c r="CC11" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="CD11">
         <v>2</v>
@@ -5015,7 +5054,7 @@
         <v>9</v>
       </c>
       <c r="CF11" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CG11">
         <v>0</v>
@@ -5027,7 +5066,7 @@
         <v>1</v>
       </c>
       <c r="CL11" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CM11">
         <v>0</v>
@@ -5039,7 +5078,7 @@
         <v>1</v>
       </c>
       <c r="DJ11" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="DK11">
         <v>0.05</v>
@@ -5054,10 +5093,10 @@
         <v>8.5</v>
       </c>
       <c r="DO11" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="DP11" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="DQ11">
         <v>0</v>
@@ -5066,10 +5105,10 @@
         <v>0</v>
       </c>
       <c r="DS11" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="DZ11" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="EA11">
         <v>0</v>
@@ -5078,28 +5117,28 @@
         <v>0</v>
       </c>
       <c r="EC11" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="EG11" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="EH11" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="EI11">
         <v>96</v>
       </c>
       <c r="EJ11" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="EK11">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="EL11" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="EM11">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="EN11">
         <v>0</v>
@@ -5135,13 +5174,13 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>4</v>
@@ -5572,10 +5611,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="F2" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="G2" t="b">
         <v>0</v>
@@ -5611,7 +5650,7 @@
         <v>1</v>
       </c>
       <c r="R2">
-        <v>16882000</v>
+        <v>15173000</v>
       </c>
       <c r="T2" t="s">
         <v>162</v>
@@ -5710,10 +5749,10 @@
         <v>1</v>
       </c>
       <c r="BG2">
-        <v>30000</v>
+        <v>20000</v>
       </c>
       <c r="BH2" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="BI2">
         <v>0</v>
@@ -5725,7 +5764,7 @@
         <v>1</v>
       </c>
       <c r="BL2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="BM2">
         <v>2</v>
@@ -5734,7 +5773,7 @@
         <v>9</v>
       </c>
       <c r="BO2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BP2">
         <v>1</v>
@@ -5746,47 +5785,47 @@
         <v>1</v>
       </c>
       <c r="BS2">
-        <v>12000</v>
+        <v>9000</v>
       </c>
       <c r="BT2" t="s">
+        <v>233</v>
+      </c>
+      <c r="BU2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BV2" t="s">
+        <v>183</v>
+      </c>
+      <c r="BW2">
+        <v>2</v>
+      </c>
+      <c r="BX2">
+        <v>9</v>
+      </c>
+      <c r="BY2" t="s">
+        <v>179</v>
+      </c>
+      <c r="BZ2">
+        <v>1</v>
+      </c>
+      <c r="CA2">
+        <v>1</v>
+      </c>
+      <c r="CB2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CC2">
+        <v>1800</v>
+      </c>
+      <c r="CD2" t="s">
+        <v>234</v>
+      </c>
+      <c r="CE2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CF2" t="s">
         <v>178</v>
       </c>
-      <c r="BU2" t="b">
-        <v>1</v>
-      </c>
-      <c r="BV2" t="s">
-        <v>182</v>
-      </c>
-      <c r="BW2">
-        <v>2</v>
-      </c>
-      <c r="BX2">
-        <v>9</v>
-      </c>
-      <c r="BY2" t="s">
-        <v>177</v>
-      </c>
-      <c r="BZ2">
-        <v>1</v>
-      </c>
-      <c r="CA2">
-        <v>1</v>
-      </c>
-      <c r="CB2" t="b">
-        <v>1</v>
-      </c>
-      <c r="CC2">
-        <v>1900</v>
-      </c>
-      <c r="CD2" t="s">
-        <v>229</v>
-      </c>
-      <c r="CE2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CF2" t="s">
-        <v>176</v>
-      </c>
       <c r="CG2">
         <v>2</v>
       </c>
@@ -5794,7 +5833,7 @@
         <v>9</v>
       </c>
       <c r="CI2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CJ2">
         <v>0</v>
@@ -5806,7 +5845,7 @@
         <v>1</v>
       </c>
       <c r="CO2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CP2">
         <v>0</v>
@@ -5818,10 +5857,10 @@
         <v>1</v>
       </c>
       <c r="DR2" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="DS2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="DT2">
         <v>1</v>
@@ -5833,10 +5872,10 @@
         <v>1</v>
       </c>
       <c r="DW2">
-        <v>17000</v>
+        <v>15000</v>
       </c>
       <c r="DX2">
-        <v>17000</v>
+        <v>15000</v>
       </c>
       <c r="DY2">
         <v>0.95</v>
@@ -5851,7 +5890,7 @@
         <v>0</v>
       </c>
       <c r="EC2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="ED2">
         <v>1</v>
@@ -5872,25 +5911,25 @@
         <v>0.1</v>
       </c>
       <c r="EJ2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="EK2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="EL2">
         <v>96</v>
       </c>
       <c r="EM2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="EN2">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="EO2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="EP2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="EQ2">
         <v>0</v>
@@ -5907,10 +5946,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="F3" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="G3" t="b">
         <v>0</v>
@@ -5946,10 +5985,10 @@
         <v>1</v>
       </c>
       <c r="R3">
-        <v>2455000</v>
+        <v>1158000</v>
       </c>
       <c r="S3" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="T3" t="s">
         <v>162</v>
@@ -5997,7 +6036,7 @@
         <v>15000000</v>
       </c>
       <c r="AL3" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="AM3">
         <v>55</v>
@@ -6027,10 +6066,10 @@
         <v>1</v>
       </c>
       <c r="AV3">
-        <v>3200</v>
+        <v>2800</v>
       </c>
       <c r="AW3" t="s">
-        <v>224</v>
+        <v>174</v>
       </c>
       <c r="AX3">
         <v>55</v>
@@ -6060,7 +6099,7 @@
         <v>1</v>
       </c>
       <c r="BL3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="BM3">
         <v>2</v>
@@ -6069,7 +6108,7 @@
         <v>9</v>
       </c>
       <c r="BO3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BP3">
         <v>0</v>
@@ -6081,7 +6120,7 @@
         <v>1</v>
       </c>
       <c r="BV3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="BW3">
         <v>2</v>
@@ -6090,7 +6129,7 @@
         <v>9</v>
       </c>
       <c r="BY3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BZ3">
         <v>0</v>
@@ -6102,7 +6141,7 @@
         <v>1</v>
       </c>
       <c r="CF3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="CG3">
         <v>2</v>
@@ -6111,7 +6150,7 @@
         <v>9</v>
       </c>
       <c r="CI3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CJ3">
         <v>0</v>
@@ -6123,7 +6162,7 @@
         <v>1</v>
       </c>
       <c r="CO3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CP3">
         <v>0</v>
@@ -6135,7 +6174,7 @@
         <v>1</v>
       </c>
       <c r="DM3" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="DN3">
         <v>0.05</v>
@@ -6150,10 +6189,10 @@
         <v>8</v>
       </c>
       <c r="DR3" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="DS3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="DT3">
         <v>0</v>
@@ -6165,7 +6204,7 @@
         <v>1</v>
       </c>
       <c r="EC3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="ED3">
         <v>0</v>
@@ -6177,25 +6216,25 @@
         <v>1</v>
       </c>
       <c r="EJ3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="EK3" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="EL3">
         <v>96</v>
       </c>
       <c r="EM3" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="EN3">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="EO3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="EP3">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="EQ3">
         <v>0</v>
@@ -6212,10 +6251,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="F4" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="G4" t="b">
         <v>0</v>
@@ -6251,10 +6290,10 @@
         <v>1</v>
       </c>
       <c r="R4">
-        <v>2012000</v>
+        <v>1546000</v>
       </c>
       <c r="S4" t="s">
-        <v>155</v>
+        <v>217</v>
       </c>
       <c r="T4" t="s">
         <v>162</v>
@@ -6302,10 +6341,10 @@
         <v>15000000</v>
       </c>
       <c r="AL4" t="s">
-        <v>169</v>
+        <v>227</v>
       </c>
       <c r="AM4">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="AN4" t="s">
         <v>162</v>
@@ -6332,10 +6371,10 @@
         <v>1</v>
       </c>
       <c r="AV4">
-        <v>2800</v>
+        <v>3200</v>
       </c>
       <c r="AW4" t="s">
-        <v>174</v>
+        <v>230</v>
       </c>
       <c r="AX4">
         <v>55</v>
@@ -6365,7 +6404,7 @@
         <v>1</v>
       </c>
       <c r="BL4" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="BM4">
         <v>2</v>
@@ -6374,7 +6413,7 @@
         <v>9</v>
       </c>
       <c r="BO4" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BP4">
         <v>0</v>
@@ -6386,7 +6425,7 @@
         <v>1</v>
       </c>
       <c r="BV4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="BW4">
         <v>2</v>
@@ -6395,7 +6434,7 @@
         <v>9</v>
       </c>
       <c r="BY4" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BZ4">
         <v>0</v>
@@ -6407,7 +6446,7 @@
         <v>1</v>
       </c>
       <c r="CF4" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="CG4">
         <v>2</v>
@@ -6416,7 +6455,7 @@
         <v>9</v>
       </c>
       <c r="CI4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CJ4">
         <v>0</v>
@@ -6428,19 +6467,49 @@
         <v>1</v>
       </c>
       <c r="CO4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CP4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CR4" t="b">
         <v>1</v>
       </c>
+      <c r="CS4" t="s">
+        <v>190</v>
+      </c>
+      <c r="CT4">
+        <v>50000</v>
+      </c>
+      <c r="CU4">
+        <v>15000</v>
+      </c>
+      <c r="CV4">
+        <v>7200</v>
+      </c>
+      <c r="CW4">
+        <v>7200</v>
+      </c>
+      <c r="CX4">
+        <v>50000</v>
+      </c>
+      <c r="CY4">
+        <v>0.9</v>
+      </c>
+      <c r="CZ4">
+        <v>0.8</v>
+      </c>
+      <c r="DA4" t="b">
+        <v>0</v>
+      </c>
+      <c r="DB4" t="b">
+        <v>0</v>
+      </c>
       <c r="DM4" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="DN4">
         <v>0.05</v>
@@ -6455,10 +6524,10 @@
         <v>8</v>
       </c>
       <c r="DR4" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="DS4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="DT4">
         <v>0</v>
@@ -6470,7 +6539,7 @@
         <v>1</v>
       </c>
       <c r="EC4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="ED4">
         <v>0</v>
@@ -6482,25 +6551,25 @@
         <v>1</v>
       </c>
       <c r="EJ4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="EK4" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="EL4">
         <v>96</v>
       </c>
       <c r="EM4" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="EN4">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="EO4" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="EP4">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="EQ4">
         <v>0</v>
@@ -6517,10 +6586,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="F5" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="G5" t="b">
         <v>0</v>
@@ -6559,7 +6628,7 @@
         <v>3296000</v>
       </c>
       <c r="S5" t="s">
-        <v>159</v>
+        <v>218</v>
       </c>
       <c r="T5" t="s">
         <v>162</v>
@@ -6607,10 +6676,10 @@
         <v>15000000</v>
       </c>
       <c r="AL5" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="AM5">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="AN5" t="s">
         <v>162</v>
@@ -6640,7 +6709,7 @@
         <v>2800</v>
       </c>
       <c r="AW5" t="s">
-        <v>224</v>
+        <v>173</v>
       </c>
       <c r="AX5">
         <v>55</v>
@@ -6670,7 +6739,7 @@
         <v>1</v>
       </c>
       <c r="BL5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="BM5">
         <v>2</v>
@@ -6679,7 +6748,7 @@
         <v>9</v>
       </c>
       <c r="BO5" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BP5">
         <v>0</v>
@@ -6691,7 +6760,7 @@
         <v>1</v>
       </c>
       <c r="BV5" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="BW5">
         <v>2</v>
@@ -6700,7 +6769,7 @@
         <v>9</v>
       </c>
       <c r="BY5" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BZ5">
         <v>0</v>
@@ -6712,7 +6781,7 @@
         <v>1</v>
       </c>
       <c r="CF5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="CG5">
         <v>2</v>
@@ -6721,7 +6790,7 @@
         <v>9</v>
       </c>
       <c r="CI5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CJ5">
         <v>0</v>
@@ -6733,49 +6802,19 @@
         <v>1</v>
       </c>
       <c r="CO5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CP5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CR5" t="b">
         <v>1</v>
       </c>
-      <c r="CS5" t="s">
-        <v>185</v>
-      </c>
-      <c r="CT5">
-        <v>50000</v>
-      </c>
-      <c r="CU5">
-        <v>15000</v>
-      </c>
-      <c r="CV5">
-        <v>7200</v>
-      </c>
-      <c r="CW5">
-        <v>7200</v>
-      </c>
-      <c r="CX5">
-        <v>50000</v>
-      </c>
-      <c r="CY5">
-        <v>0.9</v>
-      </c>
-      <c r="CZ5">
-        <v>0.8</v>
-      </c>
-      <c r="DA5" t="b">
-        <v>0</v>
-      </c>
-      <c r="DB5" t="b">
-        <v>0</v>
-      </c>
       <c r="DM5" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="DN5">
         <v>0.05</v>
@@ -6790,10 +6829,10 @@
         <v>8</v>
       </c>
       <c r="DR5" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="DS5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="DT5">
         <v>0</v>
@@ -6805,7 +6844,7 @@
         <v>1</v>
       </c>
       <c r="EC5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="ED5">
         <v>0</v>
@@ -6817,25 +6856,25 @@
         <v>1</v>
       </c>
       <c r="EJ5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="EK5" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="EL5">
         <v>96</v>
       </c>
       <c r="EM5" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="EN5">
         <v>24</v>
       </c>
       <c r="EO5" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="EP5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="EQ5">
         <v>0</v>
@@ -6852,10 +6891,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="F6" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="G6" t="b">
         <v>0</v>
@@ -6891,10 +6930,10 @@
         <v>1</v>
       </c>
       <c r="R6">
-        <v>2455000</v>
+        <v>1720000</v>
       </c>
       <c r="S6" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="T6" t="s">
         <v>162</v>
@@ -6942,7 +6981,7 @@
         <v>15000000</v>
       </c>
       <c r="AL6" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="AM6">
         <v>55</v>
@@ -6972,10 +7011,10 @@
         <v>1</v>
       </c>
       <c r="AV6">
-        <v>2400</v>
+        <v>2800</v>
       </c>
       <c r="AW6" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="AX6">
         <v>55</v>
@@ -7005,7 +7044,7 @@
         <v>1</v>
       </c>
       <c r="BL6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="BM6">
         <v>2</v>
@@ -7014,7 +7053,7 @@
         <v>9</v>
       </c>
       <c r="BO6" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BP6">
         <v>0</v>
@@ -7026,7 +7065,7 @@
         <v>1</v>
       </c>
       <c r="BV6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="BW6">
         <v>2</v>
@@ -7035,7 +7074,7 @@
         <v>9</v>
       </c>
       <c r="BY6" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BZ6">
         <v>0</v>
@@ -7047,7 +7086,7 @@
         <v>1</v>
       </c>
       <c r="CF6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="CG6">
         <v>2</v>
@@ -7056,7 +7095,7 @@
         <v>9</v>
       </c>
       <c r="CI6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CJ6">
         <v>0</v>
@@ -7068,7 +7107,7 @@
         <v>1</v>
       </c>
       <c r="CO6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CP6">
         <v>0</v>
@@ -7080,7 +7119,7 @@
         <v>1</v>
       </c>
       <c r="DM6" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="DN6">
         <v>0.05</v>
@@ -7095,10 +7134,10 @@
         <v>8</v>
       </c>
       <c r="DR6" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="DS6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="DT6">
         <v>0</v>
@@ -7110,7 +7149,7 @@
         <v>1</v>
       </c>
       <c r="EC6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="ED6">
         <v>0</v>
@@ -7122,25 +7161,25 @@
         <v>1</v>
       </c>
       <c r="EJ6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="EK6" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="EL6">
         <v>96</v>
       </c>
       <c r="EM6" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="EN6">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="EO6" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="EP6">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="EQ6">
         <v>0</v>
@@ -7157,10 +7196,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="F7" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="G7" t="b">
         <v>0</v>
@@ -7196,10 +7235,10 @@
         <v>1</v>
       </c>
       <c r="R7">
-        <v>1416000</v>
+        <v>1266000</v>
       </c>
       <c r="S7" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="T7" t="s">
         <v>162</v>
@@ -7247,7 +7286,7 @@
         <v>15000000</v>
       </c>
       <c r="AL7" t="s">
-        <v>165</v>
+        <v>229</v>
       </c>
       <c r="AM7">
         <v>55</v>
@@ -7280,7 +7319,7 @@
         <v>3200</v>
       </c>
       <c r="AW7" t="s">
-        <v>225</v>
+        <v>176</v>
       </c>
       <c r="AX7">
         <v>55</v>
@@ -7310,7 +7349,7 @@
         <v>1</v>
       </c>
       <c r="BL7" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="BM7">
         <v>2</v>
@@ -7319,7 +7358,7 @@
         <v>9</v>
       </c>
       <c r="BO7" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BP7">
         <v>0</v>
@@ -7331,7 +7370,7 @@
         <v>1</v>
       </c>
       <c r="BV7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="BW7">
         <v>2</v>
@@ -7340,7 +7379,7 @@
         <v>9</v>
       </c>
       <c r="BY7" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BZ7">
         <v>0</v>
@@ -7352,7 +7391,7 @@
         <v>1</v>
       </c>
       <c r="CF7" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="CG7">
         <v>2</v>
@@ -7361,7 +7400,7 @@
         <v>9</v>
       </c>
       <c r="CI7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CJ7">
         <v>0</v>
@@ -7373,7 +7412,7 @@
         <v>1</v>
       </c>
       <c r="CO7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CP7">
         <v>0</v>
@@ -7385,7 +7424,7 @@
         <v>1</v>
       </c>
       <c r="DM7" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="DN7">
         <v>0.05</v>
@@ -7400,10 +7439,10 @@
         <v>8</v>
       </c>
       <c r="DR7" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="DS7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="DT7">
         <v>0</v>
@@ -7415,7 +7454,7 @@
         <v>1</v>
       </c>
       <c r="EC7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="ED7">
         <v>0</v>
@@ -7427,22 +7466,22 @@
         <v>1</v>
       </c>
       <c r="EJ7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="EK7" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="EL7">
         <v>96</v>
       </c>
       <c r="EM7" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="EN7">
         <v>48</v>
       </c>
       <c r="EO7" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="EP7">
         <v>0</v>
@@ -7462,10 +7501,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="F8" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="G8" t="b">
         <v>0</v>
@@ -7501,10 +7540,10 @@
         <v>1</v>
       </c>
       <c r="R8">
-        <v>2262000</v>
+        <v>2012000</v>
       </c>
       <c r="S8" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="T8" t="s">
         <v>162</v>
@@ -7552,7 +7591,7 @@
         <v>15000000</v>
       </c>
       <c r="AL8" t="s">
-        <v>165</v>
+        <v>228</v>
       </c>
       <c r="AM8">
         <v>55</v>
@@ -7585,7 +7624,7 @@
         <v>2400</v>
       </c>
       <c r="AW8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AX8">
         <v>55</v>
@@ -7615,7 +7654,7 @@
         <v>1</v>
       </c>
       <c r="BL8" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="BM8">
         <v>2</v>
@@ -7624,7 +7663,7 @@
         <v>9</v>
       </c>
       <c r="BO8" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BP8">
         <v>0</v>
@@ -7636,7 +7675,7 @@
         <v>1</v>
       </c>
       <c r="BV8" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="BW8">
         <v>2</v>
@@ -7645,7 +7684,7 @@
         <v>9</v>
       </c>
       <c r="BY8" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BZ8">
         <v>0</v>
@@ -7657,7 +7696,7 @@
         <v>1</v>
       </c>
       <c r="CF8" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="CG8">
         <v>2</v>
@@ -7666,7 +7705,7 @@
         <v>9</v>
       </c>
       <c r="CI8" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CJ8">
         <v>0</v>
@@ -7678,49 +7717,19 @@
         <v>1</v>
       </c>
       <c r="CO8" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CP8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CR8" t="b">
         <v>1</v>
       </c>
-      <c r="CS8" t="s">
-        <v>230</v>
-      </c>
-      <c r="CT8">
-        <v>75000</v>
-      </c>
-      <c r="CU8">
-        <v>20000</v>
-      </c>
-      <c r="CV8">
-        <v>7200</v>
-      </c>
-      <c r="CW8">
-        <v>11000</v>
-      </c>
-      <c r="CX8">
-        <v>100000</v>
-      </c>
-      <c r="CY8">
-        <v>0.9</v>
-      </c>
-      <c r="CZ8">
-        <v>0.8</v>
-      </c>
-      <c r="DA8" t="b">
-        <v>0</v>
-      </c>
-      <c r="DB8" t="b">
-        <v>0</v>
-      </c>
       <c r="DM8" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="DN8">
         <v>0.05</v>
@@ -7735,10 +7744,10 @@
         <v>8</v>
       </c>
       <c r="DR8" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="DS8" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="DT8">
         <v>0</v>
@@ -7750,7 +7759,7 @@
         <v>1</v>
       </c>
       <c r="EC8" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="ED8">
         <v>0</v>
@@ -7762,25 +7771,25 @@
         <v>1</v>
       </c>
       <c r="EJ8" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="EK8" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="EL8">
         <v>96</v>
       </c>
       <c r="EM8" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="EN8">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="EO8" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="EP8">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="EQ8">
         <v>0</v>
@@ -7797,10 +7806,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="F9" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="G9" t="b">
         <v>0</v>
@@ -7836,10 +7845,10 @@
         <v>1</v>
       </c>
       <c r="R9">
-        <v>1720000</v>
+        <v>2455000</v>
       </c>
       <c r="S9" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="T9" t="s">
         <v>162</v>
@@ -7887,7 +7896,7 @@
         <v>15000000</v>
       </c>
       <c r="AL9" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="AM9">
         <v>35</v>
@@ -7917,10 +7926,10 @@
         <v>1</v>
       </c>
       <c r="AV9">
-        <v>2800</v>
+        <v>2400</v>
       </c>
       <c r="AW9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AX9">
         <v>55</v>
@@ -7950,7 +7959,7 @@
         <v>1</v>
       </c>
       <c r="BL9" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="BM9">
         <v>2</v>
@@ -7959,7 +7968,7 @@
         <v>9</v>
       </c>
       <c r="BO9" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BP9">
         <v>0</v>
@@ -7971,7 +7980,7 @@
         <v>1</v>
       </c>
       <c r="BV9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="BW9">
         <v>2</v>
@@ -7980,7 +7989,7 @@
         <v>9</v>
       </c>
       <c r="BY9" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BZ9">
         <v>0</v>
@@ -7992,7 +8001,7 @@
         <v>1</v>
       </c>
       <c r="CF9" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="CG9">
         <v>2</v>
@@ -8001,7 +8010,7 @@
         <v>9</v>
       </c>
       <c r="CI9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CJ9">
         <v>0</v>
@@ -8013,19 +8022,49 @@
         <v>1</v>
       </c>
       <c r="CO9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CP9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CR9" t="b">
         <v>1</v>
       </c>
+      <c r="CS9" t="s">
+        <v>186</v>
+      </c>
+      <c r="CT9">
+        <v>75000</v>
+      </c>
+      <c r="CU9">
+        <v>20000</v>
+      </c>
+      <c r="CV9">
+        <v>7200</v>
+      </c>
+      <c r="CW9">
+        <v>11000</v>
+      </c>
+      <c r="CX9">
+        <v>100000</v>
+      </c>
+      <c r="CY9">
+        <v>0.9</v>
+      </c>
+      <c r="CZ9">
+        <v>0.8</v>
+      </c>
+      <c r="DA9" t="b">
+        <v>0</v>
+      </c>
+      <c r="DB9" t="b">
+        <v>0</v>
+      </c>
       <c r="DM9" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="DN9">
         <v>0.05</v>
@@ -8040,10 +8079,10 @@
         <v>8</v>
       </c>
       <c r="DR9" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="DS9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="DT9">
         <v>0</v>
@@ -8055,7 +8094,7 @@
         <v>1</v>
       </c>
       <c r="EC9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="ED9">
         <v>0</v>
@@ -8067,25 +8106,25 @@
         <v>1</v>
       </c>
       <c r="EJ9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="EK9" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="EL9">
         <v>96</v>
       </c>
       <c r="EM9" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="EN9">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="EO9" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="EP9">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="EQ9">
         <v>0</v>
@@ -8102,10 +8141,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="F10" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="G10" t="b">
         <v>0</v>
@@ -8141,10 +8180,10 @@
         <v>1</v>
       </c>
       <c r="R10">
-        <v>1266000</v>
+        <v>1720000</v>
       </c>
       <c r="S10" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="T10" t="s">
         <v>162</v>
@@ -8192,10 +8231,10 @@
         <v>15000000</v>
       </c>
       <c r="AL10" t="s">
-        <v>169</v>
+        <v>228</v>
       </c>
       <c r="AM10">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="AN10" t="s">
         <v>162</v>
@@ -8225,7 +8264,7 @@
         <v>2800</v>
       </c>
       <c r="AW10" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AX10">
         <v>55</v>
@@ -8255,7 +8294,7 @@
         <v>1</v>
       </c>
       <c r="BL10" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="BM10">
         <v>2</v>
@@ -8264,7 +8303,7 @@
         <v>9</v>
       </c>
       <c r="BO10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BP10">
         <v>0</v>
@@ -8276,7 +8315,7 @@
         <v>1</v>
       </c>
       <c r="BV10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="BW10">
         <v>2</v>
@@ -8285,7 +8324,7 @@
         <v>9</v>
       </c>
       <c r="BY10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BZ10">
         <v>0</v>
@@ -8297,7 +8336,7 @@
         <v>1</v>
       </c>
       <c r="CF10" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="CG10">
         <v>2</v>
@@ -8306,7 +8345,7 @@
         <v>9</v>
       </c>
       <c r="CI10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CJ10">
         <v>0</v>
@@ -8318,7 +8357,7 @@
         <v>1</v>
       </c>
       <c r="CO10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CP10">
         <v>0</v>
@@ -8330,7 +8369,7 @@
         <v>1</v>
       </c>
       <c r="DM10" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="DN10">
         <v>0.05</v>
@@ -8345,10 +8384,10 @@
         <v>8</v>
       </c>
       <c r="DR10" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="DS10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="DT10">
         <v>0</v>
@@ -8360,7 +8399,7 @@
         <v>1</v>
       </c>
       <c r="EC10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="ED10">
         <v>0</v>
@@ -8372,25 +8411,25 @@
         <v>1</v>
       </c>
       <c r="EJ10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="EK10" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="EL10">
         <v>96</v>
       </c>
       <c r="EM10" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="EN10">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="EO10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="EP10">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="EQ10">
         <v>0</v>
@@ -8407,10 +8446,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="F11" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="G11" t="b">
         <v>0</v>
@@ -8446,7 +8485,7 @@
         <v>1</v>
       </c>
       <c r="R11">
-        <v>11278000</v>
+        <v>12880000</v>
       </c>
       <c r="T11" t="s">
         <v>162</v>
@@ -8545,10 +8584,10 @@
         <v>1</v>
       </c>
       <c r="BG11">
-        <v>16000</v>
+        <v>19000</v>
       </c>
       <c r="BH11" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="BI11">
         <v>0</v>
@@ -8560,7 +8599,7 @@
         <v>1</v>
       </c>
       <c r="BL11" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="BM11">
         <v>2</v>
@@ -8569,7 +8608,7 @@
         <v>9</v>
       </c>
       <c r="BO11" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BP11">
         <v>0</v>
@@ -8581,7 +8620,7 @@
         <v>1</v>
       </c>
       <c r="BV11" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="BW11">
         <v>2</v>
@@ -8590,7 +8629,7 @@
         <v>9</v>
       </c>
       <c r="BY11" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BZ11">
         <v>1</v>
@@ -8602,16 +8641,16 @@
         <v>1</v>
       </c>
       <c r="CC11">
-        <v>940</v>
+        <v>2800</v>
       </c>
       <c r="CD11" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="CE11" t="b">
         <v>0</v>
       </c>
       <c r="CF11" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="CG11">
         <v>2</v>
@@ -8620,7 +8659,7 @@
         <v>9</v>
       </c>
       <c r="CI11" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CJ11">
         <v>0</v>
@@ -8632,7 +8671,7 @@
         <v>1</v>
       </c>
       <c r="CO11" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CP11">
         <v>0</v>
@@ -8644,10 +8683,10 @@
         <v>1</v>
       </c>
       <c r="DR11" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="DS11" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="DT11">
         <v>1</v>
@@ -8659,10 +8698,10 @@
         <v>1</v>
       </c>
       <c r="DW11">
-        <v>11000</v>
+        <v>13000</v>
       </c>
       <c r="DX11">
-        <v>11000</v>
+        <v>13000</v>
       </c>
       <c r="DY11">
         <v>0.95</v>
@@ -8677,7 +8716,7 @@
         <v>0</v>
       </c>
       <c r="EC11" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="ED11">
         <v>1</v>
@@ -8698,25 +8737,25 @@
         <v>0.1</v>
       </c>
       <c r="EJ11" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="EK11" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="EL11">
         <v>96</v>
       </c>
       <c r="EM11" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="EN11">
         <v>48</v>
       </c>
       <c r="EO11" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="EP11">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="EQ11">
         <v>0</v>
@@ -8733,10 +8772,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="F12" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="G12" t="b">
         <v>0</v>
@@ -8772,10 +8811,10 @@
         <v>1</v>
       </c>
       <c r="R12">
-        <v>3296000</v>
+        <v>2262000</v>
       </c>
       <c r="S12" t="s">
-        <v>159</v>
+        <v>223</v>
       </c>
       <c r="T12" t="s">
         <v>162</v>
@@ -8856,7 +8895,7 @@
         <v>2100</v>
       </c>
       <c r="AW12" t="s">
-        <v>225</v>
+        <v>172</v>
       </c>
       <c r="AX12">
         <v>55</v>
@@ -8886,7 +8925,7 @@
         <v>1</v>
       </c>
       <c r="BL12" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="BM12">
         <v>2</v>
@@ -8895,7 +8934,7 @@
         <v>9</v>
       </c>
       <c r="BO12" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BP12">
         <v>0</v>
@@ -8907,7 +8946,7 @@
         <v>1</v>
       </c>
       <c r="BV12" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="BW12">
         <v>2</v>
@@ -8916,7 +8955,7 @@
         <v>9</v>
       </c>
       <c r="BY12" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BZ12">
         <v>0</v>
@@ -8928,7 +8967,7 @@
         <v>1</v>
       </c>
       <c r="CF12" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="CG12">
         <v>2</v>
@@ -8937,7 +8976,7 @@
         <v>9</v>
       </c>
       <c r="CI12" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CJ12">
         <v>0</v>
@@ -8949,7 +8988,7 @@
         <v>1</v>
       </c>
       <c r="CO12" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CP12">
         <v>0</v>
@@ -8976,10 +9015,10 @@
         <v>8</v>
       </c>
       <c r="DR12" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="DS12" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="DT12">
         <v>0</v>
@@ -8991,7 +9030,7 @@
         <v>1</v>
       </c>
       <c r="EC12" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="ED12">
         <v>0</v>
@@ -9003,25 +9042,25 @@
         <v>1</v>
       </c>
       <c r="EJ12" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="EK12" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="EL12">
         <v>96</v>
       </c>
       <c r="EM12" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="EN12">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="EO12" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="EP12">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="EQ12">
         <v>0</v>
@@ -9038,10 +9077,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="F13" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="G13" t="b">
         <v>0</v>
@@ -9077,10 +9116,10 @@
         <v>1</v>
       </c>
       <c r="R13">
-        <v>1546000</v>
+        <v>2012000</v>
       </c>
       <c r="S13" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="T13" t="s">
         <v>162</v>
@@ -9128,10 +9167,10 @@
         <v>3850000</v>
       </c>
       <c r="AL13" t="s">
-        <v>223</v>
+        <v>169</v>
       </c>
       <c r="AM13">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="AN13" t="s">
         <v>162</v>
@@ -9161,7 +9200,7 @@
         <v>2400</v>
       </c>
       <c r="AW13" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="AX13">
         <v>55</v>
@@ -9191,7 +9230,7 @@
         <v>1</v>
       </c>
       <c r="BL13" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="BM13">
         <v>2</v>
@@ -9200,7 +9239,7 @@
         <v>9</v>
       </c>
       <c r="BO13" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BP13">
         <v>0</v>
@@ -9212,7 +9251,7 @@
         <v>1</v>
       </c>
       <c r="BV13" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="BW13">
         <v>2</v>
@@ -9221,7 +9260,7 @@
         <v>9</v>
       </c>
       <c r="BY13" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BZ13">
         <v>0</v>
@@ -9233,7 +9272,7 @@
         <v>1</v>
       </c>
       <c r="CF13" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="CG13">
         <v>2</v>
@@ -9242,7 +9281,7 @@
         <v>9</v>
       </c>
       <c r="CI13" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CJ13">
         <v>0</v>
@@ -9254,7 +9293,7 @@
         <v>1</v>
       </c>
       <c r="CO13" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CP13">
         <v>0</v>
@@ -9266,7 +9305,7 @@
         <v>1</v>
       </c>
       <c r="DM13" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="DN13">
         <v>0.05</v>
@@ -9281,10 +9320,10 @@
         <v>8</v>
       </c>
       <c r="DR13" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="DS13" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="DT13">
         <v>0</v>
@@ -9296,7 +9335,7 @@
         <v>1</v>
       </c>
       <c r="EC13" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="ED13">
         <v>0</v>
@@ -9308,22 +9347,22 @@
         <v>1</v>
       </c>
       <c r="EJ13" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="EK13" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="EL13">
         <v>96</v>
       </c>
       <c r="EM13" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="EN13">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="EO13" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="EP13">
         <v>20</v>
@@ -9343,10 +9382,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="F14" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="G14" t="b">
         <v>0</v>
@@ -9382,10 +9421,10 @@
         <v>1</v>
       </c>
       <c r="R14">
-        <v>1546000</v>
+        <v>1009000</v>
       </c>
       <c r="S14" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="T14" t="s">
         <v>162</v>
@@ -9433,10 +9472,10 @@
         <v>3850000</v>
       </c>
       <c r="AL14" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="AM14">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="AN14" t="s">
         <v>162</v>
@@ -9463,10 +9502,10 @@
         <v>1</v>
       </c>
       <c r="AV14">
-        <v>1800</v>
+        <v>2400</v>
       </c>
       <c r="AW14" t="s">
-        <v>226</v>
+        <v>173</v>
       </c>
       <c r="AX14">
         <v>55</v>
@@ -9496,7 +9535,7 @@
         <v>1</v>
       </c>
       <c r="BL14" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="BM14">
         <v>2</v>
@@ -9505,7 +9544,7 @@
         <v>9</v>
       </c>
       <c r="BO14" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BP14">
         <v>0</v>
@@ -9517,7 +9556,7 @@
         <v>1</v>
       </c>
       <c r="BV14" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="BW14">
         <v>2</v>
@@ -9526,7 +9565,7 @@
         <v>9</v>
       </c>
       <c r="BY14" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BZ14">
         <v>0</v>
@@ -9538,7 +9577,7 @@
         <v>1</v>
       </c>
       <c r="CF14" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="CG14">
         <v>2</v>
@@ -9547,7 +9586,7 @@
         <v>9</v>
       </c>
       <c r="CI14" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CJ14">
         <v>0</v>
@@ -9559,79 +9598,19 @@
         <v>1</v>
       </c>
       <c r="CO14" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CP14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CR14" t="b">
         <v>1</v>
       </c>
-      <c r="CS14" t="s">
-        <v>231</v>
-      </c>
-      <c r="CT14">
-        <v>100000</v>
-      </c>
-      <c r="CU14">
-        <v>25000</v>
-      </c>
-      <c r="CV14">
-        <v>11000</v>
-      </c>
-      <c r="CW14">
-        <v>22000</v>
-      </c>
-      <c r="CX14">
-        <v>200000</v>
-      </c>
-      <c r="CY14">
-        <v>0.9</v>
-      </c>
-      <c r="CZ14">
-        <v>0.8</v>
-      </c>
-      <c r="DA14" t="b">
-        <v>0</v>
-      </c>
-      <c r="DB14" t="b">
-        <v>0</v>
-      </c>
-      <c r="DC14" t="s">
-        <v>186</v>
-      </c>
-      <c r="DD14">
-        <v>100000</v>
-      </c>
-      <c r="DE14">
-        <v>25000</v>
-      </c>
-      <c r="DF14">
-        <v>11000</v>
-      </c>
-      <c r="DG14">
-        <v>22000</v>
-      </c>
-      <c r="DH14">
-        <v>200000</v>
-      </c>
-      <c r="DI14">
-        <v>0.9</v>
-      </c>
-      <c r="DJ14">
-        <v>0.8</v>
-      </c>
-      <c r="DK14" t="b">
-        <v>0</v>
-      </c>
-      <c r="DL14" t="b">
-        <v>0</v>
-      </c>
       <c r="DM14" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="DN14">
         <v>0.05</v>
@@ -9646,10 +9625,10 @@
         <v>8</v>
       </c>
       <c r="DR14" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="DS14" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="DT14">
         <v>0</v>
@@ -9661,7 +9640,7 @@
         <v>1</v>
       </c>
       <c r="EC14" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="ED14">
         <v>0</v>
@@ -9673,25 +9652,25 @@
         <v>1</v>
       </c>
       <c r="EJ14" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="EK14" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="EL14">
         <v>96</v>
       </c>
       <c r="EM14" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="EN14">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="EO14" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="EP14">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="EQ14">
         <v>0</v>
@@ -9708,10 +9687,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="F15" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="G15" t="b">
         <v>0</v>
@@ -9747,10 +9726,10 @@
         <v>1</v>
       </c>
       <c r="R15">
-        <v>1720000</v>
+        <v>2455000</v>
       </c>
       <c r="S15" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="T15" t="s">
         <v>162</v>
@@ -9798,10 +9777,10 @@
         <v>3850000</v>
       </c>
       <c r="AL15" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="AM15">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="AN15" t="s">
         <v>162</v>
@@ -9831,7 +9810,7 @@
         <v>2100</v>
       </c>
       <c r="AW15" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AX15">
         <v>55</v>
@@ -9861,7 +9840,7 @@
         <v>1</v>
       </c>
       <c r="BL15" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="BM15">
         <v>2</v>
@@ -9870,7 +9849,7 @@
         <v>9</v>
       </c>
       <c r="BO15" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BP15">
         <v>0</v>
@@ -9882,7 +9861,7 @@
         <v>1</v>
       </c>
       <c r="BV15" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="BW15">
         <v>2</v>
@@ -9891,7 +9870,7 @@
         <v>9</v>
       </c>
       <c r="BY15" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BZ15">
         <v>0</v>
@@ -9903,7 +9882,7 @@
         <v>1</v>
       </c>
       <c r="CF15" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="CG15">
         <v>2</v>
@@ -9912,7 +9891,7 @@
         <v>9</v>
       </c>
       <c r="CI15" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CJ15">
         <v>0</v>
@@ -9924,19 +9903,49 @@
         <v>1</v>
       </c>
       <c r="CO15" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CP15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CR15" t="b">
         <v>1</v>
       </c>
+      <c r="CS15" t="s">
+        <v>235</v>
+      </c>
+      <c r="CT15">
+        <v>50000</v>
+      </c>
+      <c r="CU15">
+        <v>15000</v>
+      </c>
+      <c r="CV15">
+        <v>7200</v>
+      </c>
+      <c r="CW15">
+        <v>7200</v>
+      </c>
+      <c r="CX15">
+        <v>50000</v>
+      </c>
+      <c r="CY15">
+        <v>0.9</v>
+      </c>
+      <c r="CZ15">
+        <v>0.8</v>
+      </c>
+      <c r="DA15" t="b">
+        <v>0</v>
+      </c>
+      <c r="DB15" t="b">
+        <v>0</v>
+      </c>
       <c r="DM15" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="DN15">
         <v>0.05</v>
@@ -9951,10 +9960,10 @@
         <v>8</v>
       </c>
       <c r="DR15" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="DS15" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="DT15">
         <v>0</v>
@@ -9966,7 +9975,7 @@
         <v>1</v>
       </c>
       <c r="EC15" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="ED15">
         <v>0</v>
@@ -9978,22 +9987,22 @@
         <v>1</v>
       </c>
       <c r="EJ15" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="EK15" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="EL15">
         <v>96</v>
       </c>
       <c r="EM15" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="EN15">
         <v>12</v>
       </c>
       <c r="EO15" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="EP15">
         <v>0</v>
@@ -10013,10 +10022,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="F16" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="G16" t="b">
         <v>0</v>
@@ -10052,10 +10061,10 @@
         <v>1</v>
       </c>
       <c r="R16">
-        <v>2012000</v>
+        <v>2455000</v>
       </c>
       <c r="S16" t="s">
-        <v>155</v>
+        <v>222</v>
       </c>
       <c r="T16" t="s">
         <v>162</v>
@@ -10103,10 +10112,10 @@
         <v>3850000</v>
       </c>
       <c r="AL16" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="AM16">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="AN16" t="s">
         <v>162</v>
@@ -10136,7 +10145,7 @@
         <v>1800</v>
       </c>
       <c r="AW16" t="s">
-        <v>224</v>
+        <v>176</v>
       </c>
       <c r="AX16">
         <v>55</v>
@@ -10166,7 +10175,7 @@
         <v>1</v>
       </c>
       <c r="BL16" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="BM16">
         <v>2</v>
@@ -10175,7 +10184,7 @@
         <v>9</v>
       </c>
       <c r="BO16" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BP16">
         <v>0</v>
@@ -10187,7 +10196,7 @@
         <v>1</v>
       </c>
       <c r="BV16" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="BW16">
         <v>2</v>
@@ -10196,7 +10205,7 @@
         <v>9</v>
       </c>
       <c r="BY16" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BZ16">
         <v>0</v>
@@ -10208,7 +10217,7 @@
         <v>1</v>
       </c>
       <c r="CF16" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="CG16">
         <v>2</v>
@@ -10217,7 +10226,7 @@
         <v>9</v>
       </c>
       <c r="CI16" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CJ16">
         <v>0</v>
@@ -10229,19 +10238,49 @@
         <v>1</v>
       </c>
       <c r="CO16" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CP16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CR16" t="b">
         <v>1</v>
       </c>
+      <c r="CS16" t="s">
+        <v>236</v>
+      </c>
+      <c r="CT16">
+        <v>75000</v>
+      </c>
+      <c r="CU16">
+        <v>20000</v>
+      </c>
+      <c r="CV16">
+        <v>7200</v>
+      </c>
+      <c r="CW16">
+        <v>11000</v>
+      </c>
+      <c r="CX16">
+        <v>100000</v>
+      </c>
+      <c r="CY16">
+        <v>0.9</v>
+      </c>
+      <c r="CZ16">
+        <v>0.8</v>
+      </c>
+      <c r="DA16" t="b">
+        <v>0</v>
+      </c>
+      <c r="DB16" t="b">
+        <v>0</v>
+      </c>
       <c r="DM16" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="DN16">
         <v>0.05</v>
@@ -10256,10 +10295,10 @@
         <v>8</v>
       </c>
       <c r="DR16" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="DS16" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="DT16">
         <v>0</v>
@@ -10271,7 +10310,7 @@
         <v>1</v>
       </c>
       <c r="EC16" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="ED16">
         <v>0</v>
@@ -10283,25 +10322,25 @@
         <v>1</v>
       </c>
       <c r="EJ16" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="EK16" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="EL16">
         <v>96</v>
       </c>
       <c r="EM16" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="EN16">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="EO16" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="EP16">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="EQ16">
         <v>0</v>
@@ -10318,10 +10357,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="F17" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="G17" t="b">
         <v>0</v>
@@ -10357,10 +10396,10 @@
         <v>1</v>
       </c>
       <c r="R17">
-        <v>1158000</v>
+        <v>2687000</v>
       </c>
       <c r="S17" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="T17" t="s">
         <v>162</v>
@@ -10408,7 +10447,7 @@
         <v>3850000</v>
       </c>
       <c r="AL17" t="s">
-        <v>165</v>
+        <v>226</v>
       </c>
       <c r="AM17">
         <v>55</v>
@@ -10438,10 +10477,10 @@
         <v>1</v>
       </c>
       <c r="AV17">
-        <v>2400</v>
+        <v>1800</v>
       </c>
       <c r="AW17" t="s">
-        <v>224</v>
+        <v>176</v>
       </c>
       <c r="AX17">
         <v>55</v>
@@ -10471,7 +10510,7 @@
         <v>1</v>
       </c>
       <c r="BL17" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="BM17">
         <v>2</v>
@@ -10480,7 +10519,7 @@
         <v>9</v>
       </c>
       <c r="BO17" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BP17">
         <v>0</v>
@@ -10492,7 +10531,7 @@
         <v>1</v>
       </c>
       <c r="BV17" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="BW17">
         <v>2</v>
@@ -10501,7 +10540,7 @@
         <v>9</v>
       </c>
       <c r="BY17" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BZ17">
         <v>0</v>
@@ -10513,7 +10552,7 @@
         <v>1</v>
       </c>
       <c r="CF17" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="CG17">
         <v>2</v>
@@ -10522,7 +10561,7 @@
         <v>9</v>
       </c>
       <c r="CI17" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CJ17">
         <v>0</v>
@@ -10534,7 +10573,7 @@
         <v>1</v>
       </c>
       <c r="CO17" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CP17">
         <v>0</v>
@@ -10546,7 +10585,7 @@
         <v>1</v>
       </c>
       <c r="DM17" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="DN17">
         <v>0.05</v>
@@ -10561,10 +10600,10 @@
         <v>8</v>
       </c>
       <c r="DR17" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="DS17" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="DT17">
         <v>0</v>
@@ -10576,7 +10615,7 @@
         <v>1</v>
       </c>
       <c r="EC17" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="ED17">
         <v>0</v>
@@ -10588,25 +10627,25 @@
         <v>1</v>
       </c>
       <c r="EJ17" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="EK17" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="EL17">
         <v>96</v>
       </c>
       <c r="EM17" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="EN17">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="EO17" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="EP17">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="EQ17">
         <v>0</v>
@@ -10642,13 +10681,13 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>9</v>
@@ -10929,13 +10968,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="F2" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="G2">
-        <v>481</v>
+        <v>194</v>
       </c>
       <c r="H2">
         <v>96</v>
@@ -10953,10 +10992,10 @@
         <v>1</v>
       </c>
       <c r="M2">
-        <v>14200000</v>
+        <v>7270000</v>
       </c>
       <c r="N2" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="O2" t="s">
         <v>162</v>
@@ -10980,7 +11019,7 @@
         <v>1</v>
       </c>
       <c r="W2" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="Y2" t="s">
         <v>162</v>
@@ -10995,16 +11034,31 @@
         <v>163</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE2" t="b">
         <v>1</v>
       </c>
+      <c r="AF2">
+        <v>3450000</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>231</v>
+      </c>
+      <c r="AH2">
+        <v>-20</v>
+      </c>
+      <c r="AI2">
+        <v>50</v>
+      </c>
+      <c r="AJ2" t="b">
+        <v>1</v>
+      </c>
       <c r="AK2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AL2">
         <v>2</v>
@@ -11013,7 +11067,7 @@
         <v>9</v>
       </c>
       <c r="AN2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AO2">
         <v>0</v>
@@ -11025,7 +11079,7 @@
         <v>1</v>
       </c>
       <c r="AU2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AV2">
         <v>2</v>
@@ -11034,7 +11088,7 @@
         <v>9</v>
       </c>
       <c r="AX2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AY2">
         <v>0</v>
@@ -11046,7 +11100,7 @@
         <v>1</v>
       </c>
       <c r="BE2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="BF2">
         <v>2</v>
@@ -11055,7 +11109,7 @@
         <v>9</v>
       </c>
       <c r="BH2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="BI2">
         <v>0</v>
@@ -11067,37 +11121,55 @@
         <v>1</v>
       </c>
       <c r="CA2" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="CB2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CC2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE2" t="s">
-        <v>190</v>
+        <v>193</v>
+      </c>
+      <c r="CF2">
+        <v>7300</v>
+      </c>
+      <c r="CG2">
+        <v>15000</v>
+      </c>
+      <c r="CH2">
+        <v>0.95</v>
+      </c>
+      <c r="CI2">
+        <v>0.1</v>
+      </c>
+      <c r="CJ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CK2" t="b">
+        <v>0</v>
       </c>
       <c r="CL2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CM2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="CN2">
         <v>96</v>
       </c>
       <c r="CO2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="CP2">
         <v>60</v>
       </c>
       <c r="CQ2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="CR2">
         <v>0</v>
@@ -11117,13 +11189,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="F3" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="G3">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="H3">
         <v>96</v>
@@ -11141,10 +11213,10 @@
         <v>1</v>
       </c>
       <c r="M3">
-        <v>7140000</v>
+        <v>8040000</v>
       </c>
       <c r="N3" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="O3" t="s">
         <v>162</v>
@@ -11168,7 +11240,7 @@
         <v>1</v>
       </c>
       <c r="W3" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Y3" t="s">
         <v>162</v>
@@ -11183,31 +11255,16 @@
         <v>163</v>
       </c>
       <c r="AC3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>1</v>
       </c>
-      <c r="AF3">
-        <v>2900000</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>228</v>
-      </c>
-      <c r="AH3">
-        <v>-20</v>
-      </c>
-      <c r="AI3">
-        <v>50</v>
-      </c>
-      <c r="AJ3" t="b">
-        <v>1</v>
-      </c>
       <c r="AK3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AL3">
         <v>2</v>
@@ -11216,7 +11273,7 @@
         <v>9</v>
       </c>
       <c r="AN3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AO3">
         <v>0</v>
@@ -11228,7 +11285,7 @@
         <v>1</v>
       </c>
       <c r="AU3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AV3">
         <v>2</v>
@@ -11237,7 +11294,7 @@
         <v>9</v>
       </c>
       <c r="AX3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AY3">
         <v>0</v>
@@ -11249,7 +11306,7 @@
         <v>1</v>
       </c>
       <c r="BE3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="BF3">
         <v>2</v>
@@ -11258,70 +11315,97 @@
         <v>9</v>
       </c>
       <c r="BH3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="BI3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BJ3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK3" t="b">
         <v>1</v>
       </c>
+      <c r="BL3" t="s">
+        <v>187</v>
+      </c>
+      <c r="BM3">
+        <v>75000</v>
+      </c>
+      <c r="BN3">
+        <v>25000</v>
+      </c>
+      <c r="BO3">
+        <v>11000</v>
+      </c>
+      <c r="BP3">
+        <v>22000</v>
+      </c>
+      <c r="BQ3">
+        <v>200000</v>
+      </c>
+      <c r="BR3">
+        <v>0.9</v>
+      </c>
+      <c r="BS3">
+        <v>0.8</v>
+      </c>
+      <c r="BT3" t="b">
+        <v>0</v>
+      </c>
+      <c r="BU3" t="b">
+        <v>0</v>
+      </c>
+      <c r="BV3" t="s">
+        <v>191</v>
+      </c>
+      <c r="BW3">
+        <v>0.05</v>
+      </c>
+      <c r="BX3">
+        <v>0.5</v>
+      </c>
+      <c r="BY3">
+        <v>0.8</v>
+      </c>
+      <c r="BZ3">
+        <v>8</v>
+      </c>
       <c r="CA3" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="CB3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CC3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE3" t="s">
-        <v>190</v>
-      </c>
-      <c r="CF3">
-        <v>7100</v>
-      </c>
-      <c r="CG3">
-        <v>14000</v>
-      </c>
-      <c r="CH3">
-        <v>0.95</v>
-      </c>
-      <c r="CI3">
-        <v>0.1</v>
-      </c>
-      <c r="CJ3" t="b">
-        <v>0</v>
-      </c>
-      <c r="CK3" t="b">
-        <v>0</v>
+        <v>193</v>
       </c>
       <c r="CL3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CM3" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="CN3">
         <v>96</v>
       </c>
       <c r="CO3" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="CP3">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="CQ3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="CR3">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="CS3">
         <v>0</v>
@@ -11338,13 +11422,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="F4" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="G4">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="H4">
         <v>96</v>
@@ -11362,10 +11446,10 @@
         <v>1</v>
       </c>
       <c r="M4">
-        <v>14810000</v>
+        <v>16300000</v>
       </c>
       <c r="N4" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="O4" t="s">
         <v>162</v>
@@ -11389,7 +11473,7 @@
         <v>1</v>
       </c>
       <c r="W4" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="Y4" t="s">
         <v>162</v>
@@ -11413,10 +11497,10 @@
         <v>1</v>
       </c>
       <c r="AF4">
-        <v>7510000</v>
+        <v>6660000</v>
       </c>
       <c r="AG4" t="s">
-        <v>249</v>
+        <v>232</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -11428,7 +11512,7 @@
         <v>1</v>
       </c>
       <c r="AK4" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AL4">
         <v>2</v>
@@ -11437,7 +11521,7 @@
         <v>9</v>
       </c>
       <c r="AN4" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AO4">
         <v>0</v>
@@ -11449,7 +11533,7 @@
         <v>1</v>
       </c>
       <c r="AU4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AV4">
         <v>2</v>
@@ -11458,7 +11542,7 @@
         <v>9</v>
       </c>
       <c r="AX4" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AY4">
         <v>0</v>
@@ -11470,7 +11554,7 @@
         <v>1</v>
       </c>
       <c r="BE4" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="BF4">
         <v>2</v>
@@ -11479,67 +11563,22 @@
         <v>9</v>
       </c>
       <c r="BH4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="BI4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BJ4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK4" t="b">
         <v>1</v>
       </c>
-      <c r="BL4" t="s">
-        <v>250</v>
-      </c>
-      <c r="BM4">
-        <v>50000</v>
-      </c>
-      <c r="BN4">
-        <v>20000</v>
-      </c>
-      <c r="BO4">
-        <v>7200</v>
-      </c>
-      <c r="BP4">
-        <v>11000</v>
-      </c>
-      <c r="BQ4">
-        <v>100000</v>
-      </c>
-      <c r="BR4">
-        <v>0.9</v>
-      </c>
-      <c r="BS4">
-        <v>0.8</v>
-      </c>
-      <c r="BT4" t="b">
-        <v>0</v>
-      </c>
-      <c r="BU4" t="b">
-        <v>0</v>
-      </c>
-      <c r="BV4" t="s">
-        <v>252</v>
-      </c>
-      <c r="BW4">
-        <v>0.05</v>
-      </c>
-      <c r="BX4">
-        <v>0.5</v>
-      </c>
-      <c r="BY4">
-        <v>0.8</v>
-      </c>
-      <c r="BZ4">
-        <v>8</v>
-      </c>
       <c r="CA4" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="CB4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CC4">
         <v>1</v>
@@ -11548,13 +11587,13 @@
         <v>1</v>
       </c>
       <c r="CE4" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="CF4">
-        <v>14800</v>
+        <v>16300</v>
       </c>
       <c r="CG4">
-        <v>15000</v>
+        <v>16000</v>
       </c>
       <c r="CH4">
         <v>0.95</v>
@@ -11569,22 +11608,22 @@
         <v>0</v>
       </c>
       <c r="CL4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CM4" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="CN4">
         <v>96</v>
       </c>
       <c r="CO4" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="CP4">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="CQ4" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="CR4">
         <v>0</v>
@@ -11604,13 +11643,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="F5" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="G5">
-        <v>178</v>
+        <v>507</v>
       </c>
       <c r="H5">
         <v>96</v>
@@ -11628,10 +11667,10 @@
         <v>1</v>
       </c>
       <c r="M5">
-        <v>6420000</v>
+        <v>14620000</v>
       </c>
       <c r="N5" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="O5" t="s">
         <v>162</v>
@@ -11655,7 +11694,7 @@
         <v>1</v>
       </c>
       <c r="W5" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="Y5" t="s">
         <v>162</v>
@@ -11670,31 +11709,16 @@
         <v>163</v>
       </c>
       <c r="AC5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>1</v>
       </c>
-      <c r="AF5">
-        <v>2970000</v>
-      </c>
-      <c r="AG5" t="s">
-        <v>227</v>
-      </c>
-      <c r="AH5">
-        <v>-20</v>
-      </c>
-      <c r="AI5">
-        <v>50</v>
-      </c>
-      <c r="AJ5" t="b">
-        <v>1</v>
-      </c>
       <c r="AK5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AL5">
         <v>2</v>
@@ -11703,7 +11727,7 @@
         <v>9</v>
       </c>
       <c r="AN5" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AO5">
         <v>0</v>
@@ -11715,7 +11739,7 @@
         <v>1</v>
       </c>
       <c r="AU5" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AV5">
         <v>2</v>
@@ -11724,7 +11748,7 @@
         <v>9</v>
       </c>
       <c r="AX5" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AY5">
         <v>0</v>
@@ -11736,7 +11760,7 @@
         <v>1</v>
       </c>
       <c r="BE5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="BF5">
         <v>2</v>
@@ -11745,115 +11769,52 @@
         <v>9</v>
       </c>
       <c r="BH5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="BI5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BJ5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK5" t="b">
         <v>1</v>
       </c>
-      <c r="BL5" t="s">
-        <v>251</v>
-      </c>
-      <c r="BM5">
-        <v>75000</v>
-      </c>
-      <c r="BN5">
-        <v>25000</v>
-      </c>
-      <c r="BO5">
-        <v>11000</v>
-      </c>
-      <c r="BP5">
-        <v>22000</v>
-      </c>
-      <c r="BQ5">
-        <v>200000</v>
-      </c>
-      <c r="BR5">
-        <v>0.9</v>
-      </c>
-      <c r="BS5">
-        <v>0.8</v>
-      </c>
-      <c r="BT5" t="b">
-        <v>0</v>
-      </c>
-      <c r="BU5" t="b">
-        <v>0</v>
-      </c>
-      <c r="BV5" t="s">
-        <v>188</v>
-      </c>
-      <c r="BW5">
-        <v>0.05</v>
-      </c>
-      <c r="BX5">
-        <v>0.5</v>
-      </c>
-      <c r="BY5">
-        <v>0.8</v>
-      </c>
-      <c r="BZ5">
-        <v>8</v>
-      </c>
       <c r="CA5" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="CB5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CC5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE5" t="s">
-        <v>190</v>
-      </c>
-      <c r="CF5">
-        <v>6400</v>
-      </c>
-      <c r="CG5">
-        <v>13000</v>
-      </c>
-      <c r="CH5">
-        <v>0.95</v>
-      </c>
-      <c r="CI5">
-        <v>0.1</v>
-      </c>
-      <c r="CJ5" t="b">
-        <v>0</v>
-      </c>
-      <c r="CK5" t="b">
-        <v>0</v>
+        <v>193</v>
       </c>
       <c r="CL5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CM5" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="CN5">
         <v>96</v>
       </c>
       <c r="CO5" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="CP5">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="CQ5" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="CR5">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="CS5">
         <v>0</v>
@@ -11889,13 +11850,13 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>9</v>
@@ -12212,7 +12173,7 @@
         <v>255</v>
       </c>
       <c r="G2">
-        <v>1602</v>
+        <v>1728</v>
       </c>
       <c r="H2">
         <v>96</v>
@@ -12230,7 +12191,7 @@
         <v>1</v>
       </c>
       <c r="M2">
-        <v>537500000</v>
+        <v>668800000</v>
       </c>
       <c r="N2" t="s">
         <v>257</v>
@@ -12272,31 +12233,16 @@
         <v>163</v>
       </c>
       <c r="AC2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>1</v>
       </c>
-      <c r="AF2">
-        <v>714500000</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>227</v>
-      </c>
-      <c r="AH2">
-        <v>-20</v>
-      </c>
-      <c r="AI2">
-        <v>50</v>
-      </c>
-      <c r="AJ2" t="b">
-        <v>1</v>
-      </c>
       <c r="AK2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AL2">
         <v>2</v>
@@ -12305,7 +12251,7 @@
         <v>9</v>
       </c>
       <c r="AN2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AO2">
         <v>0</v>
@@ -12317,7 +12263,7 @@
         <v>1</v>
       </c>
       <c r="AU2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AV2">
         <v>2</v>
@@ -12326,7 +12272,7 @@
         <v>9</v>
       </c>
       <c r="AX2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AY2">
         <v>0</v>
@@ -12338,7 +12284,7 @@
         <v>1</v>
       </c>
       <c r="BE2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="BF2">
         <v>2</v>
@@ -12347,7 +12293,7 @@
         <v>9</v>
       </c>
       <c r="BH2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="BI2">
         <v>0</v>
@@ -12359,10 +12305,10 @@
         <v>1</v>
       </c>
       <c r="CK2" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="CL2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CM2">
         <v>0</v>
@@ -12371,25 +12317,25 @@
         <v>0</v>
       </c>
       <c r="CO2" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="CV2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CW2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="CX2">
         <v>96</v>
       </c>
       <c r="CY2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="CZ2">
         <v>36</v>
       </c>
       <c r="DA2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="DB2">
         <v>30</v>
@@ -12415,7 +12361,7 @@
         <v>256</v>
       </c>
       <c r="G3">
-        <v>5490</v>
+        <v>4962</v>
       </c>
       <c r="H3">
         <v>96</v>
@@ -12433,7 +12379,7 @@
         <v>1</v>
       </c>
       <c r="M3">
-        <v>1359300000</v>
+        <v>1130100000</v>
       </c>
       <c r="N3" t="s">
         <v>258</v>
@@ -12475,16 +12421,31 @@
         <v>163</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE3" t="b">
         <v>1</v>
       </c>
+      <c r="AF3">
+        <v>1418000000</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>231</v>
+      </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>40</v>
+      </c>
+      <c r="AJ3" t="b">
+        <v>1</v>
+      </c>
       <c r="AK3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AL3">
         <v>2</v>
@@ -12493,7 +12454,7 @@
         <v>9</v>
       </c>
       <c r="AN3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AO3">
         <v>0</v>
@@ -12505,7 +12466,7 @@
         <v>1</v>
       </c>
       <c r="AU3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AV3">
         <v>2</v>
@@ -12514,7 +12475,7 @@
         <v>9</v>
       </c>
       <c r="AX3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AY3">
         <v>0</v>
@@ -12526,7 +12487,7 @@
         <v>1</v>
       </c>
       <c r="BE3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="BF3">
         <v>2</v>
@@ -12535,22 +12496,67 @@
         <v>9</v>
       </c>
       <c r="BH3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="BI3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BJ3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK3" t="b">
         <v>1</v>
       </c>
+      <c r="BL3" t="s">
+        <v>259</v>
+      </c>
+      <c r="BM3">
+        <v>500000</v>
+      </c>
+      <c r="BN3">
+        <v>20000</v>
+      </c>
+      <c r="BO3">
+        <v>7200</v>
+      </c>
+      <c r="BP3">
+        <v>11000</v>
+      </c>
+      <c r="BQ3">
+        <v>100000</v>
+      </c>
+      <c r="BR3">
+        <v>0.9</v>
+      </c>
+      <c r="BS3">
+        <v>0.8</v>
+      </c>
+      <c r="BT3" t="b">
+        <v>0</v>
+      </c>
+      <c r="BU3" t="b">
+        <v>0</v>
+      </c>
+      <c r="CF3" t="s">
+        <v>260</v>
+      </c>
+      <c r="CG3">
+        <v>0.05</v>
+      </c>
+      <c r="CH3">
+        <v>0.5</v>
+      </c>
+      <c r="CI3">
+        <v>0.8</v>
+      </c>
+      <c r="CJ3">
+        <v>8</v>
+      </c>
       <c r="CK3" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="CL3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CM3">
         <v>0</v>
@@ -12559,28 +12565,28 @@
         <v>0</v>
       </c>
       <c r="CO3" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="CV3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="CW3" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="CX3">
         <v>96</v>
       </c>
       <c r="CY3" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="CZ3">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="DA3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="DB3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="DC3">
         <v>0</v>
@@ -12616,7 +12622,7 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>9</v>
@@ -12774,7 +12780,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="F2">
         <v>96</v>
@@ -12792,10 +12798,10 @@
         <v>1</v>
       </c>
       <c r="K2">
-        <v>63500000</v>
+        <v>70900000</v>
       </c>
       <c r="L2" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="M2">
         <v>20</v>
@@ -12807,7 +12813,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q2">
         <v>2</v>
@@ -12816,7 +12822,7 @@
         <v>9</v>
       </c>
       <c r="S2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AN2">
         <v>1</v>
@@ -12828,10 +12834,10 @@
         <v>1</v>
       </c>
       <c r="AQ2">
-        <v>31750000</v>
+        <v>35450000</v>
       </c>
       <c r="AR2">
-        <v>63500000</v>
+        <v>70900000</v>
       </c>
       <c r="AS2">
         <v>0.95</v>
@@ -12846,19 +12852,19 @@
         <v>1</v>
       </c>
       <c r="AW2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AX2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="AY2">
         <v>96</v>
       </c>
       <c r="AZ2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="BA2">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="BB2">
         <v>0</v>
@@ -12875,7 +12881,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F3">
         <v>96</v>
@@ -12893,22 +12899,22 @@
         <v>1</v>
       </c>
       <c r="K3">
-        <v>13300000</v>
+        <v>39800000</v>
       </c>
       <c r="L3" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="M3">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="N3">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="O3">
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q3">
         <v>2</v>
@@ -12917,7 +12923,7 @@
         <v>9</v>
       </c>
       <c r="S3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AN3">
         <v>1</v>
@@ -12929,10 +12935,10 @@
         <v>1</v>
       </c>
       <c r="AQ3">
-        <v>6650000</v>
+        <v>19900000</v>
       </c>
       <c r="AR3">
-        <v>13300000</v>
+        <v>39800000</v>
       </c>
       <c r="AS3">
         <v>0.95</v>
@@ -12947,16 +12953,16 @@
         <v>1</v>
       </c>
       <c r="AW3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AX3" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="AY3">
         <v>96</v>
       </c>
       <c r="AZ3" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="BA3">
         <v>48</v>
@@ -12976,7 +12982,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F4">
         <v>96</v>
@@ -12994,10 +13000,10 @@
         <v>1</v>
       </c>
       <c r="K4">
-        <v>16800000</v>
+        <v>15400000</v>
       </c>
       <c r="L4" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="M4">
         <v>0</v>
@@ -13009,7 +13015,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q4">
         <v>2</v>
@@ -13018,7 +13024,7 @@
         <v>9</v>
       </c>
       <c r="S4" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AN4">
         <v>1</v>
@@ -13030,10 +13036,10 @@
         <v>1</v>
       </c>
       <c r="AQ4">
-        <v>8400000</v>
+        <v>7700000</v>
       </c>
       <c r="AR4">
-        <v>16800000</v>
+        <v>15400000</v>
       </c>
       <c r="AS4">
         <v>0.95</v>
@@ -13048,19 +13054,19 @@
         <v>1</v>
       </c>
       <c r="AW4" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AX4" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="AY4">
         <v>96</v>
       </c>
       <c r="AZ4" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="BA4">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="BB4">
         <v>0</v>
@@ -13077,7 +13083,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F5">
         <v>96</v>
@@ -13095,22 +13101,22 @@
         <v>1</v>
       </c>
       <c r="K5">
-        <v>33300000</v>
+        <v>14300000</v>
       </c>
       <c r="L5" t="s">
-        <v>228</v>
+        <v>267</v>
       </c>
       <c r="M5">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="N5">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="O5">
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q5">
         <v>2</v>
@@ -13119,7 +13125,7 @@
         <v>9</v>
       </c>
       <c r="S5" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AN5">
         <v>1</v>
@@ -13131,10 +13137,10 @@
         <v>1</v>
       </c>
       <c r="AQ5">
-        <v>16650000</v>
+        <v>7150000</v>
       </c>
       <c r="AR5">
-        <v>33300000</v>
+        <v>14300000</v>
       </c>
       <c r="AS5">
         <v>0.95</v>
@@ -13149,19 +13155,19 @@
         <v>1</v>
       </c>
       <c r="AW5" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AX5" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="AY5">
         <v>96</v>
       </c>
       <c r="AZ5" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="BA5">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="BB5">
         <v>0</v>
@@ -13178,7 +13184,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F6">
         <v>96</v>
@@ -13196,16 +13202,16 @@
         <v>1</v>
       </c>
       <c r="AG6">
-        <v>20000</v>
+        <v>38500</v>
       </c>
       <c r="AH6" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="AI6" t="b">
         <v>1</v>
       </c>
       <c r="AJ6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AK6">
         <v>2</v>
@@ -13214,7 +13220,7 @@
         <v>9</v>
       </c>
       <c r="AM6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AN6">
         <v>0</v>
@@ -13226,19 +13232,19 @@
         <v>1</v>
       </c>
       <c r="AW6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AX6" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="AY6">
         <v>96</v>
       </c>
       <c r="AZ6" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="BA6">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="BB6">
         <v>0</v>
@@ -13255,7 +13261,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F7">
         <v>96</v>
@@ -13273,16 +13279,16 @@
         <v>1</v>
       </c>
       <c r="AG7">
-        <v>38200</v>
+        <v>20000</v>
       </c>
       <c r="AH7" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="AI7" t="b">
         <v>1</v>
       </c>
       <c r="AJ7" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AK7">
         <v>2</v>
@@ -13291,28 +13297,46 @@
         <v>9</v>
       </c>
       <c r="AM7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AN7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP7" t="b">
         <v>1</v>
       </c>
+      <c r="AQ7">
+        <v>6000</v>
+      </c>
+      <c r="AR7">
+        <v>20000</v>
+      </c>
+      <c r="AS7">
+        <v>0.95</v>
+      </c>
+      <c r="AT7">
+        <v>0.1</v>
+      </c>
+      <c r="AU7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="b">
+        <v>1</v>
+      </c>
       <c r="AW7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AX7" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="AY7">
         <v>96</v>
       </c>
       <c r="AZ7" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="BA7">
         <v>60</v>
@@ -13351,7 +13375,7 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>9</v>
@@ -13387,64 +13411,64 @@
         <v>128</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="AL1" s="1" t="s">
         <v>136</v>
@@ -13473,7 +13497,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F2">
         <v>96</v>
@@ -13491,10 +13515,10 @@
         <v>1</v>
       </c>
       <c r="K2">
-        <v>2169000</v>
+        <v>1050000</v>
       </c>
       <c r="L2">
-        <v>8820000</v>
+        <v>5840000</v>
       </c>
       <c r="M2">
         <v>0.95</v>
@@ -13509,19 +13533,19 @@
         <v>1</v>
       </c>
       <c r="Q2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AL2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="AM2">
         <v>96</v>
       </c>
       <c r="AN2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="AO2">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="AP2">
         <v>0</v>
@@ -13538,7 +13562,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="F3">
         <v>96</v>
@@ -13556,10 +13580,10 @@
         <v>1</v>
       </c>
       <c r="K3">
-        <v>933000</v>
+        <v>1080000</v>
       </c>
       <c r="L3">
-        <v>5370000</v>
+        <v>5770000</v>
       </c>
       <c r="M3">
         <v>0.95</v>
@@ -13574,19 +13598,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AL3" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="AM3">
         <v>96</v>
       </c>
       <c r="AN3" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="AO3">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AP3">
         <v>0</v>
@@ -13603,7 +13627,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="F4">
         <v>96</v>
@@ -13621,10 +13645,10 @@
         <v>1</v>
       </c>
       <c r="K4">
-        <v>1036000</v>
+        <v>1900000</v>
       </c>
       <c r="L4">
-        <v>5630000</v>
+        <v>6030000</v>
       </c>
       <c r="M4">
         <v>0.95</v>
@@ -13639,19 +13663,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AL4" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="AM4">
         <v>96</v>
       </c>
       <c r="AN4" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="AO4">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="AP4">
         <v>0</v>
@@ -13668,7 +13692,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F5">
         <v>96</v>
@@ -13686,10 +13710,10 @@
         <v>1</v>
       </c>
       <c r="U5">
-        <v>1050000000</v>
+        <v>844000000</v>
       </c>
       <c r="V5">
-        <v>5850000000</v>
+        <v>4680000000</v>
       </c>
       <c r="W5">
         <v>0.95</v>
@@ -13704,16 +13728,16 @@
         <v>1</v>
       </c>
       <c r="AA5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AL5" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="AM5">
         <v>96</v>
       </c>
       <c r="AN5" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="AO5">
         <v>36</v>
@@ -13733,7 +13757,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="F6">
         <v>96</v>
@@ -13751,10 +13775,10 @@
         <v>1</v>
       </c>
       <c r="U6">
-        <v>1180000000</v>
+        <v>1135000000</v>
       </c>
       <c r="V6">
-        <v>4380000000</v>
+        <v>4340000000</v>
       </c>
       <c r="W6">
         <v>0.95</v>
@@ -13769,19 +13793,19 @@
         <v>1</v>
       </c>
       <c r="AA6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AL6" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="AM6">
         <v>96</v>
       </c>
       <c r="AN6" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="AO6">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AP6">
         <v>0</v>
@@ -13798,7 +13822,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="F7">
         <v>96</v>
@@ -13816,10 +13840,10 @@
         <v>1</v>
       </c>
       <c r="U7">
-        <v>2110000000</v>
+        <v>2280000000</v>
       </c>
       <c r="V7">
-        <v>7830000000</v>
+        <v>9980000000</v>
       </c>
       <c r="W7">
         <v>0.95</v>
@@ -13834,19 +13858,19 @@
         <v>1</v>
       </c>
       <c r="AA7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AL7" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="AM7">
         <v>96</v>
       </c>
       <c r="AN7" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="AO7">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AP7">
         <v>0</v>
@@ -13863,7 +13887,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F8">
         <v>96</v>
@@ -13881,10 +13905,10 @@
         <v>1</v>
       </c>
       <c r="AE8">
-        <v>249000000</v>
+        <v>107900000</v>
       </c>
       <c r="AF8">
-        <v>721000000</v>
+        <v>429000000</v>
       </c>
       <c r="AG8">
         <v>0.95</v>
@@ -13899,19 +13923,19 @@
         <v>1</v>
       </c>
       <c r="AK8" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AL8" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="AM8">
         <v>96</v>
       </c>
       <c r="AN8" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="AO8">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AP8">
         <v>0</v>
@@ -13928,7 +13952,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="F9">
         <v>96</v>
@@ -13946,10 +13970,10 @@
         <v>1</v>
       </c>
       <c r="AE9">
-        <v>118000000</v>
+        <v>99800000</v>
       </c>
       <c r="AF9">
-        <v>542000000</v>
+        <v>458000000</v>
       </c>
       <c r="AG9">
         <v>0.95</v>
@@ -13964,19 +13988,19 @@
         <v>1</v>
       </c>
       <c r="AK9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AL9" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="AM9">
         <v>96</v>
       </c>
       <c r="AN9" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="AO9">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="AP9">
         <v>0</v>
@@ -13993,7 +14017,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="F10">
         <v>96</v>
@@ -14011,10 +14035,10 @@
         <v>1</v>
       </c>
       <c r="AE10">
-        <v>101000000</v>
+        <v>216300000</v>
       </c>
       <c r="AF10">
-        <v>496000000</v>
+        <v>890000000</v>
       </c>
       <c r="AG10">
         <v>0.95</v>
@@ -14029,19 +14053,19 @@
         <v>1</v>
       </c>
       <c r="AK10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AL10" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="AM10">
         <v>96</v>
       </c>
       <c r="AN10" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="AO10">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="AP10">
         <v>0</v>

--- a/02 - config/example_small/agents.xlsx
+++ b/02 - config/example_small/agents.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1566" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1571" uniqueCount="296">
   <si>
     <t>general/agent_id</t>
   </si>
@@ -417,6 +417,9 @@
     <t>heat_storage/has_submeter</t>
   </si>
   <si>
+    <t>heat_storage/sizing/power_0</t>
+  </si>
+  <si>
     <t>heat_storage/sizing/capacity_0</t>
   </si>
   <si>
@@ -456,373 +459,367 @@
     <t>meter/prob_missing</t>
   </si>
   <si>
-    <t>WKaDlzVqwb0qILK</t>
-  </si>
-  <si>
-    <t>mcnuVftQ2oeXVK6</t>
-  </si>
-  <si>
-    <t>sBE7lqgjreHlQGx</t>
-  </si>
-  <si>
-    <t>Ykkp2llyiKROWVf</t>
-  </si>
-  <si>
-    <t>maIjQWr9vjk0Uni</t>
-  </si>
-  <si>
-    <t>kizSgfHv1LkxSkV</t>
-  </si>
-  <si>
-    <t>TLeFhLumgkw1SdF</t>
-  </si>
-  <si>
-    <t>QToR2KzakBC9DB3</t>
-  </si>
-  <si>
-    <t>3MIheuHptB4Wuoo</t>
-  </si>
-  <si>
-    <t>wrHtoob8tnX3WC2</t>
-  </si>
-  <si>
-    <t>hh_3648_0.csv</t>
+    <t>V5KFY2321qM3VZG</t>
+  </si>
+  <si>
+    <t>GrFzIeAgXZFAHHx</t>
+  </si>
+  <si>
+    <t>wtMLbqxg2EnaMSp</t>
+  </si>
+  <si>
+    <t>M6RPWURRQ23Ha6d</t>
+  </si>
+  <si>
+    <t>uso8702Jqd9QNZz</t>
+  </si>
+  <si>
+    <t>ax2EN2iegGVBmLq</t>
+  </si>
+  <si>
+    <t>0GWSi4uvigfpQWL</t>
+  </si>
+  <si>
+    <t>94bZMCRbbj78CHT</t>
+  </si>
+  <si>
+    <t>eEA3TbFVsVJdLxh</t>
+  </si>
+  <si>
+    <t>8qY95cPfYKVYUKF</t>
+  </si>
+  <si>
+    <t>hh_3296_0.csv</t>
   </si>
   <si>
     <t>hh_5527_0.csv</t>
   </si>
   <si>
+    <t>hh_2687_0.csv</t>
+  </si>
+  <si>
+    <t>hh_4536_0.csv</t>
+  </si>
+  <si>
+    <t>hh_3125_0.csv</t>
+  </si>
+  <si>
+    <t>hh_2262_0.csv</t>
+  </si>
+  <si>
+    <t>naive_average</t>
+  </si>
+  <si>
+    <t>[2, 0, 2, 2, 0, 0, 96, 2, 0, 0, 672]</t>
+  </si>
+  <si>
+    <t>heat_gen_5_pu.csv</t>
+  </si>
+  <si>
+    <t>heat_5527_0.csv</t>
+  </si>
+  <si>
+    <t>heat_2687_0.csv</t>
+  </si>
+  <si>
+    <t>heat_gen_4_pu.csv</t>
+  </si>
+  <si>
+    <t>heat_3125_0.csv</t>
+  </si>
+  <si>
+    <t>heat_gen_1_pu.csv</t>
+  </si>
+  <si>
+    <t>heat_3296_0.csv</t>
+  </si>
+  <si>
+    <t>heat_2262_0.csv</t>
+  </si>
+  <si>
+    <t>dhw_gen_6_pu.csv</t>
+  </si>
+  <si>
+    <t>dhw_gen_2_pu.csv</t>
+  </si>
+  <si>
+    <t>dhw_gen_5_pu.csv</t>
+  </si>
+  <si>
+    <t>dhw_gen_3_pu.csv</t>
+  </si>
+  <si>
+    <t>dhw_gen_4_pu.csv</t>
+  </si>
+  <si>
+    <t>dhw_gen_0_pu.csv</t>
+  </si>
+  <si>
+    <t>dhw_gen_1_pu.csv</t>
+  </si>
+  <si>
+    <t>pv_config.json</t>
+  </si>
+  <si>
+    <t>smoothed</t>
+  </si>
+  <si>
+    <t>green_local</t>
+  </si>
+  <si>
+    <t>wind_Enercon_E-53-800_800000_53.json</t>
+  </si>
+  <si>
+    <t>wind_Senvion-REpower_3.2M122_3200000_122.json</t>
+  </si>
+  <si>
+    <t>wind_Enercon_E-101-3500-E2_3500000_101.json</t>
+  </si>
+  <si>
+    <t>wind_Nordex_MM92_3300000_131.json</t>
+  </si>
+  <si>
+    <t>wind_Siemens_SWT-3.6-130_3600000_130.json</t>
+  </si>
+  <si>
+    <t>weather</t>
+  </si>
+  <si>
+    <t>local</t>
+  </si>
+  <si>
+    <t>ev_fulltime_43.csv</t>
+  </si>
+  <si>
+    <t>ev_fulltime_41.csv</t>
+  </si>
+  <si>
+    <t>ev_parttime_90.csv</t>
+  </si>
+  <si>
+    <t>ev_freetime_2.csv</t>
+  </si>
+  <si>
+    <t>ev_freetime_1.csv</t>
+  </si>
+  <si>
+    <t>ev_fulltime_46.csv</t>
+  </si>
+  <si>
+    <t>price_sensitive</t>
+  </si>
+  <si>
+    <t>ev_close</t>
+  </si>
+  <si>
+    <t>True</t>
+  </si>
+  <si>
+    <t>naive</t>
+  </si>
+  <si>
+    <t>linear</t>
+  </si>
+  <si>
+    <t>general/sub_id</t>
+  </si>
+  <si>
+    <t>general/parameters/apartments_independent</t>
+  </si>
+  <si>
+    <t>general/parameters/apartments</t>
+  </si>
+  <si>
+    <t>DW7k2owqrV3NCQC</t>
+  </si>
+  <si>
+    <t>1Q1wCaZm6YRbzOY</t>
+  </si>
+  <si>
+    <t>main</t>
+  </si>
+  <si>
+    <t>slz9YgZktGoUbmQ</t>
+  </si>
+  <si>
+    <t>MEnfm9Keeh38L8X</t>
+  </si>
+  <si>
+    <t>GntlF1sWiCumwcY</t>
+  </si>
+  <si>
+    <t>2mMddLCIcebKcJp</t>
+  </si>
+  <si>
+    <t>T5vbszYX8mT0mtH</t>
+  </si>
+  <si>
+    <t>Cg0jUR3qwRmt9lX</t>
+  </si>
+  <si>
+    <t>2xoLDML8xk428Ql</t>
+  </si>
+  <si>
+    <t>UUCC3Ym6kLK11jA</t>
+  </si>
+  <si>
+    <t>U3Plf49wjni0xI2</t>
+  </si>
+  <si>
+    <t>hXV0y8Jk6QUcDV3</t>
+  </si>
+  <si>
+    <t>TBUu3u8cndaO5MJ</t>
+  </si>
+  <si>
+    <t>Kj1mxqv2VWSkMAF</t>
+  </si>
+  <si>
+    <t>zGm1oIGs3IJsQXh</t>
+  </si>
+  <si>
+    <t>SwPoQ6mtv3eeO2v</t>
+  </si>
+  <si>
+    <t>hh_1158_4.csv</t>
+  </si>
+  <si>
+    <t>hh_2455_0.csv</t>
+  </si>
+  <si>
+    <t>hh_1546_2.csv</t>
+  </si>
+  <si>
     <t>hh_2532_0.csv</t>
   </si>
   <si>
-    <t>hh_3863_0.csv</t>
+    <t>hh_1416_1.csv</t>
   </si>
   <si>
     <t>hh_2959_0.csv</t>
   </si>
   <si>
-    <t>hh_3125_0.csv</t>
-  </si>
-  <si>
-    <t>hh_3564_0.csv</t>
-  </si>
-  <si>
-    <t>naive_average</t>
-  </si>
-  <si>
-    <t>[2, 0, 2, 2, 0, 0, 96, 2, 0, 0, 672]</t>
-  </si>
-  <si>
-    <t>heat_3648_0.csv</t>
-  </si>
-  <si>
-    <t>heat_gen_4_pu.csv</t>
-  </si>
-  <si>
-    <t>heat_2532_0.csv</t>
-  </si>
-  <si>
-    <t>heat_3863_0.csv</t>
-  </si>
-  <si>
-    <t>heat_2959_0.csv</t>
+    <t>hh_1266_0.csv</t>
+  </si>
+  <si>
+    <t>hh_1720_0.csv</t>
+  </si>
+  <si>
+    <t>heat_gen_3_pu.csv</t>
   </si>
   <si>
     <t>heat_gen_0_pu.csv</t>
   </si>
   <si>
-    <t>heat_3564_0.csv</t>
-  </si>
-  <si>
-    <t>dhw_gen_0_pu.csv</t>
-  </si>
-  <si>
-    <t>dhw_gen_2_pu.csv</t>
-  </si>
-  <si>
-    <t>dhw_gen_3_pu.csv</t>
-  </si>
-  <si>
-    <t>dhw_gen_6_pu.csv</t>
-  </si>
-  <si>
-    <t>dhw_gen_4_pu.csv</t>
-  </si>
-  <si>
-    <t>dhw_gen_5_pu.csv</t>
-  </si>
-  <si>
-    <t>pv_config.json</t>
-  </si>
-  <si>
-    <t>smoothed</t>
-  </si>
-  <si>
-    <t>green_local</t>
-  </si>
-  <si>
-    <t>wind_Enercon_E-53-800_800000_53.json</t>
-  </si>
-  <si>
-    <t>wind_Nordex_MM92_3300000_131.json</t>
-  </si>
-  <si>
-    <t>wind_Siemens_SWT-3.6-130_3600000_130.json</t>
-  </si>
-  <si>
-    <t>weather</t>
-  </si>
-  <si>
-    <t>local</t>
-  </si>
-  <si>
-    <t>ev_fulltime_41.csv</t>
-  </si>
-  <si>
-    <t>ev_fulltime_48.csv</t>
+    <t>heat_gen_2_pu.csv</t>
+  </si>
+  <si>
+    <t>pv_1_pu.csv</t>
+  </si>
+  <si>
+    <t>pv_2_pu.csv</t>
+  </si>
+  <si>
+    <t>fixed_gen_1_pu.csv</t>
+  </si>
+  <si>
+    <t>ev_parttime_88.csv</t>
+  </si>
+  <si>
+    <t>ev_freetime_3.csv</t>
   </si>
   <si>
     <t>ev_fulltime_49.csv</t>
   </si>
   <si>
-    <t>ev_fulltime_45.csv</t>
-  </si>
-  <si>
-    <t>ev_fulltime_47.csv</t>
-  </si>
-  <si>
-    <t>ev_parttime_90.csv</t>
-  </si>
-  <si>
-    <t>price_sensitive</t>
-  </si>
-  <si>
-    <t>ev_close</t>
-  </si>
-  <si>
-    <t>True</t>
-  </si>
-  <si>
-    <t>naive</t>
-  </si>
-  <si>
-    <t>linear</t>
-  </si>
-  <si>
-    <t>general/sub_id</t>
-  </si>
-  <si>
-    <t>general/parameters/apartments_independent</t>
-  </si>
-  <si>
-    <t>general/parameters/apartments</t>
-  </si>
-  <si>
-    <t>okrkLU7dEv9zBJu</t>
-  </si>
-  <si>
-    <t>5u20qBHjWa2Ic0d</t>
-  </si>
-  <si>
-    <t>main</t>
-  </si>
-  <si>
-    <t>MORBhkg1gGsYALg</t>
-  </si>
-  <si>
-    <t>Bl3ZuCYrEkpnyDK</t>
-  </si>
-  <si>
-    <t>ae2InbMZR1Q3ylz</t>
-  </si>
-  <si>
-    <t>AMSglV9XMfUDQdc</t>
-  </si>
-  <si>
-    <t>bgMVEHxHOCD2ZHP</t>
-  </si>
-  <si>
-    <t>ZySixt5otl0xAbX</t>
-  </si>
-  <si>
-    <t>w3eCmzQpkDLZgPU</t>
-  </si>
-  <si>
-    <t>G1YXjrOhuOF8r1k</t>
-  </si>
-  <si>
-    <t>PcDKRpWO6qmoz0Z</t>
-  </si>
-  <si>
-    <t>0qnUQ37A1spIXrY</t>
-  </si>
-  <si>
-    <t>lUalunDMN7lpPO6</t>
-  </si>
-  <si>
-    <t>k3O9vOHMtRq1jRm</t>
-  </si>
-  <si>
-    <t>BurM61AIDtzgbMX</t>
-  </si>
-  <si>
-    <t>HRcyEZSSEcK9HhM</t>
-  </si>
-  <si>
-    <t>hh_1158_4.csv</t>
-  </si>
-  <si>
-    <t>hh_1546_2.csv</t>
-  </si>
-  <si>
-    <t>hh_3296_0.csv</t>
-  </si>
-  <si>
-    <t>hh_1720_0.csv</t>
-  </si>
-  <si>
-    <t>hh_1266_0.csv</t>
-  </si>
-  <si>
-    <t>hh_2012_3.csv</t>
-  </si>
-  <si>
-    <t>hh_2455_0.csv</t>
-  </si>
-  <si>
-    <t>hh_2262_0.csv</t>
-  </si>
-  <si>
-    <t>hh_1009_1.csv</t>
-  </si>
-  <si>
-    <t>hh_2687_0.csv</t>
-  </si>
-  <si>
-    <t>heat_gen_5_pu.csv</t>
-  </si>
-  <si>
-    <t>heat_gen_3_pu.csv</t>
-  </si>
-  <si>
-    <t>heat_gen_1_pu.csv</t>
-  </si>
-  <si>
-    <t>heat_gen_2_pu.csv</t>
-  </si>
-  <si>
-    <t>dhw_gen_1_pu.csv</t>
-  </si>
-  <si>
-    <t>pv_1_pu.csv</t>
-  </si>
-  <si>
-    <t>pv_2_pu.csv</t>
-  </si>
-  <si>
-    <t>wind_Vestas_V117-3.3-MW_3300000_117.json</t>
-  </si>
-  <si>
-    <t>fixed_gen_1_pu.csv</t>
-  </si>
-  <si>
-    <t>ev_freetime_1.csv</t>
-  </si>
-  <si>
-    <t>ev_freetime_2.csv</t>
+    <t>c</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>o</t>
+  </si>
+  <si>
+    <t>_</t>
   </si>
   <si>
     <t>i</t>
   </si>
   <si>
-    <t>s</t>
-  </si>
-  <si>
-    <t>o</t>
-  </si>
-  <si>
-    <t>_</t>
-  </si>
-  <si>
-    <t>c</t>
-  </si>
-  <si>
-    <t>n</t>
-  </si>
-  <si>
     <t>general/parameters/type</t>
   </si>
   <si>
     <t>general/fcast_retraining_frequency</t>
   </si>
   <si>
-    <t>ECGOnSW8WADYhYT</t>
-  </si>
-  <si>
-    <t>JLZ2nNizqi9Z6WL</t>
-  </si>
-  <si>
-    <t>pWrRQ5sGDp5e59p</t>
-  </si>
-  <si>
-    <t>grRgMFsDz987rgG</t>
+    <t>b3EJHXw5EeY8amr</t>
+  </si>
+  <si>
+    <t>tnMWoI1BhDlGi1E</t>
+  </si>
+  <si>
+    <t>johBPxSKutuPiXl</t>
+  </si>
+  <si>
+    <t>kEmhGfuLCWEw1zm</t>
+  </si>
+  <si>
+    <t>retail</t>
   </si>
   <si>
     <t>office</t>
   </si>
   <si>
-    <t>retail</t>
+    <t>retail_pu_0.csv</t>
   </si>
   <si>
     <t>office_pu_0.csv</t>
   </si>
   <si>
-    <t>retail_pu_0.csv</t>
-  </si>
-  <si>
-    <t>YrM2KlV24c6EpVK</t>
-  </si>
-  <si>
-    <t>GOw1Mue80BXXDwc</t>
+    <t>pv_3_pu.csv</t>
+  </si>
+  <si>
+    <t>ev_fulltime_42.csv</t>
+  </si>
+  <si>
+    <t>4D34vnUXgWa5kv5</t>
+  </si>
+  <si>
+    <t>lLWhENvFv0yGNe2</t>
+  </si>
+  <si>
+    <t>food</t>
   </si>
   <si>
     <t>tobacco</t>
   </si>
   <si>
-    <t>food</t>
+    <t>food_pu_0.csv</t>
   </si>
   <si>
     <t>tobacco_pu_0.csv</t>
   </si>
   <si>
-    <t>food_pu_0.csv</t>
-  </si>
-  <si>
-    <t>ev_parttime_89.csv</t>
-  </si>
-  <si>
-    <t>full</t>
-  </si>
-  <si>
-    <t>znibXFFKBylRUZR</t>
-  </si>
-  <si>
-    <t>xwTKTPT383KkdQE</t>
-  </si>
-  <si>
-    <t>TWCV1vstf48hPvT</t>
-  </si>
-  <si>
-    <t>eux7LCBDYu36BPy</t>
-  </si>
-  <si>
-    <t>SmWE7XCDFO7t9eu</t>
-  </si>
-  <si>
-    <t>tPulIZT1ZhxrczV</t>
-  </si>
-  <si>
-    <t>pv_3_pu.csv</t>
+    <t>5uMQwXWDxxOvvsF</t>
+  </si>
+  <si>
+    <t>EWF1wtzNcMBmwPR</t>
+  </si>
+  <si>
+    <t>lY7Nn9q3gRmgQrI</t>
+  </si>
+  <si>
+    <t>6b3vswBi2II6k2A</t>
+  </si>
+  <si>
+    <t>JFwlTTwFaBBYmfA</t>
+  </si>
+  <si>
+    <t>qPqZ5b3fd7TS5eX</t>
   </si>
   <si>
     <t>psh/owner</t>
@@ -885,31 +882,31 @@
     <t>hydrogen/quality</t>
   </si>
   <si>
-    <t>IrDk0suEMJe1Jrq</t>
-  </si>
-  <si>
-    <t>ca7DXvsRif58Ywi</t>
-  </si>
-  <si>
-    <t>UYHS8KkFEgWdMat</t>
-  </si>
-  <si>
-    <t>53DJ8459GxzasDU</t>
-  </si>
-  <si>
-    <t>wUdW9MWYe3v90V7</t>
-  </si>
-  <si>
-    <t>wjruqoUV91OXGae</t>
-  </si>
-  <si>
-    <t>bBt3I255Zgyiiu6</t>
-  </si>
-  <si>
-    <t>3KsTujBHlQ7RVF0</t>
-  </si>
-  <si>
-    <t>kqCfqR3JvHUAq71</t>
+    <t>WK8hgHKuluAB61t</t>
+  </si>
+  <si>
+    <t>MLNDRfxpdKeeUwS</t>
+  </si>
+  <si>
+    <t>zEalmmqvqzAwkQh</t>
+  </si>
+  <si>
+    <t>fsDA2NSUmZatNE7</t>
+  </si>
+  <si>
+    <t>44U9w1UWAmSyBgy</t>
+  </si>
+  <si>
+    <t>L8BXc8OZTghjRJq</t>
+  </si>
+  <si>
+    <t>Lk2VZ5iH3zUhNPM</t>
+  </si>
+  <si>
+    <t>L1IRdkJhAInDjcx</t>
+  </si>
+  <si>
+    <t>HgvSumIbLb6atCp</t>
   </si>
 </sst>
 </file>
@@ -1267,10 +1264,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:EP11"/>
+  <dimension ref="A1:EQ11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:146">
+    <row r="1" spans="1:147">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1706,19 +1703,22 @@
       <c r="EP1" s="1" t="s">
         <v>144</v>
       </c>
+      <c r="EQ1" s="1" t="s">
+        <v>145</v>
+      </c>
     </row>
-    <row r="2" spans="1:146">
+    <row r="2" spans="1:147">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="H2">
         <v>2</v>
@@ -1727,7 +1727,7 @@
         <v>2.6</v>
       </c>
       <c r="J2">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="K2">
         <v>1</v>
@@ -1742,10 +1742,10 @@
         <v>1</v>
       </c>
       <c r="O2">
-        <v>3648000</v>
+        <v>3296000</v>
       </c>
       <c r="P2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q2" t="s">
         <v>162</v>
@@ -1793,13 +1793,13 @@
         <v>1</v>
       </c>
       <c r="AH2">
-        <v>5500000</v>
+        <v>19500000</v>
       </c>
       <c r="AI2" t="s">
         <v>164</v>
       </c>
       <c r="AJ2">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="AK2" t="s">
         <v>162</v>
@@ -1826,10 +1826,10 @@
         <v>1</v>
       </c>
       <c r="AS2">
-        <v>2100000</v>
+        <v>2800000</v>
       </c>
       <c r="AT2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AU2">
         <v>55</v>
@@ -1859,10 +1859,10 @@
         <v>1</v>
       </c>
       <c r="BD2">
-        <v>5900</v>
+        <v>4600</v>
       </c>
       <c r="BE2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BF2">
         <v>0</v>
@@ -1874,7 +1874,7 @@
         <v>1</v>
       </c>
       <c r="BI2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="BJ2">
         <v>2</v>
@@ -1883,50 +1883,41 @@
         <v>9</v>
       </c>
       <c r="BL2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="BM2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BN2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="b">
         <v>1</v>
       </c>
-      <c r="BP2">
-        <v>2100</v>
-      </c>
-      <c r="BQ2" t="s">
+      <c r="BS2" t="s">
+        <v>187</v>
+      </c>
+      <c r="BT2">
+        <v>2</v>
+      </c>
+      <c r="BU2">
+        <v>9</v>
+      </c>
+      <c r="BV2" t="s">
+        <v>181</v>
+      </c>
+      <c r="BW2">
+        <v>0</v>
+      </c>
+      <c r="BX2">
+        <v>0</v>
+      </c>
+      <c r="BY2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CC2" t="s">
         <v>180</v>
       </c>
-      <c r="BR2" t="b">
-        <v>1</v>
-      </c>
-      <c r="BS2" t="s">
-        <v>183</v>
-      </c>
-      <c r="BT2">
-        <v>2</v>
-      </c>
-      <c r="BU2">
-        <v>9</v>
-      </c>
-      <c r="BV2" t="s">
-        <v>179</v>
-      </c>
-      <c r="BW2">
-        <v>0</v>
-      </c>
-      <c r="BX2">
-        <v>0</v>
-      </c>
-      <c r="BY2" t="b">
-        <v>1</v>
-      </c>
-      <c r="CC2" t="s">
-        <v>178</v>
-      </c>
       <c r="CD2">
         <v>2</v>
       </c>
@@ -1934,7 +1925,7 @@
         <v>9</v>
       </c>
       <c r="CF2" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="CG2">
         <v>0</v>
@@ -1946,7 +1937,7 @@
         <v>1</v>
       </c>
       <c r="CL2" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="CM2">
         <v>0</v>
@@ -1958,7 +1949,7 @@
         <v>1</v>
       </c>
       <c r="DJ2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="DK2">
         <v>0.05</v>
@@ -1973,22 +1964,40 @@
         <v>8.5</v>
       </c>
       <c r="DO2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="DP2" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="DQ2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS2" t="s">
-        <v>193</v>
+        <v>197</v>
+      </c>
+      <c r="DT2">
+        <v>3300</v>
+      </c>
+      <c r="DU2">
+        <v>3300</v>
+      </c>
+      <c r="DV2">
+        <v>0.95</v>
+      </c>
+      <c r="DW2">
+        <v>0.1</v>
+      </c>
+      <c r="DX2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DY2" t="b">
+        <v>0</v>
       </c>
       <c r="DZ2" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="EA2">
         <v>0</v>
@@ -1997,45 +2006,45 @@
         <v>0</v>
       </c>
       <c r="EC2" t="s">
-        <v>193</v>
-      </c>
-      <c r="EG2" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="EH2" t="s">
-        <v>194</v>
-      </c>
-      <c r="EI2">
+        <v>188</v>
+      </c>
+      <c r="EI2" t="s">
+        <v>198</v>
+      </c>
+      <c r="EJ2">
         <v>96</v>
       </c>
-      <c r="EJ2" t="s">
-        <v>195</v>
-      </c>
-      <c r="EK2">
-        <v>36</v>
-      </c>
-      <c r="EL2" t="s">
-        <v>179</v>
-      </c>
-      <c r="EM2">
-        <v>0</v>
+      <c r="EK2" t="s">
+        <v>199</v>
+      </c>
+      <c r="EL2">
+        <v>48</v>
+      </c>
+      <c r="EM2" t="s">
+        <v>181</v>
       </c>
       <c r="EN2">
         <v>0</v>
       </c>
       <c r="EO2">
+        <v>0</v>
+      </c>
+      <c r="EP2">
         <v>3600</v>
       </c>
-      <c r="EP2">
+      <c r="EQ2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:146">
+    <row r="3" spans="1:147">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F3">
         <v>4</v>
@@ -2068,7 +2077,7 @@
         <v>5527000</v>
       </c>
       <c r="P3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q3" t="s">
         <v>162</v>
@@ -2149,7 +2158,7 @@
         <v>1</v>
       </c>
       <c r="AS3">
-        <v>3200000</v>
+        <v>2800000</v>
       </c>
       <c r="AT3" t="s">
         <v>172</v>
@@ -2182,10 +2191,10 @@
         <v>1</v>
       </c>
       <c r="BD3">
-        <v>7200</v>
+        <v>9700</v>
       </c>
       <c r="BE3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BF3">
         <v>0</v>
@@ -2197,7 +2206,7 @@
         <v>1</v>
       </c>
       <c r="BI3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="BJ3">
         <v>2</v>
@@ -2206,19 +2215,28 @@
         <v>9</v>
       </c>
       <c r="BL3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="BM3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BN3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BO3" t="b">
         <v>1</v>
       </c>
+      <c r="BP3">
+        <v>3800</v>
+      </c>
+      <c r="BQ3" t="s">
+        <v>182</v>
+      </c>
+      <c r="BR3" t="b">
+        <v>1</v>
+      </c>
       <c r="BS3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="BT3">
         <v>2</v>
@@ -2227,7 +2245,7 @@
         <v>9</v>
       </c>
       <c r="BV3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="BW3">
         <v>0</v>
@@ -2239,7 +2257,7 @@
         <v>1</v>
       </c>
       <c r="CC3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="CD3">
         <v>2</v>
@@ -2248,7 +2266,7 @@
         <v>9</v>
       </c>
       <c r="CF3" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="CG3">
         <v>0</v>
@@ -2260,7 +2278,7 @@
         <v>1</v>
       </c>
       <c r="CL3" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="CM3">
         <v>0</v>
@@ -2272,7 +2290,7 @@
         <v>1</v>
       </c>
       <c r="DJ3" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="DK3">
         <v>0.05</v>
@@ -2287,10 +2305,10 @@
         <v>8.5</v>
       </c>
       <c r="DO3" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="DP3" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="DQ3">
         <v>1</v>
@@ -2299,7 +2317,7 @@
         <v>1</v>
       </c>
       <c r="DS3" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="DT3">
         <v>5500</v>
@@ -2320,7 +2338,7 @@
         <v>0</v>
       </c>
       <c r="DZ3" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="EA3">
         <v>0</v>
@@ -2329,51 +2347,51 @@
         <v>0</v>
       </c>
       <c r="EC3" t="s">
-        <v>193</v>
-      </c>
-      <c r="EG3" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="EH3" t="s">
-        <v>194</v>
-      </c>
-      <c r="EI3">
+        <v>188</v>
+      </c>
+      <c r="EI3" t="s">
+        <v>198</v>
+      </c>
+      <c r="EJ3">
         <v>96</v>
       </c>
-      <c r="EJ3" t="s">
-        <v>195</v>
-      </c>
-      <c r="EK3">
-        <v>60</v>
-      </c>
-      <c r="EL3" t="s">
-        <v>179</v>
-      </c>
-      <c r="EM3">
-        <v>0</v>
+      <c r="EK3" t="s">
+        <v>199</v>
+      </c>
+      <c r="EL3">
+        <v>12</v>
+      </c>
+      <c r="EM3" t="s">
+        <v>181</v>
       </c>
       <c r="EN3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="EO3">
+        <v>0</v>
+      </c>
+      <c r="EP3">
         <v>3600</v>
       </c>
-      <c r="EP3">
+      <c r="EQ3">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:146">
+    <row r="4" spans="1:147">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G4">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="H4">
         <v>2</v>
@@ -2382,7 +2400,7 @@
         <v>2.6</v>
       </c>
       <c r="J4">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="K4">
         <v>1</v>
@@ -2397,10 +2415,10 @@
         <v>1</v>
       </c>
       <c r="O4">
-        <v>2532000</v>
+        <v>2687000</v>
       </c>
       <c r="P4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q4" t="s">
         <v>162</v>
@@ -2448,13 +2466,13 @@
         <v>1</v>
       </c>
       <c r="AH4">
-        <v>5500000</v>
+        <v>19500000</v>
       </c>
       <c r="AI4" t="s">
         <v>166</v>
       </c>
       <c r="AJ4">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="AK4" t="s">
         <v>162</v>
@@ -2481,7 +2499,7 @@
         <v>1</v>
       </c>
       <c r="AS4">
-        <v>1800000</v>
+        <v>3200000</v>
       </c>
       <c r="AT4" t="s">
         <v>173</v>
@@ -2514,10 +2532,10 @@
         <v>1</v>
       </c>
       <c r="BD4">
-        <v>3700</v>
+        <v>3500</v>
       </c>
       <c r="BE4" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BF4">
         <v>0</v>
@@ -2529,7 +2547,7 @@
         <v>1</v>
       </c>
       <c r="BI4" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="BJ4">
         <v>2</v>
@@ -2538,38 +2556,29 @@
         <v>9</v>
       </c>
       <c r="BL4" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="BM4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BN4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BO4" t="b">
         <v>1</v>
       </c>
-      <c r="BP4">
-        <v>2000</v>
-      </c>
-      <c r="BQ4" t="s">
+      <c r="BS4" t="s">
+        <v>187</v>
+      </c>
+      <c r="BT4">
+        <v>2</v>
+      </c>
+      <c r="BU4">
+        <v>9</v>
+      </c>
+      <c r="BV4" t="s">
         <v>181</v>
       </c>
-      <c r="BR4" t="b">
-        <v>1</v>
-      </c>
-      <c r="BS4" t="s">
-        <v>183</v>
-      </c>
-      <c r="BT4">
-        <v>2</v>
-      </c>
-      <c r="BU4">
-        <v>9</v>
-      </c>
-      <c r="BV4" t="s">
-        <v>179</v>
-      </c>
       <c r="BW4">
         <v>0</v>
       </c>
@@ -2580,7 +2589,7 @@
         <v>1</v>
       </c>
       <c r="CC4" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="CD4">
         <v>2</v>
@@ -2589,7 +2598,7 @@
         <v>9</v>
       </c>
       <c r="CF4" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="CG4">
         <v>0</v>
@@ -2601,7 +2610,7 @@
         <v>1</v>
       </c>
       <c r="CL4" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="CM4">
         <v>0</v>
@@ -2613,7 +2622,7 @@
         <v>1</v>
       </c>
       <c r="DJ4" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="DK4">
         <v>0.05</v>
@@ -2628,10 +2637,10 @@
         <v>8.5</v>
       </c>
       <c r="DO4" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="DP4" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="DQ4">
         <v>1</v>
@@ -2640,13 +2649,13 @@
         <v>1</v>
       </c>
       <c r="DS4" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="DT4">
-        <v>2500</v>
+        <v>2700</v>
       </c>
       <c r="DU4">
-        <v>2500</v>
+        <v>2700</v>
       </c>
       <c r="DV4">
         <v>0.95</v>
@@ -2661,7 +2670,7 @@
         <v>0</v>
       </c>
       <c r="DZ4" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="EA4">
         <v>0</v>
@@ -2670,51 +2679,51 @@
         <v>0</v>
       </c>
       <c r="EC4" t="s">
-        <v>193</v>
-      </c>
-      <c r="EG4" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="EH4" t="s">
-        <v>194</v>
-      </c>
-      <c r="EI4">
+        <v>188</v>
+      </c>
+      <c r="EI4" t="s">
+        <v>198</v>
+      </c>
+      <c r="EJ4">
         <v>96</v>
       </c>
-      <c r="EJ4" t="s">
-        <v>195</v>
-      </c>
-      <c r="EK4">
-        <v>48</v>
-      </c>
-      <c r="EL4" t="s">
-        <v>179</v>
-      </c>
-      <c r="EM4">
+      <c r="EK4" t="s">
+        <v>199</v>
+      </c>
+      <c r="EL4">
+        <v>60</v>
+      </c>
+      <c r="EM4" t="s">
+        <v>181</v>
+      </c>
+      <c r="EN4">
         <v>30</v>
       </c>
-      <c r="EN4">
-        <v>0</v>
-      </c>
       <c r="EO4">
+        <v>0</v>
+      </c>
+      <c r="EP4">
         <v>3600</v>
       </c>
-      <c r="EP4">
+      <c r="EQ4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:146">
+    <row r="5" spans="1:147">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G5">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H5">
         <v>2</v>
@@ -2723,7 +2732,7 @@
         <v>2.6</v>
       </c>
       <c r="J5">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="K5">
         <v>1</v>
@@ -2738,10 +2747,10 @@
         <v>1</v>
       </c>
       <c r="O5">
-        <v>3863000</v>
+        <v>4536000</v>
       </c>
       <c r="P5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q5" t="s">
         <v>162</v>
@@ -2789,13 +2798,13 @@
         <v>1</v>
       </c>
       <c r="AH5">
-        <v>19500000</v>
+        <v>5500000</v>
       </c>
       <c r="AI5" t="s">
         <v>167</v>
       </c>
       <c r="AJ5">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="AK5" t="s">
         <v>162</v>
@@ -2822,7 +2831,7 @@
         <v>1</v>
       </c>
       <c r="AS5">
-        <v>2400000</v>
+        <v>1800000</v>
       </c>
       <c r="AT5" t="s">
         <v>174</v>
@@ -2855,10 +2864,10 @@
         <v>1</v>
       </c>
       <c r="BD5">
-        <v>4900</v>
+        <v>6500</v>
       </c>
       <c r="BE5" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BF5">
         <v>0</v>
@@ -2870,7 +2879,7 @@
         <v>1</v>
       </c>
       <c r="BI5" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="BJ5">
         <v>2</v>
@@ -2879,7 +2888,7 @@
         <v>9</v>
       </c>
       <c r="BL5" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="BM5">
         <v>1</v>
@@ -2891,26 +2900,26 @@
         <v>1</v>
       </c>
       <c r="BP5">
-        <v>2900</v>
+        <v>2800</v>
       </c>
       <c r="BQ5" t="s">
+        <v>183</v>
+      </c>
+      <c r="BR5" t="b">
+        <v>1</v>
+      </c>
+      <c r="BS5" t="s">
+        <v>187</v>
+      </c>
+      <c r="BT5">
+        <v>2</v>
+      </c>
+      <c r="BU5">
+        <v>9</v>
+      </c>
+      <c r="BV5" t="s">
         <v>181</v>
       </c>
-      <c r="BR5" t="b">
-        <v>1</v>
-      </c>
-      <c r="BS5" t="s">
-        <v>183</v>
-      </c>
-      <c r="BT5">
-        <v>2</v>
-      </c>
-      <c r="BU5">
-        <v>9</v>
-      </c>
-      <c r="BV5" t="s">
-        <v>179</v>
-      </c>
       <c r="BW5">
         <v>0</v>
       </c>
@@ -2921,7 +2930,7 @@
         <v>1</v>
       </c>
       <c r="CC5" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="CD5">
         <v>2</v>
@@ -2930,7 +2939,7 @@
         <v>9</v>
       </c>
       <c r="CF5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="CG5">
         <v>0</v>
@@ -2942,7 +2951,7 @@
         <v>1</v>
       </c>
       <c r="CL5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="CM5">
         <v>1</v>
@@ -2954,7 +2963,7 @@
         <v>1</v>
       </c>
       <c r="CP5" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="CQ5">
         <v>50000</v>
@@ -2984,7 +2993,7 @@
         <v>0</v>
       </c>
       <c r="DJ5" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="DK5">
         <v>0.05</v>
@@ -2999,10 +3008,10 @@
         <v>8.5</v>
       </c>
       <c r="DO5" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="DP5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="DQ5">
         <v>1</v>
@@ -3011,13 +3020,13 @@
         <v>1</v>
       </c>
       <c r="DS5" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="DT5">
-        <v>3900</v>
+        <v>4500</v>
       </c>
       <c r="DU5">
-        <v>3900</v>
+        <v>4500</v>
       </c>
       <c r="DV5">
         <v>0.95</v>
@@ -3032,7 +3041,7 @@
         <v>0</v>
       </c>
       <c r="DZ5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="EA5">
         <v>0</v>
@@ -3041,51 +3050,51 @@
         <v>0</v>
       </c>
       <c r="EC5" t="s">
-        <v>193</v>
-      </c>
-      <c r="EG5" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="EH5" t="s">
-        <v>194</v>
-      </c>
-      <c r="EI5">
+        <v>188</v>
+      </c>
+      <c r="EI5" t="s">
+        <v>198</v>
+      </c>
+      <c r="EJ5">
         <v>96</v>
       </c>
-      <c r="EJ5" t="s">
-        <v>195</v>
-      </c>
-      <c r="EK5">
+      <c r="EK5" t="s">
+        <v>199</v>
+      </c>
+      <c r="EL5">
         <v>60</v>
       </c>
-      <c r="EL5" t="s">
-        <v>179</v>
-      </c>
-      <c r="EM5">
-        <v>10</v>
+      <c r="EM5" t="s">
+        <v>181</v>
       </c>
       <c r="EN5">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="EO5">
+        <v>0</v>
+      </c>
+      <c r="EP5">
         <v>3600</v>
       </c>
-      <c r="EP5">
+      <c r="EQ5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:146">
+    <row r="6" spans="1:147">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G6">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="H6">
         <v>2</v>
@@ -3094,7 +3103,7 @@
         <v>2.6</v>
       </c>
       <c r="J6">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -3109,10 +3118,10 @@
         <v>1</v>
       </c>
       <c r="O6">
-        <v>2959000</v>
+        <v>3125000</v>
       </c>
       <c r="P6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q6" t="s">
         <v>162</v>
@@ -3160,7 +3169,7 @@
         <v>1</v>
       </c>
       <c r="AH6">
-        <v>5500000</v>
+        <v>19500000</v>
       </c>
       <c r="AI6" t="s">
         <v>168</v>
@@ -3193,10 +3202,10 @@
         <v>1</v>
       </c>
       <c r="AS6">
-        <v>2100000</v>
+        <v>2400000</v>
       </c>
       <c r="AT6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AU6">
         <v>55</v>
@@ -3217,31 +3226,16 @@
         <v>90</v>
       </c>
       <c r="BA6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC6" t="b">
         <v>1</v>
       </c>
-      <c r="BD6">
-        <v>3700</v>
-      </c>
-      <c r="BE6" t="s">
-        <v>177</v>
-      </c>
-      <c r="BF6">
-        <v>-20</v>
-      </c>
-      <c r="BG6">
-        <v>50</v>
-      </c>
-      <c r="BH6" t="b">
-        <v>1</v>
-      </c>
       <c r="BI6" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="BJ6">
         <v>2</v>
@@ -3250,7 +3244,7 @@
         <v>9</v>
       </c>
       <c r="BL6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="BM6">
         <v>0</v>
@@ -3262,7 +3256,7 @@
         <v>1</v>
       </c>
       <c r="BS6" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="BT6">
         <v>2</v>
@@ -3271,7 +3265,7 @@
         <v>9</v>
       </c>
       <c r="BV6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="BW6">
         <v>0</v>
@@ -3283,7 +3277,7 @@
         <v>1</v>
       </c>
       <c r="CC6" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="CD6">
         <v>2</v>
@@ -3292,7 +3286,7 @@
         <v>9</v>
       </c>
       <c r="CF6" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="CG6">
         <v>0</v>
@@ -3304,7 +3298,7 @@
         <v>1</v>
       </c>
       <c r="CL6" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="CM6">
         <v>1</v>
@@ -3316,7 +3310,7 @@
         <v>1</v>
       </c>
       <c r="CP6" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="CQ6">
         <v>75000</v>
@@ -3346,7 +3340,7 @@
         <v>0</v>
       </c>
       <c r="DJ6" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="DK6">
         <v>0.05</v>
@@ -3361,10 +3355,10 @@
         <v>8.5</v>
       </c>
       <c r="DO6" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="DP6" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="DQ6">
         <v>0</v>
@@ -3373,10 +3367,10 @@
         <v>0</v>
       </c>
       <c r="DS6" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="DZ6" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="EA6">
         <v>0</v>
@@ -3385,51 +3379,51 @@
         <v>0</v>
       </c>
       <c r="EC6" t="s">
-        <v>193</v>
-      </c>
-      <c r="EG6" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="EH6" t="s">
-        <v>194</v>
-      </c>
-      <c r="EI6">
+        <v>188</v>
+      </c>
+      <c r="EI6" t="s">
+        <v>198</v>
+      </c>
+      <c r="EJ6">
         <v>96</v>
       </c>
-      <c r="EJ6" t="s">
-        <v>195</v>
-      </c>
-      <c r="EK6">
-        <v>60</v>
-      </c>
-      <c r="EL6" t="s">
-        <v>179</v>
-      </c>
-      <c r="EM6">
+      <c r="EK6" t="s">
+        <v>199</v>
+      </c>
+      <c r="EL6">
+        <v>24</v>
+      </c>
+      <c r="EM6" t="s">
+        <v>181</v>
+      </c>
+      <c r="EN6">
         <v>30</v>
       </c>
-      <c r="EN6">
-        <v>0</v>
-      </c>
       <c r="EO6">
+        <v>0</v>
+      </c>
+      <c r="EP6">
         <v>3600</v>
       </c>
-      <c r="EP6">
+      <c r="EQ6">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:146">
+    <row r="7" spans="1:147">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G7">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="H7">
         <v>2</v>
@@ -3438,7 +3432,7 @@
         <v>2.6</v>
       </c>
       <c r="J7">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="K7">
         <v>1</v>
@@ -3453,10 +3447,10 @@
         <v>1</v>
       </c>
       <c r="O7">
-        <v>3125000</v>
+        <v>3296000</v>
       </c>
       <c r="P7" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="Q7" t="s">
         <v>162</v>
@@ -3504,7 +3498,7 @@
         <v>1</v>
       </c>
       <c r="AH7">
-        <v>5500000</v>
+        <v>19500000</v>
       </c>
       <c r="AI7" t="s">
         <v>169</v>
@@ -3537,10 +3531,10 @@
         <v>1</v>
       </c>
       <c r="AS7">
-        <v>1800000</v>
+        <v>2800000</v>
       </c>
       <c r="AT7" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="AU7">
         <v>55</v>
@@ -3570,22 +3564,22 @@
         <v>1</v>
       </c>
       <c r="BD7">
-        <v>4200</v>
+        <v>4400</v>
       </c>
       <c r="BE7" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BF7">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="BG7">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="BH7" t="b">
         <v>1</v>
       </c>
       <c r="BI7" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="BJ7">
         <v>2</v>
@@ -3594,19 +3588,28 @@
         <v>9</v>
       </c>
       <c r="BL7" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="BM7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BN7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BO7" t="b">
         <v>1</v>
       </c>
+      <c r="BP7">
+        <v>2600</v>
+      </c>
+      <c r="BQ7" t="s">
+        <v>184</v>
+      </c>
+      <c r="BR7" t="b">
+        <v>1</v>
+      </c>
       <c r="BS7" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="BT7">
         <v>2</v>
@@ -3615,7 +3618,7 @@
         <v>9</v>
       </c>
       <c r="BV7" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="BW7">
         <v>0</v>
@@ -3627,7 +3630,7 @@
         <v>1</v>
       </c>
       <c r="CC7" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="CD7">
         <v>2</v>
@@ -3636,7 +3639,7 @@
         <v>9</v>
       </c>
       <c r="CF7" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="CG7">
         <v>0</v>
@@ -3648,7 +3651,7 @@
         <v>1</v>
       </c>
       <c r="CL7" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="CM7">
         <v>0</v>
@@ -3660,7 +3663,7 @@
         <v>1</v>
       </c>
       <c r="DJ7" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="DK7">
         <v>0.05</v>
@@ -3675,40 +3678,22 @@
         <v>8.5</v>
       </c>
       <c r="DO7" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="DP7" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="DQ7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS7" t="s">
-        <v>193</v>
-      </c>
-      <c r="DT7">
-        <v>3100</v>
-      </c>
-      <c r="DU7">
-        <v>3100</v>
-      </c>
-      <c r="DV7">
-        <v>0.95</v>
-      </c>
-      <c r="DW7">
-        <v>0.1</v>
-      </c>
-      <c r="DX7" t="b">
-        <v>0</v>
-      </c>
-      <c r="DY7" t="b">
-        <v>0</v>
+        <v>197</v>
       </c>
       <c r="DZ7" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="EA7">
         <v>0</v>
@@ -3717,51 +3702,51 @@
         <v>0</v>
       </c>
       <c r="EC7" t="s">
-        <v>193</v>
-      </c>
-      <c r="EG7" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="EH7" t="s">
-        <v>194</v>
-      </c>
-      <c r="EI7">
+        <v>188</v>
+      </c>
+      <c r="EI7" t="s">
+        <v>198</v>
+      </c>
+      <c r="EJ7">
         <v>96</v>
       </c>
-      <c r="EJ7" t="s">
-        <v>195</v>
-      </c>
-      <c r="EK7">
+      <c r="EK7" t="s">
+        <v>199</v>
+      </c>
+      <c r="EL7">
         <v>48</v>
       </c>
-      <c r="EL7" t="s">
-        <v>179</v>
-      </c>
-      <c r="EM7">
-        <v>0</v>
+      <c r="EM7" t="s">
+        <v>181</v>
       </c>
       <c r="EN7">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="EO7">
+        <v>0</v>
+      </c>
+      <c r="EP7">
         <v>3600</v>
       </c>
-      <c r="EP7">
+      <c r="EQ7">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:146">
+    <row r="8" spans="1:147">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G8">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H8">
         <v>2</v>
@@ -3770,7 +3755,7 @@
         <v>2.6</v>
       </c>
       <c r="J8">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="K8">
         <v>1</v>
@@ -3785,10 +3770,10 @@
         <v>1</v>
       </c>
       <c r="O8">
-        <v>3564000</v>
+        <v>3125000</v>
       </c>
       <c r="P8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q8" t="s">
         <v>162</v>
@@ -3836,10 +3821,10 @@
         <v>1</v>
       </c>
       <c r="AH8">
-        <v>19500000</v>
+        <v>5500000</v>
       </c>
       <c r="AI8" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="AJ8">
         <v>55</v>
@@ -3869,10 +3854,10 @@
         <v>1</v>
       </c>
       <c r="AS8">
-        <v>2800000</v>
+        <v>2400000</v>
       </c>
       <c r="AT8" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AU8">
         <v>55</v>
@@ -3902,22 +3887,22 @@
         <v>1</v>
       </c>
       <c r="BD8">
-        <v>5300</v>
+        <v>5500</v>
       </c>
       <c r="BE8" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BF8">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="BG8">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="BH8" t="b">
         <v>1</v>
       </c>
       <c r="BI8" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="BJ8">
         <v>2</v>
@@ -3926,7 +3911,7 @@
         <v>9</v>
       </c>
       <c r="BL8" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="BM8">
         <v>0</v>
@@ -3938,7 +3923,7 @@
         <v>1</v>
       </c>
       <c r="BS8" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="BT8">
         <v>2</v>
@@ -3947,7 +3932,7 @@
         <v>9</v>
       </c>
       <c r="BV8" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="BW8">
         <v>0</v>
@@ -3959,7 +3944,7 @@
         <v>1</v>
       </c>
       <c r="CC8" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="CD8">
         <v>2</v>
@@ -3968,7 +3953,7 @@
         <v>9</v>
       </c>
       <c r="CF8" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="CG8">
         <v>0</v>
@@ -3980,34 +3965,34 @@
         <v>1</v>
       </c>
       <c r="CL8" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="CM8">
         <v>1</v>
       </c>
       <c r="CN8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CO8" t="b">
         <v>1</v>
       </c>
       <c r="CP8" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CQ8">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="CR8">
-        <v>25000</v>
+        <v>15000</v>
       </c>
       <c r="CS8">
-        <v>11000</v>
+        <v>7200</v>
       </c>
       <c r="CT8">
-        <v>22000</v>
+        <v>7200</v>
       </c>
       <c r="CU8">
-        <v>200000</v>
+        <v>50000</v>
       </c>
       <c r="CV8">
         <v>0.9</v>
@@ -4021,38 +4006,8 @@
       <c r="CY8" t="b">
         <v>0</v>
       </c>
-      <c r="CZ8" t="s">
-        <v>190</v>
-      </c>
-      <c r="DA8">
-        <v>75000</v>
-      </c>
-      <c r="DB8">
-        <v>20000</v>
-      </c>
-      <c r="DC8">
-        <v>7200</v>
-      </c>
-      <c r="DD8">
-        <v>11000</v>
-      </c>
-      <c r="DE8">
-        <v>100000</v>
-      </c>
-      <c r="DF8">
-        <v>0.9</v>
-      </c>
-      <c r="DG8">
-        <v>0.8</v>
-      </c>
-      <c r="DH8" t="b">
-        <v>0</v>
-      </c>
-      <c r="DI8" t="b">
-        <v>0</v>
-      </c>
       <c r="DJ8" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="DK8">
         <v>0.05</v>
@@ -4067,10 +4022,10 @@
         <v>8.5</v>
       </c>
       <c r="DO8" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="DP8" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="DQ8">
         <v>1</v>
@@ -4079,13 +4034,13 @@
         <v>1</v>
       </c>
       <c r="DS8" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="DT8">
-        <v>3600</v>
+        <v>3100</v>
       </c>
       <c r="DU8">
-        <v>3600</v>
+        <v>3100</v>
       </c>
       <c r="DV8">
         <v>0.95</v>
@@ -4100,7 +4055,7 @@
         <v>0</v>
       </c>
       <c r="DZ8" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="EA8">
         <v>0</v>
@@ -4109,51 +4064,51 @@
         <v>0</v>
       </c>
       <c r="EC8" t="s">
-        <v>193</v>
-      </c>
-      <c r="EG8" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="EH8" t="s">
-        <v>194</v>
-      </c>
-      <c r="EI8">
+        <v>188</v>
+      </c>
+      <c r="EI8" t="s">
+        <v>198</v>
+      </c>
+      <c r="EJ8">
         <v>96</v>
       </c>
-      <c r="EJ8" t="s">
-        <v>195</v>
-      </c>
-      <c r="EK8">
-        <v>24</v>
-      </c>
-      <c r="EL8" t="s">
-        <v>179</v>
-      </c>
-      <c r="EM8">
-        <v>0</v>
+      <c r="EK8" t="s">
+        <v>199</v>
+      </c>
+      <c r="EL8">
+        <v>48</v>
+      </c>
+      <c r="EM8" t="s">
+        <v>181</v>
       </c>
       <c r="EN8">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="EO8">
+        <v>0</v>
+      </c>
+      <c r="EP8">
         <v>3600</v>
       </c>
-      <c r="EP8">
+      <c r="EQ8">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:146">
+    <row r="9" spans="1:147">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G9">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H9">
         <v>2</v>
@@ -4162,7 +4117,7 @@
         <v>2.6</v>
       </c>
       <c r="J9">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="K9">
         <v>1</v>
@@ -4177,10 +4132,10 @@
         <v>1</v>
       </c>
       <c r="O9">
-        <v>3863000</v>
+        <v>3296000</v>
       </c>
       <c r="P9" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="Q9" t="s">
         <v>162</v>
@@ -4228,13 +4183,13 @@
         <v>1</v>
       </c>
       <c r="AH9">
-        <v>19500000</v>
+        <v>5500000</v>
       </c>
       <c r="AI9" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="AJ9">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="AK9" t="s">
         <v>162</v>
@@ -4261,10 +4216,10 @@
         <v>1</v>
       </c>
       <c r="AS9">
-        <v>3200000</v>
+        <v>2400000</v>
       </c>
       <c r="AT9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AU9">
         <v>55</v>
@@ -4294,10 +4249,10 @@
         <v>1</v>
       </c>
       <c r="BD9">
-        <v>4700</v>
+        <v>4200</v>
       </c>
       <c r="BE9" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BF9">
         <v>0</v>
@@ -4309,7 +4264,7 @@
         <v>1</v>
       </c>
       <c r="BI9" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="BJ9">
         <v>2</v>
@@ -4318,7 +4273,7 @@
         <v>9</v>
       </c>
       <c r="BL9" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="BM9">
         <v>1</v>
@@ -4330,16 +4285,16 @@
         <v>1</v>
       </c>
       <c r="BP9">
-        <v>2800</v>
+        <v>2100</v>
       </c>
       <c r="BQ9" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="BR9" t="b">
         <v>1</v>
       </c>
       <c r="BS9" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="BT9">
         <v>2</v>
@@ -4348,7 +4303,7 @@
         <v>9</v>
       </c>
       <c r="BV9" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="BW9">
         <v>0</v>
@@ -4360,7 +4315,7 @@
         <v>1</v>
       </c>
       <c r="CC9" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="CD9">
         <v>2</v>
@@ -4369,7 +4324,7 @@
         <v>9</v>
       </c>
       <c r="CF9" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="CG9">
         <v>0</v>
@@ -4381,7 +4336,7 @@
         <v>1</v>
       </c>
       <c r="CL9" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="CM9">
         <v>1</v>
@@ -4393,22 +4348,22 @@
         <v>1</v>
       </c>
       <c r="CP9" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="CQ9">
-        <v>75000</v>
+        <v>100000</v>
       </c>
       <c r="CR9">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="CS9">
-        <v>7200</v>
+        <v>11000</v>
       </c>
       <c r="CT9">
-        <v>11000</v>
+        <v>22000</v>
       </c>
       <c r="CU9">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="CV9">
         <v>0.9</v>
@@ -4423,7 +4378,7 @@
         <v>0</v>
       </c>
       <c r="DJ9" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="DK9">
         <v>0.05</v>
@@ -4438,10 +4393,10 @@
         <v>8.5</v>
       </c>
       <c r="DO9" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="DP9" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="DQ9">
         <v>1</v>
@@ -4450,13 +4405,13 @@
         <v>1</v>
       </c>
       <c r="DS9" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="DT9">
-        <v>3900</v>
+        <v>3300</v>
       </c>
       <c r="DU9">
-        <v>3900</v>
+        <v>3300</v>
       </c>
       <c r="DV9">
         <v>0.95</v>
@@ -4471,7 +4426,7 @@
         <v>0</v>
       </c>
       <c r="DZ9" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="EA9">
         <v>0</v>
@@ -4480,51 +4435,51 @@
         <v>0</v>
       </c>
       <c r="EC9" t="s">
-        <v>193</v>
-      </c>
-      <c r="EG9" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="EH9" t="s">
-        <v>194</v>
-      </c>
-      <c r="EI9">
+        <v>188</v>
+      </c>
+      <c r="EI9" t="s">
+        <v>198</v>
+      </c>
+      <c r="EJ9">
         <v>96</v>
       </c>
-      <c r="EJ9" t="s">
-        <v>195</v>
-      </c>
-      <c r="EK9">
-        <v>60</v>
-      </c>
-      <c r="EL9" t="s">
-        <v>179</v>
-      </c>
-      <c r="EM9">
+      <c r="EK9" t="s">
+        <v>199</v>
+      </c>
+      <c r="EL9">
+        <v>48</v>
+      </c>
+      <c r="EM9" t="s">
+        <v>181</v>
+      </c>
+      <c r="EN9">
         <v>30</v>
       </c>
-      <c r="EN9">
-        <v>0</v>
-      </c>
       <c r="EO9">
+        <v>0</v>
+      </c>
+      <c r="EP9">
         <v>3600</v>
       </c>
-      <c r="EP9">
+      <c r="EQ9">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:146">
+    <row r="10" spans="1:147">
       <c r="A10" s="1">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G10">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H10">
         <v>2</v>
@@ -4533,7 +4488,7 @@
         <v>2.6</v>
       </c>
       <c r="J10">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="K10">
         <v>1</v>
@@ -4548,7 +4503,7 @@
         <v>1</v>
       </c>
       <c r="O10">
-        <v>3564000</v>
+        <v>2262000</v>
       </c>
       <c r="P10" t="s">
         <v>161</v>
@@ -4599,10 +4554,10 @@
         <v>1</v>
       </c>
       <c r="AH10">
-        <v>19500000</v>
+        <v>5500000</v>
       </c>
       <c r="AI10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AJ10">
         <v>55</v>
@@ -4632,10 +4587,10 @@
         <v>1</v>
       </c>
       <c r="AS10">
-        <v>2800000</v>
+        <v>2100000</v>
       </c>
       <c r="AT10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AU10">
         <v>55</v>
@@ -4665,7 +4620,7 @@
         <v>1</v>
       </c>
       <c r="BI10" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="BJ10">
         <v>2</v>
@@ -4674,19 +4629,28 @@
         <v>9</v>
       </c>
       <c r="BL10" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="BM10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BN10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BO10" t="b">
         <v>1</v>
       </c>
+      <c r="BP10">
+        <v>1000</v>
+      </c>
+      <c r="BQ10" t="s">
+        <v>186</v>
+      </c>
+      <c r="BR10" t="b">
+        <v>1</v>
+      </c>
       <c r="BS10" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="BT10">
         <v>2</v>
@@ -4695,7 +4659,7 @@
         <v>9</v>
       </c>
       <c r="BV10" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="BW10">
         <v>0</v>
@@ -4707,7 +4671,7 @@
         <v>1</v>
       </c>
       <c r="CC10" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="CD10">
         <v>2</v>
@@ -4716,7 +4680,7 @@
         <v>9</v>
       </c>
       <c r="CF10" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="CG10">
         <v>0</v>
@@ -4728,34 +4692,34 @@
         <v>1</v>
       </c>
       <c r="CL10" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="CM10">
         <v>1</v>
       </c>
       <c r="CN10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CO10" t="b">
         <v>1</v>
       </c>
       <c r="CP10" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="CQ10">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="CR10">
-        <v>15000</v>
+        <v>20000</v>
       </c>
       <c r="CS10">
         <v>7200</v>
       </c>
       <c r="CT10">
-        <v>7200</v>
+        <v>11000</v>
       </c>
       <c r="CU10">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="CV10">
         <v>0.9</v>
@@ -4769,8 +4733,38 @@
       <c r="CY10" t="b">
         <v>0</v>
       </c>
+      <c r="CZ10" t="s">
+        <v>194</v>
+      </c>
+      <c r="DA10">
+        <v>75000</v>
+      </c>
+      <c r="DB10">
+        <v>20000</v>
+      </c>
+      <c r="DC10">
+        <v>7200</v>
+      </c>
+      <c r="DD10">
+        <v>11000</v>
+      </c>
+      <c r="DE10">
+        <v>100000</v>
+      </c>
+      <c r="DF10">
+        <v>0.9</v>
+      </c>
+      <c r="DG10">
+        <v>0.8</v>
+      </c>
+      <c r="DH10" t="b">
+        <v>0</v>
+      </c>
+      <c r="DI10" t="b">
+        <v>0</v>
+      </c>
       <c r="DJ10" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="DK10">
         <v>0.05</v>
@@ -4785,10 +4779,10 @@
         <v>8.5</v>
       </c>
       <c r="DO10" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="DP10" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="DQ10">
         <v>0</v>
@@ -4797,10 +4791,10 @@
         <v>0</v>
       </c>
       <c r="DS10" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="DZ10" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="EA10">
         <v>0</v>
@@ -4809,45 +4803,45 @@
         <v>0</v>
       </c>
       <c r="EC10" t="s">
-        <v>193</v>
-      </c>
-      <c r="EG10" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="EH10" t="s">
-        <v>194</v>
-      </c>
-      <c r="EI10">
+        <v>188</v>
+      </c>
+      <c r="EI10" t="s">
+        <v>198</v>
+      </c>
+      <c r="EJ10">
         <v>96</v>
       </c>
-      <c r="EJ10" t="s">
-        <v>195</v>
-      </c>
-      <c r="EK10">
-        <v>48</v>
-      </c>
-      <c r="EL10" t="s">
-        <v>179</v>
-      </c>
-      <c r="EM10">
-        <v>10</v>
+      <c r="EK10" t="s">
+        <v>199</v>
+      </c>
+      <c r="EL10">
+        <v>12</v>
+      </c>
+      <c r="EM10" t="s">
+        <v>181</v>
       </c>
       <c r="EN10">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="EO10">
+        <v>0</v>
+      </c>
+      <c r="EP10">
         <v>3600</v>
       </c>
-      <c r="EP10">
+      <c r="EQ10">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:146">
+    <row r="11" spans="1:147">
       <c r="A11" s="1">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F11">
         <v>3</v>
@@ -4880,7 +4874,7 @@
         <v>5527000</v>
       </c>
       <c r="P11" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q11" t="s">
         <v>162</v>
@@ -4961,10 +4955,10 @@
         <v>1</v>
       </c>
       <c r="AS11">
-        <v>2400000</v>
+        <v>1800000</v>
       </c>
       <c r="AT11" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="AU11">
         <v>55</v>
@@ -4985,16 +4979,31 @@
         <v>90</v>
       </c>
       <c r="BA11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC11" t="b">
         <v>1</v>
       </c>
+      <c r="BD11">
+        <v>8100</v>
+      </c>
+      <c r="BE11" t="s">
+        <v>179</v>
+      </c>
+      <c r="BF11">
+        <v>-20</v>
+      </c>
+      <c r="BG11">
+        <v>50</v>
+      </c>
+      <c r="BH11" t="b">
+        <v>1</v>
+      </c>
       <c r="BI11" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="BJ11">
         <v>2</v>
@@ -5003,38 +5012,29 @@
         <v>9</v>
       </c>
       <c r="BL11" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="BM11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BN11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BO11" t="b">
         <v>1</v>
       </c>
-      <c r="BP11">
-        <v>3300</v>
-      </c>
-      <c r="BQ11" t="s">
+      <c r="BS11" t="s">
+        <v>187</v>
+      </c>
+      <c r="BT11">
+        <v>2</v>
+      </c>
+      <c r="BU11">
+        <v>9</v>
+      </c>
+      <c r="BV11" t="s">
         <v>181</v>
       </c>
-      <c r="BR11" t="b">
-        <v>1</v>
-      </c>
-      <c r="BS11" t="s">
-        <v>183</v>
-      </c>
-      <c r="BT11">
-        <v>2</v>
-      </c>
-      <c r="BU11">
-        <v>9</v>
-      </c>
-      <c r="BV11" t="s">
-        <v>179</v>
-      </c>
       <c r="BW11">
         <v>0</v>
       </c>
@@ -5045,7 +5045,7 @@
         <v>1</v>
       </c>
       <c r="CC11" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="CD11">
         <v>2</v>
@@ -5054,7 +5054,7 @@
         <v>9</v>
       </c>
       <c r="CF11" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="CG11">
         <v>0</v>
@@ -5066,7 +5066,7 @@
         <v>1</v>
       </c>
       <c r="CL11" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="CM11">
         <v>0</v>
@@ -5078,7 +5078,7 @@
         <v>1</v>
       </c>
       <c r="DJ11" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="DK11">
         <v>0.05</v>
@@ -5093,10 +5093,10 @@
         <v>8.5</v>
       </c>
       <c r="DO11" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="DP11" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="DQ11">
         <v>0</v>
@@ -5105,10 +5105,10 @@
         <v>0</v>
       </c>
       <c r="DS11" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="DZ11" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="EA11">
         <v>0</v>
@@ -5117,36 +5117,36 @@
         <v>0</v>
       </c>
       <c r="EC11" t="s">
-        <v>193</v>
-      </c>
-      <c r="EG11" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="EH11" t="s">
-        <v>194</v>
-      </c>
-      <c r="EI11">
+        <v>188</v>
+      </c>
+      <c r="EI11" t="s">
+        <v>198</v>
+      </c>
+      <c r="EJ11">
         <v>96</v>
       </c>
-      <c r="EJ11" t="s">
-        <v>195</v>
-      </c>
-      <c r="EK11">
-        <v>60</v>
-      </c>
-      <c r="EL11" t="s">
-        <v>179</v>
-      </c>
-      <c r="EM11">
-        <v>30</v>
+      <c r="EK11" t="s">
+        <v>199</v>
+      </c>
+      <c r="EL11">
+        <v>36</v>
+      </c>
+      <c r="EM11" t="s">
+        <v>181</v>
       </c>
       <c r="EN11">
         <v>0</v>
       </c>
       <c r="EO11">
+        <v>0</v>
+      </c>
+      <c r="EP11">
         <v>3600</v>
       </c>
-      <c r="EP11">
+      <c r="EQ11">
         <v>0</v>
       </c>
     </row>
@@ -5157,10 +5157,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:ES17"/>
+  <dimension ref="A1:ET17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:149">
+    <row r="1" spans="1:150">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5174,13 +5174,13 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>4</v>
@@ -5605,28 +5605,31 @@
       <c r="ES1" s="1" t="s">
         <v>144</v>
       </c>
+      <c r="ET1" s="1" t="s">
+        <v>145</v>
+      </c>
     </row>
-    <row r="2" spans="1:149">
+    <row r="2" spans="1:150">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="F2" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="G2" t="b">
         <v>0</v>
       </c>
       <c r="H2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J2">
-        <v>800</v>
+        <v>420</v>
       </c>
       <c r="K2">
         <v>1</v>
@@ -5635,7 +5638,7 @@
         <v>2.6</v>
       </c>
       <c r="M2">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="N2">
         <v>1</v>
@@ -5650,7 +5653,7 @@
         <v>1</v>
       </c>
       <c r="R2">
-        <v>15173000</v>
+        <v>12408000</v>
       </c>
       <c r="T2" t="s">
         <v>162</v>
@@ -5695,7 +5698,7 @@
         <v>1</v>
       </c>
       <c r="AK2">
-        <v>120000000</v>
+        <v>23100000</v>
       </c>
       <c r="AN2" t="s">
         <v>162</v>
@@ -5722,7 +5725,7 @@
         <v>1</v>
       </c>
       <c r="AV2">
-        <v>22400</v>
+        <v>12600</v>
       </c>
       <c r="AY2" t="s">
         <v>162</v>
@@ -5764,7 +5767,7 @@
         <v>1</v>
       </c>
       <c r="BL2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="BM2">
         <v>2</v>
@@ -5773,7 +5776,7 @@
         <v>9</v>
       </c>
       <c r="BO2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="BP2">
         <v>1</v>
@@ -5785,46 +5788,46 @@
         <v>1</v>
       </c>
       <c r="BS2">
-        <v>9000</v>
+        <v>8300</v>
       </c>
       <c r="BT2" t="s">
+        <v>184</v>
+      </c>
+      <c r="BU2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BV2" t="s">
+        <v>187</v>
+      </c>
+      <c r="BW2">
+        <v>2</v>
+      </c>
+      <c r="BX2">
+        <v>9</v>
+      </c>
+      <c r="BY2" t="s">
+        <v>181</v>
+      </c>
+      <c r="BZ2">
+        <v>1</v>
+      </c>
+      <c r="CA2">
+        <v>1</v>
+      </c>
+      <c r="CB2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CC2">
+        <v>1200</v>
+      </c>
+      <c r="CD2" t="s">
         <v>233</v>
       </c>
-      <c r="BU2" t="b">
-        <v>1</v>
-      </c>
-      <c r="BV2" t="s">
-        <v>183</v>
-      </c>
-      <c r="BW2">
-        <v>2</v>
-      </c>
-      <c r="BX2">
-        <v>9</v>
-      </c>
-      <c r="BY2" t="s">
-        <v>179</v>
-      </c>
-      <c r="BZ2">
-        <v>1</v>
-      </c>
-      <c r="CA2">
-        <v>1</v>
-      </c>
-      <c r="CB2" t="b">
-        <v>1</v>
-      </c>
-      <c r="CC2">
-        <v>1800</v>
-      </c>
-      <c r="CD2" t="s">
-        <v>234</v>
-      </c>
       <c r="CE2" t="b">
         <v>0</v>
       </c>
       <c r="CF2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="CG2">
         <v>2</v>
@@ -5833,7 +5836,7 @@
         <v>9</v>
       </c>
       <c r="CI2" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="CJ2">
         <v>0</v>
@@ -5845,7 +5848,7 @@
         <v>1</v>
       </c>
       <c r="CO2" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="CP2">
         <v>0</v>
@@ -5857,10 +5860,10 @@
         <v>1</v>
       </c>
       <c r="DR2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="DS2" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="DT2">
         <v>1</v>
@@ -5872,10 +5875,10 @@
         <v>1</v>
       </c>
       <c r="DW2">
-        <v>15000</v>
+        <v>12000</v>
       </c>
       <c r="DX2">
-        <v>15000</v>
+        <v>12000</v>
       </c>
       <c r="DY2">
         <v>0.95</v>
@@ -5890,7 +5893,7 @@
         <v>0</v>
       </c>
       <c r="EC2" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="ED2">
         <v>1</v>
@@ -5902,66 +5905,69 @@
         <v>1</v>
       </c>
       <c r="EG2">
-        <v>120000</v>
+        <v>12000</v>
       </c>
       <c r="EH2">
+        <v>23000</v>
+      </c>
+      <c r="EI2">
         <v>0.95</v>
       </c>
-      <c r="EI2">
+      <c r="EJ2">
         <v>0.1</v>
       </c>
-      <c r="EJ2" t="s">
-        <v>184</v>
-      </c>
       <c r="EK2" t="s">
-        <v>194</v>
-      </c>
-      <c r="EL2">
+        <v>188</v>
+      </c>
+      <c r="EL2" t="s">
+        <v>198</v>
+      </c>
+      <c r="EM2">
         <v>96</v>
       </c>
-      <c r="EM2" t="s">
-        <v>195</v>
-      </c>
-      <c r="EN2">
-        <v>24</v>
-      </c>
-      <c r="EO2" t="s">
-        <v>179</v>
-      </c>
-      <c r="EP2">
-        <v>10</v>
+      <c r="EN2" t="s">
+        <v>199</v>
+      </c>
+      <c r="EO2">
+        <v>60</v>
+      </c>
+      <c r="EP2" t="s">
+        <v>181</v>
       </c>
       <c r="EQ2">
         <v>0</v>
       </c>
       <c r="ER2">
+        <v>0</v>
+      </c>
+      <c r="ES2">
         <v>3600</v>
       </c>
-      <c r="ES2">
+      <c r="ET2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:149">
+    <row r="3" spans="1:150">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="F3" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="G3" t="b">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="K3">
         <v>1</v>
@@ -5970,7 +5976,7 @@
         <v>2.6</v>
       </c>
       <c r="M3">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="N3">
         <v>1</v>
@@ -5988,7 +5994,7 @@
         <v>1158000</v>
       </c>
       <c r="S3" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="T3" t="s">
         <v>162</v>
@@ -6033,10 +6039,10 @@
         <v>1</v>
       </c>
       <c r="AK3">
-        <v>15000000</v>
+        <v>3850000</v>
       </c>
       <c r="AL3" t="s">
-        <v>226</v>
+        <v>167</v>
       </c>
       <c r="AM3">
         <v>55</v>
@@ -6066,10 +6072,10 @@
         <v>1</v>
       </c>
       <c r="AV3">
-        <v>2800</v>
+        <v>2100</v>
       </c>
       <c r="AW3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AX3">
         <v>55</v>
@@ -6099,7 +6105,7 @@
         <v>1</v>
       </c>
       <c r="BL3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="BM3">
         <v>2</v>
@@ -6108,7 +6114,7 @@
         <v>9</v>
       </c>
       <c r="BO3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="BP3">
         <v>0</v>
@@ -6120,7 +6126,7 @@
         <v>1</v>
       </c>
       <c r="BV3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="BW3">
         <v>2</v>
@@ -6129,7 +6135,7 @@
         <v>9</v>
       </c>
       <c r="BY3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="BZ3">
         <v>0</v>
@@ -6141,7 +6147,7 @@
         <v>1</v>
       </c>
       <c r="CF3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="CG3">
         <v>2</v>
@@ -6150,7 +6156,7 @@
         <v>9</v>
       </c>
       <c r="CI3" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="CJ3">
         <v>0</v>
@@ -6162,7 +6168,7 @@
         <v>1</v>
       </c>
       <c r="CO3" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="CP3">
         <v>0</v>
@@ -6189,10 +6195,10 @@
         <v>8</v>
       </c>
       <c r="DR3" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="DS3" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="DT3">
         <v>0</v>
@@ -6204,7 +6210,7 @@
         <v>1</v>
       </c>
       <c r="EC3" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="ED3">
         <v>0</v>
@@ -6215,58 +6221,58 @@
       <c r="EF3" t="b">
         <v>1</v>
       </c>
-      <c r="EJ3" t="s">
-        <v>184</v>
-      </c>
       <c r="EK3" t="s">
-        <v>194</v>
-      </c>
-      <c r="EL3">
+        <v>188</v>
+      </c>
+      <c r="EL3" t="s">
+        <v>198</v>
+      </c>
+      <c r="EM3">
         <v>96</v>
       </c>
-      <c r="EM3" t="s">
-        <v>195</v>
-      </c>
-      <c r="EN3">
-        <v>36</v>
-      </c>
-      <c r="EO3" t="s">
-        <v>179</v>
-      </c>
-      <c r="EP3">
+      <c r="EN3" t="s">
+        <v>199</v>
+      </c>
+      <c r="EO3">
+        <v>48</v>
+      </c>
+      <c r="EP3" t="s">
+        <v>181</v>
+      </c>
+      <c r="EQ3">
         <v>20</v>
       </c>
-      <c r="EQ3">
-        <v>0</v>
-      </c>
       <c r="ER3">
+        <v>0</v>
+      </c>
+      <c r="ES3">
         <v>3600</v>
       </c>
-      <c r="ES3">
+      <c r="ET3">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:149">
+    <row r="4" spans="1:150">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="F4" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="G4" t="b">
         <v>0</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J4">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="K4">
         <v>1</v>
@@ -6275,7 +6281,7 @@
         <v>2.6</v>
       </c>
       <c r="M4">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="N4">
         <v>1</v>
@@ -6290,10 +6296,10 @@
         <v>1</v>
       </c>
       <c r="R4">
-        <v>1546000</v>
+        <v>2455000</v>
       </c>
       <c r="S4" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="T4" t="s">
         <v>162</v>
@@ -6338,13 +6344,13 @@
         <v>1</v>
       </c>
       <c r="AK4">
-        <v>15000000</v>
+        <v>3850000</v>
       </c>
       <c r="AL4" t="s">
-        <v>227</v>
+        <v>169</v>
       </c>
       <c r="AM4">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="AN4" t="s">
         <v>162</v>
@@ -6371,10 +6377,10 @@
         <v>1</v>
       </c>
       <c r="AV4">
-        <v>3200</v>
+        <v>1800</v>
       </c>
       <c r="AW4" t="s">
-        <v>230</v>
+        <v>177</v>
       </c>
       <c r="AX4">
         <v>55</v>
@@ -6404,7 +6410,7 @@
         <v>1</v>
       </c>
       <c r="BL4" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="BM4">
         <v>2</v>
@@ -6413,7 +6419,7 @@
         <v>9</v>
       </c>
       <c r="BO4" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="BP4">
         <v>0</v>
@@ -6425,7 +6431,7 @@
         <v>1</v>
       </c>
       <c r="BV4" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="BW4">
         <v>2</v>
@@ -6434,7 +6440,7 @@
         <v>9</v>
       </c>
       <c r="BY4" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="BZ4">
         <v>0</v>
@@ -6446,7 +6452,7 @@
         <v>1</v>
       </c>
       <c r="CF4" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="CG4">
         <v>2</v>
@@ -6455,7 +6461,7 @@
         <v>9</v>
       </c>
       <c r="CI4" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="CJ4">
         <v>0</v>
@@ -6467,49 +6473,19 @@
         <v>1</v>
       </c>
       <c r="CO4" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="CP4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CR4" t="b">
         <v>1</v>
       </c>
-      <c r="CS4" t="s">
-        <v>190</v>
-      </c>
-      <c r="CT4">
-        <v>50000</v>
-      </c>
-      <c r="CU4">
-        <v>15000</v>
-      </c>
-      <c r="CV4">
-        <v>7200</v>
-      </c>
-      <c r="CW4">
-        <v>7200</v>
-      </c>
-      <c r="CX4">
-        <v>50000</v>
-      </c>
-      <c r="CY4">
-        <v>0.9</v>
-      </c>
-      <c r="CZ4">
-        <v>0.8</v>
-      </c>
-      <c r="DA4" t="b">
-        <v>0</v>
-      </c>
-      <c r="DB4" t="b">
-        <v>0</v>
-      </c>
       <c r="DM4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="DN4">
         <v>0.05</v>
@@ -6524,10 +6500,10 @@
         <v>8</v>
       </c>
       <c r="DR4" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="DS4" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="DT4">
         <v>0</v>
@@ -6539,7 +6515,7 @@
         <v>1</v>
       </c>
       <c r="EC4" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="ED4">
         <v>0</v>
@@ -6550,58 +6526,58 @@
       <c r="EF4" t="b">
         <v>1</v>
       </c>
-      <c r="EJ4" t="s">
-        <v>184</v>
-      </c>
       <c r="EK4" t="s">
-        <v>194</v>
-      </c>
-      <c r="EL4">
+        <v>188</v>
+      </c>
+      <c r="EL4" t="s">
+        <v>198</v>
+      </c>
+      <c r="EM4">
         <v>96</v>
       </c>
-      <c r="EM4" t="s">
-        <v>195</v>
-      </c>
-      <c r="EN4">
+      <c r="EN4" t="s">
+        <v>199</v>
+      </c>
+      <c r="EO4">
         <v>12</v>
       </c>
-      <c r="EO4" t="s">
-        <v>179</v>
-      </c>
-      <c r="EP4">
-        <v>0</v>
+      <c r="EP4" t="s">
+        <v>181</v>
       </c>
       <c r="EQ4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="ER4">
+        <v>0</v>
+      </c>
+      <c r="ES4">
         <v>3600</v>
       </c>
-      <c r="ES4">
+      <c r="ET4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:149">
+    <row r="5" spans="1:150">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="F5" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G5" t="b">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J5">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="K5">
         <v>1</v>
@@ -6610,7 +6586,7 @@
         <v>2.6</v>
       </c>
       <c r="M5">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="N5">
         <v>1</v>
@@ -6625,10 +6601,10 @@
         <v>1</v>
       </c>
       <c r="R5">
-        <v>3296000</v>
+        <v>1546000</v>
       </c>
       <c r="S5" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="T5" t="s">
         <v>162</v>
@@ -6673,10 +6649,10 @@
         <v>1</v>
       </c>
       <c r="AK5">
-        <v>15000000</v>
+        <v>3850000</v>
       </c>
       <c r="AL5" t="s">
-        <v>228</v>
+        <v>169</v>
       </c>
       <c r="AM5">
         <v>55</v>
@@ -6706,10 +6682,10 @@
         <v>1</v>
       </c>
       <c r="AV5">
-        <v>2800</v>
+        <v>2100</v>
       </c>
       <c r="AW5" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="AX5">
         <v>55</v>
@@ -6739,7 +6715,7 @@
         <v>1</v>
       </c>
       <c r="BL5" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="BM5">
         <v>2</v>
@@ -6748,7 +6724,7 @@
         <v>9</v>
       </c>
       <c r="BO5" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="BP5">
         <v>0</v>
@@ -6760,7 +6736,7 @@
         <v>1</v>
       </c>
       <c r="BV5" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="BW5">
         <v>2</v>
@@ -6769,7 +6745,7 @@
         <v>9</v>
       </c>
       <c r="BY5" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="BZ5">
         <v>0</v>
@@ -6781,7 +6757,7 @@
         <v>1</v>
       </c>
       <c r="CF5" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="CG5">
         <v>2</v>
@@ -6790,7 +6766,7 @@
         <v>9</v>
       </c>
       <c r="CI5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="CJ5">
         <v>0</v>
@@ -6802,19 +6778,79 @@
         <v>1</v>
       </c>
       <c r="CO5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="CP5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CR5" t="b">
         <v>1</v>
       </c>
+      <c r="CS5" t="s">
+        <v>234</v>
+      </c>
+      <c r="CT5">
+        <v>75000</v>
+      </c>
+      <c r="CU5">
+        <v>20000</v>
+      </c>
+      <c r="CV5">
+        <v>7200</v>
+      </c>
+      <c r="CW5">
+        <v>11000</v>
+      </c>
+      <c r="CX5">
+        <v>100000</v>
+      </c>
+      <c r="CY5">
+        <v>0.9</v>
+      </c>
+      <c r="CZ5">
+        <v>0.8</v>
+      </c>
+      <c r="DA5" t="b">
+        <v>0</v>
+      </c>
+      <c r="DB5" t="b">
+        <v>0</v>
+      </c>
+      <c r="DC5" t="s">
+        <v>191</v>
+      </c>
+      <c r="DD5">
+        <v>50000</v>
+      </c>
+      <c r="DE5">
+        <v>15000</v>
+      </c>
+      <c r="DF5">
+        <v>7200</v>
+      </c>
+      <c r="DG5">
+        <v>7200</v>
+      </c>
+      <c r="DH5">
+        <v>50000</v>
+      </c>
+      <c r="DI5">
+        <v>0.9</v>
+      </c>
+      <c r="DJ5">
+        <v>0.8</v>
+      </c>
+      <c r="DK5" t="b">
+        <v>0</v>
+      </c>
+      <c r="DL5" t="b">
+        <v>0</v>
+      </c>
       <c r="DM5" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="DN5">
         <v>0.05</v>
@@ -6829,10 +6865,10 @@
         <v>8</v>
       </c>
       <c r="DR5" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="DS5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="DT5">
         <v>0</v>
@@ -6844,7 +6880,7 @@
         <v>1</v>
       </c>
       <c r="EC5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="ED5">
         <v>0</v>
@@ -6855,58 +6891,58 @@
       <c r="EF5" t="b">
         <v>1</v>
       </c>
-      <c r="EJ5" t="s">
-        <v>184</v>
-      </c>
       <c r="EK5" t="s">
-        <v>194</v>
-      </c>
-      <c r="EL5">
+        <v>188</v>
+      </c>
+      <c r="EL5" t="s">
+        <v>198</v>
+      </c>
+      <c r="EM5">
         <v>96</v>
       </c>
-      <c r="EM5" t="s">
-        <v>195</v>
-      </c>
-      <c r="EN5">
-        <v>24</v>
-      </c>
-      <c r="EO5" t="s">
-        <v>179</v>
-      </c>
-      <c r="EP5">
-        <v>0</v>
+      <c r="EN5" t="s">
+        <v>199</v>
+      </c>
+      <c r="EO5">
+        <v>12</v>
+      </c>
+      <c r="EP5" t="s">
+        <v>181</v>
       </c>
       <c r="EQ5">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="ER5">
+        <v>0</v>
+      </c>
+      <c r="ES5">
         <v>3600</v>
       </c>
-      <c r="ES5">
+      <c r="ET5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:149">
+    <row r="6" spans="1:150">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="F6" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="G6" t="b">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J6">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -6915,7 +6951,7 @@
         <v>2.6</v>
       </c>
       <c r="M6">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="N6">
         <v>1</v>
@@ -6930,10 +6966,10 @@
         <v>1</v>
       </c>
       <c r="R6">
-        <v>1720000</v>
+        <v>2455000</v>
       </c>
       <c r="S6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="T6" t="s">
         <v>162</v>
@@ -6978,13 +7014,13 @@
         <v>1</v>
       </c>
       <c r="AK6">
-        <v>15000000</v>
+        <v>3850000</v>
       </c>
       <c r="AL6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AM6">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="AN6" t="s">
         <v>162</v>
@@ -7011,10 +7047,10 @@
         <v>1</v>
       </c>
       <c r="AV6">
-        <v>2800</v>
+        <v>1800</v>
       </c>
       <c r="AW6" t="s">
-        <v>230</v>
+        <v>173</v>
       </c>
       <c r="AX6">
         <v>55</v>
@@ -7044,7 +7080,7 @@
         <v>1</v>
       </c>
       <c r="BL6" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="BM6">
         <v>2</v>
@@ -7053,7 +7089,7 @@
         <v>9</v>
       </c>
       <c r="BO6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="BP6">
         <v>0</v>
@@ -7065,7 +7101,7 @@
         <v>1</v>
       </c>
       <c r="BV6" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="BW6">
         <v>2</v>
@@ -7074,7 +7110,7 @@
         <v>9</v>
       </c>
       <c r="BY6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="BZ6">
         <v>0</v>
@@ -7086,7 +7122,7 @@
         <v>1</v>
       </c>
       <c r="CF6" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="CG6">
         <v>2</v>
@@ -7095,7 +7131,7 @@
         <v>9</v>
       </c>
       <c r="CI6" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="CJ6">
         <v>0</v>
@@ -7107,7 +7143,7 @@
         <v>1</v>
       </c>
       <c r="CO6" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="CP6">
         <v>0</v>
@@ -7119,7 +7155,7 @@
         <v>1</v>
       </c>
       <c r="DM6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="DN6">
         <v>0.05</v>
@@ -7134,10 +7170,10 @@
         <v>8</v>
       </c>
       <c r="DR6" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="DS6" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="DT6">
         <v>0</v>
@@ -7149,7 +7185,7 @@
         <v>1</v>
       </c>
       <c r="EC6" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="ED6">
         <v>0</v>
@@ -7160,58 +7196,58 @@
       <c r="EF6" t="b">
         <v>1</v>
       </c>
-      <c r="EJ6" t="s">
-        <v>184</v>
-      </c>
       <c r="EK6" t="s">
-        <v>194</v>
-      </c>
-      <c r="EL6">
+        <v>188</v>
+      </c>
+      <c r="EL6" t="s">
+        <v>198</v>
+      </c>
+      <c r="EM6">
         <v>96</v>
       </c>
-      <c r="EM6" t="s">
-        <v>195</v>
-      </c>
-      <c r="EN6">
-        <v>12</v>
-      </c>
-      <c r="EO6" t="s">
-        <v>179</v>
-      </c>
-      <c r="EP6">
-        <v>10</v>
+      <c r="EN6" t="s">
+        <v>199</v>
+      </c>
+      <c r="EO6">
+        <v>24</v>
+      </c>
+      <c r="EP6" t="s">
+        <v>181</v>
       </c>
       <c r="EQ6">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="ER6">
+        <v>0</v>
+      </c>
+      <c r="ES6">
         <v>3600</v>
       </c>
-      <c r="ES6">
+      <c r="ET6">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:149">
+    <row r="7" spans="1:150">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="F7" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="G7" t="b">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J7">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="K7">
         <v>1</v>
@@ -7220,7 +7256,7 @@
         <v>2.6</v>
       </c>
       <c r="M7">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="N7">
         <v>1</v>
@@ -7235,10 +7271,10 @@
         <v>1</v>
       </c>
       <c r="R7">
-        <v>1266000</v>
+        <v>2262000</v>
       </c>
       <c r="S7" t="s">
-        <v>220</v>
+        <v>161</v>
       </c>
       <c r="T7" t="s">
         <v>162</v>
@@ -7283,10 +7319,10 @@
         <v>1</v>
       </c>
       <c r="AK7">
-        <v>15000000</v>
+        <v>3850000</v>
       </c>
       <c r="AL7" t="s">
-        <v>229</v>
+        <v>169</v>
       </c>
       <c r="AM7">
         <v>55</v>
@@ -7316,10 +7352,10 @@
         <v>1</v>
       </c>
       <c r="AV7">
-        <v>3200</v>
+        <v>2400</v>
       </c>
       <c r="AW7" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="AX7">
         <v>55</v>
@@ -7349,7 +7385,7 @@
         <v>1</v>
       </c>
       <c r="BL7" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="BM7">
         <v>2</v>
@@ -7358,7 +7394,7 @@
         <v>9</v>
       </c>
       <c r="BO7" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="BP7">
         <v>0</v>
@@ -7370,7 +7406,7 @@
         <v>1</v>
       </c>
       <c r="BV7" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="BW7">
         <v>2</v>
@@ -7379,7 +7415,7 @@
         <v>9</v>
       </c>
       <c r="BY7" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="BZ7">
         <v>0</v>
@@ -7391,7 +7427,7 @@
         <v>1</v>
       </c>
       <c r="CF7" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="CG7">
         <v>2</v>
@@ -7400,7 +7436,7 @@
         <v>9</v>
       </c>
       <c r="CI7" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="CJ7">
         <v>0</v>
@@ -7412,7 +7448,7 @@
         <v>1</v>
       </c>
       <c r="CO7" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="CP7">
         <v>0</v>
@@ -7424,7 +7460,7 @@
         <v>1</v>
       </c>
       <c r="DM7" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="DN7">
         <v>0.05</v>
@@ -7439,10 +7475,10 @@
         <v>8</v>
       </c>
       <c r="DR7" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="DS7" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="DT7">
         <v>0</v>
@@ -7454,7 +7490,7 @@
         <v>1</v>
       </c>
       <c r="EC7" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="ED7">
         <v>0</v>
@@ -7465,58 +7501,58 @@
       <c r="EF7" t="b">
         <v>1</v>
       </c>
-      <c r="EJ7" t="s">
-        <v>184</v>
-      </c>
       <c r="EK7" t="s">
-        <v>194</v>
-      </c>
-      <c r="EL7">
+        <v>188</v>
+      </c>
+      <c r="EL7" t="s">
+        <v>198</v>
+      </c>
+      <c r="EM7">
         <v>96</v>
       </c>
-      <c r="EM7" t="s">
-        <v>195</v>
-      </c>
-      <c r="EN7">
-        <v>48</v>
-      </c>
-      <c r="EO7" t="s">
-        <v>179</v>
-      </c>
-      <c r="EP7">
-        <v>0</v>
+      <c r="EN7" t="s">
+        <v>199</v>
+      </c>
+      <c r="EO7">
+        <v>12</v>
+      </c>
+      <c r="EP7" t="s">
+        <v>181</v>
       </c>
       <c r="EQ7">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="ER7">
+        <v>0</v>
+      </c>
+      <c r="ES7">
         <v>3600</v>
       </c>
-      <c r="ES7">
+      <c r="ET7">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:149">
+    <row r="8" spans="1:150">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="F8" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="G8" t="b">
         <v>0</v>
       </c>
       <c r="H8">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J8">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="K8">
         <v>1</v>
@@ -7525,7 +7561,7 @@
         <v>2.6</v>
       </c>
       <c r="M8">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="N8">
         <v>1</v>
@@ -7540,10 +7576,10 @@
         <v>1</v>
       </c>
       <c r="R8">
-        <v>2012000</v>
+        <v>2532000</v>
       </c>
       <c r="S8" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="T8" t="s">
         <v>162</v>
@@ -7588,13 +7624,13 @@
         <v>1</v>
       </c>
       <c r="AK8">
-        <v>15000000</v>
+        <v>3850000</v>
       </c>
       <c r="AL8" t="s">
-        <v>228</v>
+        <v>164</v>
       </c>
       <c r="AM8">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="AN8" t="s">
         <v>162</v>
@@ -7624,7 +7660,7 @@
         <v>2400</v>
       </c>
       <c r="AW8" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AX8">
         <v>55</v>
@@ -7654,7 +7690,7 @@
         <v>1</v>
       </c>
       <c r="BL8" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="BM8">
         <v>2</v>
@@ -7663,7 +7699,7 @@
         <v>9</v>
       </c>
       <c r="BO8" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="BP8">
         <v>0</v>
@@ -7675,7 +7711,7 @@
         <v>1</v>
       </c>
       <c r="BV8" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="BW8">
         <v>2</v>
@@ -7684,7 +7720,7 @@
         <v>9</v>
       </c>
       <c r="BY8" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="BZ8">
         <v>0</v>
@@ -7696,7 +7732,7 @@
         <v>1</v>
       </c>
       <c r="CF8" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="CG8">
         <v>2</v>
@@ -7705,7 +7741,7 @@
         <v>9</v>
       </c>
       <c r="CI8" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="CJ8">
         <v>0</v>
@@ -7717,7 +7753,7 @@
         <v>1</v>
       </c>
       <c r="CO8" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="CP8">
         <v>0</v>
@@ -7729,7 +7765,7 @@
         <v>1</v>
       </c>
       <c r="DM8" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="DN8">
         <v>0.05</v>
@@ -7744,10 +7780,10 @@
         <v>8</v>
       </c>
       <c r="DR8" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="DS8" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="DT8">
         <v>0</v>
@@ -7759,7 +7795,7 @@
         <v>1</v>
       </c>
       <c r="EC8" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="ED8">
         <v>0</v>
@@ -7770,46 +7806,46 @@
       <c r="EF8" t="b">
         <v>1</v>
       </c>
-      <c r="EJ8" t="s">
-        <v>184</v>
-      </c>
       <c r="EK8" t="s">
-        <v>194</v>
-      </c>
-      <c r="EL8">
+        <v>188</v>
+      </c>
+      <c r="EL8" t="s">
+        <v>198</v>
+      </c>
+      <c r="EM8">
         <v>96</v>
       </c>
-      <c r="EM8" t="s">
-        <v>195</v>
-      </c>
-      <c r="EN8">
-        <v>12</v>
-      </c>
-      <c r="EO8" t="s">
-        <v>179</v>
-      </c>
-      <c r="EP8">
-        <v>0</v>
+      <c r="EN8" t="s">
+        <v>199</v>
+      </c>
+      <c r="EO8">
+        <v>60</v>
+      </c>
+      <c r="EP8" t="s">
+        <v>181</v>
       </c>
       <c r="EQ8">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="ER8">
+        <v>0</v>
+      </c>
+      <c r="ES8">
         <v>3600</v>
       </c>
-      <c r="ES8">
+      <c r="ET8">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:149">
+    <row r="9" spans="1:150">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="F9" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="G9" t="b">
         <v>0</v>
@@ -7821,7 +7857,7 @@
         <v>4</v>
       </c>
       <c r="J9">
-        <v>100</v>
+        <v>800</v>
       </c>
       <c r="K9">
         <v>1</v>
@@ -7836,19 +7872,16 @@
         <v>1</v>
       </c>
       <c r="O9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="b">
         <v>1</v>
       </c>
       <c r="R9">
-        <v>2455000</v>
-      </c>
-      <c r="S9" t="s">
-        <v>222</v>
+        <v>14977000</v>
       </c>
       <c r="T9" t="s">
         <v>162</v>
@@ -7884,22 +7917,16 @@
         <v>163</v>
       </c>
       <c r="AH9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="b">
         <v>1</v>
       </c>
       <c r="AK9">
-        <v>15000000</v>
-      </c>
-      <c r="AL9" t="s">
-        <v>229</v>
-      </c>
-      <c r="AM9">
-        <v>35</v>
+        <v>120000000</v>
       </c>
       <c r="AN9" t="s">
         <v>162</v>
@@ -7917,22 +7944,16 @@
         <v>90</v>
       </c>
       <c r="AS9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU9" t="b">
         <v>1</v>
       </c>
       <c r="AV9">
-        <v>2400</v>
-      </c>
-      <c r="AW9" t="s">
-        <v>171</v>
-      </c>
-      <c r="AX9">
-        <v>55</v>
+        <v>22400</v>
       </c>
       <c r="AY9" t="s">
         <v>162</v>
@@ -7950,16 +7971,31 @@
         <v>90</v>
       </c>
       <c r="BD9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF9" t="b">
         <v>1</v>
       </c>
+      <c r="BG9">
+        <v>22000</v>
+      </c>
+      <c r="BH9" t="s">
+        <v>232</v>
+      </c>
+      <c r="BI9">
+        <v>0</v>
+      </c>
+      <c r="BJ9">
+        <v>40</v>
+      </c>
+      <c r="BK9" t="b">
+        <v>1</v>
+      </c>
       <c r="BL9" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="BM9">
         <v>2</v>
@@ -7968,7 +8004,7 @@
         <v>9</v>
       </c>
       <c r="BO9" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="BP9">
         <v>0</v>
@@ -7980,7 +8016,7 @@
         <v>1</v>
       </c>
       <c r="BV9" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="BW9">
         <v>2</v>
@@ -7989,19 +8025,28 @@
         <v>9</v>
       </c>
       <c r="BY9" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="BZ9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CB9" t="b">
         <v>1</v>
       </c>
+      <c r="CC9">
+        <v>1800</v>
+      </c>
+      <c r="CD9" t="s">
+        <v>233</v>
+      </c>
+      <c r="CE9" t="b">
+        <v>0</v>
+      </c>
       <c r="CF9" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="CG9">
         <v>2</v>
@@ -8010,7 +8055,7 @@
         <v>9</v>
       </c>
       <c r="CI9" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="CJ9">
         <v>0</v>
@@ -8022,129 +8067,114 @@
         <v>1</v>
       </c>
       <c r="CO9" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="CP9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CR9" t="b">
         <v>1</v>
       </c>
-      <c r="CS9" t="s">
-        <v>186</v>
-      </c>
-      <c r="CT9">
-        <v>75000</v>
-      </c>
-      <c r="CU9">
-        <v>20000</v>
-      </c>
-      <c r="CV9">
-        <v>7200</v>
-      </c>
-      <c r="CW9">
-        <v>11000</v>
-      </c>
-      <c r="CX9">
-        <v>100000</v>
-      </c>
-      <c r="CY9">
-        <v>0.9</v>
-      </c>
-      <c r="CZ9">
-        <v>0.8</v>
-      </c>
-      <c r="DA9" t="b">
-        <v>0</v>
-      </c>
-      <c r="DB9" t="b">
-        <v>0</v>
-      </c>
-      <c r="DM9" t="s">
-        <v>241</v>
-      </c>
-      <c r="DN9">
-        <v>0.05</v>
-      </c>
-      <c r="DO9">
-        <v>0.5</v>
-      </c>
-      <c r="DP9">
-        <v>0.8</v>
-      </c>
-      <c r="DQ9">
-        <v>8</v>
-      </c>
       <c r="DR9" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="DS9" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="DT9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DV9" t="b">
         <v>1</v>
       </c>
+      <c r="DW9">
+        <v>15000</v>
+      </c>
+      <c r="DX9">
+        <v>15000</v>
+      </c>
+      <c r="DY9">
+        <v>0.95</v>
+      </c>
+      <c r="DZ9">
+        <v>0.1</v>
+      </c>
+      <c r="EA9" t="b">
+        <v>0</v>
+      </c>
+      <c r="EB9" t="b">
+        <v>0</v>
+      </c>
       <c r="EC9" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="ED9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EE9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EF9" t="b">
         <v>1</v>
       </c>
-      <c r="EJ9" t="s">
-        <v>184</v>
+      <c r="EG9">
+        <v>60000</v>
+      </c>
+      <c r="EH9">
+        <v>120000</v>
+      </c>
+      <c r="EI9">
+        <v>0.95</v>
+      </c>
+      <c r="EJ9">
+        <v>0.1</v>
       </c>
       <c r="EK9" t="s">
-        <v>194</v>
-      </c>
-      <c r="EL9">
+        <v>188</v>
+      </c>
+      <c r="EL9" t="s">
+        <v>198</v>
+      </c>
+      <c r="EM9">
         <v>96</v>
       </c>
-      <c r="EM9" t="s">
-        <v>195</v>
-      </c>
-      <c r="EN9">
-        <v>24</v>
-      </c>
-      <c r="EO9" t="s">
-        <v>179</v>
-      </c>
-      <c r="EP9">
-        <v>0</v>
+      <c r="EN9" t="s">
+        <v>199</v>
+      </c>
+      <c r="EO9">
+        <v>12</v>
+      </c>
+      <c r="EP9" t="s">
+        <v>181</v>
       </c>
       <c r="EQ9">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="ER9">
+        <v>0</v>
+      </c>
+      <c r="ES9">
         <v>3600</v>
       </c>
-      <c r="ES9">
+      <c r="ET9">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:149">
+    <row r="10" spans="1:150">
       <c r="A10" s="1">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="F10" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="G10" t="b">
         <v>0</v>
@@ -8180,10 +8210,10 @@
         <v>1</v>
       </c>
       <c r="R10">
-        <v>1720000</v>
+        <v>2262000</v>
       </c>
       <c r="S10" t="s">
-        <v>219</v>
+        <v>161</v>
       </c>
       <c r="T10" t="s">
         <v>162</v>
@@ -8231,7 +8261,7 @@
         <v>15000000</v>
       </c>
       <c r="AL10" t="s">
-        <v>228</v>
+        <v>167</v>
       </c>
       <c r="AM10">
         <v>55</v>
@@ -8264,7 +8294,7 @@
         <v>2800</v>
       </c>
       <c r="AW10" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="AX10">
         <v>55</v>
@@ -8294,7 +8324,7 @@
         <v>1</v>
       </c>
       <c r="BL10" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="BM10">
         <v>2</v>
@@ -8303,7 +8333,7 @@
         <v>9</v>
       </c>
       <c r="BO10" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="BP10">
         <v>0</v>
@@ -8315,7 +8345,7 @@
         <v>1</v>
       </c>
       <c r="BV10" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="BW10">
         <v>2</v>
@@ -8324,7 +8354,7 @@
         <v>9</v>
       </c>
       <c r="BY10" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="BZ10">
         <v>0</v>
@@ -8336,7 +8366,7 @@
         <v>1</v>
       </c>
       <c r="CF10" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="CG10">
         <v>2</v>
@@ -8345,7 +8375,7 @@
         <v>9</v>
       </c>
       <c r="CI10" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="CJ10">
         <v>0</v>
@@ -8357,7 +8387,7 @@
         <v>1</v>
       </c>
       <c r="CO10" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="CP10">
         <v>0</v>
@@ -8369,7 +8399,7 @@
         <v>1</v>
       </c>
       <c r="DM10" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="DN10">
         <v>0.05</v>
@@ -8384,10 +8414,10 @@
         <v>8</v>
       </c>
       <c r="DR10" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="DS10" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="DT10">
         <v>0</v>
@@ -8399,7 +8429,7 @@
         <v>1</v>
       </c>
       <c r="EC10" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="ED10">
         <v>0</v>
@@ -8410,58 +8440,58 @@
       <c r="EF10" t="b">
         <v>1</v>
       </c>
-      <c r="EJ10" t="s">
-        <v>184</v>
-      </c>
       <c r="EK10" t="s">
-        <v>194</v>
-      </c>
-      <c r="EL10">
+        <v>188</v>
+      </c>
+      <c r="EL10" t="s">
+        <v>198</v>
+      </c>
+      <c r="EM10">
         <v>96</v>
       </c>
-      <c r="EM10" t="s">
-        <v>195</v>
-      </c>
-      <c r="EN10">
-        <v>60</v>
-      </c>
-      <c r="EO10" t="s">
-        <v>179</v>
-      </c>
-      <c r="EP10">
-        <v>30</v>
+      <c r="EN10" t="s">
+        <v>199</v>
+      </c>
+      <c r="EO10">
+        <v>48</v>
+      </c>
+      <c r="EP10" t="s">
+        <v>181</v>
       </c>
       <c r="EQ10">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="ER10">
+        <v>0</v>
+      </c>
+      <c r="ES10">
         <v>3600</v>
       </c>
-      <c r="ES10">
+      <c r="ET10">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:149">
+    <row r="11" spans="1:150">
       <c r="A11" s="1">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="F11" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="G11" t="b">
         <v>0</v>
       </c>
       <c r="H11">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J11">
-        <v>420</v>
+        <v>100</v>
       </c>
       <c r="K11">
         <v>1</v>
@@ -8470,22 +8500,25 @@
         <v>2.6</v>
       </c>
       <c r="M11">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="N11">
         <v>1</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q11" t="b">
         <v>1</v>
       </c>
       <c r="R11">
-        <v>12880000</v>
+        <v>1546000</v>
+      </c>
+      <c r="S11" t="s">
+        <v>222</v>
       </c>
       <c r="T11" t="s">
         <v>162</v>
@@ -8521,16 +8554,22 @@
         <v>163</v>
       </c>
       <c r="AH11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ11" t="b">
         <v>1</v>
       </c>
       <c r="AK11">
-        <v>23100000</v>
+        <v>15000000</v>
+      </c>
+      <c r="AL11" t="s">
+        <v>229</v>
+      </c>
+      <c r="AM11">
+        <v>55</v>
       </c>
       <c r="AN11" t="s">
         <v>162</v>
@@ -8548,16 +8587,22 @@
         <v>90</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU11" t="b">
         <v>1</v>
       </c>
       <c r="AV11">
-        <v>12600</v>
+        <v>2400</v>
+      </c>
+      <c r="AW11" t="s">
+        <v>173</v>
+      </c>
+      <c r="AX11">
+        <v>55</v>
       </c>
       <c r="AY11" t="s">
         <v>162</v>
@@ -8575,31 +8620,16 @@
         <v>90</v>
       </c>
       <c r="BD11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF11" t="b">
         <v>1</v>
       </c>
-      <c r="BG11">
-        <v>19000</v>
-      </c>
-      <c r="BH11" t="s">
-        <v>232</v>
-      </c>
-      <c r="BI11">
-        <v>0</v>
-      </c>
-      <c r="BJ11">
-        <v>40</v>
-      </c>
-      <c r="BK11" t="b">
-        <v>1</v>
-      </c>
       <c r="BL11" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="BM11">
         <v>2</v>
@@ -8608,7 +8638,7 @@
         <v>9</v>
       </c>
       <c r="BO11" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="BP11">
         <v>0</v>
@@ -8620,7 +8650,7 @@
         <v>1</v>
       </c>
       <c r="BV11" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="BW11">
         <v>2</v>
@@ -8629,165 +8659,174 @@
         <v>9</v>
       </c>
       <c r="BY11" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="BZ11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CA11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CB11" t="b">
         <v>1</v>
       </c>
-      <c r="CC11">
-        <v>2800</v>
-      </c>
-      <c r="CD11" t="s">
+      <c r="CF11" t="s">
+        <v>180</v>
+      </c>
+      <c r="CG11">
+        <v>2</v>
+      </c>
+      <c r="CH11">
+        <v>9</v>
+      </c>
+      <c r="CI11" t="s">
+        <v>188</v>
+      </c>
+      <c r="CJ11">
+        <v>0</v>
+      </c>
+      <c r="CK11">
+        <v>0</v>
+      </c>
+      <c r="CL11" t="b">
+        <v>1</v>
+      </c>
+      <c r="CO11" t="s">
+        <v>188</v>
+      </c>
+      <c r="CP11">
+        <v>1</v>
+      </c>
+      <c r="CQ11">
+        <v>1</v>
+      </c>
+      <c r="CR11" t="b">
+        <v>1</v>
+      </c>
+      <c r="CS11" t="s">
         <v>234</v>
       </c>
-      <c r="CE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="CF11" t="s">
-        <v>178</v>
-      </c>
-      <c r="CG11">
-        <v>2</v>
-      </c>
-      <c r="CH11">
-        <v>9</v>
-      </c>
-      <c r="CI11" t="s">
-        <v>184</v>
-      </c>
-      <c r="CJ11">
-        <v>0</v>
-      </c>
-      <c r="CK11">
-        <v>0</v>
-      </c>
-      <c r="CL11" t="b">
-        <v>1</v>
-      </c>
-      <c r="CO11" t="s">
-        <v>184</v>
-      </c>
-      <c r="CP11">
-        <v>0</v>
-      </c>
-      <c r="CQ11">
-        <v>0</v>
-      </c>
-      <c r="CR11" t="b">
-        <v>1</v>
+      <c r="CT11">
+        <v>50000</v>
+      </c>
+      <c r="CU11">
+        <v>15000</v>
+      </c>
+      <c r="CV11">
+        <v>7200</v>
+      </c>
+      <c r="CW11">
+        <v>7200</v>
+      </c>
+      <c r="CX11">
+        <v>50000</v>
+      </c>
+      <c r="CY11">
+        <v>0.9</v>
+      </c>
+      <c r="CZ11">
+        <v>0.8</v>
+      </c>
+      <c r="DA11" t="b">
+        <v>0</v>
+      </c>
+      <c r="DB11" t="b">
+        <v>0</v>
+      </c>
+      <c r="DM11" t="s">
+        <v>239</v>
+      </c>
+      <c r="DN11">
+        <v>0.05</v>
+      </c>
+      <c r="DO11">
+        <v>0.5</v>
+      </c>
+      <c r="DP11">
+        <v>0.8</v>
+      </c>
+      <c r="DQ11">
+        <v>8</v>
       </c>
       <c r="DR11" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="DS11" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="DT11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DV11" t="b">
         <v>1</v>
       </c>
-      <c r="DW11">
-        <v>13000</v>
-      </c>
-      <c r="DX11">
-        <v>13000</v>
-      </c>
-      <c r="DY11">
-        <v>0.95</v>
-      </c>
-      <c r="DZ11">
-        <v>0.1</v>
-      </c>
-      <c r="EA11" t="b">
-        <v>0</v>
-      </c>
-      <c r="EB11" t="b">
-        <v>0</v>
-      </c>
       <c r="EC11" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="ED11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EE11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EF11" t="b">
         <v>1</v>
       </c>
-      <c r="EG11">
-        <v>23000</v>
-      </c>
-      <c r="EH11">
-        <v>0.95</v>
-      </c>
-      <c r="EI11">
-        <v>0.1</v>
-      </c>
-      <c r="EJ11" t="s">
-        <v>184</v>
-      </c>
       <c r="EK11" t="s">
-        <v>194</v>
-      </c>
-      <c r="EL11">
+        <v>188</v>
+      </c>
+      <c r="EL11" t="s">
+        <v>198</v>
+      </c>
+      <c r="EM11">
         <v>96</v>
       </c>
-      <c r="EM11" t="s">
-        <v>195</v>
-      </c>
-      <c r="EN11">
-        <v>48</v>
-      </c>
-      <c r="EO11" t="s">
-        <v>179</v>
-      </c>
-      <c r="EP11">
-        <v>0</v>
+      <c r="EN11" t="s">
+        <v>199</v>
+      </c>
+      <c r="EO11">
+        <v>24</v>
+      </c>
+      <c r="EP11" t="s">
+        <v>181</v>
       </c>
       <c r="EQ11">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="ER11">
+        <v>0</v>
+      </c>
+      <c r="ES11">
         <v>3600</v>
       </c>
-      <c r="ES11">
+      <c r="ET11">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:149">
+    <row r="12" spans="1:150">
       <c r="A12" s="1">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="F12" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="G12" t="b">
         <v>0</v>
       </c>
       <c r="H12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J12">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="K12">
         <v>1</v>
@@ -8796,7 +8835,7 @@
         <v>2.6</v>
       </c>
       <c r="M12">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="N12">
         <v>1</v>
@@ -8811,10 +8850,10 @@
         <v>1</v>
       </c>
       <c r="R12">
-        <v>2262000</v>
+        <v>1416000</v>
       </c>
       <c r="S12" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="T12" t="s">
         <v>162</v>
@@ -8859,10 +8898,10 @@
         <v>1</v>
       </c>
       <c r="AK12">
-        <v>3850000</v>
+        <v>15000000</v>
       </c>
       <c r="AL12" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="AM12">
         <v>55</v>
@@ -8892,7 +8931,7 @@
         <v>1</v>
       </c>
       <c r="AV12">
-        <v>2100</v>
+        <v>3200</v>
       </c>
       <c r="AW12" t="s">
         <v>172</v>
@@ -8925,7 +8964,7 @@
         <v>1</v>
       </c>
       <c r="BL12" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="BM12">
         <v>2</v>
@@ -8934,7 +8973,7 @@
         <v>9</v>
       </c>
       <c r="BO12" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="BP12">
         <v>0</v>
@@ -8946,7 +8985,7 @@
         <v>1</v>
       </c>
       <c r="BV12" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="BW12">
         <v>2</v>
@@ -8955,7 +8994,7 @@
         <v>9</v>
       </c>
       <c r="BY12" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="BZ12">
         <v>0</v>
@@ -8967,7 +9006,7 @@
         <v>1</v>
       </c>
       <c r="CF12" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="CG12">
         <v>2</v>
@@ -8976,7 +9015,7 @@
         <v>9</v>
       </c>
       <c r="CI12" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="CJ12">
         <v>0</v>
@@ -8988,19 +9027,79 @@
         <v>1</v>
       </c>
       <c r="CO12" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="CP12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CR12" t="b">
         <v>1</v>
       </c>
+      <c r="CS12" t="s">
+        <v>235</v>
+      </c>
+      <c r="CT12">
+        <v>75000</v>
+      </c>
+      <c r="CU12">
+        <v>20000</v>
+      </c>
+      <c r="CV12">
+        <v>7200</v>
+      </c>
+      <c r="CW12">
+        <v>11000</v>
+      </c>
+      <c r="CX12">
+        <v>100000</v>
+      </c>
+      <c r="CY12">
+        <v>0.9</v>
+      </c>
+      <c r="CZ12">
+        <v>0.8</v>
+      </c>
+      <c r="DA12" t="b">
+        <v>0</v>
+      </c>
+      <c r="DB12" t="b">
+        <v>0</v>
+      </c>
+      <c r="DC12" t="s">
+        <v>236</v>
+      </c>
+      <c r="DD12">
+        <v>100000</v>
+      </c>
+      <c r="DE12">
+        <v>25000</v>
+      </c>
+      <c r="DF12">
+        <v>11000</v>
+      </c>
+      <c r="DG12">
+        <v>22000</v>
+      </c>
+      <c r="DH12">
+        <v>200000</v>
+      </c>
+      <c r="DI12">
+        <v>0.9</v>
+      </c>
+      <c r="DJ12">
+        <v>0.8</v>
+      </c>
+      <c r="DK12" t="b">
+        <v>0</v>
+      </c>
+      <c r="DL12" t="b">
+        <v>0</v>
+      </c>
       <c r="DM12" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="DN12">
         <v>0.05</v>
@@ -9015,10 +9114,10 @@
         <v>8</v>
       </c>
       <c r="DR12" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="DS12" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="DT12">
         <v>0</v>
@@ -9030,7 +9129,7 @@
         <v>1</v>
       </c>
       <c r="EC12" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="ED12">
         <v>0</v>
@@ -9041,58 +9140,58 @@
       <c r="EF12" t="b">
         <v>1</v>
       </c>
-      <c r="EJ12" t="s">
-        <v>184</v>
-      </c>
       <c r="EK12" t="s">
-        <v>194</v>
-      </c>
-      <c r="EL12">
+        <v>188</v>
+      </c>
+      <c r="EL12" t="s">
+        <v>198</v>
+      </c>
+      <c r="EM12">
         <v>96</v>
       </c>
-      <c r="EM12" t="s">
-        <v>195</v>
-      </c>
-      <c r="EN12">
-        <v>60</v>
-      </c>
-      <c r="EO12" t="s">
-        <v>179</v>
-      </c>
-      <c r="EP12">
-        <v>0</v>
+      <c r="EN12" t="s">
+        <v>199</v>
+      </c>
+      <c r="EO12">
+        <v>48</v>
+      </c>
+      <c r="EP12" t="s">
+        <v>181</v>
       </c>
       <c r="EQ12">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="ER12">
+        <v>0</v>
+      </c>
+      <c r="ES12">
         <v>3600</v>
       </c>
-      <c r="ES12">
+      <c r="ET12">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:149">
+    <row r="13" spans="1:150">
       <c r="A13" s="1">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="F13" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="G13" t="b">
         <v>0</v>
       </c>
       <c r="H13">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J13">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="K13">
         <v>1</v>
@@ -9101,7 +9200,7 @@
         <v>2.6</v>
       </c>
       <c r="M13">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="N13">
         <v>1</v>
@@ -9116,10 +9215,10 @@
         <v>1</v>
       </c>
       <c r="R13">
-        <v>2012000</v>
+        <v>2959000</v>
       </c>
       <c r="S13" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="T13" t="s">
         <v>162</v>
@@ -9164,13 +9263,13 @@
         <v>1</v>
       </c>
       <c r="AK13">
-        <v>3850000</v>
+        <v>15000000</v>
       </c>
       <c r="AL13" t="s">
-        <v>169</v>
+        <v>230</v>
       </c>
       <c r="AM13">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="AN13" t="s">
         <v>162</v>
@@ -9197,10 +9296,10 @@
         <v>1</v>
       </c>
       <c r="AV13">
-        <v>2400</v>
+        <v>2800</v>
       </c>
       <c r="AW13" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="AX13">
         <v>55</v>
@@ -9230,7 +9329,7 @@
         <v>1</v>
       </c>
       <c r="BL13" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="BM13">
         <v>2</v>
@@ -9239,7 +9338,7 @@
         <v>9</v>
       </c>
       <c r="BO13" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="BP13">
         <v>0</v>
@@ -9251,7 +9350,7 @@
         <v>1</v>
       </c>
       <c r="BV13" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="BW13">
         <v>2</v>
@@ -9260,7 +9359,7 @@
         <v>9</v>
       </c>
       <c r="BY13" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="BZ13">
         <v>0</v>
@@ -9272,7 +9371,7 @@
         <v>1</v>
       </c>
       <c r="CF13" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="CG13">
         <v>2</v>
@@ -9281,7 +9380,7 @@
         <v>9</v>
       </c>
       <c r="CI13" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="CJ13">
         <v>0</v>
@@ -9293,7 +9392,7 @@
         <v>1</v>
       </c>
       <c r="CO13" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="CP13">
         <v>0</v>
@@ -9305,7 +9404,7 @@
         <v>1</v>
       </c>
       <c r="DM13" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="DN13">
         <v>0.05</v>
@@ -9320,10 +9419,10 @@
         <v>8</v>
       </c>
       <c r="DR13" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="DS13" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="DT13">
         <v>0</v>
@@ -9335,7 +9434,7 @@
         <v>1</v>
       </c>
       <c r="EC13" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="ED13">
         <v>0</v>
@@ -9346,58 +9445,58 @@
       <c r="EF13" t="b">
         <v>1</v>
       </c>
-      <c r="EJ13" t="s">
-        <v>184</v>
-      </c>
       <c r="EK13" t="s">
-        <v>194</v>
-      </c>
-      <c r="EL13">
+        <v>188</v>
+      </c>
+      <c r="EL13" t="s">
+        <v>198</v>
+      </c>
+      <c r="EM13">
         <v>96</v>
       </c>
-      <c r="EM13" t="s">
-        <v>195</v>
-      </c>
-      <c r="EN13">
-        <v>12</v>
-      </c>
-      <c r="EO13" t="s">
-        <v>179</v>
-      </c>
-      <c r="EP13">
+      <c r="EN13" t="s">
+        <v>199</v>
+      </c>
+      <c r="EO13">
+        <v>24</v>
+      </c>
+      <c r="EP13" t="s">
+        <v>181</v>
+      </c>
+      <c r="EQ13">
         <v>20</v>
       </c>
-      <c r="EQ13">
-        <v>0</v>
-      </c>
       <c r="ER13">
+        <v>0</v>
+      </c>
+      <c r="ES13">
         <v>3600</v>
       </c>
-      <c r="ES13">
+      <c r="ET13">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:149">
+    <row r="14" spans="1:150">
       <c r="A14" s="1">
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="F14" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="G14" t="b">
         <v>0</v>
       </c>
       <c r="H14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J14">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="K14">
         <v>1</v>
@@ -9406,7 +9505,7 @@
         <v>2.6</v>
       </c>
       <c r="M14">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="N14">
         <v>1</v>
@@ -9421,10 +9520,10 @@
         <v>1</v>
       </c>
       <c r="R14">
-        <v>1009000</v>
+        <v>1266000</v>
       </c>
       <c r="S14" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="T14" t="s">
         <v>162</v>
@@ -9469,7 +9568,7 @@
         <v>1</v>
       </c>
       <c r="AK14">
-        <v>3850000</v>
+        <v>15000000</v>
       </c>
       <c r="AL14" t="s">
         <v>228</v>
@@ -9502,10 +9601,10 @@
         <v>1</v>
       </c>
       <c r="AV14">
-        <v>2400</v>
+        <v>2800</v>
       </c>
       <c r="AW14" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AX14">
         <v>55</v>
@@ -9535,7 +9634,7 @@
         <v>1</v>
       </c>
       <c r="BL14" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="BM14">
         <v>2</v>
@@ -9544,7 +9643,7 @@
         <v>9</v>
       </c>
       <c r="BO14" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="BP14">
         <v>0</v>
@@ -9556,7 +9655,7 @@
         <v>1</v>
       </c>
       <c r="BV14" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="BW14">
         <v>2</v>
@@ -9565,7 +9664,7 @@
         <v>9</v>
       </c>
       <c r="BY14" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="BZ14">
         <v>0</v>
@@ -9577,7 +9676,7 @@
         <v>1</v>
       </c>
       <c r="CF14" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="CG14">
         <v>2</v>
@@ -9586,7 +9685,7 @@
         <v>9</v>
       </c>
       <c r="CI14" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="CJ14">
         <v>0</v>
@@ -9598,7 +9697,7 @@
         <v>1</v>
       </c>
       <c r="CO14" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="CP14">
         <v>0</v>
@@ -9625,10 +9724,10 @@
         <v>8</v>
       </c>
       <c r="DR14" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="DS14" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="DT14">
         <v>0</v>
@@ -9640,7 +9739,7 @@
         <v>1</v>
       </c>
       <c r="EC14" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="ED14">
         <v>0</v>
@@ -9651,58 +9750,58 @@
       <c r="EF14" t="b">
         <v>1</v>
       </c>
-      <c r="EJ14" t="s">
-        <v>184</v>
-      </c>
       <c r="EK14" t="s">
-        <v>194</v>
-      </c>
-      <c r="EL14">
+        <v>188</v>
+      </c>
+      <c r="EL14" t="s">
+        <v>198</v>
+      </c>
+      <c r="EM14">
         <v>96</v>
       </c>
-      <c r="EM14" t="s">
-        <v>195</v>
-      </c>
-      <c r="EN14">
-        <v>12</v>
-      </c>
-      <c r="EO14" t="s">
-        <v>179</v>
-      </c>
-      <c r="EP14">
-        <v>10</v>
+      <c r="EN14" t="s">
+        <v>199</v>
+      </c>
+      <c r="EO14">
+        <v>60</v>
+      </c>
+      <c r="EP14" t="s">
+        <v>181</v>
       </c>
       <c r="EQ14">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="ER14">
+        <v>0</v>
+      </c>
+      <c r="ES14">
         <v>3600</v>
       </c>
-      <c r="ES14">
+      <c r="ET14">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:149">
+    <row r="15" spans="1:150">
       <c r="A15" s="1">
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="F15" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="G15" t="b">
         <v>0</v>
       </c>
       <c r="H15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J15">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="K15">
         <v>1</v>
@@ -9711,7 +9810,7 @@
         <v>2.6</v>
       </c>
       <c r="M15">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="N15">
         <v>1</v>
@@ -9726,10 +9825,10 @@
         <v>1</v>
       </c>
       <c r="R15">
-        <v>2455000</v>
+        <v>1720000</v>
       </c>
       <c r="S15" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="T15" t="s">
         <v>162</v>
@@ -9774,10 +9873,10 @@
         <v>1</v>
       </c>
       <c r="AK15">
-        <v>3850000</v>
+        <v>15000000</v>
       </c>
       <c r="AL15" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AM15">
         <v>55</v>
@@ -9807,10 +9906,10 @@
         <v>1</v>
       </c>
       <c r="AV15">
-        <v>2100</v>
+        <v>3200</v>
       </c>
       <c r="AW15" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="AX15">
         <v>55</v>
@@ -9840,7 +9939,7 @@
         <v>1</v>
       </c>
       <c r="BL15" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="BM15">
         <v>2</v>
@@ -9849,7 +9948,7 @@
         <v>9</v>
       </c>
       <c r="BO15" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="BP15">
         <v>0</v>
@@ -9861,7 +9960,7 @@
         <v>1</v>
       </c>
       <c r="BV15" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="BW15">
         <v>2</v>
@@ -9870,7 +9969,7 @@
         <v>9</v>
       </c>
       <c r="BY15" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="BZ15">
         <v>0</v>
@@ -9882,7 +9981,7 @@
         <v>1</v>
       </c>
       <c r="CF15" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="CG15">
         <v>2</v>
@@ -9891,7 +9990,7 @@
         <v>9</v>
       </c>
       <c r="CI15" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="CJ15">
         <v>0</v>
@@ -9903,49 +10002,19 @@
         <v>1</v>
       </c>
       <c r="CO15" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="CP15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CR15" t="b">
         <v>1</v>
       </c>
-      <c r="CS15" t="s">
-        <v>235</v>
-      </c>
-      <c r="CT15">
-        <v>50000</v>
-      </c>
-      <c r="CU15">
-        <v>15000</v>
-      </c>
-      <c r="CV15">
-        <v>7200</v>
-      </c>
-      <c r="CW15">
-        <v>7200</v>
-      </c>
-      <c r="CX15">
-        <v>50000</v>
-      </c>
-      <c r="CY15">
-        <v>0.9</v>
-      </c>
-      <c r="CZ15">
-        <v>0.8</v>
-      </c>
-      <c r="DA15" t="b">
-        <v>0</v>
-      </c>
-      <c r="DB15" t="b">
-        <v>0</v>
-      </c>
       <c r="DM15" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="DN15">
         <v>0.05</v>
@@ -9960,10 +10029,10 @@
         <v>8</v>
       </c>
       <c r="DR15" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="DS15" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="DT15">
         <v>0</v>
@@ -9975,7 +10044,7 @@
         <v>1</v>
       </c>
       <c r="EC15" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="ED15">
         <v>0</v>
@@ -9986,58 +10055,58 @@
       <c r="EF15" t="b">
         <v>1</v>
       </c>
-      <c r="EJ15" t="s">
-        <v>184</v>
-      </c>
       <c r="EK15" t="s">
-        <v>194</v>
-      </c>
-      <c r="EL15">
+        <v>188</v>
+      </c>
+      <c r="EL15" t="s">
+        <v>198</v>
+      </c>
+      <c r="EM15">
         <v>96</v>
       </c>
-      <c r="EM15" t="s">
-        <v>195</v>
-      </c>
-      <c r="EN15">
+      <c r="EN15" t="s">
+        <v>199</v>
+      </c>
+      <c r="EO15">
         <v>12</v>
       </c>
-      <c r="EO15" t="s">
-        <v>179</v>
-      </c>
-      <c r="EP15">
-        <v>0</v>
+      <c r="EP15" t="s">
+        <v>181</v>
       </c>
       <c r="EQ15">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="ER15">
+        <v>0</v>
+      </c>
+      <c r="ES15">
         <v>3600</v>
       </c>
-      <c r="ES15">
+      <c r="ET15">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:149">
+    <row r="16" spans="1:150">
       <c r="A16" s="1">
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="F16" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="G16" t="b">
         <v>0</v>
       </c>
       <c r="H16">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J16">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="K16">
         <v>1</v>
@@ -10046,7 +10115,7 @@
         <v>2.6</v>
       </c>
       <c r="M16">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="N16">
         <v>1</v>
@@ -10061,7 +10130,7 @@
         <v>1</v>
       </c>
       <c r="R16">
-        <v>2455000</v>
+        <v>1546000</v>
       </c>
       <c r="S16" t="s">
         <v>222</v>
@@ -10109,13 +10178,13 @@
         <v>1</v>
       </c>
       <c r="AK16">
-        <v>3850000</v>
+        <v>15000000</v>
       </c>
       <c r="AL16" t="s">
-        <v>227</v>
+        <v>164</v>
       </c>
       <c r="AM16">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="AN16" t="s">
         <v>162</v>
@@ -10142,10 +10211,10 @@
         <v>1</v>
       </c>
       <c r="AV16">
-        <v>1800</v>
+        <v>2400</v>
       </c>
       <c r="AW16" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="AX16">
         <v>55</v>
@@ -10175,7 +10244,7 @@
         <v>1</v>
       </c>
       <c r="BL16" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="BM16">
         <v>2</v>
@@ -10184,7 +10253,7 @@
         <v>9</v>
       </c>
       <c r="BO16" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="BP16">
         <v>0</v>
@@ -10196,7 +10265,7 @@
         <v>1</v>
       </c>
       <c r="BV16" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="BW16">
         <v>2</v>
@@ -10205,7 +10274,7 @@
         <v>9</v>
       </c>
       <c r="BY16" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="BZ16">
         <v>0</v>
@@ -10217,7 +10286,7 @@
         <v>1</v>
       </c>
       <c r="CF16" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="CG16">
         <v>2</v>
@@ -10226,7 +10295,7 @@
         <v>9</v>
       </c>
       <c r="CI16" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="CJ16">
         <v>0</v>
@@ -10238,49 +10307,19 @@
         <v>1</v>
       </c>
       <c r="CO16" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="CP16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CR16" t="b">
         <v>1</v>
       </c>
-      <c r="CS16" t="s">
-        <v>236</v>
-      </c>
-      <c r="CT16">
-        <v>75000</v>
-      </c>
-      <c r="CU16">
-        <v>20000</v>
-      </c>
-      <c r="CV16">
-        <v>7200</v>
-      </c>
-      <c r="CW16">
-        <v>11000</v>
-      </c>
-      <c r="CX16">
-        <v>100000</v>
-      </c>
-      <c r="CY16">
-        <v>0.9</v>
-      </c>
-      <c r="CZ16">
-        <v>0.8</v>
-      </c>
-      <c r="DA16" t="b">
-        <v>0</v>
-      </c>
-      <c r="DB16" t="b">
-        <v>0</v>
-      </c>
       <c r="DM16" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="DN16">
         <v>0.05</v>
@@ -10295,10 +10334,10 @@
         <v>8</v>
       </c>
       <c r="DR16" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="DS16" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="DT16">
         <v>0</v>
@@ -10310,7 +10349,7 @@
         <v>1</v>
       </c>
       <c r="EC16" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="ED16">
         <v>0</v>
@@ -10321,58 +10360,58 @@
       <c r="EF16" t="b">
         <v>1</v>
       </c>
-      <c r="EJ16" t="s">
-        <v>184</v>
-      </c>
       <c r="EK16" t="s">
-        <v>194</v>
-      </c>
-      <c r="EL16">
+        <v>188</v>
+      </c>
+      <c r="EL16" t="s">
+        <v>198</v>
+      </c>
+      <c r="EM16">
         <v>96</v>
       </c>
-      <c r="EM16" t="s">
-        <v>195</v>
-      </c>
-      <c r="EN16">
-        <v>36</v>
-      </c>
-      <c r="EO16" t="s">
-        <v>179</v>
-      </c>
-      <c r="EP16">
-        <v>10</v>
+      <c r="EN16" t="s">
+        <v>199</v>
+      </c>
+      <c r="EO16">
+        <v>24</v>
+      </c>
+      <c r="EP16" t="s">
+        <v>181</v>
       </c>
       <c r="EQ16">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="ER16">
+        <v>0</v>
+      </c>
+      <c r="ES16">
         <v>3600</v>
       </c>
-      <c r="ES16">
+      <c r="ET16">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:149">
+    <row r="17" spans="1:150">
       <c r="A17" s="1">
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="F17" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="G17" t="b">
         <v>0</v>
       </c>
       <c r="H17">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J17">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="K17">
         <v>1</v>
@@ -10381,7 +10420,7 @@
         <v>2.6</v>
       </c>
       <c r="M17">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="N17">
         <v>1</v>
@@ -10396,10 +10435,10 @@
         <v>1</v>
       </c>
       <c r="R17">
-        <v>2687000</v>
+        <v>2262000</v>
       </c>
       <c r="S17" t="s">
-        <v>225</v>
+        <v>161</v>
       </c>
       <c r="T17" t="s">
         <v>162</v>
@@ -10444,10 +10483,10 @@
         <v>1</v>
       </c>
       <c r="AK17">
-        <v>3850000</v>
+        <v>15000000</v>
       </c>
       <c r="AL17" t="s">
-        <v>226</v>
+        <v>164</v>
       </c>
       <c r="AM17">
         <v>55</v>
@@ -10477,10 +10516,10 @@
         <v>1</v>
       </c>
       <c r="AV17">
-        <v>1800</v>
+        <v>2800</v>
       </c>
       <c r="AW17" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="AX17">
         <v>55</v>
@@ -10510,7 +10549,7 @@
         <v>1</v>
       </c>
       <c r="BL17" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="BM17">
         <v>2</v>
@@ -10519,7 +10558,7 @@
         <v>9</v>
       </c>
       <c r="BO17" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="BP17">
         <v>0</v>
@@ -10531,7 +10570,7 @@
         <v>1</v>
       </c>
       <c r="BV17" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="BW17">
         <v>2</v>
@@ -10540,7 +10579,7 @@
         <v>9</v>
       </c>
       <c r="BY17" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="BZ17">
         <v>0</v>
@@ -10552,7 +10591,7 @@
         <v>1</v>
       </c>
       <c r="CF17" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="CG17">
         <v>2</v>
@@ -10561,7 +10600,7 @@
         <v>9</v>
       </c>
       <c r="CI17" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="CJ17">
         <v>0</v>
@@ -10573,7 +10612,7 @@
         <v>1</v>
       </c>
       <c r="CO17" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="CP17">
         <v>0</v>
@@ -10585,7 +10624,7 @@
         <v>1</v>
       </c>
       <c r="DM17" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="DN17">
         <v>0.05</v>
@@ -10600,10 +10639,10 @@
         <v>8</v>
       </c>
       <c r="DR17" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="DS17" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="DT17">
         <v>0</v>
@@ -10615,7 +10654,7 @@
         <v>1</v>
       </c>
       <c r="EC17" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="ED17">
         <v>0</v>
@@ -10626,34 +10665,34 @@
       <c r="EF17" t="b">
         <v>1</v>
       </c>
-      <c r="EJ17" t="s">
-        <v>184</v>
-      </c>
       <c r="EK17" t="s">
-        <v>194</v>
-      </c>
-      <c r="EL17">
+        <v>188</v>
+      </c>
+      <c r="EL17" t="s">
+        <v>198</v>
+      </c>
+      <c r="EM17">
         <v>96</v>
       </c>
-      <c r="EM17" t="s">
-        <v>195</v>
-      </c>
-      <c r="EN17">
-        <v>12</v>
-      </c>
-      <c r="EO17" t="s">
-        <v>179</v>
-      </c>
-      <c r="EP17">
-        <v>0</v>
+      <c r="EN17" t="s">
+        <v>199</v>
+      </c>
+      <c r="EO17">
+        <v>48</v>
+      </c>
+      <c r="EP17" t="s">
+        <v>181</v>
       </c>
       <c r="EQ17">
         <v>0</v>
       </c>
       <c r="ER17">
+        <v>0</v>
+      </c>
+      <c r="ES17">
         <v>3600</v>
       </c>
-      <c r="ES17">
+      <c r="ET17">
         <v>0</v>
       </c>
     </row>
@@ -10936,31 +10975,31 @@
         <v>128</v>
       </c>
       <c r="CM1" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="CN1" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="CO1" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="CP1" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="CQ1" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="CR1" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="CS1" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="CT1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="CU1" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="2" spans="1:99">
@@ -10974,7 +11013,7 @@
         <v>249</v>
       </c>
       <c r="G2">
-        <v>194</v>
+        <v>513</v>
       </c>
       <c r="H2">
         <v>96</v>
@@ -10992,7 +11031,7 @@
         <v>1</v>
       </c>
       <c r="M2">
-        <v>7270000</v>
+        <v>14140000</v>
       </c>
       <c r="N2" t="s">
         <v>251</v>
@@ -11043,22 +11082,22 @@
         <v>1</v>
       </c>
       <c r="AF2">
-        <v>3450000</v>
+        <v>7150000</v>
       </c>
       <c r="AG2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AH2">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="AI2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AJ2" t="b">
         <v>1</v>
       </c>
       <c r="AK2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="AL2">
         <v>2</v>
@@ -11067,7 +11106,7 @@
         <v>9</v>
       </c>
       <c r="AN2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AO2">
         <v>0</v>
@@ -11079,7 +11118,7 @@
         <v>1</v>
       </c>
       <c r="AU2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="AV2">
         <v>2</v>
@@ -11088,7 +11127,7 @@
         <v>9</v>
       </c>
       <c r="AX2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AY2">
         <v>0</v>
@@ -11100,7 +11139,7 @@
         <v>1</v>
       </c>
       <c r="BE2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="BF2">
         <v>2</v>
@@ -11109,7 +11148,7 @@
         <v>9</v>
       </c>
       <c r="BH2" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="BI2">
         <v>0</v>
@@ -11121,10 +11160,10 @@
         <v>1</v>
       </c>
       <c r="CA2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="CB2" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="CC2">
         <v>1</v>
@@ -11133,13 +11172,13 @@
         <v>1</v>
       </c>
       <c r="CE2" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="CF2">
-        <v>7300</v>
+        <v>14000</v>
       </c>
       <c r="CG2">
-        <v>15000</v>
+        <v>14000</v>
       </c>
       <c r="CH2">
         <v>0.95</v>
@@ -11154,25 +11193,25 @@
         <v>0</v>
       </c>
       <c r="CL2" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="CM2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="CN2">
         <v>96</v>
       </c>
       <c r="CO2" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="CP2">
         <v>60</v>
       </c>
       <c r="CQ2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="CR2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="CS2">
         <v>0</v>
@@ -11195,7 +11234,7 @@
         <v>249</v>
       </c>
       <c r="G3">
-        <v>204</v>
+        <v>473</v>
       </c>
       <c r="H3">
         <v>96</v>
@@ -11213,7 +11252,7 @@
         <v>1</v>
       </c>
       <c r="M3">
-        <v>8040000</v>
+        <v>13450000</v>
       </c>
       <c r="N3" t="s">
         <v>251</v>
@@ -11255,16 +11294,31 @@
         <v>163</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE3" t="b">
         <v>1</v>
       </c>
+      <c r="AF3">
+        <v>7500000</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>253</v>
+      </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>40</v>
+      </c>
+      <c r="AJ3" t="b">
+        <v>1</v>
+      </c>
       <c r="AK3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="AL3">
         <v>2</v>
@@ -11273,7 +11327,7 @@
         <v>9</v>
       </c>
       <c r="AN3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AO3">
         <v>0</v>
@@ -11285,7 +11339,7 @@
         <v>1</v>
       </c>
       <c r="AU3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="AV3">
         <v>2</v>
@@ -11294,7 +11348,7 @@
         <v>9</v>
       </c>
       <c r="AX3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AY3">
         <v>0</v>
@@ -11306,7 +11360,7 @@
         <v>1</v>
       </c>
       <c r="BE3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="BF3">
         <v>2</v>
@@ -11315,94 +11369,67 @@
         <v>9</v>
       </c>
       <c r="BH3" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="BI3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BJ3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK3" t="b">
         <v>1</v>
       </c>
-      <c r="BL3" t="s">
-        <v>187</v>
-      </c>
-      <c r="BM3">
-        <v>75000</v>
-      </c>
-      <c r="BN3">
-        <v>25000</v>
-      </c>
-      <c r="BO3">
-        <v>11000</v>
-      </c>
-      <c r="BP3">
-        <v>22000</v>
-      </c>
-      <c r="BQ3">
-        <v>200000</v>
-      </c>
-      <c r="BR3">
-        <v>0.9</v>
-      </c>
-      <c r="BS3">
-        <v>0.8</v>
-      </c>
-      <c r="BT3" t="b">
-        <v>0</v>
-      </c>
-      <c r="BU3" t="b">
-        <v>0</v>
-      </c>
-      <c r="BV3" t="s">
-        <v>191</v>
-      </c>
-      <c r="BW3">
-        <v>0.05</v>
-      </c>
-      <c r="BX3">
-        <v>0.5</v>
-      </c>
-      <c r="BY3">
-        <v>0.8</v>
-      </c>
-      <c r="BZ3">
-        <v>8</v>
-      </c>
       <c r="CA3" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="CB3" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="CC3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE3" t="s">
-        <v>193</v>
+        <v>197</v>
+      </c>
+      <c r="CF3">
+        <v>13000</v>
+      </c>
+      <c r="CG3">
+        <v>13000</v>
+      </c>
+      <c r="CH3">
+        <v>0.95</v>
+      </c>
+      <c r="CI3">
+        <v>0.1</v>
+      </c>
+      <c r="CJ3" t="b">
+        <v>0</v>
+      </c>
+      <c r="CK3" t="b">
+        <v>0</v>
       </c>
       <c r="CL3" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="CM3" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="CN3">
         <v>96</v>
       </c>
       <c r="CO3" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="CP3">
         <v>60</v>
       </c>
       <c r="CQ3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="CR3">
         <v>0</v>
@@ -11428,7 +11455,7 @@
         <v>250</v>
       </c>
       <c r="G4">
-        <v>534</v>
+        <v>200</v>
       </c>
       <c r="H4">
         <v>96</v>
@@ -11446,7 +11473,7 @@
         <v>1</v>
       </c>
       <c r="M4">
-        <v>16300000</v>
+        <v>8600000</v>
       </c>
       <c r="N4" t="s">
         <v>252</v>
@@ -11488,31 +11515,16 @@
         <v>163</v>
       </c>
       <c r="AC4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>1</v>
       </c>
-      <c r="AF4">
-        <v>6660000</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>232</v>
-      </c>
-      <c r="AH4">
-        <v>0</v>
-      </c>
-      <c r="AI4">
-        <v>40</v>
-      </c>
-      <c r="AJ4" t="b">
-        <v>1</v>
-      </c>
       <c r="AK4" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="AL4">
         <v>2</v>
@@ -11521,7 +11533,7 @@
         <v>9</v>
       </c>
       <c r="AN4" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AO4">
         <v>0</v>
@@ -11533,7 +11545,7 @@
         <v>1</v>
       </c>
       <c r="AU4" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="AV4">
         <v>2</v>
@@ -11542,7 +11554,7 @@
         <v>9</v>
       </c>
       <c r="AX4" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AY4">
         <v>0</v>
@@ -11554,7 +11566,7 @@
         <v>1</v>
       </c>
       <c r="BE4" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="BF4">
         <v>2</v>
@@ -11563,67 +11575,94 @@
         <v>9</v>
       </c>
       <c r="BH4" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="BI4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BJ4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK4" t="b">
         <v>1</v>
       </c>
+      <c r="BL4" t="s">
+        <v>254</v>
+      </c>
+      <c r="BM4">
+        <v>75000</v>
+      </c>
+      <c r="BN4">
+        <v>25000</v>
+      </c>
+      <c r="BO4">
+        <v>11000</v>
+      </c>
+      <c r="BP4">
+        <v>22000</v>
+      </c>
+      <c r="BQ4">
+        <v>200000</v>
+      </c>
+      <c r="BR4">
+        <v>0.9</v>
+      </c>
+      <c r="BS4">
+        <v>0.8</v>
+      </c>
+      <c r="BT4" t="b">
+        <v>0</v>
+      </c>
+      <c r="BU4" t="b">
+        <v>0</v>
+      </c>
+      <c r="BV4" t="s">
+        <v>195</v>
+      </c>
+      <c r="BW4">
+        <v>0.05</v>
+      </c>
+      <c r="BX4">
+        <v>0.5</v>
+      </c>
+      <c r="BY4">
+        <v>0.8</v>
+      </c>
+      <c r="BZ4">
+        <v>8</v>
+      </c>
       <c r="CA4" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="CB4" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="CC4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE4" t="s">
-        <v>193</v>
-      </c>
-      <c r="CF4">
-        <v>16300</v>
-      </c>
-      <c r="CG4">
-        <v>16000</v>
-      </c>
-      <c r="CH4">
-        <v>0.95</v>
-      </c>
-      <c r="CI4">
-        <v>0.1</v>
-      </c>
-      <c r="CJ4" t="b">
-        <v>0</v>
-      </c>
-      <c r="CK4" t="b">
-        <v>0</v>
+        <v>197</v>
       </c>
       <c r="CL4" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="CM4" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="CN4">
         <v>96</v>
       </c>
       <c r="CO4" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="CP4">
         <v>12</v>
       </c>
       <c r="CQ4" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="CR4">
         <v>0</v>
@@ -11649,7 +11688,7 @@
         <v>250</v>
       </c>
       <c r="G5">
-        <v>507</v>
+        <v>196</v>
       </c>
       <c r="H5">
         <v>96</v>
@@ -11667,7 +11706,7 @@
         <v>1</v>
       </c>
       <c r="M5">
-        <v>14620000</v>
+        <v>8000000</v>
       </c>
       <c r="N5" t="s">
         <v>252</v>
@@ -11718,7 +11757,7 @@
         <v>1</v>
       </c>
       <c r="AK5" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="AL5">
         <v>2</v>
@@ -11727,7 +11766,7 @@
         <v>9</v>
       </c>
       <c r="AN5" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AO5">
         <v>0</v>
@@ -11739,7 +11778,7 @@
         <v>1</v>
       </c>
       <c r="AU5" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="AV5">
         <v>2</v>
@@ -11748,7 +11787,7 @@
         <v>9</v>
       </c>
       <c r="AX5" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AY5">
         <v>0</v>
@@ -11760,7 +11799,7 @@
         <v>1</v>
       </c>
       <c r="BE5" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="BF5">
         <v>2</v>
@@ -11769,22 +11808,67 @@
         <v>9</v>
       </c>
       <c r="BH5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="BI5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BJ5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK5" t="b">
         <v>1</v>
       </c>
+      <c r="BL5" t="s">
+        <v>190</v>
+      </c>
+      <c r="BM5">
+        <v>75000</v>
+      </c>
+      <c r="BN5">
+        <v>25000</v>
+      </c>
+      <c r="BO5">
+        <v>11000</v>
+      </c>
+      <c r="BP5">
+        <v>22000</v>
+      </c>
+      <c r="BQ5">
+        <v>200000</v>
+      </c>
+      <c r="BR5">
+        <v>0.9</v>
+      </c>
+      <c r="BS5">
+        <v>0.8</v>
+      </c>
+      <c r="BT5" t="b">
+        <v>0</v>
+      </c>
+      <c r="BU5" t="b">
+        <v>0</v>
+      </c>
+      <c r="BV5" t="s">
+        <v>195</v>
+      </c>
+      <c r="BW5">
+        <v>0.05</v>
+      </c>
+      <c r="BX5">
+        <v>0.5</v>
+      </c>
+      <c r="BY5">
+        <v>0.8</v>
+      </c>
+      <c r="BZ5">
+        <v>8</v>
+      </c>
       <c r="CA5" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="CB5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="CC5">
         <v>0</v>
@@ -11793,28 +11877,28 @@
         <v>0</v>
       </c>
       <c r="CE5" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="CL5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="CM5" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="CN5">
         <v>96</v>
       </c>
       <c r="CO5" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="CP5">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="CQ5" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="CR5">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="CS5">
         <v>0</v>
@@ -12135,31 +12219,31 @@
         <v>128</v>
       </c>
       <c r="CW1" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="CX1" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="CY1" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="CZ1" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="DA1" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="DB1" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="DC1" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="DD1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="DE1" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="2" spans="1:109">
@@ -12167,13 +12251,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="G2">
-        <v>1728</v>
+        <v>4996</v>
       </c>
       <c r="H2">
         <v>96</v>
@@ -12191,10 +12275,10 @@
         <v>1</v>
       </c>
       <c r="M2">
-        <v>668800000</v>
+        <v>1243200000</v>
       </c>
       <c r="N2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="O2" t="s">
         <v>162</v>
@@ -12218,7 +12302,7 @@
         <v>1</v>
       </c>
       <c r="W2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Y2" t="s">
         <v>162</v>
@@ -12233,16 +12317,31 @@
         <v>163</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE2" t="b">
         <v>1</v>
       </c>
+      <c r="AF2">
+        <v>1723000000</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>232</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>40</v>
+      </c>
+      <c r="AJ2" t="b">
+        <v>1</v>
+      </c>
       <c r="AK2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="AL2">
         <v>2</v>
@@ -12251,7 +12350,7 @@
         <v>9</v>
       </c>
       <c r="AN2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AO2">
         <v>0</v>
@@ -12263,7 +12362,7 @@
         <v>1</v>
       </c>
       <c r="AU2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="AV2">
         <v>2</v>
@@ -12272,7 +12371,7 @@
         <v>9</v>
       </c>
       <c r="AX2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AY2">
         <v>0</v>
@@ -12284,7 +12383,7 @@
         <v>1</v>
       </c>
       <c r="BE2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="BF2">
         <v>2</v>
@@ -12293,7 +12392,7 @@
         <v>9</v>
       </c>
       <c r="BH2" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="BI2">
         <v>0</v>
@@ -12305,10 +12404,10 @@
         <v>1</v>
       </c>
       <c r="CK2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="CL2" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="CM2">
         <v>0</v>
@@ -12317,28 +12416,28 @@
         <v>0</v>
       </c>
       <c r="CO2" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="CV2" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="CW2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="CX2">
         <v>96</v>
       </c>
       <c r="CY2" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="CZ2">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="DA2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="DB2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="DC2">
         <v>0</v>
@@ -12355,13 +12454,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="F3" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="G3">
-        <v>4962</v>
+        <v>1686</v>
       </c>
       <c r="H3">
         <v>96</v>
@@ -12379,10 +12478,10 @@
         <v>1</v>
       </c>
       <c r="M3">
-        <v>1130100000</v>
+        <v>594600000</v>
       </c>
       <c r="N3" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="O3" t="s">
         <v>162</v>
@@ -12406,7 +12505,7 @@
         <v>1</v>
       </c>
       <c r="W3" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Y3" t="s">
         <v>162</v>
@@ -12430,22 +12529,22 @@
         <v>1</v>
       </c>
       <c r="AF3">
-        <v>1418000000</v>
+        <v>1045000000</v>
       </c>
       <c r="AG3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="AI3">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AJ3" t="b">
         <v>1</v>
       </c>
       <c r="AK3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="AL3">
         <v>2</v>
@@ -12454,19 +12553,28 @@
         <v>9</v>
       </c>
       <c r="AN3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AO3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ3" t="b">
         <v>1</v>
       </c>
+      <c r="AR3">
+        <v>70600000</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>186</v>
+      </c>
+      <c r="AT3" t="b">
+        <v>1</v>
+      </c>
       <c r="AU3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="AV3">
         <v>2</v>
@@ -12475,7 +12583,7 @@
         <v>9</v>
       </c>
       <c r="AX3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AY3">
         <v>0</v>
@@ -12487,7 +12595,7 @@
         <v>1</v>
       </c>
       <c r="BE3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="BF3">
         <v>2</v>
@@ -12496,67 +12604,22 @@
         <v>9</v>
       </c>
       <c r="BH3" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="BI3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BJ3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK3" t="b">
         <v>1</v>
       </c>
-      <c r="BL3" t="s">
-        <v>259</v>
-      </c>
-      <c r="BM3">
-        <v>500000</v>
-      </c>
-      <c r="BN3">
-        <v>20000</v>
-      </c>
-      <c r="BO3">
-        <v>7200</v>
-      </c>
-      <c r="BP3">
-        <v>11000</v>
-      </c>
-      <c r="BQ3">
-        <v>100000</v>
-      </c>
-      <c r="BR3">
-        <v>0.9</v>
-      </c>
-      <c r="BS3">
-        <v>0.8</v>
-      </c>
-      <c r="BT3" t="b">
-        <v>0</v>
-      </c>
-      <c r="BU3" t="b">
-        <v>0</v>
-      </c>
-      <c r="CF3" t="s">
-        <v>260</v>
-      </c>
-      <c r="CG3">
-        <v>0.05</v>
-      </c>
-      <c r="CH3">
-        <v>0.5</v>
-      </c>
-      <c r="CI3">
-        <v>0.8</v>
-      </c>
-      <c r="CJ3">
-        <v>8</v>
-      </c>
       <c r="CK3" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="CL3" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="CM3">
         <v>0</v>
@@ -12565,25 +12628,25 @@
         <v>0</v>
       </c>
       <c r="CO3" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="CV3" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="CW3" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="CX3">
         <v>96</v>
       </c>
       <c r="CY3" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="CZ3">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="DA3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="DB3">
         <v>0</v>
@@ -12754,25 +12817,25 @@
         <v>128</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="2" spans="1:56">
@@ -12798,10 +12861,10 @@
         <v>1</v>
       </c>
       <c r="K2">
-        <v>70900000</v>
+        <v>57600000</v>
       </c>
       <c r="L2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="M2">
         <v>20</v>
@@ -12813,7 +12876,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q2">
         <v>2</v>
@@ -12822,7 +12885,7 @@
         <v>9</v>
       </c>
       <c r="S2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AN2">
         <v>1</v>
@@ -12834,10 +12897,10 @@
         <v>1</v>
       </c>
       <c r="AQ2">
-        <v>35450000</v>
+        <v>28800000</v>
       </c>
       <c r="AR2">
-        <v>70900000</v>
+        <v>57600000</v>
       </c>
       <c r="AS2">
         <v>0.95</v>
@@ -12852,16 +12915,16 @@
         <v>1</v>
       </c>
       <c r="AW2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AX2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="AY2">
         <v>96</v>
       </c>
       <c r="AZ2" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="BA2">
         <v>36</v>
@@ -12899,10 +12962,10 @@
         <v>1</v>
       </c>
       <c r="K3">
-        <v>39800000</v>
+        <v>31900000</v>
       </c>
       <c r="L3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M3">
         <v>-20</v>
@@ -12914,7 +12977,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q3">
         <v>2</v>
@@ -12923,7 +12986,7 @@
         <v>9</v>
       </c>
       <c r="S3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AN3">
         <v>1</v>
@@ -12935,10 +12998,10 @@
         <v>1</v>
       </c>
       <c r="AQ3">
-        <v>19900000</v>
+        <v>15950000</v>
       </c>
       <c r="AR3">
-        <v>39800000</v>
+        <v>31900000</v>
       </c>
       <c r="AS3">
         <v>0.95</v>
@@ -12953,19 +13016,19 @@
         <v>1</v>
       </c>
       <c r="AW3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AX3" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="AY3">
         <v>96</v>
       </c>
       <c r="AZ3" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="BA3">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="BB3">
         <v>0</v>
@@ -13000,7 +13063,7 @@
         <v>1</v>
       </c>
       <c r="K4">
-        <v>15400000</v>
+        <v>16800000</v>
       </c>
       <c r="L4" t="s">
         <v>232</v>
@@ -13015,7 +13078,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q4">
         <v>2</v>
@@ -13024,7 +13087,7 @@
         <v>9</v>
       </c>
       <c r="S4" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AN4">
         <v>1</v>
@@ -13036,10 +13099,10 @@
         <v>1</v>
       </c>
       <c r="AQ4">
-        <v>7700000</v>
+        <v>8400000</v>
       </c>
       <c r="AR4">
-        <v>15400000</v>
+        <v>16800000</v>
       </c>
       <c r="AS4">
         <v>0.95</v>
@@ -13054,19 +13117,19 @@
         <v>1</v>
       </c>
       <c r="AW4" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AX4" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="AY4">
         <v>96</v>
       </c>
       <c r="AZ4" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="BA4">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="BB4">
         <v>0</v>
@@ -13101,10 +13164,10 @@
         <v>1</v>
       </c>
       <c r="K5">
-        <v>14300000</v>
+        <v>16900000</v>
       </c>
       <c r="L5" t="s">
-        <v>267</v>
+        <v>253</v>
       </c>
       <c r="M5">
         <v>0</v>
@@ -13116,7 +13179,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q5">
         <v>2</v>
@@ -13125,7 +13188,7 @@
         <v>9</v>
       </c>
       <c r="S5" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AN5">
         <v>1</v>
@@ -13137,10 +13200,10 @@
         <v>1</v>
       </c>
       <c r="AQ5">
-        <v>7150000</v>
+        <v>8450000</v>
       </c>
       <c r="AR5">
-        <v>14300000</v>
+        <v>16900000</v>
       </c>
       <c r="AS5">
         <v>0.95</v>
@@ -13155,19 +13218,19 @@
         <v>1</v>
       </c>
       <c r="AW5" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AX5" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="AY5">
         <v>96</v>
       </c>
       <c r="AZ5" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="BA5">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="BB5">
         <v>0</v>
@@ -13202,16 +13265,16 @@
         <v>1</v>
       </c>
       <c r="AG6">
-        <v>38500</v>
+        <v>20000</v>
       </c>
       <c r="AH6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AI6" t="b">
         <v>1</v>
       </c>
       <c r="AJ6" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="AK6">
         <v>2</v>
@@ -13220,7 +13283,7 @@
         <v>9</v>
       </c>
       <c r="AM6" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="AN6">
         <v>0</v>
@@ -13232,19 +13295,19 @@
         <v>1</v>
       </c>
       <c r="AW6" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="AX6" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="AY6">
         <v>96</v>
       </c>
       <c r="AZ6" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="BA6">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="BB6">
         <v>0</v>
@@ -13279,16 +13342,16 @@
         <v>1</v>
       </c>
       <c r="AG7">
-        <v>20000</v>
+        <v>41400</v>
       </c>
       <c r="AH7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AI7" t="b">
         <v>1</v>
       </c>
       <c r="AJ7" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="AK7">
         <v>2</v>
@@ -13297,7 +13360,7 @@
         <v>9</v>
       </c>
       <c r="AM7" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="AN7">
         <v>1</v>
@@ -13309,10 +13372,10 @@
         <v>1</v>
       </c>
       <c r="AQ7">
-        <v>6000</v>
+        <v>12420</v>
       </c>
       <c r="AR7">
-        <v>20000</v>
+        <v>41400</v>
       </c>
       <c r="AS7">
         <v>0.95</v>
@@ -13327,16 +13390,16 @@
         <v>1</v>
       </c>
       <c r="AW7" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="AX7" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="AY7">
         <v>96</v>
       </c>
       <c r="AZ7" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="BA7">
         <v>60</v>
@@ -13411,85 +13474,85 @@
         <v>128</v>
       </c>
       <c r="R1" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="S1" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="AK1" s="1" t="s">
-        <v>287</v>
-      </c>
       <c r="AL1" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="2" spans="1:44">
@@ -13497,7 +13560,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F2">
         <v>96</v>
@@ -13515,10 +13578,10 @@
         <v>1</v>
       </c>
       <c r="K2">
-        <v>1050000</v>
+        <v>849000</v>
       </c>
       <c r="L2">
-        <v>5840000</v>
+        <v>4300000</v>
       </c>
       <c r="M2">
         <v>0.95</v>
@@ -13533,19 +13596,19 @@
         <v>1</v>
       </c>
       <c r="Q2" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="AL2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="AM2">
         <v>96</v>
       </c>
       <c r="AN2" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="AO2">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="AP2">
         <v>0</v>
@@ -13562,7 +13625,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F3">
         <v>96</v>
@@ -13580,10 +13643,10 @@
         <v>1</v>
       </c>
       <c r="K3">
-        <v>1080000</v>
+        <v>1741000</v>
       </c>
       <c r="L3">
-        <v>5770000</v>
+        <v>7230000</v>
       </c>
       <c r="M3">
         <v>0.95</v>
@@ -13598,19 +13661,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="AL3" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="AM3">
         <v>96</v>
       </c>
       <c r="AN3" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="AO3">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="AP3">
         <v>0</v>
@@ -13627,7 +13690,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F4">
         <v>96</v>
@@ -13645,10 +13708,10 @@
         <v>1</v>
       </c>
       <c r="K4">
-        <v>1900000</v>
+        <v>894000</v>
       </c>
       <c r="L4">
-        <v>6030000</v>
+        <v>5300000</v>
       </c>
       <c r="M4">
         <v>0.95</v>
@@ -13663,19 +13726,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="AL4" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="AM4">
         <v>96</v>
       </c>
       <c r="AN4" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="AO4">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="AP4">
         <v>0</v>
@@ -13692,7 +13755,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F5">
         <v>96</v>
@@ -13710,10 +13773,10 @@
         <v>1</v>
       </c>
       <c r="U5">
-        <v>844000000</v>
+        <v>1505000000</v>
       </c>
       <c r="V5">
-        <v>4680000000</v>
+        <v>8690000000</v>
       </c>
       <c r="W5">
         <v>0.95</v>
@@ -13728,19 +13791,19 @@
         <v>1</v>
       </c>
       <c r="AA5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="AL5" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="AM5">
         <v>96</v>
       </c>
       <c r="AN5" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="AO5">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="AP5">
         <v>0</v>
@@ -13757,7 +13820,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F6">
         <v>96</v>
@@ -13775,10 +13838,10 @@
         <v>1</v>
       </c>
       <c r="U6">
-        <v>1135000000</v>
+        <v>972000000</v>
       </c>
       <c r="V6">
-        <v>4340000000</v>
+        <v>5220000000</v>
       </c>
       <c r="W6">
         <v>0.95</v>
@@ -13793,19 +13856,19 @@
         <v>1</v>
       </c>
       <c r="AA6" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="AL6" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="AM6">
         <v>96</v>
       </c>
       <c r="AN6" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="AO6">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="AP6">
         <v>0</v>
@@ -13822,7 +13885,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F7">
         <v>96</v>
@@ -13840,10 +13903,10 @@
         <v>1</v>
       </c>
       <c r="U7">
-        <v>2280000000</v>
+        <v>831000000</v>
       </c>
       <c r="V7">
-        <v>9980000000</v>
+        <v>5670000000</v>
       </c>
       <c r="W7">
         <v>0.95</v>
@@ -13858,19 +13921,19 @@
         <v>1</v>
       </c>
       <c r="AA7" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="AL7" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="AM7">
         <v>96</v>
       </c>
       <c r="AN7" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="AO7">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="AP7">
         <v>0</v>
@@ -13887,7 +13950,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F8">
         <v>96</v>
@@ -13905,10 +13968,10 @@
         <v>1</v>
       </c>
       <c r="AE8">
-        <v>107900000</v>
+        <v>110000000</v>
       </c>
       <c r="AF8">
-        <v>429000000</v>
+        <v>558000000</v>
       </c>
       <c r="AG8">
         <v>0.95</v>
@@ -13923,19 +13986,19 @@
         <v>1</v>
       </c>
       <c r="AK8" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="AL8" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="AM8">
         <v>96</v>
       </c>
       <c r="AN8" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="AO8">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="AP8">
         <v>0</v>
@@ -13952,7 +14015,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F9">
         <v>96</v>
@@ -13970,10 +14033,10 @@
         <v>1</v>
       </c>
       <c r="AE9">
-        <v>99800000</v>
+        <v>110000000</v>
       </c>
       <c r="AF9">
-        <v>458000000</v>
+        <v>448000000</v>
       </c>
       <c r="AG9">
         <v>0.95</v>
@@ -13988,19 +14051,19 @@
         <v>1</v>
       </c>
       <c r="AK9" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="AL9" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="AM9">
         <v>96</v>
       </c>
       <c r="AN9" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="AO9">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="AP9">
         <v>0</v>
@@ -14017,7 +14080,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F10">
         <v>96</v>
@@ -14035,10 +14098,10 @@
         <v>1</v>
       </c>
       <c r="AE10">
-        <v>216300000</v>
+        <v>169000000</v>
       </c>
       <c r="AF10">
-        <v>890000000</v>
+        <v>761000000</v>
       </c>
       <c r="AG10">
         <v>0.95</v>
@@ -14053,16 +14116,16 @@
         <v>1</v>
       </c>
       <c r="AK10" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="AL10" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="AM10">
         <v>96</v>
       </c>
       <c r="AN10" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="AO10">
         <v>48</v>

--- a/02 - config/example_small/agents.xlsx
+++ b/02 - config/example_small/agents.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1574" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1567" uniqueCount="292">
   <si>
     <t>general/agent_id</t>
   </si>
@@ -459,357 +459,357 @@
     <t>meter/prob_missing</t>
   </si>
   <si>
-    <t>CAQ4qbKndqVO5KP</t>
-  </si>
-  <si>
-    <t>P05FuuJKAHoBtll</t>
-  </si>
-  <si>
-    <t>38JpW7PalZEayze</t>
-  </si>
-  <si>
-    <t>OrzVnFyFf8KDWZb</t>
-  </si>
-  <si>
-    <t>0jX330LTbs2R0pg</t>
-  </si>
-  <si>
-    <t>qm3wd3abNgNc06L</t>
-  </si>
-  <si>
-    <t>JbNr6emSGvLnXxr</t>
-  </si>
-  <si>
-    <t>fpCwBkrz7WURF2f</t>
-  </si>
-  <si>
-    <t>mlNdcfxpXKZxCp7</t>
-  </si>
-  <si>
-    <t>bGXeG7MNEBuSaN5</t>
+    <t>85OcAnXoAWzVXiz</t>
+  </si>
+  <si>
+    <t>WUQzXQYzy4jtobE</t>
+  </si>
+  <si>
+    <t>yMnvB8vacnThvoo</t>
+  </si>
+  <si>
+    <t>CCCzQQIi4yBhbOV</t>
+  </si>
+  <si>
+    <t>m9UYvGqGKxKX6Oy</t>
+  </si>
+  <si>
+    <t>haa0bjqGLyXbli3</t>
+  </si>
+  <si>
+    <t>1Rtp5AAm1eWDQYY</t>
+  </si>
+  <si>
+    <t>EzZmpalQdDMnjVo</t>
+  </si>
+  <si>
+    <t>jtLUQSNHbKw4gUF</t>
+  </si>
+  <si>
+    <t>6ldRHmyAwMn1U39</t>
   </si>
   <si>
     <t>hh_3564_0.csv</t>
   </si>
   <si>
+    <t>hh_2959_0.csv</t>
+  </si>
+  <si>
+    <t>hh_3648_0.csv</t>
+  </si>
+  <si>
+    <t>hh_4536_0.csv</t>
+  </si>
+  <si>
     <t>hh_5527_0.csv</t>
   </si>
   <si>
+    <t>hh_2896_0.csv</t>
+  </si>
+  <si>
+    <t>naive_average</t>
+  </si>
+  <si>
+    <t>[2, 0, 2, 2, 0, 0, 96, 2, 0, 0, 672]</t>
+  </si>
+  <si>
+    <t>heat_3564_0.csv</t>
+  </si>
+  <si>
+    <t>heat_gen_1_pu.csv</t>
+  </si>
+  <si>
+    <t>heat_3648_0.csv</t>
+  </si>
+  <si>
+    <t>heat_4536_0.csv</t>
+  </si>
+  <si>
+    <t>heat_gen_0_pu.csv</t>
+  </si>
+  <si>
+    <t>heat_5527_0.csv</t>
+  </si>
+  <si>
+    <t>heat_gen_5_pu.csv</t>
+  </si>
+  <si>
+    <t>dhw_gen_5_pu.csv</t>
+  </si>
+  <si>
+    <t>dhw_gen_1_pu.csv</t>
+  </si>
+  <si>
+    <t>dhw_gen_3_pu.csv</t>
+  </si>
+  <si>
+    <t>dhw_gen_2_pu.csv</t>
+  </si>
+  <si>
+    <t>dhw_gen_0_pu.csv</t>
+  </si>
+  <si>
+    <t>pv_config.json</t>
+  </si>
+  <si>
+    <t>smoothed</t>
+  </si>
+  <si>
+    <t>green_local</t>
+  </si>
+  <si>
+    <t>wind_Enercon_E-53-800_800000_53.json</t>
+  </si>
+  <si>
+    <t>wind_Senvion-REpower_3.2M122_3200000_122.json</t>
+  </si>
+  <si>
+    <t>wind_Nordex_MM92_3300000_131.json</t>
+  </si>
+  <si>
+    <t>weather</t>
+  </si>
+  <si>
+    <t>local</t>
+  </si>
+  <si>
+    <t>ev_fulltime_45.csv</t>
+  </si>
+  <si>
+    <t>ev_parttime_89.csv</t>
+  </si>
+  <si>
+    <t>ev_freetime_3.csv</t>
+  </si>
+  <si>
+    <t>ev_parttime_88.csv</t>
+  </si>
+  <si>
+    <t>ev_freetime_0.csv</t>
+  </si>
+  <si>
+    <t>price_sensitive</t>
+  </si>
+  <si>
+    <t>ev_close</t>
+  </si>
+  <si>
+    <t>True</t>
+  </si>
+  <si>
+    <t>naive</t>
+  </si>
+  <si>
+    <t>linear</t>
+  </si>
+  <si>
+    <t>general/sub_id</t>
+  </si>
+  <si>
+    <t>general/parameters/apartments_independent</t>
+  </si>
+  <si>
+    <t>general/parameters/apartments</t>
+  </si>
+  <si>
+    <t>KSVgzUkzHWmZoxE</t>
+  </si>
+  <si>
+    <t>D3nJBkgTRextEOV</t>
+  </si>
+  <si>
+    <t>main</t>
+  </si>
+  <si>
+    <t>ljnJBCuYwGrTCqH</t>
+  </si>
+  <si>
+    <t>3yv6idHMZPaBRKM</t>
+  </si>
+  <si>
+    <t>URoantseLpgQSUn</t>
+  </si>
+  <si>
+    <t>4dZC2vYJpF0L2sf</t>
+  </si>
+  <si>
+    <t>H8jngziCeheuT4h</t>
+  </si>
+  <si>
+    <t>F0NxcAvySB924yr</t>
+  </si>
+  <si>
+    <t>fHmJ96Cs7swtOPU</t>
+  </si>
+  <si>
+    <t>DVqUcflLGmxGIeq</t>
+  </si>
+  <si>
+    <t>eohu0Ci5A4Fvhze</t>
+  </si>
+  <si>
+    <t>V6eJ541dzI0Pt50</t>
+  </si>
+  <si>
+    <t>J36fCl1ewehf2CN</t>
+  </si>
+  <si>
+    <t>CLqk9xFVGSMAMI8</t>
+  </si>
+  <si>
+    <t>QD4sT9bCmy3iHgt</t>
+  </si>
+  <si>
+    <t>tl80vkZuQBr6htJ</t>
+  </si>
+  <si>
+    <t>hh_1720_0.csv</t>
+  </si>
+  <si>
     <t>hh_2532_0.csv</t>
   </si>
   <si>
-    <t>hh_4536_0.csv</t>
-  </si>
-  <si>
-    <t>hh_3648_0.csv</t>
+    <t>hh_1009_1.csv</t>
+  </si>
+  <si>
+    <t>hh_2012_3.csv</t>
+  </si>
+  <si>
+    <t>hh_1546_2.csv</t>
+  </si>
+  <si>
+    <t>hh_1158_4.csv</t>
+  </si>
+  <si>
+    <t>hh_913_0.csv</t>
   </si>
   <si>
     <t>hh_2455_0.csv</t>
   </si>
   <si>
-    <t>naive_average</t>
-  </si>
-  <si>
-    <t>[2, 0, 2, 2, 0, 0, 96, 2, 0, 0, 672]</t>
+    <t>heat_gen_2_pu.csv</t>
+  </si>
+  <si>
+    <t>heat_gen_3_pu.csv</t>
   </si>
   <si>
     <t>heat_gen_4_pu.csv</t>
   </si>
   <si>
-    <t>heat_5527_0.csv</t>
-  </si>
-  <si>
-    <t>heat_gen_2_pu.csv</t>
-  </si>
-  <si>
-    <t>heat_4536_0.csv</t>
-  </si>
-  <si>
-    <t>heat_3648_0.csv</t>
-  </si>
-  <si>
-    <t>heat_2455_0.csv</t>
-  </si>
-  <si>
-    <t>heat_gen_3_pu.csv</t>
-  </si>
-  <si>
-    <t>dhw_gen_5_pu.csv</t>
-  </si>
-  <si>
     <t>dhw_gen_6_pu.csv</t>
   </si>
   <si>
-    <t>dhw_gen_3_pu.csv</t>
-  </si>
-  <si>
-    <t>dhw_gen_0_pu.csv</t>
-  </si>
-  <si>
-    <t>pv_config.json</t>
-  </si>
-  <si>
-    <t>smoothed</t>
-  </si>
-  <si>
-    <t>green_local</t>
-  </si>
-  <si>
-    <t>wind_Nordex_MM92_3300000_131.json</t>
-  </si>
-  <si>
-    <t>wind_Enercon_E-53-800_800000_53.json</t>
-  </si>
-  <si>
-    <t>wind_Enercon_E-101-3500-E2_3500000_101.json</t>
-  </si>
-  <si>
-    <t>weather</t>
-  </si>
-  <si>
-    <t>local</t>
-  </si>
-  <si>
-    <t>ev_fulltime_45.csv</t>
+    <t>dhw_gen_4_pu.csv</t>
+  </si>
+  <si>
+    <t>pv_3_pu.csv</t>
+  </si>
+  <si>
+    <t>pv_2_pu.csv</t>
+  </si>
+  <si>
+    <t>fixed_gen_1_pu.csv</t>
+  </si>
+  <si>
+    <t>ev_freetime_2.csv</t>
+  </si>
+  <si>
+    <t>ev_fulltime_49.csv</t>
+  </si>
+  <si>
+    <t>ev_fulltime_46.csv</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>o</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>general/parameters/type</t>
+  </si>
+  <si>
+    <t>general/fcast_retraining_frequency</t>
+  </si>
+  <si>
+    <t>TDYItO2GiYZAKhu</t>
+  </si>
+  <si>
+    <t>JFU6eluq545ccuO</t>
+  </si>
+  <si>
+    <t>wmAo1ULgFVFxYAZ</t>
+  </si>
+  <si>
+    <t>B19gFhY977lWUFj</t>
+  </si>
+  <si>
+    <t>office</t>
+  </si>
+  <si>
+    <t>retail</t>
+  </si>
+  <si>
+    <t>office_pu_0.csv</t>
+  </si>
+  <si>
+    <t>retail_pu_0.csv</t>
+  </si>
+  <si>
+    <t>full</t>
+  </si>
+  <si>
+    <t>q9rag9jEua72akX</t>
+  </si>
+  <si>
+    <t>Arvjm5ZgCBq8apL</t>
+  </si>
+  <si>
+    <t>food</t>
+  </si>
+  <si>
+    <t>tobacco</t>
+  </si>
+  <si>
+    <t>food_pu_0.csv</t>
+  </si>
+  <si>
+    <t>tobacco_pu_0.csv</t>
+  </si>
+  <si>
+    <t>ev_fulltime_44.csv</t>
   </si>
   <si>
     <t>ev_parttime_90.csv</t>
   </si>
   <si>
-    <t>ev_fulltime_42.csv</t>
-  </si>
-  <si>
-    <t>ev_fulltime_43.csv</t>
-  </si>
-  <si>
-    <t>ev_freetime_2.csv</t>
-  </si>
-  <si>
-    <t>price_sensitive</t>
-  </si>
-  <si>
-    <t>ev_close</t>
-  </si>
-  <si>
-    <t>True</t>
-  </si>
-  <si>
-    <t>naive</t>
-  </si>
-  <si>
-    <t>linear</t>
-  </si>
-  <si>
-    <t>general/sub_id</t>
-  </si>
-  <si>
-    <t>general/parameters/apartments_independent</t>
-  </si>
-  <si>
-    <t>general/parameters/apartments</t>
-  </si>
-  <si>
-    <t>fIN6RLaCSLIs34X</t>
-  </si>
-  <si>
-    <t>faG89XBS8LQGBIT</t>
-  </si>
-  <si>
-    <t>main</t>
-  </si>
-  <si>
-    <t>DPpRmoJAzEyUctg</t>
-  </si>
-  <si>
-    <t>eDCcydDkFdMhdg6</t>
-  </si>
-  <si>
-    <t>Zt7eMmbkydw68ro</t>
-  </si>
-  <si>
-    <t>b1bKdSrNn09lvTL</t>
-  </si>
-  <si>
-    <t>WDMMWj3CdvUYmAc</t>
-  </si>
-  <si>
-    <t>Rly2SV5bAywPsti</t>
-  </si>
-  <si>
-    <t>h0EK54BR0dStnX6</t>
-  </si>
-  <si>
-    <t>LWywX8b1UW7qsIv</t>
-  </si>
-  <si>
-    <t>n1aHpiesYKwTEdw</t>
-  </si>
-  <si>
-    <t>GXOwNhY6LN4QB5k</t>
-  </si>
-  <si>
-    <t>mI1HMp7xzXEQPVM</t>
-  </si>
-  <si>
-    <t>ligakxWTagqsUtW</t>
-  </si>
-  <si>
-    <t>2u0caNRWq8dkQXY</t>
-  </si>
-  <si>
-    <t>LLV6xoRvQ98GtrC</t>
-  </si>
-  <si>
-    <t>hh_2262_0.csv</t>
-  </si>
-  <si>
-    <t>hh_1720_0.csv</t>
-  </si>
-  <si>
-    <t>hh_1158_4.csv</t>
-  </si>
-  <si>
-    <t>hh_2687_0.csv</t>
-  </si>
-  <si>
-    <t>hh_1546_2.csv</t>
-  </si>
-  <si>
-    <t>hh_2012_3.csv</t>
-  </si>
-  <si>
-    <t>hh_2896_0.csv</t>
-  </si>
-  <si>
-    <t>hh_945_1.csv</t>
-  </si>
-  <si>
-    <t>heat_gen_0_pu.csv</t>
-  </si>
-  <si>
-    <t>heat_gen_1_pu.csv</t>
-  </si>
-  <si>
-    <t>dhw_gen_2_pu.csv</t>
-  </si>
-  <si>
-    <t>dhw_gen_4_pu.csv</t>
-  </si>
-  <si>
-    <t>dhw_gen_1_pu.csv</t>
-  </si>
-  <si>
-    <t>pv_2_pu.csv</t>
-  </si>
-  <si>
-    <t>pv_3_pu.csv</t>
-  </si>
-  <si>
-    <t>fixed_gen_1_pu.csv</t>
-  </si>
-  <si>
-    <t>ev_freetime_3.csv</t>
-  </si>
-  <si>
-    <t>ev_fulltime_49.csv</t>
-  </si>
-  <si>
-    <t>o</t>
-  </si>
-  <si>
-    <t>c</t>
-  </si>
-  <si>
-    <t>s</t>
-  </si>
-  <si>
-    <t>n</t>
-  </si>
-  <si>
-    <t>_</t>
-  </si>
-  <si>
-    <t>m</t>
-  </si>
-  <si>
-    <t>i</t>
-  </si>
-  <si>
-    <t>general/parameters/type</t>
-  </si>
-  <si>
-    <t>general/fcast_retraining_frequency</t>
-  </si>
-  <si>
-    <t>MiMOLDWdvO8Wy78</t>
-  </si>
-  <si>
-    <t>LmWc11DTOn0d34C</t>
-  </si>
-  <si>
-    <t>pR9hLQSVdZLInjy</t>
-  </si>
-  <si>
-    <t>d6WTzfkMUtlLlDo</t>
-  </si>
-  <si>
-    <t>retail</t>
-  </si>
-  <si>
-    <t>office</t>
-  </si>
-  <si>
-    <t>retail_pu_0.csv</t>
-  </si>
-  <si>
-    <t>office_pu_0.csv</t>
+    <t>YzrNpIZaH81XYK1</t>
+  </si>
+  <si>
+    <t>RjG9yN5f1xlSkY1</t>
+  </si>
+  <si>
+    <t>ALpYcNUGcbhsyGP</t>
+  </si>
+  <si>
+    <t>aLQaBccQhJ2nHym</t>
+  </si>
+  <si>
+    <t>X3seNe9BpEogbqy</t>
+  </si>
+  <si>
+    <t>2fklRDBuX5udtrN</t>
   </si>
   <si>
     <t>pv_1_pu.csv</t>
   </si>
   <si>
-    <t>QnFhm1Pv1aaVe0g</t>
-  </si>
-  <si>
-    <t>QOE3HKoozDCq8tw</t>
-  </si>
-  <si>
-    <t>tobacco</t>
-  </si>
-  <si>
-    <t>food</t>
-  </si>
-  <si>
-    <t>tobacco_pu_0.csv</t>
-  </si>
-  <si>
-    <t>food_pu_0.csv</t>
-  </si>
-  <si>
-    <t>wind_Siemens_SWT-3.6-130_3600000_130.json</t>
-  </si>
-  <si>
-    <t>full</t>
-  </si>
-  <si>
-    <t>kWZJYPkjAMgoDTy</t>
-  </si>
-  <si>
-    <t>Xt6DSBzm6ZkFE2b</t>
-  </si>
-  <si>
-    <t>e4NO5d4L5ogT5e1</t>
-  </si>
-  <si>
-    <t>kHfE5aklazt9gY8</t>
-  </si>
-  <si>
-    <t>MbYREwE6tBPw9O8</t>
-  </si>
-  <si>
-    <t>BDhRg5rXQtx9OCW</t>
-  </si>
-  <si>
     <t>psh/owner</t>
   </si>
   <si>
@@ -870,31 +870,31 @@
     <t>hydrogen/quality</t>
   </si>
   <si>
-    <t>VpVR0SQWDVXCpS0</t>
-  </si>
-  <si>
-    <t>sKBLdqZTKGHC4b4</t>
-  </si>
-  <si>
-    <t>PKrckh0Gawj8Y7F</t>
-  </si>
-  <si>
-    <t>Mc1s4lH5J7oAYcD</t>
-  </si>
-  <si>
-    <t>ZnZ0VFZkWBQuGen</t>
-  </si>
-  <si>
-    <t>0UaMMVpfNCH8L0A</t>
-  </si>
-  <si>
-    <t>N7C5Izpti9DJles</t>
-  </si>
-  <si>
-    <t>pLVa3kyoqiBUhUx</t>
-  </si>
-  <si>
-    <t>yAHbtlZFRelcTi6</t>
+    <t>JZTLOzrhDktoFBp</t>
+  </si>
+  <si>
+    <t>bv8qLecI0Gmft9g</t>
+  </si>
+  <si>
+    <t>cjmnPoB5PjwrOUk</t>
+  </si>
+  <si>
+    <t>D8zfKDOrEcCmwaW</t>
+  </si>
+  <si>
+    <t>Hx64ZvyXILOowRg</t>
+  </si>
+  <si>
+    <t>C5UXiO8NYmtVeVJ</t>
+  </si>
+  <si>
+    <t>L9xxc3yDFBJdsnN</t>
+  </si>
+  <si>
+    <t>HuafEubsIQck1gd</t>
+  </si>
+  <si>
+    <t>jFP8I3FhrxO0bnd</t>
   </si>
 </sst>
 </file>
@@ -1847,22 +1847,22 @@
         <v>1</v>
       </c>
       <c r="BD2">
-        <v>5800</v>
+        <v>6400</v>
       </c>
       <c r="BE2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="BF2">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="BG2">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="BH2" t="b">
         <v>1</v>
       </c>
       <c r="BI2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BJ2">
         <v>2</v>
@@ -1871,41 +1871,41 @@
         <v>9</v>
       </c>
       <c r="BL2" t="s">
+        <v>178</v>
+      </c>
+      <c r="BM2">
+        <v>0</v>
+      </c>
+      <c r="BN2">
+        <v>0</v>
+      </c>
+      <c r="BO2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BS2" t="s">
+        <v>182</v>
+      </c>
+      <c r="BT2">
+        <v>2</v>
+      </c>
+      <c r="BU2">
+        <v>9</v>
+      </c>
+      <c r="BV2" t="s">
+        <v>178</v>
+      </c>
+      <c r="BW2">
+        <v>0</v>
+      </c>
+      <c r="BX2">
+        <v>0</v>
+      </c>
+      <c r="BY2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CC2" t="s">
         <v>177</v>
       </c>
-      <c r="BM2">
-        <v>0</v>
-      </c>
-      <c r="BN2">
-        <v>0</v>
-      </c>
-      <c r="BO2" t="b">
-        <v>1</v>
-      </c>
-      <c r="BS2" t="s">
-        <v>181</v>
-      </c>
-      <c r="BT2">
-        <v>2</v>
-      </c>
-      <c r="BU2">
-        <v>9</v>
-      </c>
-      <c r="BV2" t="s">
-        <v>177</v>
-      </c>
-      <c r="BW2">
-        <v>0</v>
-      </c>
-      <c r="BX2">
-        <v>0</v>
-      </c>
-      <c r="BY2" t="b">
-        <v>1</v>
-      </c>
-      <c r="CC2" t="s">
-        <v>176</v>
-      </c>
       <c r="CD2">
         <v>2</v>
       </c>
@@ -1913,7 +1913,7 @@
         <v>9</v>
       </c>
       <c r="CF2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CG2">
         <v>0</v>
@@ -1925,79 +1925,19 @@
         <v>1</v>
       </c>
       <c r="CL2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CM2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CO2" t="b">
         <v>1</v>
       </c>
-      <c r="CP2" t="s">
-        <v>183</v>
-      </c>
-      <c r="CQ2">
-        <v>100000</v>
-      </c>
-      <c r="CR2">
-        <v>25000</v>
-      </c>
-      <c r="CS2">
-        <v>11000</v>
-      </c>
-      <c r="CT2">
-        <v>22000</v>
-      </c>
-      <c r="CU2">
-        <v>200000</v>
-      </c>
-      <c r="CV2">
-        <v>0.9</v>
-      </c>
-      <c r="CW2">
-        <v>0.8</v>
-      </c>
-      <c r="CX2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CY2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CZ2" t="s">
-        <v>183</v>
-      </c>
-      <c r="DA2">
-        <v>75000</v>
-      </c>
-      <c r="DB2">
-        <v>20000</v>
-      </c>
-      <c r="DC2">
-        <v>7200</v>
-      </c>
-      <c r="DD2">
-        <v>11000</v>
-      </c>
-      <c r="DE2">
-        <v>100000</v>
-      </c>
-      <c r="DF2">
-        <v>0.9</v>
-      </c>
-      <c r="DG2">
-        <v>0.8</v>
-      </c>
-      <c r="DH2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DI2" t="b">
-        <v>0</v>
-      </c>
       <c r="DJ2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="DK2">
         <v>0.05</v>
@@ -2012,22 +1952,40 @@
         <v>8.5</v>
       </c>
       <c r="DO2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="DP2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="DQ2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS2" t="s">
-        <v>190</v>
+        <v>191</v>
+      </c>
+      <c r="DT2">
+        <v>3600</v>
+      </c>
+      <c r="DU2">
+        <v>3600</v>
+      </c>
+      <c r="DV2">
+        <v>0.95</v>
+      </c>
+      <c r="DW2">
+        <v>0.1</v>
+      </c>
+      <c r="DX2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DY2" t="b">
+        <v>0</v>
       </c>
       <c r="DZ2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="EA2">
         <v>0</v>
@@ -2036,28 +1994,28 @@
         <v>0</v>
       </c>
       <c r="EC2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="EH2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="EI2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="EJ2">
         <v>96</v>
       </c>
       <c r="EK2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="EL2">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="EM2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="EN2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="EO2">
         <v>0</v>
@@ -2077,10 +2035,10 @@
         <v>147</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G3">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="H3">
         <v>2</v>
@@ -2089,7 +2047,7 @@
         <v>2.6</v>
       </c>
       <c r="J3">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="K3">
         <v>1</v>
@@ -2104,7 +2062,7 @@
         <v>1</v>
       </c>
       <c r="O3">
-        <v>5527000</v>
+        <v>2959000</v>
       </c>
       <c r="P3" t="s">
         <v>157</v>
@@ -2155,13 +2113,13 @@
         <v>1</v>
       </c>
       <c r="AH3">
-        <v>5500000</v>
+        <v>19500000</v>
       </c>
       <c r="AI3" t="s">
         <v>165</v>
       </c>
       <c r="AJ3">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="AK3" t="s">
         <v>162</v>
@@ -2188,7 +2146,7 @@
         <v>1</v>
       </c>
       <c r="AS3">
-        <v>2400000</v>
+        <v>2800000</v>
       </c>
       <c r="AT3" t="s">
         <v>172</v>
@@ -2212,16 +2170,31 @@
         <v>90</v>
       </c>
       <c r="BA3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC3" t="b">
         <v>1</v>
       </c>
+      <c r="BD3">
+        <v>4200</v>
+      </c>
+      <c r="BE3" t="s">
+        <v>176</v>
+      </c>
+      <c r="BF3">
+        <v>0</v>
+      </c>
+      <c r="BG3">
+        <v>40</v>
+      </c>
+      <c r="BH3" t="b">
+        <v>1</v>
+      </c>
       <c r="BI3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BJ3">
         <v>2</v>
@@ -2230,41 +2203,50 @@
         <v>9</v>
       </c>
       <c r="BL3" t="s">
+        <v>178</v>
+      </c>
+      <c r="BM3">
+        <v>1</v>
+      </c>
+      <c r="BN3">
+        <v>1</v>
+      </c>
+      <c r="BO3" t="b">
+        <v>1</v>
+      </c>
+      <c r="BP3">
+        <v>2100</v>
+      </c>
+      <c r="BQ3" t="s">
+        <v>179</v>
+      </c>
+      <c r="BR3" t="b">
+        <v>1</v>
+      </c>
+      <c r="BS3" t="s">
+        <v>182</v>
+      </c>
+      <c r="BT3">
+        <v>2</v>
+      </c>
+      <c r="BU3">
+        <v>9</v>
+      </c>
+      <c r="BV3" t="s">
+        <v>178</v>
+      </c>
+      <c r="BW3">
+        <v>0</v>
+      </c>
+      <c r="BX3">
+        <v>0</v>
+      </c>
+      <c r="BY3" t="b">
+        <v>1</v>
+      </c>
+      <c r="CC3" t="s">
         <v>177</v>
       </c>
-      <c r="BM3">
-        <v>0</v>
-      </c>
-      <c r="BN3">
-        <v>0</v>
-      </c>
-      <c r="BO3" t="b">
-        <v>1</v>
-      </c>
-      <c r="BS3" t="s">
-        <v>181</v>
-      </c>
-      <c r="BT3">
-        <v>2</v>
-      </c>
-      <c r="BU3">
-        <v>9</v>
-      </c>
-      <c r="BV3" t="s">
-        <v>177</v>
-      </c>
-      <c r="BW3">
-        <v>0</v>
-      </c>
-      <c r="BX3">
-        <v>0</v>
-      </c>
-      <c r="BY3" t="b">
-        <v>1</v>
-      </c>
-      <c r="CC3" t="s">
-        <v>176</v>
-      </c>
       <c r="CD3">
         <v>2</v>
       </c>
@@ -2272,7 +2254,7 @@
         <v>9</v>
       </c>
       <c r="CF3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CG3">
         <v>0</v>
@@ -2284,7 +2266,7 @@
         <v>1</v>
       </c>
       <c r="CL3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CM3">
         <v>0</v>
@@ -2296,7 +2278,7 @@
         <v>1</v>
       </c>
       <c r="DJ3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="DK3">
         <v>0.05</v>
@@ -2311,22 +2293,40 @@
         <v>8.5</v>
       </c>
       <c r="DO3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="DP3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="DQ3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS3" t="s">
-        <v>190</v>
+        <v>191</v>
+      </c>
+      <c r="DT3">
+        <v>3000</v>
+      </c>
+      <c r="DU3">
+        <v>3000</v>
+      </c>
+      <c r="DV3">
+        <v>0.95</v>
+      </c>
+      <c r="DW3">
+        <v>0.1</v>
+      </c>
+      <c r="DX3" t="b">
+        <v>0</v>
+      </c>
+      <c r="DY3" t="b">
+        <v>0</v>
       </c>
       <c r="DZ3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="EA3">
         <v>0</v>
@@ -2335,25 +2335,25 @@
         <v>0</v>
       </c>
       <c r="EC3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="EH3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="EI3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="EJ3">
         <v>96</v>
       </c>
       <c r="EK3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="EL3">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="EM3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="EN3">
         <v>0</v>
@@ -2376,10 +2376,10 @@
         <v>148</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G4">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="H4">
         <v>2</v>
@@ -2388,7 +2388,7 @@
         <v>2.6</v>
       </c>
       <c r="J4">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="K4">
         <v>1</v>
@@ -2403,10 +2403,10 @@
         <v>1</v>
       </c>
       <c r="O4">
-        <v>2532000</v>
+        <v>3564000</v>
       </c>
       <c r="P4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="Q4" t="s">
         <v>162</v>
@@ -2454,10 +2454,10 @@
         <v>1</v>
       </c>
       <c r="AH4">
-        <v>5500000</v>
+        <v>19500000</v>
       </c>
       <c r="AI4" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="AJ4">
         <v>55</v>
@@ -2487,7 +2487,7 @@
         <v>1</v>
       </c>
       <c r="AS4">
-        <v>1800000</v>
+        <v>3200000</v>
       </c>
       <c r="AT4" t="s">
         <v>173</v>
@@ -2520,10 +2520,10 @@
         <v>1</v>
       </c>
       <c r="BD4">
-        <v>3600</v>
+        <v>6100</v>
       </c>
       <c r="BE4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="BF4">
         <v>0</v>
@@ -2535,7 +2535,7 @@
         <v>1</v>
       </c>
       <c r="BI4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BJ4">
         <v>2</v>
@@ -2544,50 +2544,50 @@
         <v>9</v>
       </c>
       <c r="BL4" t="s">
+        <v>178</v>
+      </c>
+      <c r="BM4">
+        <v>1</v>
+      </c>
+      <c r="BN4">
+        <v>1</v>
+      </c>
+      <c r="BO4" t="b">
+        <v>1</v>
+      </c>
+      <c r="BP4">
+        <v>2400</v>
+      </c>
+      <c r="BQ4" t="s">
+        <v>180</v>
+      </c>
+      <c r="BR4" t="b">
+        <v>1</v>
+      </c>
+      <c r="BS4" t="s">
+        <v>182</v>
+      </c>
+      <c r="BT4">
+        <v>2</v>
+      </c>
+      <c r="BU4">
+        <v>9</v>
+      </c>
+      <c r="BV4" t="s">
+        <v>178</v>
+      </c>
+      <c r="BW4">
+        <v>0</v>
+      </c>
+      <c r="BX4">
+        <v>0</v>
+      </c>
+      <c r="BY4" t="b">
+        <v>1</v>
+      </c>
+      <c r="CC4" t="s">
         <v>177</v>
       </c>
-      <c r="BM4">
-        <v>1</v>
-      </c>
-      <c r="BN4">
-        <v>1</v>
-      </c>
-      <c r="BO4" t="b">
-        <v>1</v>
-      </c>
-      <c r="BP4">
-        <v>2100</v>
-      </c>
-      <c r="BQ4" t="s">
-        <v>178</v>
-      </c>
-      <c r="BR4" t="b">
-        <v>1</v>
-      </c>
-      <c r="BS4" t="s">
-        <v>181</v>
-      </c>
-      <c r="BT4">
-        <v>2</v>
-      </c>
-      <c r="BU4">
-        <v>9</v>
-      </c>
-      <c r="BV4" t="s">
-        <v>177</v>
-      </c>
-      <c r="BW4">
-        <v>0</v>
-      </c>
-      <c r="BX4">
-        <v>0</v>
-      </c>
-      <c r="BY4" t="b">
-        <v>1</v>
-      </c>
-      <c r="CC4" t="s">
-        <v>176</v>
-      </c>
       <c r="CD4">
         <v>2</v>
       </c>
@@ -2595,7 +2595,7 @@
         <v>9</v>
       </c>
       <c r="CF4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CG4">
         <v>0</v>
@@ -2607,49 +2607,19 @@
         <v>1</v>
       </c>
       <c r="CL4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CM4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO4" t="b">
         <v>1</v>
       </c>
-      <c r="CP4" t="s">
-        <v>184</v>
-      </c>
-      <c r="CQ4">
-        <v>50000</v>
-      </c>
-      <c r="CR4">
-        <v>15000</v>
-      </c>
-      <c r="CS4">
-        <v>7200</v>
-      </c>
-      <c r="CT4">
-        <v>7200</v>
-      </c>
-      <c r="CU4">
-        <v>50000</v>
-      </c>
-      <c r="CV4">
-        <v>0.9</v>
-      </c>
-      <c r="CW4">
-        <v>0.8</v>
-      </c>
-      <c r="CX4" t="b">
-        <v>0</v>
-      </c>
-      <c r="CY4" t="b">
-        <v>0</v>
-      </c>
       <c r="DJ4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="DK4">
         <v>0.05</v>
@@ -2664,10 +2634,10 @@
         <v>8.5</v>
       </c>
       <c r="DO4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="DP4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="DQ4">
         <v>1</v>
@@ -2676,13 +2646,13 @@
         <v>1</v>
       </c>
       <c r="DS4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="DT4">
-        <v>2500</v>
+        <v>3600</v>
       </c>
       <c r="DU4">
-        <v>2500</v>
+        <v>3600</v>
       </c>
       <c r="DV4">
         <v>0.95</v>
@@ -2697,7 +2667,7 @@
         <v>0</v>
       </c>
       <c r="DZ4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="EA4">
         <v>0</v>
@@ -2706,25 +2676,25 @@
         <v>0</v>
       </c>
       <c r="EC4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="EH4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="EI4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="EJ4">
         <v>96</v>
       </c>
       <c r="EK4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="EL4">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="EM4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="EN4">
         <v>30</v>
@@ -2774,10 +2744,10 @@
         <v>1</v>
       </c>
       <c r="O5">
-        <v>4536000</v>
+        <v>3648000</v>
       </c>
       <c r="P5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="Q5" t="s">
         <v>162</v>
@@ -2828,7 +2798,7 @@
         <v>19500000</v>
       </c>
       <c r="AI5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AJ5">
         <v>35</v>
@@ -2858,10 +2828,10 @@
         <v>1</v>
       </c>
       <c r="AS5">
-        <v>2400000</v>
+        <v>2800000</v>
       </c>
       <c r="AT5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AU5">
         <v>55</v>
@@ -2882,31 +2852,16 @@
         <v>90</v>
       </c>
       <c r="BA5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC5" t="b">
         <v>1</v>
       </c>
-      <c r="BD5">
-        <v>6400</v>
-      </c>
-      <c r="BE5" t="s">
-        <v>175</v>
-      </c>
-      <c r="BF5">
-        <v>-20</v>
-      </c>
-      <c r="BG5">
-        <v>50</v>
-      </c>
-      <c r="BH5" t="b">
-        <v>1</v>
-      </c>
       <c r="BI5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BJ5">
         <v>2</v>
@@ -2915,50 +2870,50 @@
         <v>9</v>
       </c>
       <c r="BL5" t="s">
+        <v>178</v>
+      </c>
+      <c r="BM5">
+        <v>1</v>
+      </c>
+      <c r="BN5">
+        <v>1</v>
+      </c>
+      <c r="BO5" t="b">
+        <v>1</v>
+      </c>
+      <c r="BP5">
+        <v>2700</v>
+      </c>
+      <c r="BQ5" t="s">
+        <v>181</v>
+      </c>
+      <c r="BR5" t="b">
+        <v>1</v>
+      </c>
+      <c r="BS5" t="s">
+        <v>182</v>
+      </c>
+      <c r="BT5">
+        <v>2</v>
+      </c>
+      <c r="BU5">
+        <v>9</v>
+      </c>
+      <c r="BV5" t="s">
+        <v>178</v>
+      </c>
+      <c r="BW5">
+        <v>0</v>
+      </c>
+      <c r="BX5">
+        <v>0</v>
+      </c>
+      <c r="BY5" t="b">
+        <v>1</v>
+      </c>
+      <c r="CC5" t="s">
         <v>177</v>
       </c>
-      <c r="BM5">
-        <v>1</v>
-      </c>
-      <c r="BN5">
-        <v>1</v>
-      </c>
-      <c r="BO5" t="b">
-        <v>1</v>
-      </c>
-      <c r="BP5">
-        <v>3100</v>
-      </c>
-      <c r="BQ5" t="s">
-        <v>179</v>
-      </c>
-      <c r="BR5" t="b">
-        <v>1</v>
-      </c>
-      <c r="BS5" t="s">
-        <v>181</v>
-      </c>
-      <c r="BT5">
-        <v>2</v>
-      </c>
-      <c r="BU5">
-        <v>9</v>
-      </c>
-      <c r="BV5" t="s">
-        <v>177</v>
-      </c>
-      <c r="BW5">
-        <v>0</v>
-      </c>
-      <c r="BX5">
-        <v>0</v>
-      </c>
-      <c r="BY5" t="b">
-        <v>1</v>
-      </c>
-      <c r="CC5" t="s">
-        <v>176</v>
-      </c>
       <c r="CD5">
         <v>2</v>
       </c>
@@ -2966,7 +2921,7 @@
         <v>9</v>
       </c>
       <c r="CF5" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CG5">
         <v>0</v>
@@ -2978,19 +2933,49 @@
         <v>1</v>
       </c>
       <c r="CL5" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CM5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO5" t="b">
         <v>1</v>
       </c>
+      <c r="CP5" t="s">
+        <v>184</v>
+      </c>
+      <c r="CQ5">
+        <v>75000</v>
+      </c>
+      <c r="CR5">
+        <v>20000</v>
+      </c>
+      <c r="CS5">
+        <v>7200</v>
+      </c>
+      <c r="CT5">
+        <v>11000</v>
+      </c>
+      <c r="CU5">
+        <v>100000</v>
+      </c>
+      <c r="CV5">
+        <v>0.9</v>
+      </c>
+      <c r="CW5">
+        <v>0.8</v>
+      </c>
+      <c r="CX5" t="b">
+        <v>0</v>
+      </c>
+      <c r="CY5" t="b">
+        <v>0</v>
+      </c>
       <c r="DJ5" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="DK5">
         <v>0.05</v>
@@ -3005,10 +2990,10 @@
         <v>8.5</v>
       </c>
       <c r="DO5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="DP5" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="DQ5">
         <v>0</v>
@@ -3017,10 +3002,10 @@
         <v>0</v>
       </c>
       <c r="DS5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="DZ5" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="EA5">
         <v>0</v>
@@ -3029,25 +3014,25 @@
         <v>0</v>
       </c>
       <c r="EC5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="EH5" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="EI5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="EJ5">
         <v>96</v>
       </c>
       <c r="EK5" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="EL5">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="EM5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="EN5">
         <v>0</v>
@@ -3070,10 +3055,10 @@
         <v>150</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H6">
         <v>2</v>
@@ -3082,7 +3067,7 @@
         <v>2.6</v>
       </c>
       <c r="J6">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -3097,10 +3082,10 @@
         <v>1</v>
       </c>
       <c r="O6">
-        <v>5527000</v>
+        <v>3564000</v>
       </c>
       <c r="P6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Q6" t="s">
         <v>162</v>
@@ -3148,10 +3133,10 @@
         <v>1</v>
       </c>
       <c r="AH6">
-        <v>19500000</v>
+        <v>5500000</v>
       </c>
       <c r="AI6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AJ6">
         <v>55</v>
@@ -3181,10 +3166,10 @@
         <v>1</v>
       </c>
       <c r="AS6">
-        <v>3200000</v>
+        <v>1800000</v>
       </c>
       <c r="AT6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AU6">
         <v>55</v>
@@ -3205,16 +3190,31 @@
         <v>90</v>
       </c>
       <c r="BA6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC6" t="b">
         <v>1</v>
       </c>
+      <c r="BD6">
+        <v>6100</v>
+      </c>
+      <c r="BE6" t="s">
+        <v>176</v>
+      </c>
+      <c r="BF6">
+        <v>0</v>
+      </c>
+      <c r="BG6">
+        <v>40</v>
+      </c>
+      <c r="BH6" t="b">
+        <v>1</v>
+      </c>
       <c r="BI6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BJ6">
         <v>2</v>
@@ -3223,41 +3223,41 @@
         <v>9</v>
       </c>
       <c r="BL6" t="s">
+        <v>178</v>
+      </c>
+      <c r="BM6">
+        <v>0</v>
+      </c>
+      <c r="BN6">
+        <v>0</v>
+      </c>
+      <c r="BO6" t="b">
+        <v>1</v>
+      </c>
+      <c r="BS6" t="s">
+        <v>182</v>
+      </c>
+      <c r="BT6">
+        <v>2</v>
+      </c>
+      <c r="BU6">
+        <v>9</v>
+      </c>
+      <c r="BV6" t="s">
+        <v>178</v>
+      </c>
+      <c r="BW6">
+        <v>0</v>
+      </c>
+      <c r="BX6">
+        <v>0</v>
+      </c>
+      <c r="BY6" t="b">
+        <v>1</v>
+      </c>
+      <c r="CC6" t="s">
         <v>177</v>
       </c>
-      <c r="BM6">
-        <v>0</v>
-      </c>
-      <c r="BN6">
-        <v>0</v>
-      </c>
-      <c r="BO6" t="b">
-        <v>1</v>
-      </c>
-      <c r="BS6" t="s">
-        <v>181</v>
-      </c>
-      <c r="BT6">
-        <v>2</v>
-      </c>
-      <c r="BU6">
-        <v>9</v>
-      </c>
-      <c r="BV6" t="s">
-        <v>177</v>
-      </c>
-      <c r="BW6">
-        <v>0</v>
-      </c>
-      <c r="BX6">
-        <v>0</v>
-      </c>
-      <c r="BY6" t="b">
-        <v>1</v>
-      </c>
-      <c r="CC6" t="s">
-        <v>176</v>
-      </c>
       <c r="CD6">
         <v>2</v>
       </c>
@@ -3265,7 +3265,7 @@
         <v>9</v>
       </c>
       <c r="CF6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CG6">
         <v>0</v>
@@ -3277,49 +3277,19 @@
         <v>1</v>
       </c>
       <c r="CL6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CM6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO6" t="b">
         <v>1</v>
       </c>
-      <c r="CP6" t="s">
-        <v>185</v>
-      </c>
-      <c r="CQ6">
-        <v>50000</v>
-      </c>
-      <c r="CR6">
-        <v>15000</v>
-      </c>
-      <c r="CS6">
-        <v>7200</v>
-      </c>
-      <c r="CT6">
-        <v>7200</v>
-      </c>
-      <c r="CU6">
-        <v>50000</v>
-      </c>
-      <c r="CV6">
-        <v>0.9</v>
-      </c>
-      <c r="CW6">
-        <v>0.8</v>
-      </c>
-      <c r="CX6" t="b">
-        <v>0</v>
-      </c>
-      <c r="CY6" t="b">
-        <v>0</v>
-      </c>
       <c r="DJ6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="DK6">
         <v>0.05</v>
@@ -3334,22 +3304,40 @@
         <v>8.5</v>
       </c>
       <c r="DO6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="DP6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="DQ6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS6" t="s">
-        <v>190</v>
+        <v>191</v>
+      </c>
+      <c r="DT6">
+        <v>3600</v>
+      </c>
+      <c r="DU6">
+        <v>3600</v>
+      </c>
+      <c r="DV6">
+        <v>0.95</v>
+      </c>
+      <c r="DW6">
+        <v>0.1</v>
+      </c>
+      <c r="DX6" t="b">
+        <v>0</v>
+      </c>
+      <c r="DY6" t="b">
+        <v>0</v>
       </c>
       <c r="DZ6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="EA6">
         <v>0</v>
@@ -3358,28 +3346,28 @@
         <v>0</v>
       </c>
       <c r="EC6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="EH6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="EI6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="EJ6">
         <v>96</v>
       </c>
       <c r="EK6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="EL6">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="EM6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="EN6">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="EO6">
         <v>0</v>
@@ -3399,10 +3387,10 @@
         <v>151</v>
       </c>
       <c r="F7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G7">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H7">
         <v>2</v>
@@ -3411,7 +3399,7 @@
         <v>2.6</v>
       </c>
       <c r="J7">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="K7">
         <v>1</v>
@@ -3426,10 +3414,10 @@
         <v>1</v>
       </c>
       <c r="O7">
-        <v>3648000</v>
+        <v>4536000</v>
       </c>
       <c r="P7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q7" t="s">
         <v>162</v>
@@ -3477,10 +3465,10 @@
         <v>1</v>
       </c>
       <c r="AH7">
-        <v>19500000</v>
+        <v>5500000</v>
       </c>
       <c r="AI7" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AJ7">
         <v>55</v>
@@ -3510,10 +3498,10 @@
         <v>1</v>
       </c>
       <c r="AS7">
-        <v>2800000</v>
+        <v>1800000</v>
       </c>
       <c r="AT7" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="AU7">
         <v>55</v>
@@ -3543,22 +3531,22 @@
         <v>1</v>
       </c>
       <c r="BD7">
-        <v>5000</v>
+        <v>7600</v>
       </c>
       <c r="BE7" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="BF7">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="BG7">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="BH7" t="b">
         <v>1</v>
       </c>
       <c r="BI7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BJ7">
         <v>2</v>
@@ -3567,41 +3555,50 @@
         <v>9</v>
       </c>
       <c r="BL7" t="s">
+        <v>178</v>
+      </c>
+      <c r="BM7">
+        <v>1</v>
+      </c>
+      <c r="BN7">
+        <v>1</v>
+      </c>
+      <c r="BO7" t="b">
+        <v>1</v>
+      </c>
+      <c r="BP7">
+        <v>2500</v>
+      </c>
+      <c r="BQ7" t="s">
+        <v>181</v>
+      </c>
+      <c r="BR7" t="b">
+        <v>1</v>
+      </c>
+      <c r="BS7" t="s">
+        <v>182</v>
+      </c>
+      <c r="BT7">
+        <v>2</v>
+      </c>
+      <c r="BU7">
+        <v>9</v>
+      </c>
+      <c r="BV7" t="s">
+        <v>178</v>
+      </c>
+      <c r="BW7">
+        <v>0</v>
+      </c>
+      <c r="BX7">
+        <v>0</v>
+      </c>
+      <c r="BY7" t="b">
+        <v>1</v>
+      </c>
+      <c r="CC7" t="s">
         <v>177</v>
       </c>
-      <c r="BM7">
-        <v>0</v>
-      </c>
-      <c r="BN7">
-        <v>0</v>
-      </c>
-      <c r="BO7" t="b">
-        <v>1</v>
-      </c>
-      <c r="BS7" t="s">
-        <v>181</v>
-      </c>
-      <c r="BT7">
-        <v>2</v>
-      </c>
-      <c r="BU7">
-        <v>9</v>
-      </c>
-      <c r="BV7" t="s">
-        <v>177</v>
-      </c>
-      <c r="BW7">
-        <v>0</v>
-      </c>
-      <c r="BX7">
-        <v>0</v>
-      </c>
-      <c r="BY7" t="b">
-        <v>1</v>
-      </c>
-      <c r="CC7" t="s">
-        <v>176</v>
-      </c>
       <c r="CD7">
         <v>2</v>
       </c>
@@ -3609,7 +3606,7 @@
         <v>9</v>
       </c>
       <c r="CF7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CG7">
         <v>0</v>
@@ -3621,19 +3618,49 @@
         <v>1</v>
       </c>
       <c r="CL7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CM7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO7" t="b">
         <v>1</v>
       </c>
+      <c r="CP7" t="s">
+        <v>185</v>
+      </c>
+      <c r="CQ7">
+        <v>50000</v>
+      </c>
+      <c r="CR7">
+        <v>15000</v>
+      </c>
+      <c r="CS7">
+        <v>7200</v>
+      </c>
+      <c r="CT7">
+        <v>7200</v>
+      </c>
+      <c r="CU7">
+        <v>50000</v>
+      </c>
+      <c r="CV7">
+        <v>0.9</v>
+      </c>
+      <c r="CW7">
+        <v>0.8</v>
+      </c>
+      <c r="CX7" t="b">
+        <v>0</v>
+      </c>
+      <c r="CY7" t="b">
+        <v>0</v>
+      </c>
       <c r="DJ7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="DK7">
         <v>0.05</v>
@@ -3648,10 +3675,10 @@
         <v>8.5</v>
       </c>
       <c r="DO7" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="DP7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="DQ7">
         <v>1</v>
@@ -3660,13 +3687,13 @@
         <v>1</v>
       </c>
       <c r="DS7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="DT7">
-        <v>3600</v>
+        <v>4500</v>
       </c>
       <c r="DU7">
-        <v>3600</v>
+        <v>4500</v>
       </c>
       <c r="DV7">
         <v>0.95</v>
@@ -3681,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="DZ7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="EA7">
         <v>0</v>
@@ -3690,25 +3717,25 @@
         <v>0</v>
       </c>
       <c r="EC7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="EH7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="EI7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="EJ7">
         <v>96</v>
       </c>
       <c r="EK7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="EL7">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="EM7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="EN7">
         <v>30</v>
@@ -3758,10 +3785,10 @@
         <v>1</v>
       </c>
       <c r="O8">
-        <v>2455000</v>
+        <v>3564000</v>
       </c>
       <c r="P8" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="Q8" t="s">
         <v>162</v>
@@ -3812,10 +3839,10 @@
         <v>19500000</v>
       </c>
       <c r="AI8" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="AJ8">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="AK8" t="s">
         <v>162</v>
@@ -3845,7 +3872,7 @@
         <v>2800000</v>
       </c>
       <c r="AT8" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AU8">
         <v>55</v>
@@ -3866,31 +3893,16 @@
         <v>90</v>
       </c>
       <c r="BA8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="b">
         <v>1</v>
       </c>
-      <c r="BD8">
-        <v>3500</v>
-      </c>
-      <c r="BE8" t="s">
-        <v>175</v>
-      </c>
-      <c r="BF8">
-        <v>0</v>
-      </c>
-      <c r="BG8">
-        <v>40</v>
-      </c>
-      <c r="BH8" t="b">
-        <v>1</v>
-      </c>
       <c r="BI8" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BJ8">
         <v>2</v>
@@ -3899,50 +3911,50 @@
         <v>9</v>
       </c>
       <c r="BL8" t="s">
+        <v>178</v>
+      </c>
+      <c r="BM8">
+        <v>1</v>
+      </c>
+      <c r="BN8">
+        <v>1</v>
+      </c>
+      <c r="BO8" t="b">
+        <v>1</v>
+      </c>
+      <c r="BP8">
+        <v>2200</v>
+      </c>
+      <c r="BQ8" t="s">
+        <v>179</v>
+      </c>
+      <c r="BR8" t="b">
+        <v>1</v>
+      </c>
+      <c r="BS8" t="s">
+        <v>182</v>
+      </c>
+      <c r="BT8">
+        <v>2</v>
+      </c>
+      <c r="BU8">
+        <v>9</v>
+      </c>
+      <c r="BV8" t="s">
+        <v>178</v>
+      </c>
+      <c r="BW8">
+        <v>0</v>
+      </c>
+      <c r="BX8">
+        <v>0</v>
+      </c>
+      <c r="BY8" t="b">
+        <v>1</v>
+      </c>
+      <c r="CC8" t="s">
         <v>177</v>
       </c>
-      <c r="BM8">
-        <v>1</v>
-      </c>
-      <c r="BN8">
-        <v>1</v>
-      </c>
-      <c r="BO8" t="b">
-        <v>1</v>
-      </c>
-      <c r="BP8">
-        <v>1400</v>
-      </c>
-      <c r="BQ8" t="s">
-        <v>178</v>
-      </c>
-      <c r="BR8" t="b">
-        <v>1</v>
-      </c>
-      <c r="BS8" t="s">
-        <v>181</v>
-      </c>
-      <c r="BT8">
-        <v>2</v>
-      </c>
-      <c r="BU8">
-        <v>9</v>
-      </c>
-      <c r="BV8" t="s">
-        <v>177</v>
-      </c>
-      <c r="BW8">
-        <v>0</v>
-      </c>
-      <c r="BX8">
-        <v>0</v>
-      </c>
-      <c r="BY8" t="b">
-        <v>1</v>
-      </c>
-      <c r="CC8" t="s">
-        <v>176</v>
-      </c>
       <c r="CD8">
         <v>2</v>
       </c>
@@ -3950,7 +3962,7 @@
         <v>9</v>
       </c>
       <c r="CF8" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CG8">
         <v>0</v>
@@ -3962,19 +3974,49 @@
         <v>1</v>
       </c>
       <c r="CL8" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CM8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO8" t="b">
         <v>1</v>
       </c>
+      <c r="CP8" t="s">
+        <v>186</v>
+      </c>
+      <c r="CQ8">
+        <v>100000</v>
+      </c>
+      <c r="CR8">
+        <v>25000</v>
+      </c>
+      <c r="CS8">
+        <v>11000</v>
+      </c>
+      <c r="CT8">
+        <v>22000</v>
+      </c>
+      <c r="CU8">
+        <v>200000</v>
+      </c>
+      <c r="CV8">
+        <v>0.9</v>
+      </c>
+      <c r="CW8">
+        <v>0.8</v>
+      </c>
+      <c r="CX8" t="b">
+        <v>0</v>
+      </c>
+      <c r="CY8" t="b">
+        <v>0</v>
+      </c>
       <c r="DJ8" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="DK8">
         <v>0.05</v>
@@ -3989,40 +4031,22 @@
         <v>8.5</v>
       </c>
       <c r="DO8" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="DP8" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="DQ8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS8" t="s">
-        <v>190</v>
-      </c>
-      <c r="DT8">
-        <v>2500</v>
-      </c>
-      <c r="DU8">
-        <v>2500</v>
-      </c>
-      <c r="DV8">
-        <v>0.95</v>
-      </c>
-      <c r="DW8">
-        <v>0.1</v>
-      </c>
-      <c r="DX8" t="b">
-        <v>0</v>
-      </c>
-      <c r="DY8" t="b">
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="DZ8" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="EA8">
         <v>0</v>
@@ -4031,28 +4055,28 @@
         <v>0</v>
       </c>
       <c r="EC8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="EH8" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="EI8" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="EJ8">
         <v>96</v>
       </c>
       <c r="EK8" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="EL8">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="EM8" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="EN8">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="EO8">
         <v>0</v>
@@ -4099,10 +4123,10 @@
         <v>1</v>
       </c>
       <c r="O9">
-        <v>4536000</v>
+        <v>5527000</v>
       </c>
       <c r="P9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q9" t="s">
         <v>162</v>
@@ -4153,10 +4177,10 @@
         <v>19500000</v>
       </c>
       <c r="AI9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AJ9">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="AK9" t="s">
         <v>162</v>
@@ -4183,10 +4207,10 @@
         <v>1</v>
       </c>
       <c r="AS9">
-        <v>2400000</v>
+        <v>2800000</v>
       </c>
       <c r="AT9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AU9">
         <v>55</v>
@@ -4216,22 +4240,22 @@
         <v>1</v>
       </c>
       <c r="BD9">
-        <v>6200</v>
+        <v>9500</v>
       </c>
       <c r="BE9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="BF9">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="BG9">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="BH9" t="b">
         <v>1</v>
       </c>
       <c r="BI9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BJ9">
         <v>2</v>
@@ -4240,50 +4264,41 @@
         <v>9</v>
       </c>
       <c r="BL9" t="s">
+        <v>178</v>
+      </c>
+      <c r="BM9">
+        <v>0</v>
+      </c>
+      <c r="BN9">
+        <v>0</v>
+      </c>
+      <c r="BO9" t="b">
+        <v>1</v>
+      </c>
+      <c r="BS9" t="s">
+        <v>182</v>
+      </c>
+      <c r="BT9">
+        <v>2</v>
+      </c>
+      <c r="BU9">
+        <v>9</v>
+      </c>
+      <c r="BV9" t="s">
+        <v>178</v>
+      </c>
+      <c r="BW9">
+        <v>0</v>
+      </c>
+      <c r="BX9">
+        <v>0</v>
+      </c>
+      <c r="BY9" t="b">
+        <v>1</v>
+      </c>
+      <c r="CC9" t="s">
         <v>177</v>
       </c>
-      <c r="BM9">
-        <v>1</v>
-      </c>
-      <c r="BN9">
-        <v>1</v>
-      </c>
-      <c r="BO9" t="b">
-        <v>1</v>
-      </c>
-      <c r="BP9">
-        <v>3300</v>
-      </c>
-      <c r="BQ9" t="s">
-        <v>180</v>
-      </c>
-      <c r="BR9" t="b">
-        <v>1</v>
-      </c>
-      <c r="BS9" t="s">
-        <v>181</v>
-      </c>
-      <c r="BT9">
-        <v>2</v>
-      </c>
-      <c r="BU9">
-        <v>9</v>
-      </c>
-      <c r="BV9" t="s">
-        <v>177</v>
-      </c>
-      <c r="BW9">
-        <v>0</v>
-      </c>
-      <c r="BX9">
-        <v>0</v>
-      </c>
-      <c r="BY9" t="b">
-        <v>1</v>
-      </c>
-      <c r="CC9" t="s">
-        <v>176</v>
-      </c>
       <c r="CD9">
         <v>2</v>
       </c>
@@ -4291,7 +4306,7 @@
         <v>9</v>
       </c>
       <c r="CF9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CG9">
         <v>0</v>
@@ -4303,7 +4318,7 @@
         <v>1</v>
       </c>
       <c r="CL9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CM9">
         <v>1</v>
@@ -4315,22 +4330,22 @@
         <v>1</v>
       </c>
       <c r="CP9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="CQ9">
-        <v>75000</v>
+        <v>50000</v>
       </c>
       <c r="CR9">
-        <v>20000</v>
+        <v>15000</v>
       </c>
       <c r="CS9">
         <v>7200</v>
       </c>
       <c r="CT9">
-        <v>11000</v>
+        <v>7200</v>
       </c>
       <c r="CU9">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="CV9">
         <v>0.9</v>
@@ -4345,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="DJ9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="DK9">
         <v>0.05</v>
@@ -4360,10 +4375,10 @@
         <v>8.5</v>
       </c>
       <c r="DO9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="DP9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="DQ9">
         <v>1</v>
@@ -4372,13 +4387,13 @@
         <v>1</v>
       </c>
       <c r="DS9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="DT9">
-        <v>4500</v>
+        <v>5500</v>
       </c>
       <c r="DU9">
-        <v>4500</v>
+        <v>5500</v>
       </c>
       <c r="DV9">
         <v>0.95</v>
@@ -4393,7 +4408,7 @@
         <v>0</v>
       </c>
       <c r="DZ9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="EA9">
         <v>0</v>
@@ -4402,28 +4417,28 @@
         <v>0</v>
       </c>
       <c r="EC9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="EH9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="EI9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="EJ9">
         <v>96</v>
       </c>
       <c r="EK9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="EL9">
         <v>36</v>
       </c>
       <c r="EM9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="EN9">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="EO9">
         <v>0</v>
@@ -4470,10 +4485,10 @@
         <v>1</v>
       </c>
       <c r="O10">
-        <v>4536000</v>
+        <v>5527000</v>
       </c>
       <c r="P10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q10" t="s">
         <v>162</v>
@@ -4524,10 +4539,10 @@
         <v>5500000</v>
       </c>
       <c r="AI10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AJ10">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="AK10" t="s">
         <v>162</v>
@@ -4554,10 +4569,10 @@
         <v>1</v>
       </c>
       <c r="AS10">
-        <v>2100000</v>
+        <v>1800000</v>
       </c>
       <c r="AT10" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AU10">
         <v>55</v>
@@ -4587,10 +4602,10 @@
         <v>1</v>
       </c>
       <c r="BD10">
-        <v>5800</v>
+        <v>8100</v>
       </c>
       <c r="BE10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="BF10">
         <v>0</v>
@@ -4602,7 +4617,7 @@
         <v>1</v>
       </c>
       <c r="BI10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BJ10">
         <v>2</v>
@@ -4611,50 +4626,41 @@
         <v>9</v>
       </c>
       <c r="BL10" t="s">
+        <v>178</v>
+      </c>
+      <c r="BM10">
+        <v>0</v>
+      </c>
+      <c r="BN10">
+        <v>0</v>
+      </c>
+      <c r="BO10" t="b">
+        <v>1</v>
+      </c>
+      <c r="BS10" t="s">
+        <v>182</v>
+      </c>
+      <c r="BT10">
+        <v>2</v>
+      </c>
+      <c r="BU10">
+        <v>9</v>
+      </c>
+      <c r="BV10" t="s">
+        <v>178</v>
+      </c>
+      <c r="BW10">
+        <v>0</v>
+      </c>
+      <c r="BX10">
+        <v>0</v>
+      </c>
+      <c r="BY10" t="b">
+        <v>1</v>
+      </c>
+      <c r="CC10" t="s">
         <v>177</v>
       </c>
-      <c r="BM10">
-        <v>1</v>
-      </c>
-      <c r="BN10">
-        <v>1</v>
-      </c>
-      <c r="BO10" t="b">
-        <v>1</v>
-      </c>
-      <c r="BP10">
-        <v>2400</v>
-      </c>
-      <c r="BQ10" t="s">
-        <v>179</v>
-      </c>
-      <c r="BR10" t="b">
-        <v>1</v>
-      </c>
-      <c r="BS10" t="s">
-        <v>181</v>
-      </c>
-      <c r="BT10">
-        <v>2</v>
-      </c>
-      <c r="BU10">
-        <v>9</v>
-      </c>
-      <c r="BV10" t="s">
-        <v>177</v>
-      </c>
-      <c r="BW10">
-        <v>0</v>
-      </c>
-      <c r="BX10">
-        <v>0</v>
-      </c>
-      <c r="BY10" t="b">
-        <v>1</v>
-      </c>
-      <c r="CC10" t="s">
-        <v>176</v>
-      </c>
       <c r="CD10">
         <v>2</v>
       </c>
@@ -4662,7 +4668,7 @@
         <v>9</v>
       </c>
       <c r="CF10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CG10">
         <v>0</v>
@@ -4674,7 +4680,7 @@
         <v>1</v>
       </c>
       <c r="CL10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CM10">
         <v>0</v>
@@ -4686,7 +4692,7 @@
         <v>1</v>
       </c>
       <c r="DJ10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="DK10">
         <v>0.05</v>
@@ -4701,40 +4707,22 @@
         <v>8.5</v>
       </c>
       <c r="DO10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="DP10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="DQ10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS10" t="s">
-        <v>190</v>
-      </c>
-      <c r="DT10">
-        <v>4500</v>
-      </c>
-      <c r="DU10">
-        <v>4500</v>
-      </c>
-      <c r="DV10">
-        <v>0.95</v>
-      </c>
-      <c r="DW10">
-        <v>0.1</v>
-      </c>
-      <c r="DX10" t="b">
-        <v>0</v>
-      </c>
-      <c r="DY10" t="b">
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="DZ10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="EA10">
         <v>0</v>
@@ -4743,28 +4731,28 @@
         <v>0</v>
       </c>
       <c r="EC10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="EH10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="EI10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="EJ10">
         <v>96</v>
       </c>
       <c r="EK10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="EL10">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="EM10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="EN10">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="EO10">
         <v>0</v>
@@ -4811,10 +4799,10 @@
         <v>1</v>
       </c>
       <c r="O11">
-        <v>3648000</v>
+        <v>2896000</v>
       </c>
       <c r="P11" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q11" t="s">
         <v>162</v>
@@ -4865,7 +4853,7 @@
         <v>5500000</v>
       </c>
       <c r="AI11" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="AJ11">
         <v>55</v>
@@ -4895,7 +4883,7 @@
         <v>1</v>
       </c>
       <c r="AS11">
-        <v>2100000</v>
+        <v>2400000</v>
       </c>
       <c r="AT11" t="s">
         <v>171</v>
@@ -4928,10 +4916,10 @@
         <v>1</v>
       </c>
       <c r="BD11">
-        <v>6300</v>
+        <v>3800</v>
       </c>
       <c r="BE11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="BF11">
         <v>0</v>
@@ -4943,7 +4931,7 @@
         <v>1</v>
       </c>
       <c r="BI11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BJ11">
         <v>2</v>
@@ -4952,41 +4940,41 @@
         <v>9</v>
       </c>
       <c r="BL11" t="s">
+        <v>178</v>
+      </c>
+      <c r="BM11">
+        <v>0</v>
+      </c>
+      <c r="BN11">
+        <v>0</v>
+      </c>
+      <c r="BO11" t="b">
+        <v>1</v>
+      </c>
+      <c r="BS11" t="s">
+        <v>182</v>
+      </c>
+      <c r="BT11">
+        <v>2</v>
+      </c>
+      <c r="BU11">
+        <v>9</v>
+      </c>
+      <c r="BV11" t="s">
+        <v>178</v>
+      </c>
+      <c r="BW11">
+        <v>0</v>
+      </c>
+      <c r="BX11">
+        <v>0</v>
+      </c>
+      <c r="BY11" t="b">
+        <v>1</v>
+      </c>
+      <c r="CC11" t="s">
         <v>177</v>
       </c>
-      <c r="BM11">
-        <v>0</v>
-      </c>
-      <c r="BN11">
-        <v>0</v>
-      </c>
-      <c r="BO11" t="b">
-        <v>1</v>
-      </c>
-      <c r="BS11" t="s">
-        <v>181</v>
-      </c>
-      <c r="BT11">
-        <v>2</v>
-      </c>
-      <c r="BU11">
-        <v>9</v>
-      </c>
-      <c r="BV11" t="s">
-        <v>177</v>
-      </c>
-      <c r="BW11">
-        <v>0</v>
-      </c>
-      <c r="BX11">
-        <v>0</v>
-      </c>
-      <c r="BY11" t="b">
-        <v>1</v>
-      </c>
-      <c r="CC11" t="s">
-        <v>176</v>
-      </c>
       <c r="CD11">
         <v>2</v>
       </c>
@@ -4994,7 +4982,7 @@
         <v>9</v>
       </c>
       <c r="CF11" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CG11">
         <v>0</v>
@@ -5006,7 +4994,7 @@
         <v>1</v>
       </c>
       <c r="CL11" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CM11">
         <v>1</v>
@@ -5018,7 +5006,7 @@
         <v>1</v>
       </c>
       <c r="CP11" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="CQ11">
         <v>75000</v>
@@ -5048,7 +5036,7 @@
         <v>0</v>
       </c>
       <c r="DJ11" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="DK11">
         <v>0.05</v>
@@ -5063,40 +5051,22 @@
         <v>8.5</v>
       </c>
       <c r="DO11" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="DP11" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="DQ11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS11" t="s">
-        <v>190</v>
-      </c>
-      <c r="DT11">
-        <v>3600</v>
-      </c>
-      <c r="DU11">
-        <v>3600</v>
-      </c>
-      <c r="DV11">
-        <v>0.95</v>
-      </c>
-      <c r="DW11">
-        <v>0.1</v>
-      </c>
-      <c r="DX11" t="b">
-        <v>0</v>
-      </c>
-      <c r="DY11" t="b">
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="DZ11" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="EA11">
         <v>0</v>
@@ -5105,28 +5075,28 @@
         <v>0</v>
       </c>
       <c r="EC11" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="EH11" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="EI11" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="EJ11">
         <v>96</v>
       </c>
       <c r="EK11" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="EL11">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="EM11" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="EN11">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="EO11">
         <v>0</v>
@@ -5162,13 +5132,13 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>4</v>
@@ -5602,10 +5572,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G2" t="b">
         <v>0</v>
@@ -5641,7 +5611,7 @@
         <v>1</v>
       </c>
       <c r="R2">
-        <v>11635000</v>
+        <v>10831000</v>
       </c>
       <c r="T2" t="s">
         <v>162</v>
@@ -5740,10 +5710,10 @@
         <v>1</v>
       </c>
       <c r="BG2">
-        <v>17000</v>
+        <v>14000</v>
       </c>
       <c r="BH2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="BI2">
         <v>0</v>
@@ -5755,7 +5725,7 @@
         <v>1</v>
       </c>
       <c r="BL2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BM2">
         <v>2</v>
@@ -5764,28 +5734,19 @@
         <v>9</v>
       </c>
       <c r="BO2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="BP2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR2" t="b">
         <v>1</v>
       </c>
-      <c r="BS2">
-        <v>8400</v>
-      </c>
-      <c r="BT2" t="s">
-        <v>180</v>
-      </c>
-      <c r="BU2" t="b">
-        <v>1</v>
-      </c>
       <c r="BV2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="BW2">
         <v>2</v>
@@ -5794,7 +5755,7 @@
         <v>9</v>
       </c>
       <c r="BY2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="BZ2">
         <v>1</v>
@@ -5809,13 +5770,13 @@
         <v>1900</v>
       </c>
       <c r="CD2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="CE2" t="b">
         <v>0</v>
       </c>
       <c r="CF2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="CG2">
         <v>2</v>
@@ -5824,7 +5785,7 @@
         <v>9</v>
       </c>
       <c r="CI2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CJ2">
         <v>0</v>
@@ -5836,7 +5797,7 @@
         <v>1</v>
       </c>
       <c r="CO2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CP2">
         <v>0</v>
@@ -5848,10 +5809,10 @@
         <v>1</v>
       </c>
       <c r="DR2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="DS2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="DT2">
         <v>1</v>
@@ -5863,10 +5824,10 @@
         <v>1</v>
       </c>
       <c r="DW2">
-        <v>12000</v>
+        <v>11000</v>
       </c>
       <c r="DX2">
-        <v>12000</v>
+        <v>11000</v>
       </c>
       <c r="DY2">
         <v>0.95</v>
@@ -5881,7 +5842,7 @@
         <v>0</v>
       </c>
       <c r="EC2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="ED2">
         <v>1</v>
@@ -5905,22 +5866,22 @@
         <v>0.1</v>
       </c>
       <c r="EK2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="EL2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="EM2">
         <v>96</v>
       </c>
       <c r="EN2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="EO2">
         <v>48</v>
       </c>
       <c r="EP2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="EQ2">
         <v>0</v>
@@ -5940,10 +5901,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G3" t="b">
         <v>0</v>
@@ -5979,10 +5940,10 @@
         <v>1</v>
       </c>
       <c r="R3">
-        <v>2262000</v>
+        <v>1720000</v>
       </c>
       <c r="S3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="T3" t="s">
         <v>162</v>
@@ -6030,10 +5991,10 @@
         <v>3850000</v>
       </c>
       <c r="AL3" t="s">
-        <v>164</v>
+        <v>222</v>
       </c>
       <c r="AM3">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="AN3" t="s">
         <v>162</v>
@@ -6060,10 +6021,10 @@
         <v>1</v>
       </c>
       <c r="AV3">
-        <v>2400</v>
+        <v>2100</v>
       </c>
       <c r="AW3" t="s">
-        <v>223</v>
+        <v>175</v>
       </c>
       <c r="AX3">
         <v>55</v>
@@ -6093,7 +6054,7 @@
         <v>1</v>
       </c>
       <c r="BL3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BM3">
         <v>2</v>
@@ -6102,41 +6063,41 @@
         <v>9</v>
       </c>
       <c r="BO3" t="s">
+        <v>178</v>
+      </c>
+      <c r="BP3">
+        <v>0</v>
+      </c>
+      <c r="BQ3">
+        <v>0</v>
+      </c>
+      <c r="BR3" t="b">
+        <v>1</v>
+      </c>
+      <c r="BV3" t="s">
+        <v>182</v>
+      </c>
+      <c r="BW3">
+        <v>2</v>
+      </c>
+      <c r="BX3">
+        <v>9</v>
+      </c>
+      <c r="BY3" t="s">
+        <v>178</v>
+      </c>
+      <c r="BZ3">
+        <v>0</v>
+      </c>
+      <c r="CA3">
+        <v>0</v>
+      </c>
+      <c r="CB3" t="b">
+        <v>1</v>
+      </c>
+      <c r="CF3" t="s">
         <v>177</v>
       </c>
-      <c r="BP3">
-        <v>0</v>
-      </c>
-      <c r="BQ3">
-        <v>0</v>
-      </c>
-      <c r="BR3" t="b">
-        <v>1</v>
-      </c>
-      <c r="BV3" t="s">
-        <v>181</v>
-      </c>
-      <c r="BW3">
-        <v>2</v>
-      </c>
-      <c r="BX3">
-        <v>9</v>
-      </c>
-      <c r="BY3" t="s">
-        <v>177</v>
-      </c>
-      <c r="BZ3">
-        <v>0</v>
-      </c>
-      <c r="CA3">
-        <v>0</v>
-      </c>
-      <c r="CB3" t="b">
-        <v>1</v>
-      </c>
-      <c r="CF3" t="s">
-        <v>176</v>
-      </c>
       <c r="CG3">
         <v>2</v>
       </c>
@@ -6144,7 +6105,7 @@
         <v>9</v>
       </c>
       <c r="CI3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CJ3">
         <v>0</v>
@@ -6156,19 +6117,79 @@
         <v>1</v>
       </c>
       <c r="CO3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CP3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CR3" t="b">
         <v>1</v>
       </c>
+      <c r="CS3" t="s">
+        <v>230</v>
+      </c>
+      <c r="CT3">
+        <v>100000</v>
+      </c>
+      <c r="CU3">
+        <v>25000</v>
+      </c>
+      <c r="CV3">
+        <v>11000</v>
+      </c>
+      <c r="CW3">
+        <v>22000</v>
+      </c>
+      <c r="CX3">
+        <v>200000</v>
+      </c>
+      <c r="CY3">
+        <v>0.9</v>
+      </c>
+      <c r="CZ3">
+        <v>0.8</v>
+      </c>
+      <c r="DA3" t="b">
+        <v>0</v>
+      </c>
+      <c r="DB3" t="b">
+        <v>0</v>
+      </c>
+      <c r="DC3" t="s">
+        <v>232</v>
+      </c>
+      <c r="DD3">
+        <v>75000</v>
+      </c>
+      <c r="DE3">
+        <v>20000</v>
+      </c>
+      <c r="DF3">
+        <v>7200</v>
+      </c>
+      <c r="DG3">
+        <v>11000</v>
+      </c>
+      <c r="DH3">
+        <v>100000</v>
+      </c>
+      <c r="DI3">
+        <v>0.9</v>
+      </c>
+      <c r="DJ3">
+        <v>0.8</v>
+      </c>
+      <c r="DK3" t="b">
+        <v>0</v>
+      </c>
+      <c r="DL3" t="b">
+        <v>0</v>
+      </c>
       <c r="DM3" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="DN3">
         <v>0.05</v>
@@ -6183,10 +6204,10 @@
         <v>8</v>
       </c>
       <c r="DR3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="DS3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="DT3">
         <v>0</v>
@@ -6198,7 +6219,7 @@
         <v>1</v>
       </c>
       <c r="EC3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="ED3">
         <v>0</v>
@@ -6210,25 +6231,25 @@
         <v>1</v>
       </c>
       <c r="EK3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="EL3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="EM3">
         <v>96</v>
       </c>
       <c r="EN3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="EO3">
         <v>12</v>
       </c>
       <c r="EP3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="EQ3">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="ER3">
         <v>0</v>
@@ -6245,10 +6266,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G4" t="b">
         <v>0</v>
@@ -6284,10 +6305,10 @@
         <v>1</v>
       </c>
       <c r="R4">
-        <v>1720000</v>
+        <v>2532000</v>
       </c>
       <c r="S4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="T4" t="s">
         <v>162</v>
@@ -6335,7 +6356,7 @@
         <v>3850000</v>
       </c>
       <c r="AL4" t="s">
-        <v>164</v>
+        <v>223</v>
       </c>
       <c r="AM4">
         <v>55</v>
@@ -6365,10 +6386,10 @@
         <v>1</v>
       </c>
       <c r="AV4">
-        <v>2100</v>
+        <v>1800</v>
       </c>
       <c r="AW4" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AX4">
         <v>55</v>
@@ -6398,7 +6419,7 @@
         <v>1</v>
       </c>
       <c r="BL4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BM4">
         <v>2</v>
@@ -6407,41 +6428,41 @@
         <v>9</v>
       </c>
       <c r="BO4" t="s">
+        <v>178</v>
+      </c>
+      <c r="BP4">
+        <v>0</v>
+      </c>
+      <c r="BQ4">
+        <v>0</v>
+      </c>
+      <c r="BR4" t="b">
+        <v>1</v>
+      </c>
+      <c r="BV4" t="s">
+        <v>182</v>
+      </c>
+      <c r="BW4">
+        <v>2</v>
+      </c>
+      <c r="BX4">
+        <v>9</v>
+      </c>
+      <c r="BY4" t="s">
+        <v>178</v>
+      </c>
+      <c r="BZ4">
+        <v>0</v>
+      </c>
+      <c r="CA4">
+        <v>0</v>
+      </c>
+      <c r="CB4" t="b">
+        <v>1</v>
+      </c>
+      <c r="CF4" t="s">
         <v>177</v>
       </c>
-      <c r="BP4">
-        <v>0</v>
-      </c>
-      <c r="BQ4">
-        <v>0</v>
-      </c>
-      <c r="BR4" t="b">
-        <v>1</v>
-      </c>
-      <c r="BV4" t="s">
-        <v>181</v>
-      </c>
-      <c r="BW4">
-        <v>2</v>
-      </c>
-      <c r="BX4">
-        <v>9</v>
-      </c>
-      <c r="BY4" t="s">
-        <v>177</v>
-      </c>
-      <c r="BZ4">
-        <v>0</v>
-      </c>
-      <c r="CA4">
-        <v>0</v>
-      </c>
-      <c r="CB4" t="b">
-        <v>1</v>
-      </c>
-      <c r="CF4" t="s">
-        <v>176</v>
-      </c>
       <c r="CG4">
         <v>2</v>
       </c>
@@ -6449,7 +6470,7 @@
         <v>9</v>
       </c>
       <c r="CI4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CJ4">
         <v>0</v>
@@ -6461,49 +6482,19 @@
         <v>1</v>
       </c>
       <c r="CO4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CP4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CR4" t="b">
         <v>1</v>
       </c>
-      <c r="CS4" t="s">
-        <v>184</v>
-      </c>
-      <c r="CT4">
-        <v>50000</v>
-      </c>
-      <c r="CU4">
-        <v>15000</v>
-      </c>
-      <c r="CV4">
-        <v>7200</v>
-      </c>
-      <c r="CW4">
-        <v>7200</v>
-      </c>
-      <c r="CX4">
-        <v>50000</v>
-      </c>
-      <c r="CY4">
-        <v>0.9</v>
-      </c>
-      <c r="CZ4">
-        <v>0.8</v>
-      </c>
-      <c r="DA4" t="b">
-        <v>0</v>
-      </c>
-      <c r="DB4" t="b">
-        <v>0</v>
-      </c>
       <c r="DM4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="DN4">
         <v>0.05</v>
@@ -6518,10 +6509,10 @@
         <v>8</v>
       </c>
       <c r="DR4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="DS4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="DT4">
         <v>0</v>
@@ -6533,7 +6524,7 @@
         <v>1</v>
       </c>
       <c r="EC4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="ED4">
         <v>0</v>
@@ -6545,22 +6536,22 @@
         <v>1</v>
       </c>
       <c r="EK4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="EL4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="EM4">
         <v>96</v>
       </c>
       <c r="EN4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="EO4">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="EP4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="EQ4">
         <v>0</v>
@@ -6580,10 +6571,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F5" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G5" t="b">
         <v>0</v>
@@ -6619,10 +6610,10 @@
         <v>1</v>
       </c>
       <c r="R5">
-        <v>2262000</v>
+        <v>1009000</v>
       </c>
       <c r="S5" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="T5" t="s">
         <v>162</v>
@@ -6670,10 +6661,10 @@
         <v>3850000</v>
       </c>
       <c r="AL5" t="s">
-        <v>221</v>
+        <v>168</v>
       </c>
       <c r="AM5">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="AN5" t="s">
         <v>162</v>
@@ -6703,7 +6694,7 @@
         <v>2400</v>
       </c>
       <c r="AW5" t="s">
-        <v>224</v>
+        <v>172</v>
       </c>
       <c r="AX5">
         <v>55</v>
@@ -6733,7 +6724,7 @@
         <v>1</v>
       </c>
       <c r="BL5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BM5">
         <v>2</v>
@@ -6742,41 +6733,41 @@
         <v>9</v>
       </c>
       <c r="BO5" t="s">
+        <v>178</v>
+      </c>
+      <c r="BP5">
+        <v>0</v>
+      </c>
+      <c r="BQ5">
+        <v>0</v>
+      </c>
+      <c r="BR5" t="b">
+        <v>1</v>
+      </c>
+      <c r="BV5" t="s">
+        <v>182</v>
+      </c>
+      <c r="BW5">
+        <v>2</v>
+      </c>
+      <c r="BX5">
+        <v>9</v>
+      </c>
+      <c r="BY5" t="s">
+        <v>178</v>
+      </c>
+      <c r="BZ5">
+        <v>0</v>
+      </c>
+      <c r="CA5">
+        <v>0</v>
+      </c>
+      <c r="CB5" t="b">
+        <v>1</v>
+      </c>
+      <c r="CF5" t="s">
         <v>177</v>
       </c>
-      <c r="BP5">
-        <v>0</v>
-      </c>
-      <c r="BQ5">
-        <v>0</v>
-      </c>
-      <c r="BR5" t="b">
-        <v>1</v>
-      </c>
-      <c r="BV5" t="s">
-        <v>181</v>
-      </c>
-      <c r="BW5">
-        <v>2</v>
-      </c>
-      <c r="BX5">
-        <v>9</v>
-      </c>
-      <c r="BY5" t="s">
-        <v>177</v>
-      </c>
-      <c r="BZ5">
-        <v>0</v>
-      </c>
-      <c r="CA5">
-        <v>0</v>
-      </c>
-      <c r="CB5" t="b">
-        <v>1</v>
-      </c>
-      <c r="CF5" t="s">
-        <v>176</v>
-      </c>
       <c r="CG5">
         <v>2</v>
       </c>
@@ -6784,7 +6775,7 @@
         <v>9</v>
       </c>
       <c r="CI5" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CJ5">
         <v>0</v>
@@ -6796,7 +6787,7 @@
         <v>1</v>
       </c>
       <c r="CO5" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CP5">
         <v>0</v>
@@ -6808,7 +6799,7 @@
         <v>1</v>
       </c>
       <c r="DM5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="DN5">
         <v>0.05</v>
@@ -6823,10 +6814,10 @@
         <v>8</v>
       </c>
       <c r="DR5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="DS5" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="DT5">
         <v>0</v>
@@ -6838,7 +6829,7 @@
         <v>1</v>
       </c>
       <c r="EC5" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="ED5">
         <v>0</v>
@@ -6850,25 +6841,25 @@
         <v>1</v>
       </c>
       <c r="EK5" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="EL5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="EM5">
         <v>96</v>
       </c>
       <c r="EN5" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="EO5">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="EP5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="EQ5">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="ER5">
         <v>0</v>
@@ -6885,10 +6876,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G6" t="b">
         <v>0</v>
@@ -6924,10 +6915,10 @@
         <v>1</v>
       </c>
       <c r="R6">
-        <v>1158000</v>
+        <v>2012000</v>
       </c>
       <c r="S6" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="T6" t="s">
         <v>162</v>
@@ -6975,10 +6966,10 @@
         <v>3850000</v>
       </c>
       <c r="AL6" t="s">
-        <v>222</v>
+        <v>165</v>
       </c>
       <c r="AM6">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="AN6" t="s">
         <v>162</v>
@@ -7008,7 +6999,7 @@
         <v>1800</v>
       </c>
       <c r="AW6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AX6">
         <v>55</v>
@@ -7038,7 +7029,7 @@
         <v>1</v>
       </c>
       <c r="BL6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BM6">
         <v>2</v>
@@ -7047,41 +7038,41 @@
         <v>9</v>
       </c>
       <c r="BO6" t="s">
+        <v>178</v>
+      </c>
+      <c r="BP6">
+        <v>0</v>
+      </c>
+      <c r="BQ6">
+        <v>0</v>
+      </c>
+      <c r="BR6" t="b">
+        <v>1</v>
+      </c>
+      <c r="BV6" t="s">
+        <v>182</v>
+      </c>
+      <c r="BW6">
+        <v>2</v>
+      </c>
+      <c r="BX6">
+        <v>9</v>
+      </c>
+      <c r="BY6" t="s">
+        <v>178</v>
+      </c>
+      <c r="BZ6">
+        <v>0</v>
+      </c>
+      <c r="CA6">
+        <v>0</v>
+      </c>
+      <c r="CB6" t="b">
+        <v>1</v>
+      </c>
+      <c r="CF6" t="s">
         <v>177</v>
       </c>
-      <c r="BP6">
-        <v>0</v>
-      </c>
-      <c r="BQ6">
-        <v>0</v>
-      </c>
-      <c r="BR6" t="b">
-        <v>1</v>
-      </c>
-      <c r="BV6" t="s">
-        <v>181</v>
-      </c>
-      <c r="BW6">
-        <v>2</v>
-      </c>
-      <c r="BX6">
-        <v>9</v>
-      </c>
-      <c r="BY6" t="s">
-        <v>177</v>
-      </c>
-      <c r="BZ6">
-        <v>0</v>
-      </c>
-      <c r="CA6">
-        <v>0</v>
-      </c>
-      <c r="CB6" t="b">
-        <v>1</v>
-      </c>
-      <c r="CF6" t="s">
-        <v>176</v>
-      </c>
       <c r="CG6">
         <v>2</v>
       </c>
@@ -7089,7 +7080,7 @@
         <v>9</v>
       </c>
       <c r="CI6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CJ6">
         <v>0</v>
@@ -7101,49 +7092,19 @@
         <v>1</v>
       </c>
       <c r="CO6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CP6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CR6" t="b">
         <v>1</v>
       </c>
-      <c r="CS6" t="s">
-        <v>229</v>
-      </c>
-      <c r="CT6">
-        <v>75000</v>
-      </c>
-      <c r="CU6">
-        <v>20000</v>
-      </c>
-      <c r="CV6">
-        <v>7200</v>
-      </c>
-      <c r="CW6">
-        <v>11000</v>
-      </c>
-      <c r="CX6">
-        <v>100000</v>
-      </c>
-      <c r="CY6">
-        <v>0.9</v>
-      </c>
-      <c r="CZ6">
-        <v>0.8</v>
-      </c>
-      <c r="DA6" t="b">
-        <v>0</v>
-      </c>
-      <c r="DB6" t="b">
-        <v>0</v>
-      </c>
       <c r="DM6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="DN6">
         <v>0.05</v>
@@ -7158,10 +7119,10 @@
         <v>8</v>
       </c>
       <c r="DR6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="DS6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="DT6">
         <v>0</v>
@@ -7173,7 +7134,7 @@
         <v>1</v>
       </c>
       <c r="EC6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="ED6">
         <v>0</v>
@@ -7185,25 +7146,25 @@
         <v>1</v>
       </c>
       <c r="EK6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="EL6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="EM6">
         <v>96</v>
       </c>
       <c r="EN6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="EO6">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="EP6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="EQ6">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="ER6">
         <v>0</v>
@@ -7220,10 +7181,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G7" t="b">
         <v>0</v>
@@ -7259,10 +7220,10 @@
         <v>1</v>
       </c>
       <c r="R7">
-        <v>2687000</v>
+        <v>1546000</v>
       </c>
       <c r="S7" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="T7" t="s">
         <v>162</v>
@@ -7310,7 +7271,7 @@
         <v>3850000</v>
       </c>
       <c r="AL7" t="s">
-        <v>222</v>
+        <v>170</v>
       </c>
       <c r="AM7">
         <v>55</v>
@@ -7340,10 +7301,10 @@
         <v>1</v>
       </c>
       <c r="AV7">
-        <v>1800</v>
+        <v>2400</v>
       </c>
       <c r="AW7" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AX7">
         <v>55</v>
@@ -7373,7 +7334,7 @@
         <v>1</v>
       </c>
       <c r="BL7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BM7">
         <v>2</v>
@@ -7382,41 +7343,41 @@
         <v>9</v>
       </c>
       <c r="BO7" t="s">
+        <v>178</v>
+      </c>
+      <c r="BP7">
+        <v>0</v>
+      </c>
+      <c r="BQ7">
+        <v>0</v>
+      </c>
+      <c r="BR7" t="b">
+        <v>1</v>
+      </c>
+      <c r="BV7" t="s">
+        <v>182</v>
+      </c>
+      <c r="BW7">
+        <v>2</v>
+      </c>
+      <c r="BX7">
+        <v>9</v>
+      </c>
+      <c r="BY7" t="s">
+        <v>178</v>
+      </c>
+      <c r="BZ7">
+        <v>0</v>
+      </c>
+      <c r="CA7">
+        <v>0</v>
+      </c>
+      <c r="CB7" t="b">
+        <v>1</v>
+      </c>
+      <c r="CF7" t="s">
         <v>177</v>
       </c>
-      <c r="BP7">
-        <v>0</v>
-      </c>
-      <c r="BQ7">
-        <v>0</v>
-      </c>
-      <c r="BR7" t="b">
-        <v>1</v>
-      </c>
-      <c r="BV7" t="s">
-        <v>181</v>
-      </c>
-      <c r="BW7">
-        <v>2</v>
-      </c>
-      <c r="BX7">
-        <v>9</v>
-      </c>
-      <c r="BY7" t="s">
-        <v>177</v>
-      </c>
-      <c r="BZ7">
-        <v>0</v>
-      </c>
-      <c r="CA7">
-        <v>0</v>
-      </c>
-      <c r="CB7" t="b">
-        <v>1</v>
-      </c>
-      <c r="CF7" t="s">
-        <v>176</v>
-      </c>
       <c r="CG7">
         <v>2</v>
       </c>
@@ -7424,7 +7385,7 @@
         <v>9</v>
       </c>
       <c r="CI7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CJ7">
         <v>0</v>
@@ -7436,7 +7397,7 @@
         <v>1</v>
       </c>
       <c r="CO7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CP7">
         <v>0</v>
@@ -7463,10 +7424,10 @@
         <v>8</v>
       </c>
       <c r="DR7" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="DS7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="DT7">
         <v>0</v>
@@ -7478,7 +7439,7 @@
         <v>1</v>
       </c>
       <c r="EC7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="ED7">
         <v>0</v>
@@ -7490,22 +7451,22 @@
         <v>1</v>
       </c>
       <c r="EK7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="EL7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="EM7">
         <v>96</v>
       </c>
       <c r="EN7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="EO7">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="EP7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="EQ7">
         <v>0</v>
@@ -7525,10 +7486,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F8" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G8" t="b">
         <v>0</v>
@@ -7564,7 +7525,7 @@
         <v>1</v>
       </c>
       <c r="R8">
-        <v>1546000</v>
+        <v>2012000</v>
       </c>
       <c r="S8" t="s">
         <v>217</v>
@@ -7615,10 +7576,10 @@
         <v>3850000</v>
       </c>
       <c r="AL8" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AM8">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="AN8" t="s">
         <v>162</v>
@@ -7648,7 +7609,7 @@
         <v>2100</v>
       </c>
       <c r="AW8" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AX8">
         <v>55</v>
@@ -7678,7 +7639,7 @@
         <v>1</v>
       </c>
       <c r="BL8" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BM8">
         <v>2</v>
@@ -7687,41 +7648,41 @@
         <v>9</v>
       </c>
       <c r="BO8" t="s">
+        <v>178</v>
+      </c>
+      <c r="BP8">
+        <v>0</v>
+      </c>
+      <c r="BQ8">
+        <v>0</v>
+      </c>
+      <c r="BR8" t="b">
+        <v>1</v>
+      </c>
+      <c r="BV8" t="s">
+        <v>182</v>
+      </c>
+      <c r="BW8">
+        <v>2</v>
+      </c>
+      <c r="BX8">
+        <v>9</v>
+      </c>
+      <c r="BY8" t="s">
+        <v>178</v>
+      </c>
+      <c r="BZ8">
+        <v>0</v>
+      </c>
+      <c r="CA8">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="b">
+        <v>1</v>
+      </c>
+      <c r="CF8" t="s">
         <v>177</v>
       </c>
-      <c r="BP8">
-        <v>0</v>
-      </c>
-      <c r="BQ8">
-        <v>0</v>
-      </c>
-      <c r="BR8" t="b">
-        <v>1</v>
-      </c>
-      <c r="BV8" t="s">
-        <v>181</v>
-      </c>
-      <c r="BW8">
-        <v>2</v>
-      </c>
-      <c r="BX8">
-        <v>9</v>
-      </c>
-      <c r="BY8" t="s">
-        <v>177</v>
-      </c>
-      <c r="BZ8">
-        <v>0</v>
-      </c>
-      <c r="CA8">
-        <v>0</v>
-      </c>
-      <c r="CB8" t="b">
-        <v>1</v>
-      </c>
-      <c r="CF8" t="s">
-        <v>176</v>
-      </c>
       <c r="CG8">
         <v>2</v>
       </c>
@@ -7729,7 +7690,7 @@
         <v>9</v>
       </c>
       <c r="CI8" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CJ8">
         <v>0</v>
@@ -7741,7 +7702,7 @@
         <v>1</v>
       </c>
       <c r="CO8" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CP8">
         <v>0</v>
@@ -7753,7 +7714,7 @@
         <v>1</v>
       </c>
       <c r="DM8" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="DN8">
         <v>0.05</v>
@@ -7768,10 +7729,10 @@
         <v>8</v>
       </c>
       <c r="DR8" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="DS8" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="DT8">
         <v>0</v>
@@ -7783,7 +7744,7 @@
         <v>1</v>
       </c>
       <c r="EC8" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="ED8">
         <v>0</v>
@@ -7795,25 +7756,25 @@
         <v>1</v>
       </c>
       <c r="EK8" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="EL8" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="EM8">
         <v>96</v>
       </c>
       <c r="EN8" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="EO8">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="EP8" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="EQ8">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="ER8">
         <v>0</v>
@@ -7830,10 +7791,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G9" t="b">
         <v>0</v>
@@ -7869,7 +7830,7 @@
         <v>1</v>
       </c>
       <c r="R9">
-        <v>14531000</v>
+        <v>13764000</v>
       </c>
       <c r="T9" t="s">
         <v>162</v>
@@ -7941,7 +7902,7 @@
         <v>1</v>
       </c>
       <c r="AV9">
-        <v>22400</v>
+        <v>22000</v>
       </c>
       <c r="AY9" t="s">
         <v>162</v>
@@ -7968,10 +7929,10 @@
         <v>1</v>
       </c>
       <c r="BG9">
-        <v>21000</v>
+        <v>24000</v>
       </c>
       <c r="BH9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="BI9">
         <v>0</v>
@@ -7983,7 +7944,7 @@
         <v>1</v>
       </c>
       <c r="BL9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BM9">
         <v>2</v>
@@ -7992,50 +7953,59 @@
         <v>9</v>
       </c>
       <c r="BO9" t="s">
+        <v>178</v>
+      </c>
+      <c r="BP9">
+        <v>1</v>
+      </c>
+      <c r="BQ9">
+        <v>1</v>
+      </c>
+      <c r="BR9" t="b">
+        <v>1</v>
+      </c>
+      <c r="BS9">
+        <v>9600</v>
+      </c>
+      <c r="BT9" t="s">
+        <v>179</v>
+      </c>
+      <c r="BU9" t="b">
+        <v>1</v>
+      </c>
+      <c r="BV9" t="s">
+        <v>182</v>
+      </c>
+      <c r="BW9">
+        <v>2</v>
+      </c>
+      <c r="BX9">
+        <v>9</v>
+      </c>
+      <c r="BY9" t="s">
+        <v>178</v>
+      </c>
+      <c r="BZ9">
+        <v>1</v>
+      </c>
+      <c r="CA9">
+        <v>1</v>
+      </c>
+      <c r="CB9" t="b">
+        <v>1</v>
+      </c>
+      <c r="CC9">
+        <v>1300</v>
+      </c>
+      <c r="CD9" t="s">
+        <v>229</v>
+      </c>
+      <c r="CE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="CF9" t="s">
         <v>177</v>
       </c>
-      <c r="BP9">
-        <v>0</v>
-      </c>
-      <c r="BQ9">
-        <v>0</v>
-      </c>
-      <c r="BR9" t="b">
-        <v>1</v>
-      </c>
-      <c r="BV9" t="s">
-        <v>181</v>
-      </c>
-      <c r="BW9">
-        <v>2</v>
-      </c>
-      <c r="BX9">
-        <v>9</v>
-      </c>
-      <c r="BY9" t="s">
-        <v>177</v>
-      </c>
-      <c r="BZ9">
-        <v>1</v>
-      </c>
-      <c r="CA9">
-        <v>1</v>
-      </c>
-      <c r="CB9" t="b">
-        <v>1</v>
-      </c>
-      <c r="CC9">
-        <v>1600</v>
-      </c>
-      <c r="CD9" t="s">
-        <v>228</v>
-      </c>
-      <c r="CE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="CF9" t="s">
-        <v>176</v>
-      </c>
       <c r="CG9">
         <v>2</v>
       </c>
@@ -8043,7 +8013,7 @@
         <v>9</v>
       </c>
       <c r="CI9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CJ9">
         <v>0</v>
@@ -8055,7 +8025,7 @@
         <v>1</v>
       </c>
       <c r="CO9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CP9">
         <v>0</v>
@@ -8067,10 +8037,10 @@
         <v>1</v>
       </c>
       <c r="DR9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="DS9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="DT9">
         <v>1</v>
@@ -8082,10 +8052,10 @@
         <v>1</v>
       </c>
       <c r="DW9">
-        <v>15000</v>
+        <v>14000</v>
       </c>
       <c r="DX9">
-        <v>15000</v>
+        <v>14000</v>
       </c>
       <c r="DY9">
         <v>0.95</v>
@@ -8100,7 +8070,7 @@
         <v>0</v>
       </c>
       <c r="EC9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="ED9">
         <v>1</v>
@@ -8124,25 +8094,25 @@
         <v>0.1</v>
       </c>
       <c r="EK9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="EL9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="EM9">
         <v>96</v>
       </c>
       <c r="EN9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="EO9">
         <v>12</v>
       </c>
       <c r="EP9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="EQ9">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="ER9">
         <v>0</v>
@@ -8159,10 +8129,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G10" t="b">
         <v>0</v>
@@ -8198,10 +8168,10 @@
         <v>1</v>
       </c>
       <c r="R10">
-        <v>2455000</v>
+        <v>1158000</v>
       </c>
       <c r="S10" t="s">
-        <v>161</v>
+        <v>219</v>
       </c>
       <c r="T10" t="s">
         <v>162</v>
@@ -8249,7 +8219,7 @@
         <v>15000000</v>
       </c>
       <c r="AL10" t="s">
-        <v>166</v>
+        <v>224</v>
       </c>
       <c r="AM10">
         <v>55</v>
@@ -8282,7 +8252,7 @@
         <v>2800</v>
       </c>
       <c r="AW10" t="s">
-        <v>225</v>
+        <v>172</v>
       </c>
       <c r="AX10">
         <v>55</v>
@@ -8312,7 +8282,7 @@
         <v>1</v>
       </c>
       <c r="BL10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BM10">
         <v>2</v>
@@ -8321,41 +8291,41 @@
         <v>9</v>
       </c>
       <c r="BO10" t="s">
+        <v>178</v>
+      </c>
+      <c r="BP10">
+        <v>0</v>
+      </c>
+      <c r="BQ10">
+        <v>0</v>
+      </c>
+      <c r="BR10" t="b">
+        <v>1</v>
+      </c>
+      <c r="BV10" t="s">
+        <v>182</v>
+      </c>
+      <c r="BW10">
+        <v>2</v>
+      </c>
+      <c r="BX10">
+        <v>9</v>
+      </c>
+      <c r="BY10" t="s">
+        <v>178</v>
+      </c>
+      <c r="BZ10">
+        <v>0</v>
+      </c>
+      <c r="CA10">
+        <v>0</v>
+      </c>
+      <c r="CB10" t="b">
+        <v>1</v>
+      </c>
+      <c r="CF10" t="s">
         <v>177</v>
       </c>
-      <c r="BP10">
-        <v>0</v>
-      </c>
-      <c r="BQ10">
-        <v>0</v>
-      </c>
-      <c r="BR10" t="b">
-        <v>1</v>
-      </c>
-      <c r="BV10" t="s">
-        <v>181</v>
-      </c>
-      <c r="BW10">
-        <v>2</v>
-      </c>
-      <c r="BX10">
-        <v>9</v>
-      </c>
-      <c r="BY10" t="s">
-        <v>177</v>
-      </c>
-      <c r="BZ10">
-        <v>0</v>
-      </c>
-      <c r="CA10">
-        <v>0</v>
-      </c>
-      <c r="CB10" t="b">
-        <v>1</v>
-      </c>
-      <c r="CF10" t="s">
-        <v>176</v>
-      </c>
       <c r="CG10">
         <v>2</v>
       </c>
@@ -8363,7 +8333,7 @@
         <v>9</v>
       </c>
       <c r="CI10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CJ10">
         <v>0</v>
@@ -8375,19 +8345,49 @@
         <v>1</v>
       </c>
       <c r="CO10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CP10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CR10" t="b">
         <v>1</v>
       </c>
+      <c r="CS10" t="s">
+        <v>231</v>
+      </c>
+      <c r="CT10">
+        <v>50000</v>
+      </c>
+      <c r="CU10">
+        <v>15000</v>
+      </c>
+      <c r="CV10">
+        <v>7200</v>
+      </c>
+      <c r="CW10">
+        <v>7200</v>
+      </c>
+      <c r="CX10">
+        <v>50000</v>
+      </c>
+      <c r="CY10">
+        <v>0.9</v>
+      </c>
+      <c r="CZ10">
+        <v>0.8</v>
+      </c>
+      <c r="DA10" t="b">
+        <v>0</v>
+      </c>
+      <c r="DB10" t="b">
+        <v>0</v>
+      </c>
       <c r="DM10" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="DN10">
         <v>0.05</v>
@@ -8402,10 +8402,10 @@
         <v>8</v>
       </c>
       <c r="DR10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="DS10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="DT10">
         <v>0</v>
@@ -8417,7 +8417,7 @@
         <v>1</v>
       </c>
       <c r="EC10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="ED10">
         <v>0</v>
@@ -8429,25 +8429,25 @@
         <v>1</v>
       </c>
       <c r="EK10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="EL10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="EM10">
         <v>96</v>
       </c>
       <c r="EN10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="EO10">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="EP10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="EQ10">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="ER10">
         <v>0</v>
@@ -8464,10 +8464,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G11" t="b">
         <v>0</v>
@@ -8503,10 +8503,10 @@
         <v>1</v>
       </c>
       <c r="R11">
-        <v>1546000</v>
+        <v>1720000</v>
       </c>
       <c r="S11" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="T11" t="s">
         <v>162</v>
@@ -8554,10 +8554,10 @@
         <v>15000000</v>
       </c>
       <c r="AL11" t="s">
-        <v>221</v>
+        <v>168</v>
       </c>
       <c r="AM11">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="AN11" t="s">
         <v>162</v>
@@ -8584,10 +8584,10 @@
         <v>1</v>
       </c>
       <c r="AV11">
-        <v>3200</v>
+        <v>2400</v>
       </c>
       <c r="AW11" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AX11">
         <v>55</v>
@@ -8617,7 +8617,7 @@
         <v>1</v>
       </c>
       <c r="BL11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BM11">
         <v>2</v>
@@ -8626,41 +8626,41 @@
         <v>9</v>
       </c>
       <c r="BO11" t="s">
+        <v>178</v>
+      </c>
+      <c r="BP11">
+        <v>0</v>
+      </c>
+      <c r="BQ11">
+        <v>0</v>
+      </c>
+      <c r="BR11" t="b">
+        <v>1</v>
+      </c>
+      <c r="BV11" t="s">
+        <v>182</v>
+      </c>
+      <c r="BW11">
+        <v>2</v>
+      </c>
+      <c r="BX11">
+        <v>9</v>
+      </c>
+      <c r="BY11" t="s">
+        <v>178</v>
+      </c>
+      <c r="BZ11">
+        <v>0</v>
+      </c>
+      <c r="CA11">
+        <v>0</v>
+      </c>
+      <c r="CB11" t="b">
+        <v>1</v>
+      </c>
+      <c r="CF11" t="s">
         <v>177</v>
       </c>
-      <c r="BP11">
-        <v>0</v>
-      </c>
-      <c r="BQ11">
-        <v>0</v>
-      </c>
-      <c r="BR11" t="b">
-        <v>1</v>
-      </c>
-      <c r="BV11" t="s">
-        <v>181</v>
-      </c>
-      <c r="BW11">
-        <v>2</v>
-      </c>
-      <c r="BX11">
-        <v>9</v>
-      </c>
-      <c r="BY11" t="s">
-        <v>177</v>
-      </c>
-      <c r="BZ11">
-        <v>0</v>
-      </c>
-      <c r="CA11">
-        <v>0</v>
-      </c>
-      <c r="CB11" t="b">
-        <v>1</v>
-      </c>
-      <c r="CF11" t="s">
-        <v>176</v>
-      </c>
       <c r="CG11">
         <v>2</v>
       </c>
@@ -8668,7 +8668,7 @@
         <v>9</v>
       </c>
       <c r="CI11" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CJ11">
         <v>0</v>
@@ -8680,49 +8680,19 @@
         <v>1</v>
       </c>
       <c r="CO11" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CP11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CR11" t="b">
         <v>1</v>
       </c>
-      <c r="CS11" t="s">
-        <v>229</v>
-      </c>
-      <c r="CT11">
-        <v>50000</v>
-      </c>
-      <c r="CU11">
-        <v>15000</v>
-      </c>
-      <c r="CV11">
-        <v>7200</v>
-      </c>
-      <c r="CW11">
-        <v>7200</v>
-      </c>
-      <c r="CX11">
-        <v>50000</v>
-      </c>
-      <c r="CY11">
-        <v>0.9</v>
-      </c>
-      <c r="CZ11">
-        <v>0.8</v>
-      </c>
-      <c r="DA11" t="b">
-        <v>0</v>
-      </c>
-      <c r="DB11" t="b">
-        <v>0</v>
-      </c>
       <c r="DM11" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="DN11">
         <v>0.05</v>
@@ -8737,10 +8707,10 @@
         <v>8</v>
       </c>
       <c r="DR11" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="DS11" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="DT11">
         <v>0</v>
@@ -8752,7 +8722,7 @@
         <v>1</v>
       </c>
       <c r="EC11" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="ED11">
         <v>0</v>
@@ -8764,25 +8734,25 @@
         <v>1</v>
       </c>
       <c r="EK11" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="EL11" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="EM11">
         <v>96</v>
       </c>
       <c r="EN11" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="EO11">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="EP11" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="EQ11">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="ER11">
         <v>0</v>
@@ -8799,10 +8769,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F12" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G12" t="b">
         <v>0</v>
@@ -8838,10 +8808,10 @@
         <v>1</v>
       </c>
       <c r="R12">
-        <v>2012000</v>
+        <v>1720000</v>
       </c>
       <c r="S12" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="T12" t="s">
         <v>162</v>
@@ -8889,7 +8859,7 @@
         <v>15000000</v>
       </c>
       <c r="AL12" t="s">
-        <v>221</v>
+        <v>170</v>
       </c>
       <c r="AM12">
         <v>55</v>
@@ -8919,10 +8889,10 @@
         <v>1</v>
       </c>
       <c r="AV12">
-        <v>2400</v>
+        <v>3200</v>
       </c>
       <c r="AW12" t="s">
-        <v>224</v>
+        <v>175</v>
       </c>
       <c r="AX12">
         <v>55</v>
@@ -8952,7 +8922,7 @@
         <v>1</v>
       </c>
       <c r="BL12" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BM12">
         <v>2</v>
@@ -8961,41 +8931,41 @@
         <v>9</v>
       </c>
       <c r="BO12" t="s">
+        <v>178</v>
+      </c>
+      <c r="BP12">
+        <v>0</v>
+      </c>
+      <c r="BQ12">
+        <v>0</v>
+      </c>
+      <c r="BR12" t="b">
+        <v>1</v>
+      </c>
+      <c r="BV12" t="s">
+        <v>182</v>
+      </c>
+      <c r="BW12">
+        <v>2</v>
+      </c>
+      <c r="BX12">
+        <v>9</v>
+      </c>
+      <c r="BY12" t="s">
+        <v>178</v>
+      </c>
+      <c r="BZ12">
+        <v>0</v>
+      </c>
+      <c r="CA12">
+        <v>0</v>
+      </c>
+      <c r="CB12" t="b">
+        <v>1</v>
+      </c>
+      <c r="CF12" t="s">
         <v>177</v>
       </c>
-      <c r="BP12">
-        <v>0</v>
-      </c>
-      <c r="BQ12">
-        <v>0</v>
-      </c>
-      <c r="BR12" t="b">
-        <v>1</v>
-      </c>
-      <c r="BV12" t="s">
-        <v>181</v>
-      </c>
-      <c r="BW12">
-        <v>2</v>
-      </c>
-      <c r="BX12">
-        <v>9</v>
-      </c>
-      <c r="BY12" t="s">
-        <v>177</v>
-      </c>
-      <c r="BZ12">
-        <v>0</v>
-      </c>
-      <c r="CA12">
-        <v>0</v>
-      </c>
-      <c r="CB12" t="b">
-        <v>1</v>
-      </c>
-      <c r="CF12" t="s">
-        <v>176</v>
-      </c>
       <c r="CG12">
         <v>2</v>
       </c>
@@ -9003,7 +8973,7 @@
         <v>9</v>
       </c>
       <c r="CI12" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CJ12">
         <v>0</v>
@@ -9015,7 +8985,7 @@
         <v>1</v>
       </c>
       <c r="CO12" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CP12">
         <v>0</v>
@@ -9042,10 +9012,10 @@
         <v>8</v>
       </c>
       <c r="DR12" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="DS12" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="DT12">
         <v>0</v>
@@ -9057,7 +9027,7 @@
         <v>1</v>
       </c>
       <c r="EC12" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="ED12">
         <v>0</v>
@@ -9069,25 +9039,25 @@
         <v>1</v>
       </c>
       <c r="EK12" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="EL12" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="EM12">
         <v>96</v>
       </c>
       <c r="EN12" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="EO12">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="EP12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="EQ12">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="ER12">
         <v>0</v>
@@ -9104,10 +9074,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F13" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G13" t="b">
         <v>0</v>
@@ -9143,10 +9113,10 @@
         <v>1</v>
       </c>
       <c r="R13">
-        <v>2896000</v>
+        <v>913000</v>
       </c>
       <c r="S13" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="T13" t="s">
         <v>162</v>
@@ -9194,7 +9164,7 @@
         <v>15000000</v>
       </c>
       <c r="AL13" t="s">
-        <v>221</v>
+        <v>170</v>
       </c>
       <c r="AM13">
         <v>55</v>
@@ -9224,7 +9194,7 @@
         <v>1</v>
       </c>
       <c r="AV13">
-        <v>2400</v>
+        <v>2800</v>
       </c>
       <c r="AW13" t="s">
         <v>173</v>
@@ -9257,7 +9227,7 @@
         <v>1</v>
       </c>
       <c r="BL13" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BM13">
         <v>2</v>
@@ -9266,41 +9236,41 @@
         <v>9</v>
       </c>
       <c r="BO13" t="s">
+        <v>178</v>
+      </c>
+      <c r="BP13">
+        <v>0</v>
+      </c>
+      <c r="BQ13">
+        <v>0</v>
+      </c>
+      <c r="BR13" t="b">
+        <v>1</v>
+      </c>
+      <c r="BV13" t="s">
+        <v>182</v>
+      </c>
+      <c r="BW13">
+        <v>2</v>
+      </c>
+      <c r="BX13">
+        <v>9</v>
+      </c>
+      <c r="BY13" t="s">
+        <v>178</v>
+      </c>
+      <c r="BZ13">
+        <v>0</v>
+      </c>
+      <c r="CA13">
+        <v>0</v>
+      </c>
+      <c r="CB13" t="b">
+        <v>1</v>
+      </c>
+      <c r="CF13" t="s">
         <v>177</v>
       </c>
-      <c r="BP13">
-        <v>0</v>
-      </c>
-      <c r="BQ13">
-        <v>0</v>
-      </c>
-      <c r="BR13" t="b">
-        <v>1</v>
-      </c>
-      <c r="BV13" t="s">
-        <v>181</v>
-      </c>
-      <c r="BW13">
-        <v>2</v>
-      </c>
-      <c r="BX13">
-        <v>9</v>
-      </c>
-      <c r="BY13" t="s">
-        <v>177</v>
-      </c>
-      <c r="BZ13">
-        <v>0</v>
-      </c>
-      <c r="CA13">
-        <v>0</v>
-      </c>
-      <c r="CB13" t="b">
-        <v>1</v>
-      </c>
-      <c r="CF13" t="s">
-        <v>176</v>
-      </c>
       <c r="CG13">
         <v>2</v>
       </c>
@@ -9308,7 +9278,7 @@
         <v>9</v>
       </c>
       <c r="CI13" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CJ13">
         <v>0</v>
@@ -9320,7 +9290,7 @@
         <v>1</v>
       </c>
       <c r="CO13" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CP13">
         <v>0</v>
@@ -9332,7 +9302,7 @@
         <v>1</v>
       </c>
       <c r="DM13" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="DN13">
         <v>0.05</v>
@@ -9347,10 +9317,10 @@
         <v>8</v>
       </c>
       <c r="DR13" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="DS13" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="DT13">
         <v>0</v>
@@ -9362,7 +9332,7 @@
         <v>1</v>
       </c>
       <c r="EC13" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="ED13">
         <v>0</v>
@@ -9374,22 +9344,22 @@
         <v>1</v>
       </c>
       <c r="EK13" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="EL13" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="EM13">
         <v>96</v>
       </c>
       <c r="EN13" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="EO13">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="EP13" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="EQ13">
         <v>0</v>
@@ -9409,10 +9379,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F14" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G14" t="b">
         <v>0</v>
@@ -9448,10 +9418,10 @@
         <v>1</v>
       </c>
       <c r="R14">
-        <v>945000</v>
+        <v>2455000</v>
       </c>
       <c r="S14" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="T14" t="s">
         <v>162</v>
@@ -9499,10 +9469,10 @@
         <v>15000000</v>
       </c>
       <c r="AL14" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AM14">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="AN14" t="s">
         <v>162</v>
@@ -9532,7 +9502,7 @@
         <v>2800</v>
       </c>
       <c r="AW14" t="s">
-        <v>225</v>
+        <v>175</v>
       </c>
       <c r="AX14">
         <v>55</v>
@@ -9562,7 +9532,7 @@
         <v>1</v>
       </c>
       <c r="BL14" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BM14">
         <v>2</v>
@@ -9571,41 +9541,41 @@
         <v>9</v>
       </c>
       <c r="BO14" t="s">
+        <v>178</v>
+      </c>
+      <c r="BP14">
+        <v>0</v>
+      </c>
+      <c r="BQ14">
+        <v>0</v>
+      </c>
+      <c r="BR14" t="b">
+        <v>1</v>
+      </c>
+      <c r="BV14" t="s">
+        <v>182</v>
+      </c>
+      <c r="BW14">
+        <v>2</v>
+      </c>
+      <c r="BX14">
+        <v>9</v>
+      </c>
+      <c r="BY14" t="s">
+        <v>178</v>
+      </c>
+      <c r="BZ14">
+        <v>0</v>
+      </c>
+      <c r="CA14">
+        <v>0</v>
+      </c>
+      <c r="CB14" t="b">
+        <v>1</v>
+      </c>
+      <c r="CF14" t="s">
         <v>177</v>
       </c>
-      <c r="BP14">
-        <v>0</v>
-      </c>
-      <c r="BQ14">
-        <v>0</v>
-      </c>
-      <c r="BR14" t="b">
-        <v>1</v>
-      </c>
-      <c r="BV14" t="s">
-        <v>181</v>
-      </c>
-      <c r="BW14">
-        <v>2</v>
-      </c>
-      <c r="BX14">
-        <v>9</v>
-      </c>
-      <c r="BY14" t="s">
-        <v>177</v>
-      </c>
-      <c r="BZ14">
-        <v>0</v>
-      </c>
-      <c r="CA14">
-        <v>0</v>
-      </c>
-      <c r="CB14" t="b">
-        <v>1</v>
-      </c>
-      <c r="CF14" t="s">
-        <v>176</v>
-      </c>
       <c r="CG14">
         <v>2</v>
       </c>
@@ -9613,7 +9583,7 @@
         <v>9</v>
       </c>
       <c r="CI14" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CJ14">
         <v>0</v>
@@ -9625,7 +9595,7 @@
         <v>1</v>
       </c>
       <c r="CO14" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CP14">
         <v>0</v>
@@ -9637,7 +9607,7 @@
         <v>1</v>
       </c>
       <c r="DM14" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="DN14">
         <v>0.05</v>
@@ -9652,10 +9622,10 @@
         <v>8</v>
       </c>
       <c r="DR14" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="DS14" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="DT14">
         <v>0</v>
@@ -9667,7 +9637,7 @@
         <v>1</v>
       </c>
       <c r="EC14" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="ED14">
         <v>0</v>
@@ -9679,25 +9649,25 @@
         <v>1</v>
       </c>
       <c r="EK14" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="EL14" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="EM14">
         <v>96</v>
       </c>
       <c r="EN14" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="EO14">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="EP14" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="EQ14">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="ER14">
         <v>0</v>
@@ -9714,10 +9684,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F15" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G15" t="b">
         <v>0</v>
@@ -9753,10 +9723,10 @@
         <v>1</v>
       </c>
       <c r="R15">
-        <v>945000</v>
+        <v>2532000</v>
       </c>
       <c r="S15" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="T15" t="s">
         <v>162</v>
@@ -9804,10 +9774,10 @@
         <v>15000000</v>
       </c>
       <c r="AL15" t="s">
-        <v>166</v>
+        <v>222</v>
       </c>
       <c r="AM15">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="AN15" t="s">
         <v>162</v>
@@ -9834,10 +9804,10 @@
         <v>1</v>
       </c>
       <c r="AV15">
-        <v>2800</v>
+        <v>3200</v>
       </c>
       <c r="AW15" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AX15">
         <v>55</v>
@@ -9867,7 +9837,7 @@
         <v>1</v>
       </c>
       <c r="BL15" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BM15">
         <v>2</v>
@@ -9876,41 +9846,41 @@
         <v>9</v>
       </c>
       <c r="BO15" t="s">
+        <v>178</v>
+      </c>
+      <c r="BP15">
+        <v>0</v>
+      </c>
+      <c r="BQ15">
+        <v>0</v>
+      </c>
+      <c r="BR15" t="b">
+        <v>1</v>
+      </c>
+      <c r="BV15" t="s">
+        <v>182</v>
+      </c>
+      <c r="BW15">
+        <v>2</v>
+      </c>
+      <c r="BX15">
+        <v>9</v>
+      </c>
+      <c r="BY15" t="s">
+        <v>178</v>
+      </c>
+      <c r="BZ15">
+        <v>0</v>
+      </c>
+      <c r="CA15">
+        <v>0</v>
+      </c>
+      <c r="CB15" t="b">
+        <v>1</v>
+      </c>
+      <c r="CF15" t="s">
         <v>177</v>
       </c>
-      <c r="BP15">
-        <v>0</v>
-      </c>
-      <c r="BQ15">
-        <v>0</v>
-      </c>
-      <c r="BR15" t="b">
-        <v>1</v>
-      </c>
-      <c r="BV15" t="s">
-        <v>181</v>
-      </c>
-      <c r="BW15">
-        <v>2</v>
-      </c>
-      <c r="BX15">
-        <v>9</v>
-      </c>
-      <c r="BY15" t="s">
-        <v>177</v>
-      </c>
-      <c r="BZ15">
-        <v>0</v>
-      </c>
-      <c r="CA15">
-        <v>0</v>
-      </c>
-      <c r="CB15" t="b">
-        <v>1</v>
-      </c>
-      <c r="CF15" t="s">
-        <v>176</v>
-      </c>
       <c r="CG15">
         <v>2</v>
       </c>
@@ -9918,7 +9888,7 @@
         <v>9</v>
       </c>
       <c r="CI15" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CJ15">
         <v>0</v>
@@ -9930,7 +9900,7 @@
         <v>1</v>
       </c>
       <c r="CO15" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CP15">
         <v>0</v>
@@ -9942,7 +9912,7 @@
         <v>1</v>
       </c>
       <c r="DM15" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="DN15">
         <v>0.05</v>
@@ -9957,10 +9927,10 @@
         <v>8</v>
       </c>
       <c r="DR15" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="DS15" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="DT15">
         <v>0</v>
@@ -9972,7 +9942,7 @@
         <v>1</v>
       </c>
       <c r="EC15" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="ED15">
         <v>0</v>
@@ -9984,25 +9954,25 @@
         <v>1</v>
       </c>
       <c r="EK15" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="EL15" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="EM15">
         <v>96</v>
       </c>
       <c r="EN15" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="EO15">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="EP15" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="EQ15">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="ER15">
         <v>0</v>
@@ -10019,10 +9989,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F16" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G16" t="b">
         <v>0</v>
@@ -10058,10 +10028,10 @@
         <v>1</v>
       </c>
       <c r="R16">
-        <v>2012000</v>
+        <v>1720000</v>
       </c>
       <c r="S16" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="T16" t="s">
         <v>162</v>
@@ -10109,10 +10079,10 @@
         <v>15000000</v>
       </c>
       <c r="AL16" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="AM16">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="AN16" t="s">
         <v>162</v>
@@ -10139,10 +10109,10 @@
         <v>1</v>
       </c>
       <c r="AV16">
-        <v>3200</v>
+        <v>2400</v>
       </c>
       <c r="AW16" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AX16">
         <v>55</v>
@@ -10172,7 +10142,7 @@
         <v>1</v>
       </c>
       <c r="BL16" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BM16">
         <v>2</v>
@@ -10181,41 +10151,41 @@
         <v>9</v>
       </c>
       <c r="BO16" t="s">
+        <v>178</v>
+      </c>
+      <c r="BP16">
+        <v>0</v>
+      </c>
+      <c r="BQ16">
+        <v>0</v>
+      </c>
+      <c r="BR16" t="b">
+        <v>1</v>
+      </c>
+      <c r="BV16" t="s">
+        <v>182</v>
+      </c>
+      <c r="BW16">
+        <v>2</v>
+      </c>
+      <c r="BX16">
+        <v>9</v>
+      </c>
+      <c r="BY16" t="s">
+        <v>178</v>
+      </c>
+      <c r="BZ16">
+        <v>0</v>
+      </c>
+      <c r="CA16">
+        <v>0</v>
+      </c>
+      <c r="CB16" t="b">
+        <v>1</v>
+      </c>
+      <c r="CF16" t="s">
         <v>177</v>
       </c>
-      <c r="BP16">
-        <v>0</v>
-      </c>
-      <c r="BQ16">
-        <v>0</v>
-      </c>
-      <c r="BR16" t="b">
-        <v>1</v>
-      </c>
-      <c r="BV16" t="s">
-        <v>181</v>
-      </c>
-      <c r="BW16">
-        <v>2</v>
-      </c>
-      <c r="BX16">
-        <v>9</v>
-      </c>
-      <c r="BY16" t="s">
-        <v>177</v>
-      </c>
-      <c r="BZ16">
-        <v>0</v>
-      </c>
-      <c r="CA16">
-        <v>0</v>
-      </c>
-      <c r="CB16" t="b">
-        <v>1</v>
-      </c>
-      <c r="CF16" t="s">
-        <v>176</v>
-      </c>
       <c r="CG16">
         <v>2</v>
       </c>
@@ -10223,7 +10193,7 @@
         <v>9</v>
       </c>
       <c r="CI16" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CJ16">
         <v>0</v>
@@ -10235,19 +10205,49 @@
         <v>1</v>
       </c>
       <c r="CO16" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CP16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CR16" t="b">
         <v>1</v>
       </c>
+      <c r="CS16" t="s">
+        <v>185</v>
+      </c>
+      <c r="CT16">
+        <v>75000</v>
+      </c>
+      <c r="CU16">
+        <v>20000</v>
+      </c>
+      <c r="CV16">
+        <v>7200</v>
+      </c>
+      <c r="CW16">
+        <v>11000</v>
+      </c>
+      <c r="CX16">
+        <v>100000</v>
+      </c>
+      <c r="CY16">
+        <v>0.9</v>
+      </c>
+      <c r="CZ16">
+        <v>0.8</v>
+      </c>
+      <c r="DA16" t="b">
+        <v>0</v>
+      </c>
+      <c r="DB16" t="b">
+        <v>0</v>
+      </c>
       <c r="DM16" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="DN16">
         <v>0.05</v>
@@ -10262,10 +10262,10 @@
         <v>8</v>
       </c>
       <c r="DR16" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="DS16" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="DT16">
         <v>0</v>
@@ -10277,7 +10277,7 @@
         <v>1</v>
       </c>
       <c r="EC16" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="ED16">
         <v>0</v>
@@ -10289,22 +10289,22 @@
         <v>1</v>
       </c>
       <c r="EK16" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="EL16" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="EM16">
         <v>96</v>
       </c>
       <c r="EN16" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="EO16">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="EP16" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="EQ16">
         <v>0</v>
@@ -10324,10 +10324,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F17" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G17" t="b">
         <v>0</v>
@@ -10363,10 +10363,10 @@
         <v>1</v>
       </c>
       <c r="R17">
-        <v>1720000</v>
+        <v>1546000</v>
       </c>
       <c r="S17" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="T17" t="s">
         <v>162</v>
@@ -10414,10 +10414,10 @@
         <v>15000000</v>
       </c>
       <c r="AL17" t="s">
-        <v>222</v>
+        <v>165</v>
       </c>
       <c r="AM17">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="AN17" t="s">
         <v>162</v>
@@ -10444,10 +10444,10 @@
         <v>1</v>
       </c>
       <c r="AV17">
-        <v>2800</v>
+        <v>2400</v>
       </c>
       <c r="AW17" t="s">
-        <v>224</v>
+        <v>174</v>
       </c>
       <c r="AX17">
         <v>55</v>
@@ -10477,7 +10477,7 @@
         <v>1</v>
       </c>
       <c r="BL17" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BM17">
         <v>2</v>
@@ -10486,41 +10486,41 @@
         <v>9</v>
       </c>
       <c r="BO17" t="s">
+        <v>178</v>
+      </c>
+      <c r="BP17">
+        <v>0</v>
+      </c>
+      <c r="BQ17">
+        <v>0</v>
+      </c>
+      <c r="BR17" t="b">
+        <v>1</v>
+      </c>
+      <c r="BV17" t="s">
+        <v>182</v>
+      </c>
+      <c r="BW17">
+        <v>2</v>
+      </c>
+      <c r="BX17">
+        <v>9</v>
+      </c>
+      <c r="BY17" t="s">
+        <v>178</v>
+      </c>
+      <c r="BZ17">
+        <v>0</v>
+      </c>
+      <c r="CA17">
+        <v>0</v>
+      </c>
+      <c r="CB17" t="b">
+        <v>1</v>
+      </c>
+      <c r="CF17" t="s">
         <v>177</v>
       </c>
-      <c r="BP17">
-        <v>0</v>
-      </c>
-      <c r="BQ17">
-        <v>0</v>
-      </c>
-      <c r="BR17" t="b">
-        <v>1</v>
-      </c>
-      <c r="BV17" t="s">
-        <v>181</v>
-      </c>
-      <c r="BW17">
-        <v>2</v>
-      </c>
-      <c r="BX17">
-        <v>9</v>
-      </c>
-      <c r="BY17" t="s">
-        <v>177</v>
-      </c>
-      <c r="BZ17">
-        <v>0</v>
-      </c>
-      <c r="CA17">
-        <v>0</v>
-      </c>
-      <c r="CB17" t="b">
-        <v>1</v>
-      </c>
-      <c r="CF17" t="s">
-        <v>176</v>
-      </c>
       <c r="CG17">
         <v>2</v>
       </c>
@@ -10528,7 +10528,7 @@
         <v>9</v>
       </c>
       <c r="CI17" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CJ17">
         <v>0</v>
@@ -10540,79 +10540,19 @@
         <v>1</v>
       </c>
       <c r="CO17" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CP17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CR17" t="b">
         <v>1</v>
       </c>
-      <c r="CS17" t="s">
-        <v>185</v>
-      </c>
-      <c r="CT17">
-        <v>75000</v>
-      </c>
-      <c r="CU17">
-        <v>20000</v>
-      </c>
-      <c r="CV17">
-        <v>7200</v>
-      </c>
-      <c r="CW17">
-        <v>11000</v>
-      </c>
-      <c r="CX17">
-        <v>100000</v>
-      </c>
-      <c r="CY17">
-        <v>0.9</v>
-      </c>
-      <c r="CZ17">
-        <v>0.8</v>
-      </c>
-      <c r="DA17" t="b">
-        <v>0</v>
-      </c>
-      <c r="DB17" t="b">
-        <v>0</v>
-      </c>
-      <c r="DC17" t="s">
-        <v>230</v>
-      </c>
-      <c r="DD17">
-        <v>50000</v>
-      </c>
-      <c r="DE17">
-        <v>15000</v>
-      </c>
-      <c r="DF17">
-        <v>7200</v>
-      </c>
-      <c r="DG17">
-        <v>7200</v>
-      </c>
-      <c r="DH17">
-        <v>50000</v>
-      </c>
-      <c r="DI17">
-        <v>0.9</v>
-      </c>
-      <c r="DJ17">
-        <v>0.8</v>
-      </c>
-      <c r="DK17" t="b">
-        <v>0</v>
-      </c>
-      <c r="DL17" t="b">
-        <v>0</v>
-      </c>
       <c r="DM17" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="DN17">
         <v>0.05</v>
@@ -10627,10 +10567,10 @@
         <v>8</v>
       </c>
       <c r="DR17" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="DS17" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="DT17">
         <v>0</v>
@@ -10642,7 +10582,7 @@
         <v>1</v>
       </c>
       <c r="EC17" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="ED17">
         <v>0</v>
@@ -10654,22 +10594,22 @@
         <v>1</v>
       </c>
       <c r="EK17" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="EL17" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="EM17">
         <v>96</v>
       </c>
       <c r="EN17" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="EO17">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="EP17" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="EQ17">
         <v>0</v>
@@ -10708,13 +10648,13 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>9</v>
@@ -10995,13 +10935,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G2">
-        <v>543</v>
+        <v>208</v>
       </c>
       <c r="H2">
         <v>96</v>
@@ -11019,10 +10959,10 @@
         <v>1</v>
       </c>
       <c r="M2">
-        <v>15120000</v>
+        <v>8950000</v>
       </c>
       <c r="N2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="O2" t="s">
         <v>162</v>
@@ -11046,7 +10986,7 @@
         <v>1</v>
       </c>
       <c r="W2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Y2" t="s">
         <v>162</v>
@@ -11070,22 +11010,22 @@
         <v>1</v>
       </c>
       <c r="AF2">
-        <v>8630000</v>
+        <v>4510000</v>
       </c>
       <c r="AG2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="AI2">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AJ2" t="b">
         <v>1</v>
       </c>
       <c r="AK2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AL2">
         <v>2</v>
@@ -11094,41 +11034,41 @@
         <v>9</v>
       </c>
       <c r="AN2" t="s">
+        <v>178</v>
+      </c>
+      <c r="AO2">
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU2" t="s">
+        <v>182</v>
+      </c>
+      <c r="AV2">
+        <v>2</v>
+      </c>
+      <c r="AW2">
+        <v>9</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>178</v>
+      </c>
+      <c r="AY2">
+        <v>0</v>
+      </c>
+      <c r="AZ2">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BE2" t="s">
         <v>177</v>
       </c>
-      <c r="AO2">
-        <v>0</v>
-      </c>
-      <c r="AP2">
-        <v>0</v>
-      </c>
-      <c r="AQ2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AU2" t="s">
-        <v>181</v>
-      </c>
-      <c r="AV2">
-        <v>2</v>
-      </c>
-      <c r="AW2">
-        <v>9</v>
-      </c>
-      <c r="AX2" t="s">
-        <v>177</v>
-      </c>
-      <c r="AY2">
-        <v>0</v>
-      </c>
-      <c r="AZ2">
-        <v>0</v>
-      </c>
-      <c r="BA2" t="b">
-        <v>1</v>
-      </c>
-      <c r="BE2" t="s">
-        <v>176</v>
-      </c>
       <c r="BF2">
         <v>2</v>
       </c>
@@ -11136,7 +11076,7 @@
         <v>9</v>
       </c>
       <c r="BH2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="BI2">
         <v>0</v>
@@ -11148,10 +11088,10 @@
         <v>1</v>
       </c>
       <c r="CA2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="CB2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CC2">
         <v>1</v>
@@ -11160,13 +11100,13 @@
         <v>1</v>
       </c>
       <c r="CE2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="CF2">
-        <v>15100</v>
+        <v>9000</v>
       </c>
       <c r="CG2">
-        <v>15000</v>
+        <v>18000</v>
       </c>
       <c r="CH2">
         <v>0.95</v>
@@ -11181,22 +11121,22 @@
         <v>0</v>
       </c>
       <c r="CL2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CM2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="CN2">
         <v>96</v>
       </c>
       <c r="CO2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="CP2">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="CQ2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="CR2">
         <v>0</v>
@@ -11216,13 +11156,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G3">
-        <v>184</v>
+        <v>499</v>
       </c>
       <c r="H3">
         <v>96</v>
@@ -11240,10 +11180,10 @@
         <v>1</v>
       </c>
       <c r="M3">
-        <v>6850000</v>
+        <v>15260000</v>
       </c>
       <c r="N3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O3" t="s">
         <v>162</v>
@@ -11267,7 +11207,7 @@
         <v>1</v>
       </c>
       <c r="W3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Y3" t="s">
         <v>162</v>
@@ -11282,31 +11222,16 @@
         <v>163</v>
       </c>
       <c r="AC3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>1</v>
       </c>
-      <c r="AF3">
-        <v>3260000</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>248</v>
-      </c>
-      <c r="AH3">
-        <v>-20</v>
-      </c>
-      <c r="AI3">
-        <v>50</v>
-      </c>
-      <c r="AJ3" t="b">
-        <v>1</v>
-      </c>
       <c r="AK3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AL3">
         <v>2</v>
@@ -11315,41 +11240,41 @@
         <v>9</v>
       </c>
       <c r="AN3" t="s">
+        <v>178</v>
+      </c>
+      <c r="AO3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU3" t="s">
+        <v>182</v>
+      </c>
+      <c r="AV3">
+        <v>2</v>
+      </c>
+      <c r="AW3">
+        <v>9</v>
+      </c>
+      <c r="AX3" t="s">
+        <v>178</v>
+      </c>
+      <c r="AY3">
+        <v>0</v>
+      </c>
+      <c r="AZ3">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="b">
+        <v>1</v>
+      </c>
+      <c r="BE3" t="s">
         <v>177</v>
       </c>
-      <c r="AO3">
-        <v>0</v>
-      </c>
-      <c r="AP3">
-        <v>0</v>
-      </c>
-      <c r="AQ3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AU3" t="s">
-        <v>181</v>
-      </c>
-      <c r="AV3">
-        <v>2</v>
-      </c>
-      <c r="AW3">
-        <v>9</v>
-      </c>
-      <c r="AX3" t="s">
-        <v>177</v>
-      </c>
-      <c r="AY3">
-        <v>0</v>
-      </c>
-      <c r="AZ3">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="b">
-        <v>1</v>
-      </c>
-      <c r="BE3" t="s">
-        <v>176</v>
-      </c>
       <c r="BF3">
         <v>2</v>
       </c>
@@ -11357,115 +11282,52 @@
         <v>9</v>
       </c>
       <c r="BH3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="BI3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BJ3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK3" t="b">
         <v>1</v>
       </c>
-      <c r="BL3" t="s">
-        <v>183</v>
-      </c>
-      <c r="BM3">
-        <v>75000</v>
-      </c>
-      <c r="BN3">
-        <v>25000</v>
-      </c>
-      <c r="BO3">
-        <v>11000</v>
-      </c>
-      <c r="BP3">
-        <v>22000</v>
-      </c>
-      <c r="BQ3">
-        <v>200000</v>
-      </c>
-      <c r="BR3">
-        <v>0.9</v>
-      </c>
-      <c r="BS3">
-        <v>0.8</v>
-      </c>
-      <c r="BT3" t="b">
-        <v>0</v>
-      </c>
-      <c r="BU3" t="b">
-        <v>0</v>
-      </c>
-      <c r="BV3" t="s">
-        <v>188</v>
-      </c>
-      <c r="BW3">
-        <v>0.05</v>
-      </c>
-      <c r="BX3">
-        <v>0.5</v>
-      </c>
-      <c r="BY3">
-        <v>0.8</v>
-      </c>
-      <c r="BZ3">
-        <v>8</v>
-      </c>
       <c r="CA3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="CB3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CC3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE3" t="s">
-        <v>190</v>
-      </c>
-      <c r="CF3">
-        <v>6800</v>
-      </c>
-      <c r="CG3">
-        <v>14000</v>
-      </c>
-      <c r="CH3">
-        <v>0.95</v>
-      </c>
-      <c r="CI3">
-        <v>0.1</v>
-      </c>
-      <c r="CJ3" t="b">
-        <v>0</v>
-      </c>
-      <c r="CK3" t="b">
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="CL3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CM3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="CN3">
         <v>96</v>
       </c>
       <c r="CO3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="CP3">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="CQ3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="CR3">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="CS3">
         <v>0</v>
@@ -11482,13 +11344,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F4" t="s">
         <v>244</v>
       </c>
       <c r="G4">
-        <v>526</v>
+        <v>535</v>
       </c>
       <c r="H4">
         <v>96</v>
@@ -11506,7 +11368,7 @@
         <v>1</v>
       </c>
       <c r="M4">
-        <v>15360000</v>
+        <v>14610000</v>
       </c>
       <c r="N4" t="s">
         <v>246</v>
@@ -11548,16 +11410,31 @@
         <v>163</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE4" t="b">
         <v>1</v>
       </c>
+      <c r="AF4">
+        <v>6650000</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>227</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>40</v>
+      </c>
+      <c r="AJ4" t="b">
+        <v>1</v>
+      </c>
       <c r="AK4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AL4">
         <v>2</v>
@@ -11566,41 +11443,41 @@
         <v>9</v>
       </c>
       <c r="AN4" t="s">
+        <v>178</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU4" t="s">
+        <v>182</v>
+      </c>
+      <c r="AV4">
+        <v>2</v>
+      </c>
+      <c r="AW4">
+        <v>9</v>
+      </c>
+      <c r="AX4" t="s">
+        <v>178</v>
+      </c>
+      <c r="AY4">
+        <v>0</v>
+      </c>
+      <c r="AZ4">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="b">
+        <v>1</v>
+      </c>
+      <c r="BE4" t="s">
         <v>177</v>
       </c>
-      <c r="AO4">
-        <v>0</v>
-      </c>
-      <c r="AP4">
-        <v>0</v>
-      </c>
-      <c r="AQ4" t="b">
-        <v>1</v>
-      </c>
-      <c r="AU4" t="s">
-        <v>181</v>
-      </c>
-      <c r="AV4">
-        <v>2</v>
-      </c>
-      <c r="AW4">
-        <v>9</v>
-      </c>
-      <c r="AX4" t="s">
-        <v>177</v>
-      </c>
-      <c r="AY4">
-        <v>0</v>
-      </c>
-      <c r="AZ4">
-        <v>0</v>
-      </c>
-      <c r="BA4" t="b">
-        <v>1</v>
-      </c>
-      <c r="BE4" t="s">
-        <v>176</v>
-      </c>
       <c r="BF4">
         <v>2</v>
       </c>
@@ -11608,52 +11485,115 @@
         <v>9</v>
       </c>
       <c r="BH4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="BI4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BJ4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK4" t="b">
         <v>1</v>
       </c>
+      <c r="BL4" t="s">
+        <v>230</v>
+      </c>
+      <c r="BM4">
+        <v>50000</v>
+      </c>
+      <c r="BN4">
+        <v>20000</v>
+      </c>
+      <c r="BO4">
+        <v>7200</v>
+      </c>
+      <c r="BP4">
+        <v>11000</v>
+      </c>
+      <c r="BQ4">
+        <v>100000</v>
+      </c>
+      <c r="BR4">
+        <v>0.9</v>
+      </c>
+      <c r="BS4">
+        <v>0.8</v>
+      </c>
+      <c r="BT4" t="b">
+        <v>0</v>
+      </c>
+      <c r="BU4" t="b">
+        <v>0</v>
+      </c>
+      <c r="BV4" t="s">
+        <v>247</v>
+      </c>
+      <c r="BW4">
+        <v>0.05</v>
+      </c>
+      <c r="BX4">
+        <v>0.5</v>
+      </c>
+      <c r="BY4">
+        <v>0.8</v>
+      </c>
+      <c r="BZ4">
+        <v>8</v>
+      </c>
       <c r="CA4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="CB4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CC4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE4" t="s">
-        <v>190</v>
+        <v>191</v>
+      </c>
+      <c r="CF4">
+        <v>14600</v>
+      </c>
+      <c r="CG4">
+        <v>15000</v>
+      </c>
+      <c r="CH4">
+        <v>0.95</v>
+      </c>
+      <c r="CI4">
+        <v>0.1</v>
+      </c>
+      <c r="CJ4" t="b">
+        <v>0</v>
+      </c>
+      <c r="CK4" t="b">
+        <v>0</v>
       </c>
       <c r="CL4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CM4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="CN4">
         <v>96</v>
       </c>
       <c r="CO4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="CP4">
         <v>12</v>
       </c>
       <c r="CQ4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="CR4">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="CS4">
         <v>0</v>
@@ -11670,13 +11610,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
+        <v>242</v>
+      </c>
+      <c r="F5" t="s">
         <v>243</v>
       </c>
-      <c r="F5" t="s">
-        <v>245</v>
-      </c>
       <c r="G5">
-        <v>192</v>
+        <v>223</v>
       </c>
       <c r="H5">
         <v>96</v>
@@ -11694,10 +11634,10 @@
         <v>1</v>
       </c>
       <c r="M5">
-        <v>7730000</v>
+        <v>8800000</v>
       </c>
       <c r="N5" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="O5" t="s">
         <v>162</v>
@@ -11721,7 +11661,7 @@
         <v>1</v>
       </c>
       <c r="W5" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="Y5" t="s">
         <v>162</v>
@@ -11736,31 +11676,16 @@
         <v>163</v>
       </c>
       <c r="AC5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>1</v>
       </c>
-      <c r="AF5">
-        <v>4380000</v>
-      </c>
-      <c r="AG5" t="s">
-        <v>226</v>
-      </c>
-      <c r="AH5">
-        <v>-20</v>
-      </c>
-      <c r="AI5">
-        <v>50</v>
-      </c>
-      <c r="AJ5" t="b">
-        <v>1</v>
-      </c>
       <c r="AK5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AL5">
         <v>2</v>
@@ -11769,41 +11694,41 @@
         <v>9</v>
       </c>
       <c r="AN5" t="s">
+        <v>178</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU5" t="s">
+        <v>182</v>
+      </c>
+      <c r="AV5">
+        <v>2</v>
+      </c>
+      <c r="AW5">
+        <v>9</v>
+      </c>
+      <c r="AX5" t="s">
+        <v>178</v>
+      </c>
+      <c r="AY5">
+        <v>0</v>
+      </c>
+      <c r="AZ5">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="b">
+        <v>1</v>
+      </c>
+      <c r="BE5" t="s">
         <v>177</v>
       </c>
-      <c r="AO5">
-        <v>0</v>
-      </c>
-      <c r="AP5">
-        <v>0</v>
-      </c>
-      <c r="AQ5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AU5" t="s">
-        <v>181</v>
-      </c>
-      <c r="AV5">
-        <v>2</v>
-      </c>
-      <c r="AW5">
-        <v>9</v>
-      </c>
-      <c r="AX5" t="s">
-        <v>177</v>
-      </c>
-      <c r="AY5">
-        <v>0</v>
-      </c>
-      <c r="AZ5">
-        <v>0</v>
-      </c>
-      <c r="BA5" t="b">
-        <v>1</v>
-      </c>
-      <c r="BE5" t="s">
-        <v>176</v>
-      </c>
       <c r="BF5">
         <v>2</v>
       </c>
@@ -11811,7 +11736,7 @@
         <v>9</v>
       </c>
       <c r="BH5" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="BI5">
         <v>0</v>
@@ -11823,58 +11748,40 @@
         <v>1</v>
       </c>
       <c r="CA5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="CB5" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CC5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE5" t="s">
-        <v>190</v>
-      </c>
-      <c r="CF5">
-        <v>7700</v>
-      </c>
-      <c r="CG5">
-        <v>15000</v>
-      </c>
-      <c r="CH5">
-        <v>0.95</v>
-      </c>
-      <c r="CI5">
-        <v>0.1</v>
-      </c>
-      <c r="CJ5" t="b">
-        <v>0</v>
-      </c>
-      <c r="CK5" t="b">
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="CL5" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CM5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="CN5">
         <v>96</v>
       </c>
       <c r="CO5" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="CP5">
         <v>36</v>
       </c>
       <c r="CQ5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="CR5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="CS5">
         <v>0</v>
@@ -11910,13 +11817,13 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>9</v>
@@ -12227,13 +12134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G2">
-        <v>2135</v>
+        <v>5397</v>
       </c>
       <c r="H2">
         <v>96</v>
@@ -12251,10 +12158,10 @@
         <v>1</v>
       </c>
       <c r="M2">
-        <v>1002000000</v>
+        <v>1241500000</v>
       </c>
       <c r="N2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="O2" t="s">
         <v>162</v>
@@ -12278,7 +12185,7 @@
         <v>1</v>
       </c>
       <c r="W2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Y2" t="s">
         <v>162</v>
@@ -12293,31 +12200,16 @@
         <v>163</v>
       </c>
       <c r="AC2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>1</v>
       </c>
-      <c r="AF2">
-        <v>1229000000</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>248</v>
-      </c>
-      <c r="AH2">
-        <v>-20</v>
-      </c>
-      <c r="AI2">
-        <v>50</v>
-      </c>
-      <c r="AJ2" t="b">
-        <v>1</v>
-      </c>
       <c r="AK2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AL2">
         <v>2</v>
@@ -12326,50 +12218,41 @@
         <v>9</v>
       </c>
       <c r="AN2" t="s">
+        <v>178</v>
+      </c>
+      <c r="AO2">
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU2" t="s">
+        <v>182</v>
+      </c>
+      <c r="AV2">
+        <v>2</v>
+      </c>
+      <c r="AW2">
+        <v>9</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>178</v>
+      </c>
+      <c r="AY2">
+        <v>0</v>
+      </c>
+      <c r="AZ2">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BE2" t="s">
         <v>177</v>
       </c>
-      <c r="AO2">
-        <v>1</v>
-      </c>
-      <c r="AP2">
-        <v>1</v>
-      </c>
-      <c r="AQ2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AR2">
-        <v>104300000</v>
-      </c>
-      <c r="AS2" t="s">
-        <v>255</v>
-      </c>
-      <c r="AT2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AU2" t="s">
-        <v>181</v>
-      </c>
-      <c r="AV2">
-        <v>2</v>
-      </c>
-      <c r="AW2">
-        <v>9</v>
-      </c>
-      <c r="AX2" t="s">
-        <v>177</v>
-      </c>
-      <c r="AY2">
-        <v>0</v>
-      </c>
-      <c r="AZ2">
-        <v>0</v>
-      </c>
-      <c r="BA2" t="b">
-        <v>1</v>
-      </c>
-      <c r="BE2" t="s">
-        <v>176</v>
-      </c>
       <c r="BF2">
         <v>2</v>
       </c>
@@ -12377,97 +12260,22 @@
         <v>9</v>
       </c>
       <c r="BH2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="BI2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BJ2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="b">
         <v>1</v>
       </c>
-      <c r="BL2" t="s">
-        <v>229</v>
-      </c>
-      <c r="BM2">
-        <v>750000</v>
-      </c>
-      <c r="BN2">
-        <v>25000</v>
-      </c>
-      <c r="BO2">
-        <v>11000</v>
-      </c>
-      <c r="BP2">
-        <v>22000</v>
-      </c>
-      <c r="BQ2">
-        <v>200000</v>
-      </c>
-      <c r="BR2">
-        <v>0.9</v>
-      </c>
-      <c r="BS2">
-        <v>0.8</v>
-      </c>
-      <c r="BT2" t="b">
-        <v>0</v>
-      </c>
-      <c r="BU2" t="b">
-        <v>0</v>
-      </c>
-      <c r="BV2" t="s">
-        <v>186</v>
-      </c>
-      <c r="BW2">
-        <v>750000</v>
-      </c>
-      <c r="BX2">
-        <v>25000</v>
-      </c>
-      <c r="BY2">
-        <v>11000</v>
-      </c>
-      <c r="BZ2">
-        <v>22000</v>
-      </c>
-      <c r="CA2">
-        <v>200000</v>
-      </c>
-      <c r="CB2">
-        <v>0.9</v>
-      </c>
-      <c r="CC2">
-        <v>0.8</v>
-      </c>
-      <c r="CD2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CE2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CF2" t="s">
-        <v>188</v>
-      </c>
-      <c r="CG2">
-        <v>0.05</v>
-      </c>
-      <c r="CH2">
-        <v>0.5</v>
-      </c>
-      <c r="CI2">
-        <v>0.8</v>
-      </c>
-      <c r="CJ2">
-        <v>8</v>
-      </c>
       <c r="CK2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="CL2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CM2">
         <v>0</v>
@@ -12476,25 +12284,25 @@
         <v>0</v>
       </c>
       <c r="CO2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="CV2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CW2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="CX2">
         <v>96</v>
       </c>
       <c r="CY2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="CZ2">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="DA2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="DB2">
         <v>30</v>
@@ -12514,13 +12322,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G3">
-        <v>4819</v>
+        <v>1969</v>
       </c>
       <c r="H3">
         <v>96</v>
@@ -12538,10 +12346,10 @@
         <v>1</v>
       </c>
       <c r="M3">
-        <v>1211000000</v>
+        <v>757600000</v>
       </c>
       <c r="N3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O3" t="s">
         <v>162</v>
@@ -12565,7 +12373,7 @@
         <v>1</v>
       </c>
       <c r="W3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="Y3" t="s">
         <v>162</v>
@@ -12589,7 +12397,7 @@
         <v>1</v>
       </c>
       <c r="AK3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AL3">
         <v>2</v>
@@ -12598,41 +12406,41 @@
         <v>9</v>
       </c>
       <c r="AN3" t="s">
+        <v>178</v>
+      </c>
+      <c r="AO3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU3" t="s">
+        <v>182</v>
+      </c>
+      <c r="AV3">
+        <v>2</v>
+      </c>
+      <c r="AW3">
+        <v>9</v>
+      </c>
+      <c r="AX3" t="s">
+        <v>178</v>
+      </c>
+      <c r="AY3">
+        <v>0</v>
+      </c>
+      <c r="AZ3">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="b">
+        <v>1</v>
+      </c>
+      <c r="BE3" t="s">
         <v>177</v>
       </c>
-      <c r="AO3">
-        <v>0</v>
-      </c>
-      <c r="AP3">
-        <v>0</v>
-      </c>
-      <c r="AQ3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AU3" t="s">
-        <v>181</v>
-      </c>
-      <c r="AV3">
-        <v>2</v>
-      </c>
-      <c r="AW3">
-        <v>9</v>
-      </c>
-      <c r="AX3" t="s">
-        <v>177</v>
-      </c>
-      <c r="AY3">
-        <v>0</v>
-      </c>
-      <c r="AZ3">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="b">
-        <v>1</v>
-      </c>
-      <c r="BE3" t="s">
-        <v>176</v>
-      </c>
       <c r="BF3">
         <v>2</v>
       </c>
@@ -12640,34 +12448,34 @@
         <v>9</v>
       </c>
       <c r="BH3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="BI3">
         <v>1</v>
       </c>
       <c r="BJ3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BK3" t="b">
         <v>1</v>
       </c>
       <c r="BL3" t="s">
-        <v>185</v>
+        <v>254</v>
       </c>
       <c r="BM3">
-        <v>500000</v>
+        <v>750000</v>
       </c>
       <c r="BN3">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="BO3">
-        <v>7200</v>
+        <v>11000</v>
       </c>
       <c r="BP3">
-        <v>11000</v>
+        <v>22000</v>
       </c>
       <c r="BQ3">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="BR3">
         <v>0.9</v>
@@ -12681,8 +12489,38 @@
       <c r="BU3" t="b">
         <v>0</v>
       </c>
+      <c r="BV3" t="s">
+        <v>255</v>
+      </c>
+      <c r="BW3">
+        <v>750000</v>
+      </c>
+      <c r="BX3">
+        <v>25000</v>
+      </c>
+      <c r="BY3">
+        <v>11000</v>
+      </c>
+      <c r="BZ3">
+        <v>22000</v>
+      </c>
+      <c r="CA3">
+        <v>200000</v>
+      </c>
+      <c r="CB3">
+        <v>0.9</v>
+      </c>
+      <c r="CC3">
+        <v>0.8</v>
+      </c>
+      <c r="CD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="CE3" t="b">
+        <v>0</v>
+      </c>
       <c r="CF3" t="s">
-        <v>256</v>
+        <v>189</v>
       </c>
       <c r="CG3">
         <v>0.05</v>
@@ -12697,10 +12535,10 @@
         <v>8</v>
       </c>
       <c r="CK3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="CL3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CM3">
         <v>0</v>
@@ -12709,28 +12547,28 @@
         <v>0</v>
       </c>
       <c r="CO3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="CV3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="CW3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="CX3">
         <v>96</v>
       </c>
       <c r="CY3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="CZ3">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="DA3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="DB3">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="DC3">
         <v>0</v>
@@ -12766,7 +12604,7 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>9</v>
@@ -12924,7 +12762,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F2">
         <v>96</v>
@@ -12942,22 +12780,22 @@
         <v>1</v>
       </c>
       <c r="K2">
-        <v>32100000</v>
+        <v>63700000</v>
       </c>
       <c r="L2" t="s">
-        <v>227</v>
+        <v>262</v>
       </c>
       <c r="M2">
-        <v>-20</v>
+        <v>20</v>
       </c>
       <c r="N2">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="O2">
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q2">
         <v>2</v>
@@ -12966,7 +12804,7 @@
         <v>9</v>
       </c>
       <c r="S2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AN2">
         <v>1</v>
@@ -12978,10 +12816,10 @@
         <v>1</v>
       </c>
       <c r="AQ2">
-        <v>16050000</v>
+        <v>31850000</v>
       </c>
       <c r="AR2">
-        <v>32100000</v>
+        <v>63700000</v>
       </c>
       <c r="AS2">
         <v>0.95</v>
@@ -12996,19 +12834,19 @@
         <v>1</v>
       </c>
       <c r="AW2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AX2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AY2">
         <v>96</v>
       </c>
       <c r="AZ2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="BA2">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="BB2">
         <v>0</v>
@@ -13025,7 +12863,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F3">
         <v>96</v>
@@ -13043,10 +12881,10 @@
         <v>1</v>
       </c>
       <c r="K3">
-        <v>14000000</v>
+        <v>11400000</v>
       </c>
       <c r="L3" t="s">
-        <v>227</v>
+        <v>262</v>
       </c>
       <c r="M3">
         <v>0</v>
@@ -13058,7 +12896,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q3">
         <v>2</v>
@@ -13067,7 +12905,7 @@
         <v>9</v>
       </c>
       <c r="S3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AN3">
         <v>1</v>
@@ -13079,10 +12917,10 @@
         <v>1</v>
       </c>
       <c r="AQ3">
-        <v>7000000</v>
+        <v>5700000</v>
       </c>
       <c r="AR3">
-        <v>14000000</v>
+        <v>11400000</v>
       </c>
       <c r="AS3">
         <v>0.95</v>
@@ -13097,16 +12935,16 @@
         <v>1</v>
       </c>
       <c r="AW3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AX3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AY3">
         <v>96</v>
       </c>
       <c r="AZ3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="BA3">
         <v>48</v>
@@ -13126,7 +12964,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F4">
         <v>96</v>
@@ -13144,22 +12982,22 @@
         <v>1</v>
       </c>
       <c r="K4">
-        <v>59800000</v>
+        <v>32100000</v>
       </c>
       <c r="L4" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="M4">
-        <v>20</v>
+        <v>-20</v>
       </c>
       <c r="N4">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="O4">
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q4">
         <v>2</v>
@@ -13168,7 +13006,7 @@
         <v>9</v>
       </c>
       <c r="S4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AN4">
         <v>1</v>
@@ -13180,10 +13018,10 @@
         <v>1</v>
       </c>
       <c r="AQ4">
-        <v>29900000</v>
+        <v>16050000</v>
       </c>
       <c r="AR4">
-        <v>59800000</v>
+        <v>32100000</v>
       </c>
       <c r="AS4">
         <v>0.95</v>
@@ -13198,19 +13036,19 @@
         <v>1</v>
       </c>
       <c r="AW4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AX4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AY4">
         <v>96</v>
       </c>
       <c r="AZ4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="BA4">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="BB4">
         <v>0</v>
@@ -13227,7 +13065,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F5">
         <v>96</v>
@@ -13245,10 +13083,10 @@
         <v>1</v>
       </c>
       <c r="K5">
-        <v>15500000</v>
+        <v>19000000</v>
       </c>
       <c r="L5" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="M5">
         <v>0</v>
@@ -13260,7 +13098,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q5">
         <v>2</v>
@@ -13269,7 +13107,7 @@
         <v>9</v>
       </c>
       <c r="S5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AN5">
         <v>1</v>
@@ -13281,10 +13119,10 @@
         <v>1</v>
       </c>
       <c r="AQ5">
-        <v>7750000</v>
+        <v>9500000</v>
       </c>
       <c r="AR5">
-        <v>15500000</v>
+        <v>19000000</v>
       </c>
       <c r="AS5">
         <v>0.95</v>
@@ -13299,19 +13137,19 @@
         <v>1</v>
       </c>
       <c r="AW5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AX5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AY5">
         <v>96</v>
       </c>
       <c r="AZ5" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="BA5">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="BB5">
         <v>0</v>
@@ -13328,7 +13166,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F6">
         <v>96</v>
@@ -13349,13 +13187,13 @@
         <v>20000</v>
       </c>
       <c r="AH6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AI6" t="b">
         <v>1</v>
       </c>
       <c r="AJ6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AK6">
         <v>2</v>
@@ -13364,31 +13202,49 @@
         <v>9</v>
       </c>
       <c r="AM6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AN6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP6" t="b">
         <v>1</v>
       </c>
+      <c r="AQ6">
+        <v>6000</v>
+      </c>
+      <c r="AR6">
+        <v>20000</v>
+      </c>
+      <c r="AS6">
+        <v>0.95</v>
+      </c>
+      <c r="AT6">
+        <v>0.1</v>
+      </c>
+      <c r="AU6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="b">
+        <v>1</v>
+      </c>
       <c r="AW6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AX6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AY6">
         <v>96</v>
       </c>
       <c r="AZ6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="BA6">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="BB6">
         <v>0</v>
@@ -13405,7 +13261,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F7">
         <v>96</v>
@@ -13423,16 +13279,16 @@
         <v>1</v>
       </c>
       <c r="AG7">
-        <v>38100</v>
+        <v>39600</v>
       </c>
       <c r="AH7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AI7" t="b">
         <v>1</v>
       </c>
       <c r="AJ7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AK7">
         <v>2</v>
@@ -13441,7 +13297,7 @@
         <v>9</v>
       </c>
       <c r="AM7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AN7">
         <v>0</v>
@@ -13453,19 +13309,19 @@
         <v>1</v>
       </c>
       <c r="AW7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AX7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AY7">
         <v>96</v>
       </c>
       <c r="AZ7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="BA7">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="BB7">
         <v>0</v>
@@ -13501,7 +13357,7 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>9</v>
@@ -13641,10 +13497,10 @@
         <v>1</v>
       </c>
       <c r="K2">
-        <v>852000</v>
+        <v>1100000</v>
       </c>
       <c r="L2">
-        <v>5380000</v>
+        <v>4160000</v>
       </c>
       <c r="M2">
         <v>0.95</v>
@@ -13659,16 +13515,16 @@
         <v>1</v>
       </c>
       <c r="Q2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AL2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AM2">
         <v>96</v>
       </c>
       <c r="AN2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AO2">
         <v>24</v>
@@ -13706,10 +13562,10 @@
         <v>1</v>
       </c>
       <c r="K3">
-        <v>1056000</v>
+        <v>1070000</v>
       </c>
       <c r="L3">
-        <v>4310000</v>
+        <v>4810000</v>
       </c>
       <c r="M3">
         <v>0.95</v>
@@ -13724,19 +13580,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AL3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AM3">
         <v>96</v>
       </c>
       <c r="AN3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AO3">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AP3">
         <v>0</v>
@@ -13771,10 +13627,10 @@
         <v>1</v>
       </c>
       <c r="K4">
-        <v>1875000</v>
+        <v>1940000</v>
       </c>
       <c r="L4">
-        <v>8240000</v>
+        <v>7530000</v>
       </c>
       <c r="M4">
         <v>0.95</v>
@@ -13789,19 +13645,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AL4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AM4">
         <v>96</v>
       </c>
       <c r="AN4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AO4">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="AP4">
         <v>0</v>
@@ -13836,10 +13692,10 @@
         <v>1</v>
       </c>
       <c r="U5">
-        <v>2150000000</v>
+        <v>1857000000</v>
       </c>
       <c r="V5">
-        <v>9790000000</v>
+        <v>7890000000</v>
       </c>
       <c r="W5">
         <v>0.95</v>
@@ -13854,19 +13710,19 @@
         <v>1</v>
       </c>
       <c r="AA5" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AL5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AM5">
         <v>96</v>
       </c>
       <c r="AN5" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AO5">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="AP5">
         <v>0</v>
@@ -13901,10 +13757,10 @@
         <v>1</v>
       </c>
       <c r="U6">
-        <v>1150000000</v>
+        <v>1065000000</v>
       </c>
       <c r="V6">
-        <v>5090000000</v>
+        <v>5400000000</v>
       </c>
       <c r="W6">
         <v>0.95</v>
@@ -13919,19 +13775,19 @@
         <v>1</v>
       </c>
       <c r="AA6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AL6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AM6">
         <v>96</v>
       </c>
       <c r="AN6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AO6">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="AP6">
         <v>0</v>
@@ -13966,10 +13822,10 @@
         <v>1</v>
       </c>
       <c r="U7">
-        <v>1160000000</v>
+        <v>870000000</v>
       </c>
       <c r="V7">
-        <v>4320000000</v>
+        <v>5110000000</v>
       </c>
       <c r="W7">
         <v>0.95</v>
@@ -13984,19 +13840,19 @@
         <v>1</v>
       </c>
       <c r="AA7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AL7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AM7">
         <v>96</v>
       </c>
       <c r="AN7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AO7">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="AP7">
         <v>0</v>
@@ -14031,10 +13887,10 @@
         <v>1</v>
       </c>
       <c r="AE8">
-        <v>201100000</v>
+        <v>108000000</v>
       </c>
       <c r="AF8">
-        <v>668000000</v>
+        <v>553000000</v>
       </c>
       <c r="AG8">
         <v>0.95</v>
@@ -14049,19 +13905,19 @@
         <v>1</v>
       </c>
       <c r="AK8" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AL8" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AM8">
         <v>96</v>
       </c>
       <c r="AN8" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AO8">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="AP8">
         <v>0</v>
@@ -14096,10 +13952,10 @@
         <v>1</v>
       </c>
       <c r="AE9">
-        <v>90500000</v>
+        <v>102000000</v>
       </c>
       <c r="AF9">
-        <v>476000000</v>
+        <v>562000000</v>
       </c>
       <c r="AG9">
         <v>0.95</v>
@@ -14114,19 +13970,19 @@
         <v>1</v>
       </c>
       <c r="AK9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AL9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AM9">
         <v>96</v>
       </c>
       <c r="AN9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AO9">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="AP9">
         <v>0</v>
@@ -14161,10 +14017,10 @@
         <v>1</v>
       </c>
       <c r="AE10">
-        <v>94300000</v>
+        <v>182000000</v>
       </c>
       <c r="AF10">
-        <v>561000000</v>
+        <v>736000000</v>
       </c>
       <c r="AG10">
         <v>0.95</v>
@@ -14179,19 +14035,19 @@
         <v>1</v>
       </c>
       <c r="AK10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AL10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AM10">
         <v>96</v>
       </c>
       <c r="AN10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AO10">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="AP10">
         <v>0</v>
